--- a/decks/7-day-kitchens/keyword-research.xlsx
+++ b/decks/7-day-kitchens/keyword-research.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Remodeling Contractors Charlotte NC: Fixed Pricing, Finished in 7 Days</t>
+          <t>Remodeling Contractors Charlotte NC: Built Around Your Home and Budget</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kitchen Designers Charlotte: What the Process Looks Like Here</t>
+          <t>Kitchen Designers Charlotte: The 7-Day Difference, Explained</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Home Additions Charlotte: What Separates Great From Cheap</t>
+          <t>Home Additions Charlotte: Fixed Pricing, Finished in 7 Days</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Renovation Company Charlotte NC: Local Crews, Lifetime Warranty</t>
+          <t>Renovation Company Charlotte NC: The 7-Day Difference, Explained</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Best Kitchen Remodeler Charlotte: What Separates Great From Cheap</t>
+          <t>Best Kitchen Remodeler Charlotte: Fixed Pricing, Finished in 7 Days</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -864,12 +864,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bathroom Renovation Charlotte: Local Crews, Lifetime Warranty</t>
+          <t>Charlotte Home Renovations: Where Speed Meets Craftsmanship</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>bathroom renovation charlotte</t>
+          <t>charlotte home renovations</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -888,10 +888,10 @@
         </is>
       </c>
       <c r="G10" s="3" t="n">
-        <v>390</v>
-      </c>
-      <c r="H10" s="5" t="n">
-        <v>33</v>
+        <v>170</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="11">
@@ -902,12 +902,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bath Remodel Charlotte, Done the Fixed-Price Way</t>
+          <t>Remodeling in Charlotte: One Local Crew, Start to Finish</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>bath remodel charlotte</t>
+          <t>remodeling in charlotte</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="G11" s="3" t="n">
-        <v>110</v>
-      </c>
-      <c r="H11" s="4" t="n">
-        <v>28</v>
+        <v>90</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>37</v>
       </c>
     </row>
     <row r="12">
@@ -940,12 +940,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Local Kitchen Remodeler with Transparent Pricing: Fixed Pricing, No Surprises</t>
+          <t>How Much Is a Kitchen Remodel in Charlotte? Local Price Ranges</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>local kitchen remodeler with transparent pricing</t>
+          <t>how much is a kitchen remodel in charlotte</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -964,10 +964,10 @@
         </is>
       </c>
       <c r="G12" s="3" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13">
@@ -978,12 +978,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Kitchen Remodel Cost in Charlotte, NC: What Drives the Number</t>
+          <t>Why a Fixed-Price Kitchen Remodel Beats Hourly Surprises</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>kitchen remodel cost charlotte nc</t>
+          <t>fixed price kitchen remodel</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="G13" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="H13" s="4" t="n">
-        <v>18</v>
+        <v>40</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="14">
@@ -1016,12 +1016,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Kitchen Restoration Company Prices: What You Pay, Line by Line</t>
+          <t>Does a Kitchen Remodel Add Value? The Resale Math</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>kitchen restoration company prices</t>
+          <t>does a kitchen remodel add value</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="G14" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="H14" s="5" t="n">
-        <v>30</v>
+        <v>40</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="15">
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>How Much to Remodel a Kitchen: What Drives the Final Price</t>
+          <t>The Average Cost of a Kitchen Remodel, and Why Yours May Differ</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>how much to remodel a kitchen</t>
+          <t>average cost of kitchen remodel</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="G15" s="3" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="H15" s="4" t="n">
         <v>24</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Small Kitchen Remodel Cost: Where the Money Really Goes</t>
+          <t>Kitchen Remodel Cost: Budget, Mid-Range, and High-End Compared</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>small kitchen remodel cost</t>
+          <t>kitchen remodel cost</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="H16" s="4" t="n">
-        <v>24</v>
+        <v>193</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="17">
@@ -1130,12 +1130,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Kitchen Estimate: The Real Numbers for 2026</t>
+          <t>Affordable Kitchen Remodels: Where to Save Without Regret</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>kitchen estimate</t>
+          <t>affordable kitchen remodel</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="G17" s="3" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -1168,12 +1168,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Kitchen Remodel Price: The Numbers Behind the Choice</t>
+          <t>Kitchen Remodel ROI: How Much Value It Actually Adds</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>kitchen remodel price</t>
+          <t>kitchen remodel roi</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1206,12 +1206,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>How to Set a Kitchen Remodel Budget You Won't Blow Through</t>
+          <t>Getting a Kitchen Remodel Estimate: What to Expect</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>kitchen remodel budget</t>
+          <t>kitchen remodel estimate</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="H19" s="5" t="n">
         <v>38</v>
@@ -1244,22 +1244,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cabinet Refacing in Charlotte, NC: When It Makes Sense</t>
+          <t>Comparing Kitchen Remodel Quotes: A Side-by-Side Guide</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>cabinet refacing charlotte nc</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>compare kitchen prices</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>Cost &amp; Budget</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1268,10 +1268,10 @@
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>102</v>
-      </c>
-      <c r="H20" s="4" t="n">
-        <v>18</v>
+        <v>15</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="21">
@@ -1282,22 +1282,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Kitchen Renovation Services: The Choices That Hold Up</t>
+          <t>How to Set a Kitchen Remodel Budget You Won't Blow Through</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>kitchen renovation services</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>kitchen remodel budget</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Cost &amp; Budget</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1306,7 +1306,7 @@
         </is>
       </c>
       <c r="G21" s="3" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="H21" s="5" t="n">
         <v>38</v>
@@ -1320,12 +1320,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Choosing Kitchen Cabinets: Styles, Finishes, and What Lasts</t>
+          <t>Cabinet Refacing in Charlotte, NC: When It Makes Sense</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>kitchen cabinets</t>
+          <t>cabinet refacing charlotte nc</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1344,10 +1344,10 @@
         </is>
       </c>
       <c r="G22" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="H22" s="5" t="n">
-        <v>38</v>
+        <v>102</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="23">
@@ -1358,12 +1358,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Kitchen Countertop Alternatives to Quartz and Granite</t>
+          <t>Best Kitchen Remodeling Company: A No-Nonsense Buyer's Guide</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>kitchen countertop alternatives to quartz and granite</t>
+          <t>best kitchen remodeling company</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="G23" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="H23" s="4" t="n">
-        <v>24</v>
+        <v>16</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="24">
@@ -1396,12 +1396,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Kitchen Remodeling: Compared on Cost, Durability, and Looks</t>
+          <t>Quartz vs Granite Countertops: Which Wins for Your Kitchen</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>kitchen remodeling</t>
+          <t>quartz vs granite</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
@@ -1420,10 +1420,10 @@
         </is>
       </c>
       <c r="G24" s="3" t="n">
-        <v>374</v>
+        <v>40</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
     </row>
     <row r="25">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Kitchen Island Ideas: Sizing, Seating, and Smart Storage</t>
+          <t>Kitchen Layout Basics: Work Triangles, Walkways, and Flow</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>kitchen island ideas</t>
+          <t>kitchen layout</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="G25" s="3" t="n">
         <v>40</v>
       </c>
       <c r="H25" s="5" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26">
@@ -1472,12 +1472,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Kitchen Cabinet Colors: What's Timeless vs What's Trendy</t>
+          <t>Kitchen Lighting Ideas: Layering Task, Ambient, and Accent</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>kitchen cabinet colors</t>
+          <t>kitchen lighting ideas</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
@@ -1492,7 +1492,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G26" s="3" t="n">
@@ -1510,12 +1510,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Kitchen Trends 2026: Bold Cabinets, Brass, and What to Skip</t>
+          <t>Modern Kitchen Design: Clean Lines Without the Cold Feel</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>kitchen trends 2026</t>
+          <t>modern kitchen design</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="G27" s="3" t="n">
@@ -1548,12 +1548,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Kitchen Sink Ideas: Materials, Mounts, and the Right Size</t>
+          <t>Pantry Ideas: Designing Storage That Earns Its Footprint</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>kitchen sink ideas</t>
+          <t>pantry ideas</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
@@ -1575,7 +1575,7 @@
         <v>40</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
     </row>
     <row r="29">
@@ -1586,12 +1586,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Open-Concept Kitchens: When Knocking Down a Wall Pays Off</t>
+          <t>Kitchen Paint Colors That Flatter Cabinets and Counters</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>open concept kitchen</t>
+          <t>kitchen paint colors</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Cabinet Hardware: The Small Detail That Sets the Tone</t>
+          <t>Kitchen Appliances: Where to Splurge and Where to Save</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>cabinet hardware ideas</t>
+          <t>kitchen appliances</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
@@ -1639,19 +1639,19 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="G30" s="3" t="n">
         <v>40</v>
       </c>
       <c r="H30" s="5" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
     </row>
     <row r="31">
@@ -1662,12 +1662,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Butcher Block Countertops: Warm Looks, Real Trade-offs</t>
+          <t>Kitchen Builders vs Remodelers: Which One You Need</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>butcher block countertops</t>
+          <t>kitchen builders</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
@@ -1686,10 +1686,10 @@
         </is>
       </c>
       <c r="G31" s="3" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="H31" s="5" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
     </row>
     <row r="32">
@@ -1700,12 +1700,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Fast Kitchen Remodel: Compared on Cost, Durability, and Looks</t>
+          <t>Kitchen Remodel Ideas That Work in Real Charlotte Homes</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>fast kitchen remodel</t>
+          <t>kitchen remodel ideas</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
@@ -1715,16 +1715,16 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G32" s="3" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="H32" s="5" t="n">
         <v>38</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Custom Kitchen Remodel: How the Top Options Stack Up</t>
+          <t>Kitchen Remodel Contractors in Rock Hill, SC</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>custom kitchen remodel</t>
-        </is>
-      </c>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>contractor for kitchen remodel rock hill sc</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>Process &amp; Planning</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1762,10 +1762,10 @@
         </is>
       </c>
       <c r="G33" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="H33" s="5" t="n">
-        <v>38</v>
+        <v>10</v>
+      </c>
+      <c r="H33" s="4" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="34">
@@ -1776,31 +1776,31 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Kitchen Remodel Ideas That Work in Real Charlotte Homes</t>
+          <t>Vetting a Kitchen Remodeling Contractor: Red and Green Flags</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>kitchen remodel ideas</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>kitchen remodeling contractor</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>Process &amp; Planning</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="H34" s="5" t="n">
         <v>38</v>
@@ -1814,12 +1814,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Kitchen Remodeler: What to Expect, Day by Day</t>
+          <t>Choosing a Contractor for Your Kitchen Renovation</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>kitchen remodeler</t>
+          <t>contractor for kitchen renovation</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
@@ -1838,10 +1838,10 @@
         </is>
       </c>
       <c r="G35" s="3" t="n">
-        <v>151</v>
+        <v>10</v>
       </c>
       <c r="H35" s="5" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
     </row>
     <row r="36">
@@ -1852,12 +1852,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Kitchen Contractor: Done Right the First Time</t>
+          <t>Living Through a Kitchen Remodel: How to Stay in Your Home</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>kitchen contractor</t>
+          <t>living through a kitchen remodel</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1876,10 +1876,10 @@
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>36</v>
-      </c>
-      <c r="H36" s="5" t="n">
-        <v>48</v>
+        <v>40</v>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="37">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>How to Plan a Kitchen Remodel Before Demo Day</t>
+          <t>Working With an Interior Designer: Why It's Built Into Our Process</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>how to plan a kitchen remodel</t>
+          <t>working with an interior designer</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="G37" s="3" t="n">
@@ -1928,12 +1928,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Kitchen Remodel Timeline: How Long a Renovation Really Takes</t>
+          <t>How to Prepare Your Home for a Kitchen Remodel</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>kitchen remodel timeline</t>
+          <t>how to prepare for a kitchen remodel</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
@@ -1948,14 +1948,14 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G38" s="3" t="n">
-        <v>114</v>
-      </c>
-      <c r="H38" s="5" t="n">
-        <v>38</v>
+        <v>10</v>
+      </c>
+      <c r="H38" s="4" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="39">
@@ -1966,12 +1966,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Do You Need a Permit for a Kitchen Remodel in North Carolina?</t>
+          <t>Kitchen Remodel Mistakes to Avoid (and How We Prevent Them)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>kitchen remodel permits</t>
+          <t>kitchen remodel mistakes</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
@@ -2004,12 +2004,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Sustainable Kitchen Remodeling: The Eco Cheat Codes That Pay Off</t>
+          <t>Kitchen Demolition: What Tear-Out Day Actually Involves</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>sustainable kitchen remodel</t>
+          <t>kitchen demolition</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
@@ -2031,7 +2031,7 @@
         <v>40</v>
       </c>
       <c r="H40" s="5" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
     </row>
     <row r="41">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Order of Kitchen Remodel: Timelines, Trade-offs, and Questions to Ask</t>
+          <t>The Right Order of a Kitchen Remodel, Step by Step</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Home Remodeling Charlotte: What to Know Before You Commit</t>
+          <t>Home Remodeling Charlotte: What the Process Looks Like Here</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>A Homeowner's Guide to Kitchen Contractor Charlotte</t>
+          <t>Hiring a Kitchen Contractor in Charlotte: A Vetting Guide</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Kitchen Contractors Charlotte NC: A Faster Path to Your Dream Kitchen</t>
+          <t>Kitchen Contractors Charlotte NC: What Separates Great From Cheap</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Charlotte Home Renovations: Local Crews, Lifetime Warranty</t>
+          <t>Bathroom Remodel in Charlotte, NC: The Kitchen-Plus Approach</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>charlotte home renovations</t>
+          <t>bathroom remodel charlotte nc</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="G50" s="3" t="n">
-        <v>170</v>
-      </c>
-      <c r="H50" s="4" t="n">
-        <v>27</v>
+        <v>590</v>
+      </c>
+      <c r="H50" s="5" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="51">
@@ -2422,12 +2422,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Remodeling in Charlotte: What the Process Looks Like Here</t>
+          <t>Charlotte NC Remodeling: Local Crews, Lifetime Warranty</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>remodeling in charlotte</t>
+          <t>charlotte nc remodeling</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -2446,10 +2446,10 @@
         </is>
       </c>
       <c r="G51" s="3" t="n">
-        <v>90</v>
+        <v>170</v>
       </c>
       <c r="H51" s="5" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="52">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>How Much Is a Kitchen Remodel in Charlotte? Local Price Ranges</t>
+          <t>How Much It Costs to Remodel a Kitchen in 2026</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>how much is a kitchen remodel in charlotte</t>
+          <t>how much to remodel a kitchen</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
@@ -2484,10 +2484,10 @@
         </is>
       </c>
       <c r="G52" s="3" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="53">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Why a Fixed-Price Kitchen Remodel Beats Hourly Surprises</t>
+          <t>Small Kitchen Remodel Cost: Where the Money Really Goes</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>fixed price kitchen remodel</t>
+          <t>small kitchen remodel cost</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
@@ -2513,7 +2513,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2522,10 +2522,10 @@
         </is>
       </c>
       <c r="G53" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="H53" s="5" t="n">
-        <v>30</v>
+        <v>10</v>
+      </c>
+      <c r="H53" s="4" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="54">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>How Much Does a Kitchen Remodel Cost? A Real 2026 Breakdown</t>
+          <t>How to Read a Kitchen Remodel Estimate, Line by Line</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>how much does a kitchen remodel cost</t>
+          <t>kitchen estimate</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
@@ -2560,10 +2560,10 @@
         </is>
       </c>
       <c r="G54" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="H54" s="4" t="n">
-        <v>24</v>
+        <v>61</v>
+      </c>
+      <c r="H54" s="5" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="55">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Luxury Kitchen Remodel Cost: What High-End Really Buys</t>
+          <t>What Drives Your Kitchen Remodel Price: A Cost-Factor Guide</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>luxury kitchen remodel cost</t>
+          <t>kitchen remodel price</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
@@ -2598,10 +2598,10 @@
         </is>
       </c>
       <c r="G55" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="H55" s="4" t="n">
-        <v>24</v>
+        <v>40</v>
+      </c>
+      <c r="H55" s="5" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="56">
@@ -2612,12 +2612,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Free Kitchen Remodel Estimate: Where Most Homeowners Get It Wrong</t>
+          <t>What a Brand-New Kitchen Costs vs a Remodel</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>free kitchen remodel estimate</t>
+          <t>new kitchen prices</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
@@ -2636,10 +2636,10 @@
         </is>
       </c>
       <c r="G56" s="3" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H56" s="5" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
     </row>
     <row r="57">
@@ -2650,12 +2650,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Kitchen Prices: A 2026 Buyer's Guide</t>
+          <t>Financing a Kitchen Remodel: Options Weighed Honestly</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>kitchen prices</t>
+          <t>kitchen remodel financing</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
@@ -2674,10 +2674,10 @@
         </is>
       </c>
       <c r="G57" s="3" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="H57" s="5" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
     </row>
     <row r="58">
@@ -2688,22 +2688,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Financing a Kitchen Remodel: Options Weighed Honestly</t>
+          <t>What Full-Service Kitchen Remodeling Actually Covers</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>kitchen remodel financing</t>
-        </is>
-      </c>
-      <c r="D58" s="6" t="inlineStr">
-        <is>
-          <t>Cost &amp; Budget</t>
+          <t>kitchen remodeling services</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2712,10 +2712,10 @@
         </is>
       </c>
       <c r="G58" s="3" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="H58" s="5" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
     </row>
     <row r="59">
@@ -2726,12 +2726,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Best Kitchen Remodeling Company: A No-Nonsense Buyer's Guide</t>
+          <t>What to Look for in a Kitchen Remodeling Company</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>best kitchen remodeling company</t>
+          <t>kitchen remodeling company</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
@@ -2750,10 +2750,10 @@
         </is>
       </c>
       <c r="G59" s="3" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H59" s="5" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
     </row>
     <row r="60">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Kitchen Remodel Before and After: What a Week Can Change</t>
+          <t>Choosing Kitchen Cabinets: Styles, Finishes, and What Lasts</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>kitchen remodel before and after</t>
+          <t>kitchen cabinets</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
@@ -2779,19 +2779,19 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="G60" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="H60" s="4" t="n">
-        <v>24</v>
+        <v>10</v>
+      </c>
+      <c r="H60" s="5" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="61">
@@ -2802,12 +2802,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Kitchen Renovation: How the Top Options Stack Up</t>
+          <t>Kitchen Countertop Alternatives to Quartz and Granite</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>kitchen renovation</t>
+          <t>kitchen countertop alternatives to quartz and granite</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="G61" s="3" t="n">
-        <v>232</v>
-      </c>
-      <c r="H61" s="5" t="n">
-        <v>48</v>
+        <v>40</v>
+      </c>
+      <c r="H61" s="4" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="62">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Kitchen Cabinet Installation: Worth It, or Overrated?</t>
+          <t>Kitchen Remodeling 101: What the Project Really Involves</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>kitchen cabinet installation</t>
+          <t>kitchen remodeling</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="G62" s="3" t="n">
-        <v>96</v>
+        <v>374</v>
       </c>
       <c r="H62" s="5" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
     </row>
     <row r="63">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Kitchen and Bath Remodeling: What Designers Pick and Why</t>
+          <t>Kitchen Island Ideas: Sizing, Seating, and Smart Storage</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>kitchen and bath remodeling</t>
+          <t>kitchen island ideas</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
@@ -2893,19 +2893,19 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G63" s="3" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="H63" s="5" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
     </row>
     <row r="64">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Kitchen Design Ideas: Layouts, Light, and Lasting Style</t>
+          <t>Kitchen Cabinet Colors: What's Timeless vs What's Trendy</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>kitchen design ideas</t>
+          <t>kitchen cabinet colors</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="G64" s="3" t="n">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Kitchen Backsplash Ideas That Pull a Remodel Together</t>
+          <t>Kitchen Trends 2026: Bold Cabinets, Brass, and What to Skip</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>kitchen backsplash ideas</t>
+          <t>kitchen trends 2026</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
@@ -2992,12 +2992,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Kitchen Flooring Options Ranked for Durability and Looks</t>
+          <t>Kitchen Sink Ideas: Materials, Mounts, and the Right Size</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>kitchen flooring options</t>
+          <t>kitchen sink ideas</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
@@ -3007,12 +3007,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G66" s="3" t="n">
@@ -3030,12 +3030,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Farmhouse Kitchen Ideas That Still Feel Fresh in 2026</t>
+          <t>Open-Concept Kitchens: When Knocking Down a Wall Pays Off</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>farmhouse kitchen ideas</t>
+          <t>open concept kitchen</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="G67" s="3" t="n">
@@ -3068,12 +3068,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Choosing a Kitchen Faucet: Finishes, Features, and Value</t>
+          <t>Cabinet Hardware: The Small Detail That Sets the Tone</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>kitchen faucet ideas</t>
+          <t>cabinet hardware ideas</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Small Kitchen Ideas: Making a Compact Space Feel Open</t>
+          <t>Butcher Block Countertops: Warm Looks, Real Trade-offs</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>small kitchen ideas</t>
+          <t>butcher block countertops</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="G69" s="3" t="n">
@@ -3144,12 +3144,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Two-Tone Kitchen Cabinets: How to Mix Without a Mess</t>
+          <t>Fast Kitchen Remodels: How a 7-Day Timeline Works</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>two tone kitchen cabinets</t>
+          <t>fast kitchen remodel</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
@@ -3159,7 +3159,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3168,10 +3168,10 @@
         </is>
       </c>
       <c r="G70" s="3" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="H70" s="5" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
     </row>
     <row r="71">
@@ -3182,12 +3182,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Kitchen Storage Ideas That Use Every Inch</t>
+          <t>Custom Kitchen Remodels: When Bespoke Is Worth the Spend</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>kitchen storage ideas</t>
+          <t>custom kitchen remodel</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
@@ -3197,16 +3197,16 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="G71" s="3" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="H71" s="5" t="n">
         <v>38</v>
@@ -3258,12 +3258,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Contractor for Kitchen Remodel Rock Hill Sc: What to Know Before You Commit</t>
+          <t>Do You Need a General Contractor for a Bathroom Remodel?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>contractor for kitchen remodel rock hill sc</t>
+          <t>bathroom remodel general contractor</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr">
@@ -3284,8 +3284,8 @@
       <c r="G73" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="H73" s="4" t="n">
-        <v>24</v>
+      <c r="H73" s="5" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="74">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>A Homeowner's Guide to Local Contractors for Kitchen Remodel</t>
+          <t>Finding Local Contractors for a Kitchen Remodel</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3334,12 +3334,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Kitchen Remodeling Contractor: What Separates Great From Cheap</t>
+          <t>Kitchen Remodel Steps in Order: The Complete Sequence</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>kitchen remodeling contractor</t>
+          <t>kitchen remodel steps in order</t>
         </is>
       </c>
       <c r="D75" s="8" t="inlineStr">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3358,10 +3358,10 @@
         </is>
       </c>
       <c r="G75" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="H75" s="5" t="n">
-        <v>38</v>
+        <v>19</v>
+      </c>
+      <c r="H75" s="4" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="76">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Best Kitchen Remodel Contractors: Done Right the First Time</t>
+          <t>What to Look for When Hiring a Bathroom Remodeler</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>best kitchen remodel contractors</t>
+          <t>bathroom remodeler</t>
         </is>
       </c>
       <c r="D76" s="8" t="inlineStr">
@@ -3396,10 +3396,10 @@
         </is>
       </c>
       <c r="G76" s="3" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H76" s="5" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
     </row>
     <row r="77">
@@ -3410,12 +3410,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>How Long Does a Kitchen Remodel Take? Why Ours Takes 7 Days</t>
+          <t>How to Plan a Kitchen Remodel Before Demo Day</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>how long does a kitchen remodel take</t>
+          <t>how to plan a kitchen remodel</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3434,7 +3434,7 @@
         </is>
       </c>
       <c r="G77" s="3" t="n">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="H77" s="4" t="n">
         <v>24</v>
@@ -3448,12 +3448,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>How to Choose a Kitchen Contractor You Can Actually Trust</t>
+          <t>Kitchen Remodel Timeline: How Long a Renovation Really Takes</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>how to choose a kitchen contractor</t>
+          <t>kitchen remodel timeline</t>
         </is>
       </c>
       <c r="D78" s="8" t="inlineStr">
@@ -3463,7 +3463,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3472,10 +3472,10 @@
         </is>
       </c>
       <c r="G78" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="H78" s="4" t="n">
-        <v>24</v>
+        <v>114</v>
+      </c>
+      <c r="H78" s="5" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="79">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>The Kitchen Remodel Checklist Every Homeowner Should Use</t>
+          <t>Do You Need a Permit for a Kitchen Remodel in North Carolina?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>kitchen remodel checklist</t>
+          <t>kitchen remodel permits</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="G79" s="3" t="n">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Questions to Ask a Kitchen Remodel Contractor Before You Sign</t>
+          <t>Sustainable Kitchen Remodeling: The Eco Cheat Codes That Pay Off</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>kitchen remodel contractor questions</t>
+          <t>sustainable kitchen remodel</t>
         </is>
       </c>
       <c r="D80" s="8" t="inlineStr">
@@ -3539,7 +3539,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3551,7 +3551,7 @@
         <v>40</v>
       </c>
       <c r="H80" s="5" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
     </row>
     <row r="81">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Kitchen Renovation Timeline: How to Pick the Right Pro</t>
+          <t>Kitchen Renovation Timeline: Week by Week, What Happens</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Bathroom Renovation Services Ballantyne NC: A Faster Path to Your Dream Kitchen</t>
+          <t>Bathroom Renovation Services Ballantyne NC: One Local Crew, Start to Finish</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Bathroom Designers Charlotte: Fixed Pricing, Finished in 7 Days</t>
+          <t>Bathroom Designers Charlotte: Where Speed Meets Craftsmanship</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Home Renovation Contractors Charlotte: A No-Nonsense Buyer's Guide</t>
+          <t>Home Renovation Contractors Charlotte: The Questions to Ask First</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3904,12 +3904,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Bathroom Remodel in Charlotte, NC: The Kitchen-Plus Approach</t>
+          <t>Bathroom Renovation Charlotte: Local Crews, Lifetime Warranty</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>bathroom remodel charlotte nc</t>
+          <t>bathroom renovation charlotte</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -3928,10 +3928,10 @@
         </is>
       </c>
       <c r="G90" s="3" t="n">
-        <v>590</v>
+        <v>390</v>
       </c>
       <c r="H90" s="5" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="91">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Charlotte NC Remodeling: The Questions to Ask First</t>
+          <t>Bath Remodel Charlotte: Built Around Your Home and Budget</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>charlotte nc remodeling</t>
+          <t>bath remodel charlotte</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -3966,10 +3966,10 @@
         </is>
       </c>
       <c r="G91" s="3" t="n">
-        <v>170</v>
-      </c>
-      <c r="H91" s="5" t="n">
-        <v>42</v>
+        <v>110</v>
+      </c>
+      <c r="H91" s="4" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="92">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Does a Kitchen Remodel Add Value? The Resale Math</t>
+          <t>Kitchen Remodel Cost in Charlotte, NC: What Drives the Number</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>does a kitchen remodel add value</t>
+          <t>kitchen remodel cost charlotte nc</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -4004,10 +4004,10 @@
         </is>
       </c>
       <c r="G92" s="3" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H92" s="4" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="93">
@@ -4018,12 +4018,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>The Average Cost of a Kitchen Remodel, and Why Yours May Differ</t>
+          <t>How Much Does a Kitchen Remodel Cost? A Real 2026 Breakdown</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>average cost of kitchen remodel</t>
+          <t>how much does a kitchen remodel cost</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
@@ -4042,7 +4042,7 @@
         </is>
       </c>
       <c r="G93" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H93" s="4" t="n">
         <v>24</v>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Kitchen Remodel Cost: Budget, Mid-Range, and High-End Compared</t>
+          <t>Luxury Kitchen Remodel Cost: What High-End Really Buys</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>kitchen remodel cost</t>
+          <t>luxury kitchen remodel cost</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
@@ -4080,10 +4080,10 @@
         </is>
       </c>
       <c r="G94" s="3" t="n">
-        <v>193</v>
-      </c>
-      <c r="H94" s="5" t="n">
-        <v>38</v>
+        <v>10</v>
+      </c>
+      <c r="H94" s="4" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="95">
@@ -4094,12 +4094,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Affordable Kitchen Remodel: Where the Money Goes, and Where to Save</t>
+          <t>What a Free Kitchen Remodel Estimate Should Tell You</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>affordable kitchen remodel</t>
+          <t>free kitchen remodel estimate</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
@@ -4118,10 +4118,10 @@
         </is>
       </c>
       <c r="G95" s="3" t="n">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="H95" s="5" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="96">
@@ -4132,12 +4132,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Kitchen Remodel ROI: How Much Value It Actually Adds</t>
+          <t>Kitchen Remodel Prices in 2026: What Sets the Range</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>kitchen remodel roi</t>
+          <t>kitchen prices</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -4156,10 +4156,10 @@
         </is>
       </c>
       <c r="G96" s="3" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="H96" s="5" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
     </row>
     <row r="97">
@@ -4170,12 +4170,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Kitchen Remodel Estimate: What to Know Before You Commit</t>
+          <t>What a Kitchen Installation Estimate Should Include</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>kitchen remodel estimate</t>
+          <t>kitchen installation cost estimate</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
@@ -4194,10 +4194,10 @@
         </is>
       </c>
       <c r="G97" s="3" t="n">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="H97" s="5" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="98">
@@ -4208,12 +4208,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Is Kitchen Installation Cost Estimate Worth It?</t>
+          <t>Full Kitchen Remodel Cost: Where the Money Goes, and Where to Save</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>kitchen installation cost estimate</t>
+          <t>full kitchen remodel cost</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
@@ -4232,7 +4232,7 @@
         </is>
       </c>
       <c r="G98" s="3" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H98" s="5" t="n">
         <v>30</v>
@@ -4246,12 +4246,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Compare Kitchen Prices, Compared</t>
+          <t>Kitchen Renovation Cost: A Room-by-Room Money Map</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>compare kitchen prices</t>
+          <t>kitchen renovation cost</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
@@ -4270,10 +4270,10 @@
         </is>
       </c>
       <c r="G99" s="3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H99" s="5" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="100">
@@ -4284,22 +4284,22 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Kitchen Renovation Cost: A Room-by-Room Money Map</t>
+          <t>Full-Service Kitchen Renovation: What's Included</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>kitchen renovation cost</t>
-        </is>
-      </c>
-      <c r="D100" s="6" t="inlineStr">
-        <is>
-          <t>Cost &amp; Budget</t>
+          <t>kitchen renovation services</t>
+        </is>
+      </c>
+      <c r="D100" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -4308,10 +4308,10 @@
         </is>
       </c>
       <c r="G100" s="3" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="H100" s="5" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
     </row>
     <row r="101">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Kitchen Remodeling Services: Picked for How You Actually Cook</t>
+          <t>Kitchen Remodel Before and After: What a Week Can Change</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>kitchen remodeling services</t>
+          <t>kitchen remodel before and after</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
@@ -4337,19 +4337,19 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G101" s="3" t="n">
-        <v>38</v>
-      </c>
-      <c r="H101" s="5" t="n">
-        <v>38</v>
+        <v>40</v>
+      </c>
+      <c r="H101" s="4" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="102">
@@ -4360,12 +4360,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Kitchen Remodeling Company: Built to Last, Styled to Sell</t>
+          <t>Kitchen Renovation, Start to Finish: A Homeowner's Overview</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>kitchen remodeling company</t>
+          <t>kitchen renovation</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
@@ -4375,7 +4375,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -4384,10 +4384,10 @@
         </is>
       </c>
       <c r="G102" s="3" t="n">
-        <v>19</v>
+        <v>232</v>
       </c>
       <c r="H102" s="5" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
     </row>
     <row r="103">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Quartz vs Granite Countertops: Which Wins for Your Kitchen</t>
+          <t>Kitchen Cabinet Installation: How It's Done Right</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>quartz vs granite</t>
+          <t>kitchen cabinet installation</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
@@ -4422,7 +4422,7 @@
         </is>
       </c>
       <c r="G103" s="3" t="n">
-        <v>40</v>
+        <v>96</v>
       </c>
       <c r="H103" s="5" t="n">
         <v>38</v>
@@ -4436,12 +4436,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Kitchen Layout Basics: Work Triangles, Walkways, and Flow</t>
+          <t>Kitchen and Bath Remodeling Together: One Project or Two?</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>kitchen layout</t>
+          <t>kitchen and bath remodeling</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4460,10 +4460,10 @@
         </is>
       </c>
       <c r="G104" s="3" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="H104" s="5" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
     </row>
     <row r="105">
@@ -4474,12 +4474,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Kitchen Lighting Ideas: Layering Task, Ambient, and Accent</t>
+          <t>Kitchen Design Ideas: Layouts, Light, and Lasting Style</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>kitchen lighting ideas</t>
+          <t>kitchen design ideas</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
@@ -4512,12 +4512,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Modern Kitchen Design: Clean Lines Without the Cold Feel</t>
+          <t>Kitchen Backsplash Ideas That Pull a Remodel Together</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>modern kitchen design</t>
+          <t>kitchen backsplash ideas</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G106" s="3" t="n">
@@ -4550,12 +4550,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Pantry Ideas: Designing Storage That Earns Its Footprint</t>
+          <t>Kitchen Flooring Options Ranked for Durability and Looks</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>pantry ideas</t>
+          <t>kitchen flooring options</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
@@ -4565,19 +4565,19 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="G107" s="3" t="n">
         <v>40</v>
       </c>
       <c r="H107" s="5" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
     </row>
     <row r="108">
@@ -4588,12 +4588,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Kitchen Paint Colors That Flatter Cabinets and Counters</t>
+          <t>Farmhouse Kitchen Ideas That Still Feel Fresh in 2026</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>kitchen paint colors</t>
+          <t>farmhouse kitchen ideas</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G108" s="3" t="n">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Kitchen Appliances: Where to Splurge and Where to Save</t>
+          <t>Choosing a Kitchen Faucet: Finishes, Features, and Value</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>kitchen appliances</t>
+          <t>kitchen faucet ideas</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr">
@@ -4646,14 +4646,14 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G109" s="3" t="n">
         <v>40</v>
       </c>
       <c r="H109" s="5" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
     </row>
     <row r="110">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Kitchen Builders: Worth It, or Overrated?</t>
+          <t>Small Kitchen Ideas: Making a Compact Space Feel Open</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>kitchen builders</t>
+          <t>small kitchen ideas</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
@@ -4679,19 +4679,19 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G110" s="3" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="H110" s="5" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
     </row>
     <row r="111">
@@ -4702,12 +4702,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>White Kitchen Cabinets: Why They Endure, and How to Keep Them Clean</t>
+          <t>Two-Tone Kitchen Cabinets: How to Mix Without a Mess</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>white kitchen cabinets</t>
+          <t>two tone kitchen cabinets</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr">
@@ -4726,10 +4726,10 @@
         </is>
       </c>
       <c r="G111" s="3" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="H111" s="5" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="112">
@@ -4740,34 +4740,34 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Bathroom Remodel General Contractor: What to Expect, Day by Day</t>
+          <t>Kitchen Storage Ideas That Use Every Inch</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>bathroom remodel general contractor</t>
-        </is>
-      </c>
-      <c r="D112" s="8" t="inlineStr">
-        <is>
-          <t>Process &amp; Planning</t>
+          <t>kitchen storage ideas</t>
+        </is>
+      </c>
+      <c r="D112" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G112" s="3" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="H112" s="5" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
     </row>
     <row r="113">
@@ -4778,22 +4778,22 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Outdoor Kitchen Contractors Barclay Downs, Done the Fixed-Price Way</t>
+          <t>White Kitchen Cabinets: Why They Endure, and How to Keep Them Clean</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>outdoor kitchen contractors barclay downs</t>
-        </is>
-      </c>
-      <c r="D113" s="8" t="inlineStr">
-        <is>
-          <t>Process &amp; Planning</t>
+          <t>white kitchen cabinets</t>
+        </is>
+      </c>
+      <c r="D113" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4804,8 +4804,8 @@
       <c r="G113" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="H113" s="4" t="n">
-        <v>24</v>
+      <c r="H113" s="5" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="114">
@@ -4816,12 +4816,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Kitchen Remodel Steps in Order: The Complete Sequence</t>
+          <t>Custom Bathroom Remodel Contractor: A No-Nonsense Buyer's Guide</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>kitchen remodel steps in order</t>
+          <t>custom bathroom remodel contractor</t>
         </is>
       </c>
       <c r="D114" s="8" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4840,10 +4840,10 @@
         </is>
       </c>
       <c r="G114" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="H114" s="4" t="n">
-        <v>24</v>
+        <v>10</v>
+      </c>
+      <c r="H114" s="5" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="115">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Bathroom Remodeler: The Questions to Ask First</t>
+          <t>What Separates a Great Kitchen Remodeler From the Rest</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>bathroom remodeler</t>
+          <t>kitchen remodeler</t>
         </is>
       </c>
       <c r="D115" s="8" t="inlineStr">
@@ -4878,7 +4878,7 @@
         </is>
       </c>
       <c r="G115" s="3" t="n">
-        <v>14</v>
+        <v>151</v>
       </c>
       <c r="H115" s="5" t="n">
         <v>48</v>
@@ -4892,12 +4892,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Contractor for Kitchen Renovation: A No-Nonsense Buyer's Guide</t>
+          <t>What a Kitchen Contractor Handles on a Remodel</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>contractor for kitchen renovation</t>
+          <t>kitchen contractor</t>
         </is>
       </c>
       <c r="D116" s="8" t="inlineStr">
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="G116" s="3" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="H116" s="5" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
     </row>
     <row r="117">
@@ -4930,12 +4930,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Living Through a Kitchen Remodel: How to Stay in Your Home</t>
+          <t>How to Compare the Best Kitchen Remodel Contractors</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>living through a kitchen remodel</t>
+          <t>best kitchen remodel contractors</t>
         </is>
       </c>
       <c r="D117" s="8" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4954,10 +4954,10 @@
         </is>
       </c>
       <c r="G117" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="H117" s="4" t="n">
-        <v>24</v>
+        <v>10</v>
+      </c>
+      <c r="H117" s="5" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="118">
@@ -4968,12 +4968,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Working With an Interior Designer: Why It's Built Into Our Process</t>
+          <t>How Long Does a Kitchen Remodel Take? Why Ours Takes 7 Days</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>working with an interior designer</t>
+          <t>how long does a kitchen remodel take</t>
         </is>
       </c>
       <c r="D118" s="8" t="inlineStr">
@@ -4983,16 +4983,16 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G118" s="3" t="n">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="H118" s="4" t="n">
         <v>24</v>
@@ -5006,12 +5006,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>How to Prepare Your Home for a Kitchen Remodel</t>
+          <t>How to Choose a Kitchen Contractor You Can Actually Trust</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>how to prepare for a kitchen remodel</t>
+          <t>how to choose a kitchen contractor</t>
         </is>
       </c>
       <c r="D119" s="8" t="inlineStr">
@@ -5021,16 +5021,16 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="G119" s="3" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="H119" s="4" t="n">
         <v>24</v>
@@ -5044,12 +5044,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Kitchen Remodel Mistakes to Avoid (and How We Prevent Them)</t>
+          <t>The Kitchen Remodel Checklist Every Homeowner Should Use</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>kitchen remodel mistakes</t>
+          <t>kitchen remodel checklist</t>
         </is>
       </c>
       <c r="D120" s="8" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G120" s="3" t="n">
@@ -5082,12 +5082,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Kitchen Demolition: What Tear-Out Day Actually Involves</t>
+          <t>Questions to Ask a Kitchen Remodel Contractor Before You Sign</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>kitchen demolition</t>
+          <t>kitchen remodel contractor questions</t>
         </is>
       </c>
       <c r="D121" s="8" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -5109,7 +5109,7 @@
         <v>40</v>
       </c>
       <c r="H121" s="5" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -9126,9 +9126,9 @@
       <c r="F121" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G121" s="9" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -9357,9 +9357,9 @@
       <c r="F128" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G128" s="9" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -10851,17 +10851,17 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>kitchen restoration</t>
-        </is>
-      </c>
-      <c r="B174" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>oak kitchen cabinets near me</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -10872,8 +10872,8 @@
       <c r="E174" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F174" s="5" t="n">
-        <v>48</v>
+      <c r="F174" s="4" t="n">
+        <v>18</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
@@ -10884,7 +10884,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>oak kitchen cabinets near me</t>
+          <t>pantry renovation near me</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
@@ -10917,7 +10917,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>pantry renovation near me</t>
+          <t>remodeling companies near me</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
@@ -10950,17 +10950,17 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>remodeling companies near me</t>
-        </is>
-      </c>
-      <c r="B177" s="2" t="inlineStr">
-        <is>
-          <t>Charlotte &amp; Local</t>
+          <t>replacing kitchen cabinets</t>
+        </is>
+      </c>
+      <c r="B177" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -10971,8 +10971,8 @@
       <c r="E177" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F177" s="4" t="n">
-        <v>18</v>
+      <c r="F177" s="5" t="n">
+        <v>38</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
@@ -10983,7 +10983,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>replacing kitchen cabinets</t>
+          <t>small bathroom remodel</t>
         </is>
       </c>
       <c r="B178" s="7" t="inlineStr">
@@ -11016,7 +11016,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>small bathroom remodel</t>
+          <t>#kitchendesign</t>
         </is>
       </c>
       <c r="B179" s="7" t="inlineStr">
@@ -11038,7 +11038,7 @@
         <v>10</v>
       </c>
       <c r="F179" s="5" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
@@ -11049,7 +11049,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>#kitchendesign</t>
+          <t>#kitchenremodeling</t>
         </is>
       </c>
       <c r="B180" s="7" t="inlineStr">
@@ -11082,7 +11082,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>#kitchenremodeling</t>
+          <t>#kitchenrenovation</t>
         </is>
       </c>
       <c r="B181" s="7" t="inlineStr">
@@ -11115,7 +11115,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>#kitchenrenovation</t>
+          <t>$500 kitchen remodel</t>
         </is>
       </c>
       <c r="B182" s="7" t="inlineStr">
@@ -11137,7 +11137,7 @@
         <v>10</v>
       </c>
       <c r="F182" s="5" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
@@ -11148,7 +11148,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>$500 kitchen remodel</t>
+          <t>07807 commercial kitchen design</t>
         </is>
       </c>
       <c r="B183" s="7" t="inlineStr">
@@ -11170,7 +11170,7 @@
         <v>10</v>
       </c>
       <c r="F183" s="5" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
@@ -11181,7 +11181,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>07807 commercial kitchen design</t>
+          <t>07887 commercial kitchen design</t>
         </is>
       </c>
       <c r="B184" s="7" t="inlineStr">
@@ -11214,7 +11214,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>07887 commercial kitchen design</t>
+          <t>1 day bathroom remodel</t>
         </is>
       </c>
       <c r="B185" s="7" t="inlineStr">
@@ -11247,7 +11247,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>1 day bathroom remodel</t>
+          <t>1 week kitchens</t>
         </is>
       </c>
       <c r="B186" s="7" t="inlineStr">
@@ -11269,7 +11269,7 @@
         <v>10</v>
       </c>
       <c r="F186" s="5" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
@@ -11280,7 +11280,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>1 week kitchens</t>
+          <t>10 day kitchen</t>
         </is>
       </c>
       <c r="B187" s="7" t="inlineStr">
@@ -11313,7 +11313,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>10 day kitchen</t>
+          <t>10 day kitchen remodel</t>
         </is>
       </c>
       <c r="B188" s="7" t="inlineStr">
@@ -11335,7 +11335,7 @@
         <v>10</v>
       </c>
       <c r="F188" s="5" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
@@ -11346,12 +11346,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>10 day kitchen remodel</t>
-        </is>
-      </c>
-      <c r="B189" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>10x20 kitchen remodel cost</t>
+        </is>
+      </c>
+      <c r="B189" s="6" t="inlineStr">
+        <is>
+          <t>Cost &amp; Budget</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -11379,12 +11379,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>10x20 kitchen remodel cost</t>
-        </is>
-      </c>
-      <c r="B190" s="6" t="inlineStr">
-        <is>
-          <t>Cost &amp; Budget</t>
+          <t>2 day bathroom remodel</t>
+        </is>
+      </c>
+      <c r="B190" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -11412,7 +11412,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2 day bathroom remodel</t>
+          <t>2026 kitchen remodel</t>
         </is>
       </c>
       <c r="B191" s="7" t="inlineStr">
@@ -11434,7 +11434,7 @@
         <v>10</v>
       </c>
       <c r="F191" s="5" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
@@ -11445,7 +11445,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026 kitchen remodel</t>
+          <t>2026 kitchens</t>
         </is>
       </c>
       <c r="B192" s="7" t="inlineStr">
@@ -11467,7 +11467,7 @@
         <v>10</v>
       </c>
       <c r="F192" s="5" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
@@ -11478,7 +11478,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026 kitchens</t>
+          <t>20k kitchen remodel</t>
         </is>
       </c>
       <c r="B193" s="7" t="inlineStr">
@@ -11500,7 +11500,7 @@
         <v>10</v>
       </c>
       <c r="F193" s="5" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
@@ -11511,7 +11511,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>20k kitchen remodel</t>
+          <t>25k kitchen remodel</t>
         </is>
       </c>
       <c r="B194" s="7" t="inlineStr">
@@ -11544,7 +11544,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>25k kitchen remodel</t>
+          <t>3 day bath and kitchen</t>
         </is>
       </c>
       <c r="B195" s="7" t="inlineStr">
@@ -11565,8 +11565,8 @@
       <c r="E195" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F195" s="5" t="n">
-        <v>38</v>
+      <c r="F195" s="4" t="n">
+        <v>24</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
@@ -11577,7 +11577,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>3 day bath and kitchen</t>
+          <t>3 day kitchen remodel</t>
         </is>
       </c>
       <c r="B196" s="7" t="inlineStr">
@@ -11598,8 +11598,8 @@
       <c r="E196" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F196" s="4" t="n">
-        <v>24</v>
+      <c r="F196" s="5" t="n">
+        <v>30</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
@@ -11610,7 +11610,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>3 day kitchen remodel</t>
+          <t>3 day kitchens</t>
         </is>
       </c>
       <c r="B197" s="7" t="inlineStr">
@@ -11632,7 +11632,7 @@
         <v>10</v>
       </c>
       <c r="F197" s="5" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
@@ -11643,7 +11643,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>3 day kitchens</t>
+          <t>36 vs 42 kitchen cabinets</t>
         </is>
       </c>
       <c r="B198" s="7" t="inlineStr">
@@ -11664,8 +11664,8 @@
       <c r="E198" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F198" s="5" t="n">
-        <v>38</v>
+      <c r="F198" s="4" t="n">
+        <v>24</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
@@ -11676,7 +11676,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>36 vs 42 kitchen cabinets</t>
+          <t>3d rendering kitchen remodel</t>
         </is>
       </c>
       <c r="B199" s="7" t="inlineStr">
@@ -11697,8 +11697,8 @@
       <c r="E199" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F199" s="4" t="n">
-        <v>24</v>
+      <c r="F199" s="5" t="n">
+        <v>30</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
@@ -11709,7 +11709,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>3d rendering kitchen remodel</t>
+          <t>42 bar height cabinets</t>
         </is>
       </c>
       <c r="B200" s="7" t="inlineStr">
@@ -11742,7 +11742,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>42 bar height cabinets</t>
+          <t>42 cabinets</t>
         </is>
       </c>
       <c r="B201" s="7" t="inlineStr">
@@ -11764,7 +11764,7 @@
         <v>10</v>
       </c>
       <c r="F201" s="5" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>42 cabinets</t>
+          <t>42 in kitchen cabinets</t>
         </is>
       </c>
       <c r="B202" s="7" t="inlineStr">
@@ -11797,7 +11797,7 @@
         <v>10</v>
       </c>
       <c r="F202" s="5" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
@@ -11808,7 +11808,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>42 in kitchen cabinets</t>
+          <t>42 in upper cabinets</t>
         </is>
       </c>
       <c r="B203" s="7" t="inlineStr">
@@ -11841,7 +11841,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>42 in upper cabinets</t>
+          <t>42 inch cabinets 8 foot ceiling</t>
         </is>
       </c>
       <c r="B204" s="7" t="inlineStr">
@@ -11862,8 +11862,8 @@
       <c r="E204" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F204" s="5" t="n">
-        <v>30</v>
+      <c r="F204" s="4" t="n">
+        <v>24</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
@@ -11874,7 +11874,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>42 inch cabinets 8 foot ceiling</t>
+          <t>42 inch cabinets vs 36</t>
         </is>
       </c>
       <c r="B205" s="7" t="inlineStr">
@@ -11907,7 +11907,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>42 inch cabinets vs 36</t>
+          <t>42 inch height cabinets</t>
         </is>
       </c>
       <c r="B206" s="7" t="inlineStr">
@@ -11928,8 +11928,8 @@
       <c r="E206" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F206" s="4" t="n">
-        <v>24</v>
+      <c r="F206" s="5" t="n">
+        <v>30</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
@@ -11940,7 +11940,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>42 inch height cabinets</t>
+          <t>42 inch high upper kitchen cabinets</t>
         </is>
       </c>
       <c r="B207" s="7" t="inlineStr">
@@ -11961,8 +11961,8 @@
       <c r="E207" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F207" s="5" t="n">
-        <v>30</v>
+      <c r="F207" s="4" t="n">
+        <v>24</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
@@ -11973,7 +11973,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>42 inch high upper kitchen cabinets</t>
+          <t>42 inch tall cabinets</t>
         </is>
       </c>
       <c r="B208" s="7" t="inlineStr">
@@ -11994,8 +11994,8 @@
       <c r="E208" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F208" s="4" t="n">
-        <v>24</v>
+      <c r="F208" s="5" t="n">
+        <v>30</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
@@ -12006,7 +12006,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>42 inch tall cabinets</t>
+          <t>42 inch tall kitchen cabinets</t>
         </is>
       </c>
       <c r="B209" s="7" t="inlineStr">
@@ -12027,8 +12027,8 @@
       <c r="E209" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F209" s="5" t="n">
-        <v>30</v>
+      <c r="F209" s="4" t="n">
+        <v>24</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
@@ -12039,7 +12039,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>42 inch tall kitchen cabinets</t>
+          <t>42 inch tall upper kitchen cabinets</t>
         </is>
       </c>
       <c r="B210" s="7" t="inlineStr">
@@ -12072,7 +12072,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>42 inch tall upper kitchen cabinets</t>
+          <t>42 inch upper cabinets</t>
         </is>
       </c>
       <c r="B211" s="7" t="inlineStr">
@@ -12093,8 +12093,8 @@
       <c r="E211" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F211" s="4" t="n">
-        <v>24</v>
+      <c r="F211" s="5" t="n">
+        <v>30</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
@@ -12105,7 +12105,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>42 inch upper cabinets</t>
+          <t>42 inch upper kitchen cabinets</t>
         </is>
       </c>
       <c r="B212" s="7" t="inlineStr">
@@ -12126,8 +12126,8 @@
       <c r="E212" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F212" s="5" t="n">
-        <v>30</v>
+      <c r="F212" s="4" t="n">
+        <v>24</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
@@ -12138,7 +12138,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>42 inch upper kitchen cabinets</t>
+          <t>42 inch vs 36 inch kitchen cabinets</t>
         </is>
       </c>
       <c r="B213" s="7" t="inlineStr">
@@ -12171,7 +12171,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>42 inch vs 36 inch kitchen cabinets</t>
+          <t>42 inch wall cabinets for kitchen</t>
         </is>
       </c>
       <c r="B214" s="7" t="inlineStr">
@@ -12204,7 +12204,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>42 inch wall cabinets for kitchen</t>
+          <t>42 tall upper kitchen cabinets</t>
         </is>
       </c>
       <c r="B215" s="7" t="inlineStr">
@@ -12237,7 +12237,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>42 tall upper kitchen cabinets</t>
+          <t>42 upper kitchen cabinets</t>
         </is>
       </c>
       <c r="B216" s="7" t="inlineStr">
@@ -12258,8 +12258,8 @@
       <c r="E216" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F216" s="4" t="n">
-        <v>24</v>
+      <c r="F216" s="5" t="n">
+        <v>30</v>
       </c>
       <c r="G216" t="inlineStr">
         <is>
@@ -12270,7 +12270,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>42 upper kitchen cabinets</t>
+          <t>42in cabinets</t>
         </is>
       </c>
       <c r="B217" s="7" t="inlineStr">
@@ -12292,7 +12292,7 @@
         <v>10</v>
       </c>
       <c r="F217" s="5" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="G217" t="inlineStr">
         <is>
@@ -12303,7 +12303,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>42in cabinets</t>
+          <t>5 day kitchens</t>
         </is>
       </c>
       <c r="B218" s="7" t="inlineStr">
@@ -12325,7 +12325,7 @@
         <v>10</v>
       </c>
       <c r="F218" s="5" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
@@ -12336,17 +12336,17 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>5 day kitchens</t>
-        </is>
-      </c>
-      <c r="B219" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>affordable bathroom remodel charlotte</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -12357,8 +12357,8 @@
       <c r="E219" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F219" s="5" t="n">
-        <v>38</v>
+      <c r="F219" s="4" t="n">
+        <v>18</v>
       </c>
       <c r="G219" t="inlineStr">
         <is>
@@ -12369,7 +12369,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>affordable bathroom remodel charlotte</t>
+          <t>affordable bathroom remodel charlotte nc</t>
         </is>
       </c>
       <c r="B220" s="2" t="inlineStr">
@@ -12402,17 +12402,17 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>affordable bathroom remodel charlotte nc</t>
-        </is>
-      </c>
-      <c r="B221" s="2" t="inlineStr">
-        <is>
-          <t>Charlotte &amp; Local</t>
+          <t>affordable kitchen design</t>
+        </is>
+      </c>
+      <c r="B221" s="6" t="inlineStr">
+        <is>
+          <t>Cost &amp; Budget</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -12423,8 +12423,8 @@
       <c r="E221" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F221" s="4" t="n">
-        <v>18</v>
+      <c r="F221" s="5" t="n">
+        <v>38</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
@@ -12435,17 +12435,17 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>affordable kitchen design</t>
-        </is>
-      </c>
-      <c r="B222" s="6" t="inlineStr">
-        <is>
-          <t>Cost &amp; Budget</t>
+          <t>affordable kitchen remodel charlotte nc</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -12456,8 +12456,8 @@
       <c r="E222" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F222" s="5" t="n">
-        <v>38</v>
+      <c r="F222" s="4" t="n">
+        <v>18</v>
       </c>
       <c r="G222" t="inlineStr">
         <is>
@@ -12468,17 +12468,17 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>affordable kitchen remodel charlotte nc</t>
-        </is>
-      </c>
-      <c r="B223" s="2" t="inlineStr">
-        <is>
-          <t>Charlotte &amp; Local</t>
+          <t>ai kitchen remodel</t>
+        </is>
+      </c>
+      <c r="B223" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -12489,8 +12489,8 @@
       <c r="E223" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F223" s="4" t="n">
-        <v>18</v>
+      <c r="F223" s="5" t="n">
+        <v>38</v>
       </c>
       <c r="G223" t="inlineStr">
         <is>
@@ -12501,7 +12501,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>ai kitchen remodel</t>
+          <t>ai kitchen remodel free</t>
         </is>
       </c>
       <c r="B224" s="7" t="inlineStr">
@@ -12523,7 +12523,7 @@
         <v>10</v>
       </c>
       <c r="F224" s="5" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="G224" t="inlineStr">
         <is>
@@ -12534,7 +12534,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>ai kitchen remodel free</t>
+          <t>ai renovation design</t>
         </is>
       </c>
       <c r="B225" s="7" t="inlineStr">
@@ -12556,7 +12556,7 @@
         <v>10</v>
       </c>
       <c r="F225" s="5" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="G225" t="inlineStr">
         <is>
@@ -12567,7 +12567,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>ai renovation design</t>
+          <t>all day kitchen</t>
         </is>
       </c>
       <c r="B226" s="7" t="inlineStr">
@@ -12600,7 +12600,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>all day kitchen</t>
+          <t>amazing kitchens</t>
         </is>
       </c>
       <c r="B227" s="7" t="inlineStr">
@@ -12622,7 +12622,7 @@
         <v>10</v>
       </c>
       <c r="F227" s="5" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G227" t="inlineStr">
         <is>
@@ -12633,7 +12633,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>amazing kitchens</t>
+          <t>andrea granger kitchen makeover</t>
         </is>
       </c>
       <c r="B228" s="7" t="inlineStr">
@@ -12655,7 +12655,7 @@
         <v>10</v>
       </c>
       <c r="F228" s="5" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="G228" t="inlineStr">
         <is>
@@ -12666,7 +12666,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>andrea granger kitchen makeover</t>
+          <t>angie's list bathroom remodel</t>
         </is>
       </c>
       <c r="B229" s="7" t="inlineStr">
@@ -12699,7 +12699,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>angie's list bathroom remodel</t>
+          <t>apartment cabinet renovation</t>
         </is>
       </c>
       <c r="B230" s="7" t="inlineStr">
@@ -12721,7 +12721,7 @@
         <v>10</v>
       </c>
       <c r="F230" s="5" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="G230" t="inlineStr">
         <is>
@@ -12732,7 +12732,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>apartment cabinet renovation</t>
+          <t>apartment kitchen reno</t>
         </is>
       </c>
       <c r="B231" s="7" t="inlineStr">
@@ -12765,7 +12765,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>apartment kitchen reno</t>
+          <t>apartment kitchen renovation</t>
         </is>
       </c>
       <c r="B232" s="7" t="inlineStr">
@@ -12798,12 +12798,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>apartment kitchen renovation</t>
-        </is>
-      </c>
-      <c r="B233" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>approximate cost of kitchen remodel</t>
+        </is>
+      </c>
+      <c r="B233" s="6" t="inlineStr">
+        <is>
+          <t>Cost &amp; Budget</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -12819,8 +12819,8 @@
       <c r="E233" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F233" s="5" t="n">
-        <v>38</v>
+      <c r="F233" s="4" t="n">
+        <v>24</v>
       </c>
       <c r="G233" t="inlineStr">
         <is>
@@ -12831,12 +12831,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>approximate cost of kitchen remodel</t>
-        </is>
-      </c>
-      <c r="B234" s="6" t="inlineStr">
-        <is>
-          <t>Cost &amp; Budget</t>
+          <t>architectural design kitchens</t>
+        </is>
+      </c>
+      <c r="B234" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -12852,8 +12852,8 @@
       <c r="E234" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F234" s="4" t="n">
-        <v>24</v>
+      <c r="F234" s="5" t="n">
+        <v>38</v>
       </c>
       <c r="G234" t="inlineStr">
         <is>
@@ -12864,7 +12864,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>architectural design kitchens</t>
+          <t>are 42 inch cabinets standard</t>
         </is>
       </c>
       <c r="B235" s="7" t="inlineStr">
@@ -12885,8 +12885,8 @@
       <c r="E235" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F235" s="5" t="n">
-        <v>38</v>
+      <c r="F235" s="4" t="n">
+        <v>24</v>
       </c>
       <c r="G235" t="inlineStr">
         <is>
@@ -12897,12 +12897,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>are 42 inch cabinets standard</t>
-        </is>
-      </c>
-      <c r="B236" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>average cost for a kitchen remodel</t>
+        </is>
+      </c>
+      <c r="B236" s="6" t="inlineStr">
+        <is>
+          <t>Cost &amp; Budget</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -12930,7 +12930,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>average cost for a kitchen remodel</t>
+          <t>average cost of a complete kitchen remodel</t>
         </is>
       </c>
       <c r="B237" s="6" t="inlineStr">
@@ -12963,7 +12963,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>average cost of a complete kitchen remodel</t>
+          <t>average cost of a full kitchen remodel</t>
         </is>
       </c>
       <c r="B238" s="6" t="inlineStr">
@@ -12996,7 +12996,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>average cost of a full kitchen remodel</t>
+          <t>average cost of a kitchen remodel 2024</t>
         </is>
       </c>
       <c r="B239" s="6" t="inlineStr">
@@ -13029,7 +13029,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>average cost of a kitchen remodel 2024</t>
+          <t>average cost of a new kitchen remodel</t>
         </is>
       </c>
       <c r="B240" s="6" t="inlineStr">
@@ -13062,7 +13062,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>average cost of a new kitchen remodel</t>
+          <t>average cost of galley kitchen remodel</t>
         </is>
       </c>
       <c r="B241" s="6" t="inlineStr">
@@ -13095,7 +13095,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>average cost of galley kitchen remodel</t>
+          <t>average cost of kitchen remodel 2021</t>
         </is>
       </c>
       <c r="B242" s="6" t="inlineStr">
@@ -13128,7 +13128,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>average cost of kitchen remodel 2021</t>
+          <t>average cost of kitchen remodel in colorado</t>
         </is>
       </c>
       <c r="B243" s="6" t="inlineStr">
@@ -13161,7 +13161,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>average cost of kitchen remodel in colorado</t>
+          <t>average cost of kitchen renovation</t>
         </is>
       </c>
       <c r="B244" s="6" t="inlineStr">
@@ -13194,7 +13194,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>average cost of kitchen renovation</t>
+          <t>average cost of large kitchen remodel</t>
         </is>
       </c>
       <c r="B245" s="6" t="inlineStr">
@@ -13227,7 +13227,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>average cost of large kitchen remodel</t>
+          <t>average cost of redoing a kitchen</t>
         </is>
       </c>
       <c r="B246" s="6" t="inlineStr">
@@ -13260,7 +13260,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>average cost of redoing a kitchen</t>
+          <t>average cost to update a kitchen</t>
         </is>
       </c>
       <c r="B247" s="6" t="inlineStr">
@@ -13293,7 +13293,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>average cost to update a kitchen</t>
+          <t>average cost to upgrade kitchen</t>
         </is>
       </c>
       <c r="B248" s="6" t="inlineStr">
@@ -13326,12 +13326,12 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>average cost to upgrade kitchen</t>
-        </is>
-      </c>
-      <c r="B249" s="6" t="inlineStr">
-        <is>
-          <t>Cost &amp; Budget</t>
+          <t>average height of kitchen cabinets</t>
+        </is>
+      </c>
+      <c r="B249" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -13359,7 +13359,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>average height of kitchen cabinets</t>
+          <t>average kitchen remodel</t>
         </is>
       </c>
       <c r="B250" s="7" t="inlineStr">
@@ -13380,8 +13380,8 @@
       <c r="E250" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F250" s="4" t="n">
-        <v>24</v>
+      <c r="F250" s="5" t="n">
+        <v>38</v>
       </c>
       <c r="G250" t="inlineStr">
         <is>
@@ -13392,7 +13392,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>average kitchen remodel</t>
+          <t>average kitchen remodel time</t>
         </is>
       </c>
       <c r="B251" s="7" t="inlineStr">
@@ -13414,7 +13414,7 @@
         <v>10</v>
       </c>
       <c r="F251" s="5" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="G251" t="inlineStr">
         <is>
@@ -13425,12 +13425,12 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>average kitchen remodel time</t>
-        </is>
-      </c>
-      <c r="B252" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>average price for a kitchen remodel</t>
+        </is>
+      </c>
+      <c r="B252" s="6" t="inlineStr">
+        <is>
+          <t>Cost &amp; Budget</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -13446,8 +13446,8 @@
       <c r="E252" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F252" s="5" t="n">
-        <v>30</v>
+      <c r="F252" s="4" t="n">
+        <v>24</v>
       </c>
       <c r="G252" t="inlineStr">
         <is>
@@ -13458,12 +13458,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>average price for a kitchen remodel</t>
-        </is>
-      </c>
-      <c r="B253" s="6" t="inlineStr">
-        <is>
-          <t>Cost &amp; Budget</t>
+          <t>average time to renovate a kitchen</t>
+        </is>
+      </c>
+      <c r="B253" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -13491,7 +13491,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>average time to renovate a kitchen</t>
+          <t>award-winning kitchen remodel</t>
         </is>
       </c>
       <c r="B254" s="7" t="inlineStr">
@@ -13512,8 +13512,8 @@
       <c r="E254" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F254" s="4" t="n">
-        <v>24</v>
+      <c r="F254" s="5" t="n">
+        <v>38</v>
       </c>
       <c r="G254" t="inlineStr">
         <is>
@@ -13524,7 +13524,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>award-winning kitchen remodel</t>
+          <t>basic kitchen remodel</t>
         </is>
       </c>
       <c r="B255" s="7" t="inlineStr">
@@ -13557,17 +13557,17 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>basic kitchen remodel</t>
-        </is>
-      </c>
-      <c r="B256" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>bath and vanity stores near me</t>
+        </is>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -13578,8 +13578,8 @@
       <c r="E256" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F256" s="5" t="n">
-        <v>38</v>
+      <c r="F256" s="4" t="n">
+        <v>18</v>
       </c>
       <c r="G256" t="inlineStr">
         <is>
@@ -13590,7 +13590,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>bath and vanity stores near me</t>
+          <t>bath design near me</t>
         </is>
       </c>
       <c r="B257" s="2" t="inlineStr">
@@ -13623,17 +13623,17 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>bath design near me</t>
-        </is>
-      </c>
-      <c r="B258" s="2" t="inlineStr">
-        <is>
-          <t>Charlotte &amp; Local</t>
+          <t>bath plus kitchen</t>
+        </is>
+      </c>
+      <c r="B258" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -13644,8 +13644,8 @@
       <c r="E258" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F258" s="4" t="n">
-        <v>18</v>
+      <c r="F258" s="5" t="n">
+        <v>38</v>
       </c>
       <c r="G258" t="inlineStr">
         <is>
@@ -13656,7 +13656,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>bath plus kitchen</t>
+          <t>bath remodel companies</t>
         </is>
       </c>
       <c r="B259" s="7" t="inlineStr">
@@ -13666,7 +13666,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -13689,7 +13689,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>bath remodel companies</t>
+          <t>bath remodel ideas</t>
         </is>
       </c>
       <c r="B260" s="7" t="inlineStr">
@@ -13699,12 +13699,12 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="E260" s="3" t="n">
@@ -13722,29 +13722,29 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>bath remodel ideas</t>
-        </is>
-      </c>
-      <c r="B261" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>bath remodel stores near me</t>
+        </is>
+      </c>
+      <c r="B261" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="E261" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F261" s="5" t="n">
-        <v>38</v>
+      <c r="F261" s="4" t="n">
+        <v>18</v>
       </c>
       <c r="G261" t="inlineStr">
         <is>
@@ -13755,7 +13755,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>bath remodel stores near me</t>
+          <t>bath remodeling showrooms near me</t>
         </is>
       </c>
       <c r="B262" s="2" t="inlineStr">
@@ -13788,7 +13788,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>bath remodeling showrooms near me</t>
+          <t>bath renovations charlotte</t>
         </is>
       </c>
       <c r="B263" s="2" t="inlineStr">
@@ -13810,7 +13810,7 @@
         <v>10</v>
       </c>
       <c r="F263" s="4" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G263" t="inlineStr">
         <is>
@@ -13821,17 +13821,17 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>bath renovations charlotte</t>
-        </is>
-      </c>
-      <c r="B264" s="2" t="inlineStr">
-        <is>
-          <t>Charlotte &amp; Local</t>
+          <t>bathroom</t>
+        </is>
+      </c>
+      <c r="B264" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -13842,8 +13842,8 @@
       <c r="E264" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F264" s="4" t="n">
-        <v>24</v>
+      <c r="F264" s="5" t="n">
+        <v>48</v>
       </c>
       <c r="G264" t="inlineStr">
         <is>
@@ -13854,7 +13854,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>bathroom</t>
+          <t>bathroom and kitchen</t>
         </is>
       </c>
       <c r="B265" s="7" t="inlineStr">
@@ -13876,7 +13876,7 @@
         <v>10</v>
       </c>
       <c r="F265" s="5" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="G265" t="inlineStr">
         <is>
@@ -13887,7 +13887,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>bathroom and kitchen</t>
+          <t>bathroom and kitchen remodel</t>
         </is>
       </c>
       <c r="B266" s="7" t="inlineStr">
@@ -13909,7 +13909,7 @@
         <v>10</v>
       </c>
       <c r="F266" s="5" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="G266" t="inlineStr">
         <is>
@@ -13920,17 +13920,17 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>bathroom and kitchen remodel</t>
-        </is>
-      </c>
-      <c r="B267" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>bathroom and kitchen remodel contractors near me</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -13941,8 +13941,8 @@
       <c r="E267" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F267" s="5" t="n">
-        <v>30</v>
+      <c r="F267" s="4" t="n">
+        <v>18</v>
       </c>
       <c r="G267" t="inlineStr">
         <is>
@@ -13953,17 +13953,17 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>bathroom and kitchen remodel contractors near me</t>
-        </is>
-      </c>
-      <c r="B268" s="2" t="inlineStr">
-        <is>
-          <t>Charlotte &amp; Local</t>
+          <t>bathroom and kitchen remodel cost</t>
+        </is>
+      </c>
+      <c r="B268" s="6" t="inlineStr">
+        <is>
+          <t>Cost &amp; Budget</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -13975,7 +13975,7 @@
         <v>10</v>
       </c>
       <c r="F268" s="4" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G268" t="inlineStr">
         <is>
@@ -13986,12 +13986,12 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>bathroom and kitchen remodel cost</t>
-        </is>
-      </c>
-      <c r="B269" s="6" t="inlineStr">
-        <is>
-          <t>Cost &amp; Budget</t>
+          <t>bathroom and kitchen renovation</t>
+        </is>
+      </c>
+      <c r="B269" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -14007,8 +14007,8 @@
       <c r="E269" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F269" s="4" t="n">
-        <v>24</v>
+      <c r="F269" s="5" t="n">
+        <v>30</v>
       </c>
       <c r="G269" t="inlineStr">
         <is>
@@ -14019,7 +14019,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>bathroom and kitchen renovation</t>
+          <t>bathroom and kitchen store</t>
         </is>
       </c>
       <c r="B270" s="7" t="inlineStr">
@@ -14052,17 +14052,17 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>bathroom and kitchen store</t>
-        </is>
-      </c>
-      <c r="B271" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>bathroom cabinet refacing near me</t>
+        </is>
+      </c>
+      <c r="B271" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -14073,8 +14073,8 @@
       <c r="E271" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F271" s="5" t="n">
-        <v>30</v>
+      <c r="F271" s="4" t="n">
+        <v>18</v>
       </c>
       <c r="G271" t="inlineStr">
         <is>
@@ -14085,7 +14085,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>bathroom cabinet refacing near me</t>
+          <t>bathroom cabinet services charlotte nc</t>
         </is>
       </c>
       <c r="B272" s="2" t="inlineStr">
@@ -14118,7 +14118,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>bathroom cabinet services charlotte nc</t>
+          <t>bathroom contractor charlotte</t>
         </is>
       </c>
       <c r="B273" s="2" t="inlineStr">
@@ -14140,7 +14140,7 @@
         <v>10</v>
       </c>
       <c r="F273" s="4" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -14151,12 +14151,12 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>bathroom contractor charlotte</t>
-        </is>
-      </c>
-      <c r="B274" s="2" t="inlineStr">
-        <is>
-          <t>Charlotte &amp; Local</t>
+          <t>bathroom contractors</t>
+        </is>
+      </c>
+      <c r="B274" s="8" t="inlineStr">
+        <is>
+          <t>Process &amp; Planning</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -14172,8 +14172,8 @@
       <c r="E274" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F274" s="4" t="n">
-        <v>24</v>
+      <c r="F274" s="5" t="n">
+        <v>48</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -14184,12 +14184,12 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>bathroom contractors</t>
-        </is>
-      </c>
-      <c r="B275" s="8" t="inlineStr">
-        <is>
-          <t>Process &amp; Planning</t>
+          <t>bathroom contractors charlotte nc</t>
+        </is>
+      </c>
+      <c r="B275" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -14205,8 +14205,8 @@
       <c r="E275" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F275" s="5" t="n">
-        <v>48</v>
+      <c r="F275" s="4" t="n">
+        <v>18</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -14217,7 +14217,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>bathroom contractors charlotte nc</t>
+          <t>bathroom countertop replacement near me</t>
         </is>
       </c>
       <c r="B276" s="2" t="inlineStr">
@@ -14250,17 +14250,17 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>bathroom countertop replacement near me</t>
-        </is>
-      </c>
-      <c r="B277" s="2" t="inlineStr">
-        <is>
-          <t>Charlotte &amp; Local</t>
+          <t>bathroom countertops</t>
+        </is>
+      </c>
+      <c r="B277" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -14271,8 +14271,8 @@
       <c r="E277" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F277" s="4" t="n">
-        <v>18</v>
+      <c r="F277" s="5" t="n">
+        <v>48</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
@@ -14283,17 +14283,17 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>bathroom countertops</t>
-        </is>
-      </c>
-      <c r="B278" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>bathroom demolition near me</t>
+        </is>
+      </c>
+      <c r="B278" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -14304,8 +14304,8 @@
       <c r="E278" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F278" s="5" t="n">
-        <v>48</v>
+      <c r="F278" s="4" t="n">
+        <v>18</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -14316,7 +14316,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>bathroom demolition near me</t>
+          <t>bathroom design and remodel near me</t>
         </is>
       </c>
       <c r="B279" s="2" t="inlineStr">
@@ -14349,7 +14349,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>bathroom design and remodel near me</t>
+          <t>bathroom design center near me</t>
         </is>
       </c>
       <c r="B280" s="2" t="inlineStr">
@@ -14382,7 +14382,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>bathroom design center near me</t>
+          <t>bathroom design near me</t>
         </is>
       </c>
       <c r="B281" s="2" t="inlineStr">
@@ -14415,7 +14415,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>bathroom design near me</t>
+          <t>bathroom designer near me</t>
         </is>
       </c>
       <c r="B282" s="2" t="inlineStr">
@@ -14448,17 +14448,17 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>bathroom designer near me</t>
-        </is>
-      </c>
-      <c r="B283" s="2" t="inlineStr">
-        <is>
-          <t>Charlotte &amp; Local</t>
+          <t>bathroom makeover</t>
+        </is>
+      </c>
+      <c r="B283" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -14469,8 +14469,8 @@
       <c r="E283" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F283" s="4" t="n">
-        <v>18</v>
+      <c r="F283" s="5" t="n">
+        <v>48</v>
       </c>
       <c r="G283" t="inlineStr">
         <is>
@@ -14481,7 +14481,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>bathroom makeover</t>
+          <t>bathroom redesign</t>
         </is>
       </c>
       <c r="B284" s="7" t="inlineStr">
@@ -14514,17 +14514,17 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>bathroom redesign</t>
-        </is>
-      </c>
-      <c r="B285" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>bathroom remodel belmont</t>
+        </is>
+      </c>
+      <c r="B285" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -14535,8 +14535,8 @@
       <c r="E285" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F285" s="5" t="n">
-        <v>48</v>
+      <c r="F285" s="4" t="n">
+        <v>24</v>
       </c>
       <c r="G285" t="inlineStr">
         <is>
@@ -14547,7 +14547,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>bathroom remodel belmont</t>
+          <t>bathroom remodel companies near me</t>
         </is>
       </c>
       <c r="B286" s="2" t="inlineStr">
@@ -14569,7 +14569,7 @@
         <v>10</v>
       </c>
       <c r="F286" s="4" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G286" t="inlineStr">
         <is>
@@ -14580,7 +14580,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>bathroom remodel companies near me</t>
+          <t>bathroom remodel contractor charlotte nc</t>
         </is>
       </c>
       <c r="B287" s="2" t="inlineStr">
@@ -14613,12 +14613,12 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>bathroom remodel contractor charlotte nc</t>
-        </is>
-      </c>
-      <c r="B288" s="2" t="inlineStr">
-        <is>
-          <t>Charlotte &amp; Local</t>
+          <t>bathroom remodel contractors</t>
+        </is>
+      </c>
+      <c r="B288" s="8" t="inlineStr">
+        <is>
+          <t>Process &amp; Planning</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -14634,8 +14634,8 @@
       <c r="E288" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F288" s="4" t="n">
-        <v>18</v>
+      <c r="F288" s="5" t="n">
+        <v>38</v>
       </c>
       <c r="G288" t="inlineStr">
         <is>
@@ -14646,12 +14646,12 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>bathroom remodel contractors</t>
-        </is>
-      </c>
-      <c r="B289" s="8" t="inlineStr">
-        <is>
-          <t>Process &amp; Planning</t>
+          <t>bathroom remodel cost charlotte nc</t>
+        </is>
+      </c>
+      <c r="B289" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -14667,8 +14667,8 @@
       <c r="E289" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F289" s="5" t="n">
-        <v>38</v>
+      <c r="F289" s="4" t="n">
+        <v>18</v>
       </c>
       <c r="G289" t="inlineStr">
         <is>
@@ -14679,12 +14679,12 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>bathroom remodel cost charlotte nc</t>
-        </is>
-      </c>
-      <c r="B290" s="2" t="inlineStr">
-        <is>
-          <t>Charlotte &amp; Local</t>
+          <t>bathroom remodel general contractor</t>
+        </is>
+      </c>
+      <c r="B290" s="8" t="inlineStr">
+        <is>
+          <t>Process &amp; Planning</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -14700,29 +14700,29 @@
       <c r="E290" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F290" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="G290" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="F290" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="G290" s="9" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>bathroom remodel general contractor</t>
-        </is>
-      </c>
-      <c r="B291" s="8" t="inlineStr">
-        <is>
-          <t>Process &amp; Planning</t>
+          <t>bathroom remodel huntersville</t>
+        </is>
+      </c>
+      <c r="B291" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -14733,19 +14733,19 @@
       <c r="E291" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F291" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="G291" s="9" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="F291" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>bathroom remodel huntersville</t>
+          <t>bathroom remodel madison park nc</t>
         </is>
       </c>
       <c r="B292" s="2" t="inlineStr">
@@ -14755,7 +14755,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -14767,7 +14767,7 @@
         <v>10</v>
       </c>
       <c r="F292" s="4" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G292" t="inlineStr">
         <is>
@@ -14778,17 +14778,17 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>bathroom remodel madison park nc</t>
-        </is>
-      </c>
-      <c r="B293" s="2" t="inlineStr">
-        <is>
-          <t>Charlotte &amp; Local</t>
+          <t>bathroom remodel paw creek</t>
+        </is>
+      </c>
+      <c r="B293" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -14799,8 +14799,8 @@
       <c r="E293" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F293" s="4" t="n">
-        <v>18</v>
+      <c r="F293" s="5" t="n">
+        <v>30</v>
       </c>
       <c r="G293" t="inlineStr">
         <is>
@@ -14811,7 +14811,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>bathroom remodel paw creek</t>
+          <t>bathroom remodel pineville</t>
         </is>
       </c>
       <c r="B294" s="7" t="inlineStr">
@@ -14833,7 +14833,7 @@
         <v>10</v>
       </c>
       <c r="F294" s="5" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="G294" t="inlineStr">
         <is>
@@ -14844,17 +14844,17 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>bathroom remodel pineville</t>
-        </is>
-      </c>
-      <c r="B295" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>bathroom remodeler charlotte</t>
+        </is>
+      </c>
+      <c r="B295" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -14865,8 +14865,8 @@
       <c r="E295" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F295" s="5" t="n">
-        <v>38</v>
+      <c r="F295" s="4" t="n">
+        <v>24</v>
       </c>
       <c r="G295" t="inlineStr">
         <is>
@@ -14877,7 +14877,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>bathroom remodeler charlotte</t>
+          <t>bathroom remodeler charlotte, nc</t>
         </is>
       </c>
       <c r="B296" s="2" t="inlineStr">
@@ -14899,7 +14899,7 @@
         <v>10</v>
       </c>
       <c r="F296" s="4" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G296" t="inlineStr">
         <is>
@@ -14910,7 +14910,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>bathroom remodeler charlotte, nc</t>
+          <t>bathroom remodeling companies charlotte</t>
         </is>
       </c>
       <c r="B297" s="2" t="inlineStr">
@@ -14943,7 +14943,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>bathroom remodeling companies charlotte</t>
+          <t>bathroom remodeling companies charlotte nc</t>
         </is>
       </c>
       <c r="B298" s="2" t="inlineStr">
@@ -14976,7 +14976,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>bathroom remodeling companies charlotte nc</t>
+          <t>bathroom remodeling company charlotte</t>
         </is>
       </c>
       <c r="B299" s="2" t="inlineStr">
@@ -15009,17 +15009,17 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>bathroom remodeling company charlotte</t>
-        </is>
-      </c>
-      <c r="B300" s="2" t="inlineStr">
-        <is>
-          <t>Charlotte &amp; Local</t>
+          <t>bathroom remodeling gastonia</t>
+        </is>
+      </c>
+      <c r="B300" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -15030,8 +15030,8 @@
       <c r="E300" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F300" s="4" t="n">
-        <v>18</v>
+      <c r="F300" s="5" t="n">
+        <v>38</v>
       </c>
       <c r="G300" t="inlineStr">
         <is>
@@ -15042,7 +15042,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>bathroom remodeling gastonia</t>
+          <t>bathroom remodeling leads</t>
         </is>
       </c>
       <c r="B301" s="7" t="inlineStr">
@@ -15075,17 +15075,17 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>bathroom remodeling leads</t>
-        </is>
-      </c>
-      <c r="B302" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>bathroom remodeling mooresville nc</t>
+        </is>
+      </c>
+      <c r="B302" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -15096,8 +15096,8 @@
       <c r="E302" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F302" s="5" t="n">
-        <v>38</v>
+      <c r="F302" s="4" t="n">
+        <v>18</v>
       </c>
       <c r="G302" t="inlineStr">
         <is>
@@ -15108,12 +15108,12 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>bathroom remodeling mooresville nc</t>
-        </is>
-      </c>
-      <c r="B303" s="2" t="inlineStr">
-        <is>
-          <t>Charlotte &amp; Local</t>
+          <t>bathroom remodeling services</t>
+        </is>
+      </c>
+      <c r="B303" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -15129,8 +15129,8 @@
       <c r="E303" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F303" s="4" t="n">
-        <v>18</v>
+      <c r="F303" s="5" t="n">
+        <v>38</v>
       </c>
       <c r="G303" t="inlineStr">
         <is>
@@ -15141,12 +15141,12 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>bathroom remodeling services</t>
-        </is>
-      </c>
-      <c r="B304" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>bathroom remodeling services charlotte</t>
+        </is>
+      </c>
+      <c r="B304" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -15162,8 +15162,8 @@
       <c r="E304" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F304" s="5" t="n">
-        <v>38</v>
+      <c r="F304" s="4" t="n">
+        <v>18</v>
       </c>
       <c r="G304" t="inlineStr">
         <is>
@@ -15174,17 +15174,17 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>bathroom remodeling services charlotte</t>
-        </is>
-      </c>
-      <c r="B305" s="2" t="inlineStr">
-        <is>
-          <t>Charlotte &amp; Local</t>
+          <t>bathroom remodeling teacher</t>
+        </is>
+      </c>
+      <c r="B305" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -15195,8 +15195,8 @@
       <c r="E305" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F305" s="4" t="n">
-        <v>18</v>
+      <c r="F305" s="5" t="n">
+        <v>38</v>
       </c>
       <c r="G305" t="inlineStr">
         <is>
@@ -15207,17 +15207,17 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>bathroom remodeling teacher</t>
-        </is>
-      </c>
-      <c r="B306" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>bathroom renovation belmont</t>
+        </is>
+      </c>
+      <c r="B306" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -15228,8 +15228,8 @@
       <c r="E306" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F306" s="5" t="n">
-        <v>38</v>
+      <c r="F306" s="4" t="n">
+        <v>24</v>
       </c>
       <c r="G306" t="inlineStr">
         <is>
@@ -15240,12 +15240,12 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>bathroom renovation belmont</t>
-        </is>
-      </c>
-      <c r="B307" s="2" t="inlineStr">
-        <is>
-          <t>Charlotte &amp; Local</t>
+          <t>bathroom renovation contractors</t>
+        </is>
+      </c>
+      <c r="B307" s="8" t="inlineStr">
+        <is>
+          <t>Process &amp; Planning</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -15261,8 +15261,8 @@
       <c r="E307" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F307" s="4" t="n">
-        <v>24</v>
+      <c r="F307" s="5" t="n">
+        <v>38</v>
       </c>
       <c r="G307" t="inlineStr">
         <is>
@@ -15273,17 +15273,17 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>bathroom renovation contractors</t>
-        </is>
-      </c>
-      <c r="B308" s="8" t="inlineStr">
-        <is>
-          <t>Process &amp; Planning</t>
+          <t>bathroom renovation harrisburg</t>
+        </is>
+      </c>
+      <c r="B308" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -15306,7 +15306,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>bathroom renovation harrisburg</t>
+          <t>bathroom renovation in a day</t>
         </is>
       </c>
       <c r="B309" s="7" t="inlineStr">
@@ -15327,8 +15327,8 @@
       <c r="E309" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F309" s="5" t="n">
-        <v>38</v>
+      <c r="F309" s="4" t="n">
+        <v>24</v>
       </c>
       <c r="G309" t="inlineStr">
         <is>
@@ -15339,7 +15339,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>bathroom renovation in a day</t>
+          <t>bathroom renovation paw creek</t>
         </is>
       </c>
       <c r="B310" s="7" t="inlineStr">
@@ -15360,8 +15360,8 @@
       <c r="E310" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F310" s="4" t="n">
-        <v>24</v>
+      <c r="F310" s="5" t="n">
+        <v>30</v>
       </c>
       <c r="G310" t="inlineStr">
         <is>
@@ -15372,7 +15372,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>bathroom renovation paw creek</t>
+          <t>bathroom renovation pineville</t>
         </is>
       </c>
       <c r="B311" s="7" t="inlineStr">
@@ -15394,7 +15394,7 @@
         <v>10</v>
       </c>
       <c r="F311" s="5" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="G311" t="inlineStr">
         <is>
@@ -15405,17 +15405,17 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>bathroom renovation pineville</t>
-        </is>
-      </c>
-      <c r="B312" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>bathroom renovation stores near me</t>
+        </is>
+      </c>
+      <c r="B312" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -15426,8 +15426,8 @@
       <c r="E312" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F312" s="5" t="n">
-        <v>38</v>
+      <c r="F312" s="4" t="n">
+        <v>18</v>
       </c>
       <c r="G312" t="inlineStr">
         <is>
@@ -15438,7 +15438,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>bathroom renovation stores near me</t>
+          <t>bathroom renovators near me</t>
         </is>
       </c>
       <c r="B313" s="2" t="inlineStr">
@@ -15471,17 +15471,17 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>bathroom renovators near me</t>
-        </is>
-      </c>
-      <c r="B314" s="2" t="inlineStr">
-        <is>
-          <t>Charlotte &amp; Local</t>
+          <t>bathroom vanities</t>
+        </is>
+      </c>
+      <c r="B314" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -15492,8 +15492,8 @@
       <c r="E314" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F314" s="4" t="n">
-        <v>18</v>
+      <c r="F314" s="5" t="n">
+        <v>48</v>
       </c>
       <c r="G314" t="inlineStr">
         <is>
@@ -15504,17 +15504,17 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>bathroom restoration</t>
-        </is>
-      </c>
-      <c r="B315" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>bathroom vanities charlotte nc</t>
+        </is>
+      </c>
+      <c r="B315" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -15525,8 +15525,8 @@
       <c r="E315" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F315" s="5" t="n">
-        <v>48</v>
+      <c r="F315" s="4" t="n">
+        <v>18</v>
       </c>
       <c r="G315" t="inlineStr">
         <is>
@@ -15537,7 +15537,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>bathroom vanities</t>
+          <t>bathroom vanity 72 inch</t>
         </is>
       </c>
       <c r="B316" s="7" t="inlineStr">
@@ -15559,7 +15559,7 @@
         <v>10</v>
       </c>
       <c r="F316" s="5" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="G316" t="inlineStr">
         <is>
@@ -15570,7 +15570,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>bathroom vanities charlotte nc</t>
+          <t>bathroom vanity charlotte nc</t>
         </is>
       </c>
       <c r="B317" s="2" t="inlineStr">
@@ -15603,17 +15603,17 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>bathroom vanity 72 inch</t>
-        </is>
-      </c>
-      <c r="B318" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>bathtub installation near me</t>
+        </is>
+      </c>
+      <c r="B318" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -15624,8 +15624,8 @@
       <c r="E318" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F318" s="5" t="n">
-        <v>30</v>
+      <c r="F318" s="4" t="n">
+        <v>18</v>
       </c>
       <c r="G318" t="inlineStr">
         <is>
@@ -15636,17 +15636,17 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>bathroom vanity charlotte nc</t>
-        </is>
-      </c>
-      <c r="B319" s="2" t="inlineStr">
-        <is>
-          <t>Charlotte &amp; Local</t>
+          <t>beautiful kitchen renovations</t>
+        </is>
+      </c>
+      <c r="B319" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -15657,8 +15657,8 @@
       <c r="E319" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F319" s="4" t="n">
-        <v>18</v>
+      <c r="F319" s="5" t="n">
+        <v>38</v>
       </c>
       <c r="G319" t="inlineStr">
         <is>
@@ -15669,7 +15669,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>bathtub installation near me</t>
+          <t>belmont kitchen luxury renovation</t>
         </is>
       </c>
       <c r="B320" s="2" t="inlineStr">
@@ -15702,17 +15702,17 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>beautiful kitchen renovations</t>
-        </is>
-      </c>
-      <c r="B321" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>belmont park kitchen remodel</t>
+        </is>
+      </c>
+      <c r="B321" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -15723,8 +15723,8 @@
       <c r="E321" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F321" s="5" t="n">
-        <v>38</v>
+      <c r="F321" s="4" t="n">
+        <v>18</v>
       </c>
       <c r="G321" t="inlineStr">
         <is>

--- a/decks/7-day-kitchens/keyword-research.xlsx
+++ b/decks/7-day-kitchens/keyword-research.xlsx
@@ -8,9 +8,10 @@
   </bookViews>
   <sheets>
     <sheet name="Article Plan" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Keyword Universe" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Excluded" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Read Me" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Service Pages" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Keyword Universe" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Excluded" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Read Me" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,6 +33,9 @@
       <b val="1"/>
       <color rgb="00F5EFE6"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -52,7 +56,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -94,6 +98,16 @@
         <fgColor rgb="00162f41"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8D7DA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFECE6"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -107,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -125,13 +139,28 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -5123,6 +5152,1216 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="66" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Group</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Service Page</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Primary Keyword</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>US Vol</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Intent</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Why / Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Core Kitchen</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Kitchen Remodeling</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>kitchen remodeling charlotte</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>320</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="H2" s="10" t="inlineStr">
+        <is>
+          <t>Have — expand</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Flagship money page. Strengthen with schema + internal links from the blog.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Core Kitchen</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Kitchen Design</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>kitchen design</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>22200</v>
+      </c>
+      <c r="F3" s="11" t="n">
+        <v>65</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="H3" s="10" t="inlineStr">
+        <is>
+          <t>Have — expand</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Existing page. Design-led buyers; rank the local slice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kitchen + X</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Kitchen + Bath Remodeling</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>kitchen and bath remodeling</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>4400</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>The anchor combo. Real demand + the 'get it all done at once' buyer Barry described.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kitchen + X</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Kitchen + Walk-in Pantry</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>walk in pantry</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>4400</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Low KD, strong demand. Premium add-on to a kitchen remodel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Segment</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Small Kitchen Remodeling</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>small kitchen remodel</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>6600</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Easy win, high demand. Condo / townhome buyers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Segment</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Luxury Kitchen Remodeling</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>luxury kitchen remodel</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>2400</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Very low KD, matches your premium fixed-price positioning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Service Area</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Charlotte (hub)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>kitchen remodeling charlotte</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>320</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>Have</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Core geo page every suburb page links up to.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Service Area</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Waxhaw, NC</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>kitchen remodeling waxhaw nc</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>Have</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Existing service-area page. Map-pack + exact local intent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Service Area</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Matthews, NC</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>kitchen remodeling matthews nc</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Very winnable suburb (KD 4).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kitchen + X</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Kitchen + Scullery / Butler's Pantry</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>butlers pantry</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>9900</v>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Huge feature-research demand (scullery 18.1K, butler's pantry 9.9K). Premium differentiator.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kitchen + X</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Kitchen + Laundry Room</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>kitchen and laundry room</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>140</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Low direct search but a common combo; routes AI/Google to the right page (Onn's point).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Segment</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Open-Concept Kitchen</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>open concept kitchen</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>1900</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Wall-removal / layout-change projects.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Segment</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Galley Kitchen Remodeling</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>galley kitchen remodel</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Layout-specific segment page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Custom Kitchen Cabinets</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>custom kitchen cabinets</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>8100</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>54</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>High-intent sub-service; part of every remodel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Kitchen Cabinet Refacing</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>kitchen cabinet refacing</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>6600</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Budget-tier service; you already rank ~#6 locally (GSC).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Service Area</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Marvin, NC</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>kitchen remodeling marvin nc</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Affluent suburb; you have a featured project there already.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Service Area</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Monroe, NC</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>kitchen remodeling monroe nc</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Union County.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Service Area</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ballantyne</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>kitchen remodeling ballantyne</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Affluent South Charlotte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kitchen + X</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Kitchen + Mudroom</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>kitchen and mudroom</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Intent-accuracy; supporting page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Segment</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Custom Kitchens</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>custom kitchen</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>1600</v>
+      </c>
+      <c r="F21" s="11" t="n">
+        <v>58</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Bespoke positioning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Kitchen Countertops</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>kitchen countertops</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>40500</v>
+      </c>
+      <c r="F22" s="11" t="n">
+        <v>58</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Massive demand; feature-as-service that funnels to full remodels.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Kitchen Islands</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>kitchen island</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>90500</v>
+      </c>
+      <c r="F23" s="11" t="n">
+        <v>61</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Highest demand of all (90.5K); high KD. Feature page funneling to remodels.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Kitchen Backsplash</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>kitchen backsplash</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>27100</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>High-demand feature page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Service Area</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Weddington, NC</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>kitchen remodeling weddington nc</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Expansion suburb.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Service Area</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Fort Mill, SC</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>kitchen remodeling fort mill sc</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F26" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>SC side of the metro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="14" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Service Area</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Huntersville / Mooresville / Belmont</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>kitchen remodeling &lt;suburb&gt; nc</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>North / west metro expansion pages.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -5199,7 +6438,7 @@
       <c r="F2" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="G2" s="9" t="inlineStr">
+      <c r="G2" s="10" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -5232,7 +6471,7 @@
       <c r="F3" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="G3" s="9" t="inlineStr">
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -5265,7 +6504,7 @@
       <c r="F4" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -5298,7 +6537,7 @@
       <c r="F5" s="5" t="n">
         <v>48</v>
       </c>
-      <c r="G5" s="9" t="inlineStr">
+      <c r="G5" s="10" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -5397,7 +6636,7 @@
       <c r="F8" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="G8" s="9" t="inlineStr">
+      <c r="G8" s="10" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -5430,7 +6669,7 @@
       <c r="F9" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="G9" s="9" t="inlineStr">
+      <c r="G9" s="10" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -5463,7 +6702,7 @@
       <c r="F10" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="G10" s="9" t="inlineStr">
+      <c r="G10" s="10" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -5496,7 +6735,7 @@
       <c r="F11" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="G11" s="9" t="inlineStr">
+      <c r="G11" s="10" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -5562,7 +6801,7 @@
       <c r="F13" s="5" t="n">
         <v>41</v>
       </c>
-      <c r="G13" s="9" t="inlineStr">
+      <c r="G13" s="10" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -5628,7 +6867,7 @@
       <c r="F15" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="G15" s="9" t="inlineStr">
+      <c r="G15" s="10" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -5661,7 +6900,7 @@
       <c r="F16" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="G16" s="9" t="inlineStr">
+      <c r="G16" s="10" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -5694,7 +6933,7 @@
       <c r="F17" s="5" t="n">
         <v>42</v>
       </c>
-      <c r="G17" s="9" t="inlineStr">
+      <c r="G17" s="10" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -5727,7 +6966,7 @@
       <c r="F18" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="G18" s="9" t="inlineStr">
+      <c r="G18" s="10" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -5793,7 +7032,7 @@
       <c r="F20" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="G20" s="9" t="inlineStr">
+      <c r="G20" s="10" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -5826,7 +7065,7 @@
       <c r="F21" s="5" t="n">
         <v>48</v>
       </c>
-      <c r="G21" s="9" t="inlineStr">
+      <c r="G21" s="10" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -5859,7 +7098,7 @@
       <c r="F22" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="G22" s="9" t="inlineStr">
+      <c r="G22" s="10" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -5892,7 +7131,7 @@
       <c r="F23" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="G23" s="9" t="inlineStr">
+      <c r="G23" s="10" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -5925,7 +7164,7 @@
       <c r="F24" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="G24" s="9" t="inlineStr">
+      <c r="G24" s="10" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -5958,7 +7197,7 @@
       <c r="F25" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="G25" s="9" t="inlineStr">
+      <c r="G25" s="10" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -5991,7 +7230,7 @@
       <c r="F26" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="G26" s="9" t="inlineStr">
+      <c r="G26" s="10" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -6057,7 +7296,7 @@
       <c r="F28" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="G28" s="9" t="inlineStr">
+      <c r="G28" s="10" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -6090,7 +7329,7 @@
       <c r="F29" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G29" s="9" t="inlineStr">
+      <c r="G29" s="10" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -6123,7 +7362,7 @@
       <c r="F30" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="G30" s="9" t="inlineStr">
+      <c r="G30" s="10" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -6156,7 +7395,7 @@
       <c r="F31" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="G31" s="9" t="inlineStr">
+      <c r="G31" s="10" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -6189,7 +7428,7 @@
       <c r="F32" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="G32" s="9" t="inlineStr">
+      <c r="G32" s="10" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -6222,7 +7461,7 @@
       <c r="F33" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="G33" s="9" t="inlineStr">
+      <c r="G33" s="10" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -6288,7 +7527,7 @@
       <c r="F35" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="G35" s="9" t="inlineStr">
+      <c r="G35" s="10" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -6321,7 +7560,7 @@
       <c r="F36" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="G36" s="9" t="inlineStr">
+      <c r="G36" s="10" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -6354,7 +7593,7 @@
       <c r="F37" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="G37" s="9" t="inlineStr">
+      <c r="G37" s="10" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -6387,7 +7626,7 @@
       <c r="F38" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="G38" s="9" t="inlineStr">
+      <c r="G38" s="10" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -6453,7 +7692,7 @@
       <c r="F40" s="5" t="n">
         <v>48</v>
       </c>
-      <c r="G40" s="9" t="inlineStr">
+      <c r="G40" s="10" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -6486,7 +7725,7 @@
       <c r="F41" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="G41" s="9" t="inlineStr">
+      <c r="G41" s="10" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -6519,7 +7758,7 @@
       <c r="F42" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="G42" s="9" t="inlineStr">
+      <c r="G42" s="10" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -6849,7 +8088,7 @@
       <c r="F52" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="G52" s="9" t="inlineStr">
+      <c r="G52" s="10" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -6882,7 +8121,7 @@
       <c r="F53" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="G53" s="9" t="inlineStr">
+      <c r="G53" s="10" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -7146,7 +8385,7 @@
       <c r="F61" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="G61" s="9" t="inlineStr">
+      <c r="G61" s="10" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -7245,7 +8484,7 @@
       <c r="F64" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="G64" s="9" t="inlineStr">
+      <c r="G64" s="10" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -7278,7 +8517,7 @@
       <c r="F65" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="G65" s="9" t="inlineStr">
+      <c r="G65" s="10" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -7377,7 +8616,7 @@
       <c r="F68" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="G68" s="9" t="inlineStr">
+      <c r="G68" s="10" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -7410,7 +8649,7 @@
       <c r="F69" s="5" t="n">
         <v>48</v>
       </c>
-      <c r="G69" s="9" t="inlineStr">
+      <c r="G69" s="10" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -7443,7 +8682,7 @@
       <c r="F70" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="G70" s="9" t="inlineStr">
+      <c r="G70" s="10" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -7509,7 +8748,7 @@
       <c r="F72" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="G72" s="9" t="inlineStr">
+      <c r="G72" s="10" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -7575,7 +8814,7 @@
       <c r="F74" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="G74" s="9" t="inlineStr">
+      <c r="G74" s="10" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -7608,7 +8847,7 @@
       <c r="F75" s="5" t="n">
         <v>48</v>
       </c>
-      <c r="G75" s="9" t="inlineStr">
+      <c r="G75" s="10" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -7674,7 +8913,7 @@
       <c r="F77" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="G77" s="9" t="inlineStr">
+      <c r="G77" s="10" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -7740,7 +8979,7 @@
       <c r="F79" s="5" t="n">
         <v>48</v>
       </c>
-      <c r="G79" s="9" t="inlineStr">
+      <c r="G79" s="10" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -7872,7 +9111,7 @@
       <c r="F83" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="G83" s="9" t="inlineStr">
+      <c r="G83" s="10" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -7905,7 +9144,7 @@
       <c r="F84" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="G84" s="9" t="inlineStr">
+      <c r="G84" s="10" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -7938,7 +9177,7 @@
       <c r="F85" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="G85" s="9" t="inlineStr">
+      <c r="G85" s="10" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -8004,7 +9243,7 @@
       <c r="F87" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="G87" s="9" t="inlineStr">
+      <c r="G87" s="10" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -8136,7 +9375,7 @@
       <c r="F91" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="G91" s="9" t="inlineStr">
+      <c r="G91" s="10" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -8169,7 +9408,7 @@
       <c r="F92" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="G92" s="9" t="inlineStr">
+      <c r="G92" s="10" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -8301,7 +9540,7 @@
       <c r="F96" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="G96" s="9" t="inlineStr">
+      <c r="G96" s="10" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -8730,7 +9969,7 @@
       <c r="F109" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="G109" s="9" t="inlineStr">
+      <c r="G109" s="10" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -8829,7 +10068,7 @@
       <c r="F112" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="G112" s="9" t="inlineStr">
+      <c r="G112" s="10" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -8961,7 +10200,7 @@
       <c r="F116" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="G116" s="9" t="inlineStr">
+      <c r="G116" s="10" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -8994,7 +10233,7 @@
       <c r="F117" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="G117" s="9" t="inlineStr">
+      <c r="G117" s="10" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -9126,7 +10365,7 @@
       <c r="F121" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="G121" s="9" t="inlineStr">
+      <c r="G121" s="10" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -9357,7 +10596,7 @@
       <c r="F128" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="G128" s="9" t="inlineStr">
+      <c r="G128" s="10" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -9588,7 +10827,7 @@
       <c r="F135" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="G135" s="9" t="inlineStr">
+      <c r="G135" s="10" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -14703,7 +15942,7 @@
       <c r="F290" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="G290" s="9" t="inlineStr">
+      <c r="G290" s="10" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -15737,7 +16976,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15992,13 +17231,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -16006,172 +17245,184 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>7 Day Kitchens, Keyword Research Workbook</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr"/>
+      <c r="B1" s="16" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>Prepared by</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="16" t="inlineStr">
         <is>
           <t>EmberTribe · SEO &amp; AI Growth Roadmap</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr"/>
-      <c r="B3" s="11" t="inlineStr"/>
+      <c r="A3" s="17" t="inlineStr"/>
+      <c r="B3" s="16" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="18" t="inlineStr">
         <is>
           <t>What's in here</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr"/>
+      <c r="B4" s="16" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>Article Plan</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>The 120 articles in your 90-day plan: title, primary keyword, pillar, funnel stage, monthly demand, and difficulty (KD). 40 per month.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>Service Pages</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>The recommended service-page architecture beyond Kitchen Remodeling + Kitchen Design: core kitchen, Kitchen + X combos (bath, walk-in pantry, scullery, laundry), segment pages (small/luxury/galley/open-concept), component pages (cabinets, refacing, countertops, islands), and suburb service-area pages. Prioritized P1/P2/P3. The blog articles link into these pages. Head-term volume is US topic demand; the local page captures the Charlotte + suburb + long-tail slice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>Keyword Universe</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>The wider opportunity (top 320 on-strategy keywords). 'Yes (planned)' = covered by an article; 'Overflow' = held for later months.</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>Excluded</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>Keywords we deliberately left out, and why. Mostly competitor brands, wrong-city terms, and DIY/retail intent.</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr"/>
-      <c r="B8" s="11" t="inlineStr"/>
-    </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr"/>
+      <c r="B9" s="16" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>A note on demand</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>Demand/mo blends two verified sources: SEMrush search volume for the local commercial terms, and your own Google Search Console monthly impressions for everything you already appear for. Both are real, not estimates.</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="12" t="inlineStr"/>
-      <c r="B10" s="11" t="inlineStr"/>
-    </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="17" t="inlineStr"/>
+      <c r="B11" s="16" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="18" t="inlineStr">
         <is>
           <t>How to read the colors</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>Pillar</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>Gold = Cost &amp; Budget · Blue = Design &amp; Materials · Green = Process &amp; Planning · Tan = Charlotte &amp; Local.</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>KD (difficulty)</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>Green = easy (under 30) · Yellow = moderate (30-49) · Red = hard (50+). Lower is faster to rank.</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>Funnel</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>BoFu = decision-stage (ready to remodel) · MoFu = comparison · ToFu = inspiration / education.</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="12" t="inlineStr"/>
-      <c r="B15" s="11" t="inlineStr"/>
-    </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="17" t="inlineStr"/>
+      <c r="B16" s="16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="18" t="inlineStr">
         <is>
           <t>Why these pillars</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="B17" s="16" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>Strategy</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B18" s="16" t="inlineStr">
         <is>
           <t>Win the local Charlotte and suburb searches first (your money pages), answer the cost and budget questions where your fixed-price model is the edge, build trust with process and timeline content, and cast a wide net with design and materials inspiration, all routed toward a quote through internal links.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="12" t="inlineStr"/>
-      <c r="B18" s="11" t="inlineStr"/>
-    </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
+      <c r="A19" s="17" t="inlineStr"/>
+      <c r="B19" s="16" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>Next step</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B20" s="16" t="inlineStr">
         <is>
           <t>Review the plan, then let's lock Month 1 and start production. Questions? Reply to the email this was shared from.</t>
         </is>

--- a/decks/7-day-kitchens/keyword-research.xlsx
+++ b/decks/7-day-kitchens/keyword-research.xlsx
@@ -75,12 +75,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
+        <fgColor rgb="00F1E4CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F1E4CE"/>
+        <fgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
     <fill>
@@ -133,10 +133,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -149,7 +149,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -609,7 +609,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G2" s="3" t="n">
@@ -627,12 +627,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kitchen Remodeling in Waxhaw, NC: Local Process and Timeline</t>
+          <t>Kitchen Remodeling in Matthews, NC: What to Expect</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>kitchen remodeling waxhaw nc</t>
+          <t>kitchen remodeling matthews nc</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -647,11 +647,11 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G3" s="3" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H3" s="4" t="n">
         <v>18</v>
@@ -665,12 +665,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Remodeling Contractors Charlotte NC: Built Around Your Home and Budget</t>
+          <t>Kitchen Remodeling in Huntersville, NC: Costs, Timelines, and Local Style</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>remodeling contractors charlotte nc</t>
+          <t>kitchen remodeling huntersville nc</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -685,14 +685,14 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G4" s="3" t="n">
-        <v>210</v>
-      </c>
-      <c r="H4" s="5" t="n">
-        <v>41</v>
+        <v>10</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="5">
@@ -723,7 +723,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G5" s="3" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kitchen Designers Charlotte: The 7-Day Difference, Explained</t>
+          <t>Kitchen Designers Charlotte: What the Process Looks Like Here</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -761,7 +761,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G6" s="3" t="n">
@@ -779,12 +779,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Home Additions Charlotte: Fixed Pricing, Finished in 7 Days</t>
+          <t>Kitchen Remodeling Company Charlotte: Where Speed Meets Craftsmanship</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>home additions charlotte</t>
+          <t>kitchen remodeling company charlotte</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -799,14 +799,14 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G7" s="3" t="n">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
@@ -817,12 +817,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Renovation Company Charlotte NC: The 7-Day Difference, Explained</t>
+          <t>Kitchen Renovation Services Charlotte: Local Crews, Lifetime Warranty</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>renovation company charlotte nc</t>
+          <t>kitchen renovation services charlotte</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -837,14 +837,14 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G8" s="3" t="n">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
@@ -855,12 +855,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Best Kitchen Remodeler Charlotte: Fixed Pricing, Finished in 7 Days</t>
+          <t>Kitchen Remodeling South West Charlotte: One Local Crew, Start to Finish</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>best kitchen remodeler charlotte</t>
+          <t>kitchen remodeling south west charlotte</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -875,14 +875,14 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G9" s="3" t="n">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -893,12 +893,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Charlotte Home Renovations: Where Speed Meets Craftsmanship</t>
+          <t>Kitchen Remodeling in Concord, NC: A Local Renovation Guide</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>charlotte home renovations</t>
+          <t>kitchen remodeling concord nc</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -913,14 +913,14 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G10" s="3" t="n">
-        <v>170</v>
+        <v>14</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
@@ -931,12 +931,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Remodeling in Charlotte: One Local Crew, Start to Finish</t>
+          <t>Kitchen Remodeling in Indian Trail, NC: Costs and What to Expect</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>remodeling in charlotte</t>
+          <t>kitchen remodeling indian trail nc</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -951,14 +951,14 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G11" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="H11" s="5" t="n">
-        <v>37</v>
+        <v>10</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="12">
@@ -969,34 +969,34 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>How Much Is a Kitchen Remodel in Charlotte? Local Price Ranges</t>
+          <t>Why a Fixed-Price Kitchen Remodel Beats Hourly Surprises</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>how much is a kitchen remodel in charlotte</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
+          <t>fixed price kitchen remodel</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>Cost &amp; Budget</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G12" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="H12" s="4" t="n">
-        <v>18</v>
+      <c r="H12" s="6" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="13">
@@ -1007,34 +1007,34 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Why a Fixed-Price Kitchen Remodel Beats Hourly Surprises</t>
+          <t>The Average Cost of a Kitchen Remodel, and Why Yours May Differ</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>fixed price kitchen remodel</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
+          <t>average cost of kitchen remodel</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>Cost &amp; Budget</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G13" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="H13" s="5" t="n">
-        <v>30</v>
+        <v>10</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="14">
@@ -1045,31 +1045,31 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Does a Kitchen Remodel Add Value? The Resale Math</t>
+          <t>Average Cost of a Full Kitchen Remodel: The Real Numbers for 2026</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>does a kitchen remodel add value</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
+          <t>average cost of a full kitchen remodel</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>Cost &amp; Budget</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G14" s="3" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="H14" s="4" t="n">
         <v>24</v>
@@ -1083,15 +1083,15 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The Average Cost of a Kitchen Remodel, and Why Yours May Differ</t>
+          <t>Average Cost of Galley Kitchen Remodel: What to Know Before You Commit</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>average cost of kitchen remodel</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
+          <t>average cost of galley kitchen remodel</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>Cost &amp; Budget</t>
         </is>
@@ -1103,7 +1103,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G15" s="3" t="n">
@@ -1121,15 +1121,15 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Kitchen Remodel Cost: Budget, Mid-Range, and High-End Compared</t>
+          <t>Is Average Cost to Update a Kitchen Worth It?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>kitchen remodel cost</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
+          <t>average cost to update a kitchen</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>Cost &amp; Budget</t>
         </is>
@@ -1141,14 +1141,14 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>193</v>
-      </c>
-      <c r="H16" s="5" t="n">
-        <v>38</v>
+        <v>10</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="17">
@@ -1159,15 +1159,15 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Affordable Kitchen Remodels: Where to Save Without Regret</t>
+          <t>How to Read a Kitchen Remodel Estimate, Line by Line</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>affordable kitchen remodel</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
+          <t>kitchen estimate</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>Cost &amp; Budget</t>
         </is>
@@ -1179,14 +1179,14 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G17" s="3" t="n">
-        <v>63</v>
-      </c>
-      <c r="H17" s="5" t="n">
-        <v>38</v>
+        <v>61</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="18">
@@ -1197,33 +1197,33 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Kitchen Remodel ROI: How Much Value It Actually Adds</t>
+          <t>Getting a Kitchen Remodel Estimate: What to Expect</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>kitchen remodel roi</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
+          <t>kitchen remodel estimate</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>Cost &amp; Budget</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G18" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="H18" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="H18" s="6" t="n">
         <v>38</v>
       </c>
     </row>
@@ -1235,15 +1235,15 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Getting a Kitchen Remodel Estimate: What to Expect</t>
+          <t>Kitchen Remodel Prices in 2026: What Sets the Range</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>kitchen remodel estimate</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
+          <t>kitchen prices</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>Cost &amp; Budget</t>
         </is>
@@ -1255,14 +1255,14 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>37</v>
-      </c>
-      <c r="H19" s="5" t="n">
-        <v>38</v>
+        <v>24</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="20">
@@ -1273,15 +1273,15 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Comparing Kitchen Remodel Quotes: A Side-by-Side Guide</t>
+          <t>What a Kitchen Installation Estimate Should Include</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>compare kitchen prices</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
+          <t>kitchen installation cost estimate</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>Cost &amp; Budget</t>
         </is>
@@ -1293,14 +1293,14 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="H20" s="5" t="n">
-        <v>38</v>
+        <v>16</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -1319,7 +1319,7 @@
           <t>kitchen remodel budget</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>Cost &amp; Budget</t>
         </is>
@@ -1331,13 +1331,13 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G21" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="H21" s="5" t="n">
+      <c r="H21" s="6" t="n">
         <v>38</v>
       </c>
     </row>
@@ -1349,12 +1349,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cabinet Refacing in Charlotte, NC: When It Makes Sense</t>
+          <t>Kitchen and Laundry Room Combos: Designing the Two as One Project</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>cabinet refacing charlotte nc</t>
+          <t>kitchen and laundry room remodel</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
@@ -1364,19 +1364,19 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G22" s="3" t="n">
-        <v>102</v>
+        <v>40</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Best Kitchen Remodeling Company: A No-Nonsense Buyer's Guide</t>
+          <t>Kitchen Renovation, Start to Finish: A Homeowner's Overview</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>best kitchen remodeling company</t>
+          <t>kitchen renovation</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
@@ -1402,19 +1402,19 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G23" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="H23" s="5" t="n">
-        <v>30</v>
+        <v>232</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="24">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Quartz vs Granite Countertops: Which Wins for Your Kitchen</t>
+          <t>Kitchen Design Ideas: Layouts, Light, and Lasting Style</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>quartz vs granite</t>
+          <t>kitchen design ideas</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
@@ -1440,18 +1440,18 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G24" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="H24" s="5" t="n">
+      <c r="H24" s="6" t="n">
         <v>38</v>
       </c>
     </row>
@@ -1463,12 +1463,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Kitchen Layout Basics: Work Triangles, Walkways, and Flow</t>
+          <t>Kitchen Backsplash Ideas That Pull a Remodel Together</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>kitchen layout</t>
+          <t>kitchen backsplash ideas</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
@@ -1483,14 +1483,14 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G25" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="H25" s="5" t="n">
-        <v>48</v>
+      <c r="H25" s="6" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="26">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Kitchen Lighting Ideas: Layering Task, Ambient, and Accent</t>
+          <t>Kitchen Flooring Options Ranked for Durability and Looks</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>kitchen lighting ideas</t>
+          <t>kitchen flooring options</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
@@ -1516,18 +1516,18 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G26" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="H26" s="5" t="n">
+      <c r="H26" s="6" t="n">
         <v>38</v>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Modern Kitchen Design: Clean Lines Without the Cold Feel</t>
+          <t>Farmhouse Kitchen Ideas That Still Feel Fresh in 2026</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>modern kitchen design</t>
+          <t>farmhouse kitchen ideas</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
@@ -1559,13 +1559,13 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G27" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="H27" s="5" t="n">
+      <c r="H27" s="6" t="n">
         <v>38</v>
       </c>
     </row>
@@ -1577,12 +1577,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Pantry Ideas: Designing Storage That Earns Its Footprint</t>
+          <t>Choosing a Kitchen Faucet: Finishes, Features, and Value</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>pantry ideas</t>
+          <t>kitchen faucet ideas</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1603,8 +1603,8 @@
       <c r="G28" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="H28" s="5" t="n">
-        <v>48</v>
+      <c r="H28" s="6" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="29">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Kitchen Paint Colors That Flatter Cabinets and Counters</t>
+          <t>Small Kitchen Ideas: Making a Compact Space Feel Open</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>kitchen paint colors</t>
+          <t>small kitchen ideas</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
@@ -1635,13 +1635,13 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G29" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="H29" s="5" t="n">
+      <c r="H29" s="6" t="n">
         <v>38</v>
       </c>
     </row>
@@ -1653,12 +1653,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Kitchen Appliances: Where to Splurge and Where to Save</t>
+          <t>Two-Tone Kitchen Cabinets: How to Mix Without a Mess</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>kitchen appliances</t>
+          <t>two tone kitchen cabinets</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
@@ -1668,19 +1668,19 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G30" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="H30" s="5" t="n">
-        <v>48</v>
+      <c r="H30" s="6" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="31">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Kitchen Builders vs Remodelers: Which One You Need</t>
+          <t>Kitchen Storage Ideas That Use Every Inch</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>kitchen builders</t>
+          <t>kitchen storage ideas</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
@@ -1706,19 +1706,19 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G31" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="H31" s="5" t="n">
-        <v>48</v>
+        <v>40</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="32">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Kitchen Remodel Ideas That Work in Real Charlotte Homes</t>
+          <t>Walk-In Pantry Ideas for Your Kitchen Remodel</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>kitchen remodel ideas</t>
+          <t>walk in pantry ideas</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
@@ -1753,10 +1753,10 @@
         </is>
       </c>
       <c r="G32" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="H32" s="5" t="n">
-        <v>38</v>
+        <v>40</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="33">
@@ -1767,34 +1767,34 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Kitchen Remodel Contractors in Rock Hill, SC</t>
+          <t>Waterfall Islands: The Statement Feature Worth the Splurge</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>contractor for kitchen remodel rock hill sc</t>
-        </is>
-      </c>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t>Process &amp; Planning</t>
+          <t>waterfall island</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G33" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="H33" s="4" t="n">
-        <v>24</v>
+        <v>40</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="34">
@@ -1805,34 +1805,34 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Vetting a Kitchen Remodeling Contractor: Red and Green Flags</t>
+          <t>Kitchen Countertops Compared: Quartz, Granite, and the Alternatives</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>kitchen remodeling contractor</t>
-        </is>
-      </c>
-      <c r="D34" s="8" t="inlineStr">
-        <is>
-          <t>Process &amp; Planning</t>
+          <t>kitchen countertops</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="H34" s="5" t="n">
-        <v>38</v>
+        <v>10</v>
+      </c>
+      <c r="H34" s="6" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="35">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Choosing a Contractor for Your Kitchen Renovation</t>
+          <t>Kitchen Remodel Contractors in Rock Hill, SC</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>contractor for kitchen renovation</t>
+          <t>contractor for kitchen remodel rock hill sc</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
@@ -1863,14 +1863,14 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G35" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="H35" s="5" t="n">
-        <v>30</v>
+      <c r="H35" s="4" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="36">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Living Through a Kitchen Remodel: How to Stay in Your Home</t>
+          <t>Kitchen Remodeler Gastonia: What Separates Great From Cheap</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>living through a kitchen remodel</t>
+          <t>kitchen remodeler gastonia</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
@@ -1896,19 +1896,19 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="H36" s="4" t="n">
-        <v>24</v>
+        <v>10</v>
+      </c>
+      <c r="H36" s="6" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="37">
@@ -1919,12 +1919,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Working With an Interior Designer: Why It's Built Into Our Process</t>
+          <t>Kitchen and Bath Remodeling Contractors: What Separates Great From Cheap</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>working with an interior designer</t>
+          <t>kitchen and bath remodeling contractors</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
@@ -1934,16 +1934,16 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G37" s="3" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="H37" s="4" t="n">
         <v>24</v>
@@ -1957,12 +1957,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>How to Prepare Your Home for a Kitchen Remodel</t>
+          <t>How to Compare the Best Kitchen Remodel Contractors</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>how to prepare for a kitchen remodel</t>
+          <t>best kitchen remodel contractors</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
@@ -1972,19 +1972,19 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G38" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="H38" s="4" t="n">
-        <v>24</v>
+      <c r="H38" s="6" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="39">
@@ -1995,12 +1995,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Kitchen Remodel Mistakes to Avoid (and How We Prevent Them)</t>
+          <t>Kitchen Remodeler Eastway Park, Done the Fixed-Price Way</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>kitchen remodel mistakes</t>
+          <t>kitchen remodeler eastway park</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
@@ -2010,19 +2010,19 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G39" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="H39" s="5" t="n">
-        <v>38</v>
+        <v>10</v>
+      </c>
+      <c r="H39" s="6" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="40">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Kitchen Demolition: What Tear-Out Day Actually Involves</t>
+          <t>Kitchen Remodeler Contractor: What to Expect, Day by Day</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>kitchen demolition</t>
+          <t>kitchen remodeler contractor</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
@@ -2048,19 +2048,19 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G40" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="H40" s="5" t="n">
-        <v>48</v>
+        <v>10</v>
+      </c>
+      <c r="H40" s="6" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="41">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>The Right Order of a Kitchen Remodel, Step by Step</t>
+          <t>The Kitchen Remodel Checklist Every Homeowner Should Use</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>order of kitchen remodel</t>
+          <t>kitchen remodel checklist</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
@@ -2086,19 +2086,19 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G41" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="H41" s="5" t="n">
-        <v>30</v>
+        <v>40</v>
+      </c>
+      <c r="H41" s="6" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="42">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Kitchen Remodel in Marvin, NC: Full Tear-Out in One Week</t>
+          <t>Kitchen Design and Build Charlotte NC: What the Process Looks Like Here</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>kitchen remodel marvin nc</t>
+          <t>kitchen design and build charlotte nc</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -2129,11 +2129,11 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G42" s="3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H42" s="4" t="n">
         <v>18</v>
@@ -2147,12 +2147,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Home Remodeling in Charlotte, NC: Where Kitchens Lead the Way</t>
+          <t>Kitchen Remodeling in Mooresville, NC: A Lake Norman Homeowner's Guide</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>home remodeling charlotte nc</t>
+          <t>kitchen remodeling mooresville nc</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2167,14 +2167,14 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G43" s="3" t="n">
-        <v>320</v>
+        <v>18</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
     </row>
     <row r="44">
@@ -2205,13 +2205,13 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G44" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="H44" s="5" t="n">
+      <c r="H44" s="6" t="n">
         <v>30</v>
       </c>
     </row>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G45" s="3" t="n">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Home Remodeling Charlotte: What the Process Looks Like Here</t>
+          <t>Hiring a Kitchen Contractor in Charlotte: A Vetting Guide</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>home remodeling charlotte</t>
+          <t>kitchen contractor charlotte</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2281,14 +2281,14 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G46" s="3" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="47">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Hiring a Kitchen Contractor in Charlotte: A Vetting Guide</t>
+          <t>Best Kitchen Remodeler Charlotte: The 7-Day Difference, Explained</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>kitchen contractor charlotte</t>
+          <t>best kitchen remodeler charlotte</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -2319,14 +2319,14 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G47" s="3" t="n">
-        <v>90</v>
+        <v>56</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="48">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Kitchen Contractors Charlotte NC: What Separates Great From Cheap</t>
+          <t>Ballantyne Kitchen Remodeling: Premium Results Without the Wait</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>kitchen contractors charlotte nc</t>
+          <t>kitchen remodeling ballantyne</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -2357,14 +2357,14 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="49">
@@ -2375,12 +2375,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Ballantyne Kitchen Remodeling: Premium Results Without the Wait</t>
+          <t>Kitchen Remodelers Charlotte NC: A Faster Path to Your Dream Kitchen</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>kitchen remodeling ballantyne</t>
+          <t>kitchen remodelers charlotte nc</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -2395,14 +2395,14 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G49" s="3" t="n">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="50">
@@ -2413,12 +2413,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Bathroom Remodel in Charlotte, NC: The Kitchen-Plus Approach</t>
+          <t>Kitchen Remodeling in Fort Mill, SC: What Local Homeowners Should Know</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>bathroom remodel charlotte nc</t>
+          <t>kitchen remodeling fort mill sc</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -2433,14 +2433,14 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G50" s="3" t="n">
-        <v>590</v>
-      </c>
-      <c r="H50" s="5" t="n">
-        <v>35</v>
+        <v>10</v>
+      </c>
+      <c r="H50" s="4" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="51">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Charlotte NC Remodeling: Local Crews, Lifetime Warranty</t>
+          <t>Kitchen Remodeling in Mint Hill, NC: A Local Homeowner's Guide</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>charlotte nc remodeling</t>
+          <t>kitchen remodeling mint hill nc</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -2471,14 +2471,14 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G51" s="3" t="n">
-        <v>170</v>
-      </c>
-      <c r="H51" s="5" t="n">
-        <v>42</v>
+        <v>10</v>
+      </c>
+      <c r="H51" s="4" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="52">
@@ -2489,15 +2489,15 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>How Much It Costs to Remodel a Kitchen in 2026</t>
+          <t>Approximate Cost of Kitchen Remodel: Budget, Mid-Range, and High-End Compared</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>how much to remodel a kitchen</t>
-        </is>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
+          <t>approximate cost of kitchen remodel</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
         <is>
           <t>Cost &amp; Budget</t>
         </is>
@@ -2509,11 +2509,11 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G52" s="3" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="H52" s="4" t="n">
         <v>24</v>
@@ -2527,15 +2527,15 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Small Kitchen Remodel Cost: Where the Money Really Goes</t>
+          <t>Average Cost of a Kitchen Remodel 2024: What Drives the Final Price</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>small kitchen remodel cost</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
+          <t>average cost of a kitchen remodel 2024</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
         <is>
           <t>Cost &amp; Budget</t>
         </is>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G53" s="3" t="n">
@@ -2565,15 +2565,15 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>How to Read a Kitchen Remodel Estimate, Line by Line</t>
+          <t>Average Cost of Large Kitchen Remodel: Where Most Homeowners Get It Wrong</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>kitchen estimate</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
+          <t>average cost of large kitchen remodel</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
         <is>
           <t>Cost &amp; Budget</t>
         </is>
@@ -2585,14 +2585,14 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G54" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="H54" s="5" t="n">
-        <v>48</v>
+        <v>10</v>
+      </c>
+      <c r="H54" s="4" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="55">
@@ -2603,15 +2603,15 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>What Drives Your Kitchen Remodel Price: A Cost-Factor Guide</t>
+          <t>Kitchen Remodeling Cost: Where the Money Goes, and Where to Save</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>kitchen remodel price</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
+          <t>kitchen remodeling cost</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
         <is>
           <t>Cost &amp; Budget</t>
         </is>
@@ -2623,13 +2623,13 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G55" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="H55" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="H55" s="6" t="n">
         <v>38</v>
       </c>
     </row>
@@ -2641,15 +2641,15 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>What a Brand-New Kitchen Costs vs a Remodel</t>
+          <t>Comparing Kitchen Remodel Quotes: A Side-by-Side Guide</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>new kitchen prices</t>
-        </is>
-      </c>
-      <c r="D56" s="6" t="inlineStr">
+          <t>compare kitchen prices</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
         <is>
           <t>Cost &amp; Budget</t>
         </is>
@@ -2661,13 +2661,13 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G56" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="H56" s="5" t="n">
+      <c r="H56" s="6" t="n">
         <v>38</v>
       </c>
     </row>
@@ -2687,7 +2687,7 @@
           <t>kitchen remodel financing</t>
         </is>
       </c>
-      <c r="D57" s="6" t="inlineStr">
+      <c r="D57" s="5" t="inlineStr">
         <is>
           <t>Cost &amp; Budget</t>
         </is>
@@ -2699,13 +2699,13 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G57" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="H57" s="5" t="n">
+      <c r="H57" s="6" t="n">
         <v>30</v>
       </c>
     </row>
@@ -2737,13 +2737,13 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G58" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="H58" s="5" t="n">
+      <c r="H58" s="6" t="n">
         <v>38</v>
       </c>
     </row>
@@ -2755,12 +2755,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>What to Look for in a Kitchen Remodeling Company</t>
+          <t>Choosing Kitchen Cabinets: Styles, Finishes, and What Lasts</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>kitchen remodeling company</t>
+          <t>kitchen cabinets</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
@@ -2770,18 +2770,18 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G59" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="H59" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="H59" s="6" t="n">
         <v>38</v>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Choosing Kitchen Cabinets: Styles, Finishes, and What Lasts</t>
+          <t>Kitchen Cabinet Installation: How It's Done Right</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>kitchen cabinets</t>
+          <t>kitchen cabinet installation</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
@@ -2813,13 +2813,13 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G60" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="H60" s="5" t="n">
+        <v>96</v>
+      </c>
+      <c r="H60" s="6" t="n">
         <v>38</v>
       </c>
     </row>
@@ -2831,12 +2831,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Kitchen Countertop Alternatives to Quartz and Granite</t>
+          <t>Quartz vs Granite Countertops: Which Wins for Your Kitchen</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>kitchen countertop alternatives to quartz and granite</t>
+          <t>quartz vs granite</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
@@ -2846,19 +2846,19 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G61" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="H61" s="4" t="n">
-        <v>24</v>
+      <c r="H61" s="6" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="62">
@@ -2869,12 +2869,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Kitchen Remodeling 101: What the Project Really Involves</t>
+          <t>Kitchen Layout Basics: Work Triangles, Walkways, and Flow</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>kitchen remodeling</t>
+          <t>kitchen layout</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
@@ -2884,18 +2884,18 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G62" s="3" t="n">
-        <v>374</v>
-      </c>
-      <c r="H62" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="H62" s="6" t="n">
         <v>48</v>
       </c>
     </row>
@@ -2907,12 +2907,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Kitchen Island Ideas: Sizing, Seating, and Smart Storage</t>
+          <t>Kitchen Lighting Ideas: Layering Task, Ambient, and Accent</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>kitchen island ideas</t>
+          <t>kitchen lighting ideas</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
@@ -2933,7 +2933,7 @@
       <c r="G63" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="H63" s="5" t="n">
+      <c r="H63" s="6" t="n">
         <v>38</v>
       </c>
     </row>
@@ -2945,12 +2945,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Kitchen Cabinet Colors: What's Timeless vs What's Trendy</t>
+          <t>Modern Kitchen Design: Clean Lines Without the Cold Feel</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>kitchen cabinet colors</t>
+          <t>modern kitchen design</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
@@ -2965,13 +2965,13 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G64" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="H64" s="5" t="n">
+      <c r="H64" s="6" t="n">
         <v>38</v>
       </c>
     </row>
@@ -2983,12 +2983,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Kitchen Trends 2026: Bold Cabinets, Brass, and What to Skip</t>
+          <t>Pantry Ideas: Designing Storage That Earns Its Footprint</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>kitchen trends 2026</t>
+          <t>pantry ideas</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
@@ -3009,8 +3009,8 @@
       <c r="G65" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="H65" s="5" t="n">
-        <v>38</v>
+      <c r="H65" s="6" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="66">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Kitchen Sink Ideas: Materials, Mounts, and the Right Size</t>
+          <t>Kitchen Paint Colors That Flatter Cabinets and Counters</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>kitchen sink ideas</t>
+          <t>kitchen paint colors</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
@@ -3041,13 +3041,13 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G66" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="H66" s="5" t="n">
+      <c r="H66" s="6" t="n">
         <v>38</v>
       </c>
     </row>
@@ -3059,12 +3059,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Open-Concept Kitchens: When Knocking Down a Wall Pays Off</t>
+          <t>Kitchen Appliances: Where to Splurge and Where to Save</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>open concept kitchen</t>
+          <t>kitchen appliances</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
@@ -3074,19 +3074,19 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G67" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="H67" s="5" t="n">
-        <v>38</v>
+      <c r="H67" s="6" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="68">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Cabinet Hardware: The Small Detail That Sets the Tone</t>
+          <t>Adding a Scullery to Your Kitchen: The Hidden Prep-Space Trend</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>cabinet hardware ideas</t>
+          <t>kitchen scullery</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
@@ -3117,14 +3117,14 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G68" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="H68" s="5" t="n">
-        <v>38</v>
+      <c r="H68" s="6" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="69">
@@ -3135,12 +3135,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Butcher Block Countertops: Warm Looks, Real Trade-offs</t>
+          <t>Kitchen and Mudroom Combos: A Smarter Family Entryway</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>butcher block countertops</t>
+          <t>kitchen and mudroom</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
@@ -3150,18 +3150,18 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G69" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="H69" s="5" t="n">
+      <c r="H69" s="6" t="n">
         <v>38</v>
       </c>
     </row>
@@ -3173,12 +3173,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Fast Kitchen Remodels: How a 7-Day Timeline Works</t>
+          <t>Galley Kitchen Ideas: Big Function in a Narrow Footprint</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>fast kitchen remodel</t>
+          <t>galley kitchen ideas</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
@@ -3188,18 +3188,18 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G70" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="H70" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="H70" s="6" t="n">
         <v>38</v>
       </c>
     </row>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Custom Kitchen Remodels: When Bespoke Is Worth the Spend</t>
+          <t>White Kitchen Cabinets: Why They Endure, and How to Keep Them Clean</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>custom kitchen remodel</t>
+          <t>white kitchen cabinets</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
@@ -3226,18 +3226,18 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G71" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="H71" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="H71" s="6" t="n">
         <v>38</v>
       </c>
     </row>
@@ -3249,34 +3249,34 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Kitchen Countertops Compared: Quartz, Granite, and the Alternatives</t>
+          <t>Kitchen Remodeler Rock Hill: Done Right the First Time</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>kitchen countertops</t>
-        </is>
-      </c>
-      <c r="D72" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>kitchen remodeler rock hill</t>
+        </is>
+      </c>
+      <c r="D72" s="8" t="inlineStr">
+        <is>
+          <t>Process &amp; Planning</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G72" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="H72" s="5" t="n">
-        <v>48</v>
+      <c r="H72" s="6" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="73">
@@ -3287,12 +3287,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Do You Need a General Contractor for a Bathroom Remodel?</t>
+          <t>Kitchen Remodeler Concord, Done the Fixed-Price Way</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>bathroom remodel general contractor</t>
+          <t>kitchen remodeler concord</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr">
@@ -3307,14 +3307,14 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G73" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="H73" s="5" t="n">
-        <v>30</v>
+      <c r="H73" s="6" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="74">
@@ -3345,7 +3345,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G74" s="3" t="n">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Kitchen Remodel Steps in Order: The Complete Sequence</t>
+          <t>Choosing a Contractor for Your Kitchen Renovation</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>kitchen remodel steps in order</t>
+          <t>contractor for kitchen renovation</t>
         </is>
       </c>
       <c r="D75" s="8" t="inlineStr">
@@ -3378,19 +3378,19 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G75" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="H75" s="4" t="n">
-        <v>24</v>
+        <v>10</v>
+      </c>
+      <c r="H75" s="6" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="76">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>What to Look for When Hiring a Bathroom Remodeler</t>
+          <t>Best Kitchen Remodeler: The Questions to Ask First</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>bathroom remodeler</t>
+          <t>best kitchen remodeler</t>
         </is>
       </c>
       <c r="D76" s="8" t="inlineStr">
@@ -3421,14 +3421,14 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G76" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="H76" s="5" t="n">
-        <v>48</v>
+        <v>10</v>
+      </c>
+      <c r="H76" s="6" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="77">
@@ -3477,12 +3477,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Kitchen Remodel Timeline: How Long a Renovation Really Takes</t>
+          <t>How to Prepare Your Home for a Kitchen Remodel</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>kitchen remodel timeline</t>
+          <t>how to prepare for a kitchen remodel</t>
         </is>
       </c>
       <c r="D78" s="8" t="inlineStr">
@@ -3497,14 +3497,14 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G78" s="3" t="n">
-        <v>114</v>
-      </c>
-      <c r="H78" s="5" t="n">
-        <v>38</v>
+        <v>10</v>
+      </c>
+      <c r="H78" s="4" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="79">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Do You Need a Permit for a Kitchen Remodel in North Carolina?</t>
+          <t>Kitchen Demolition: What Tear-Out Day Actually Involves</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>kitchen remodel permits</t>
+          <t>kitchen demolition</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
@@ -3535,14 +3535,14 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G79" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="H79" s="5" t="n">
-        <v>38</v>
+      <c r="H79" s="6" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="80">
@@ -3553,12 +3553,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Sustainable Kitchen Remodeling: The Eco Cheat Codes That Pay Off</t>
+          <t>Kitchen Remodeling Timeline: Timelines, Trade-offs, and Questions to Ask</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>sustainable kitchen remodel</t>
+          <t>kitchen remodeling timeline</t>
         </is>
       </c>
       <c r="D80" s="8" t="inlineStr">
@@ -3568,18 +3568,18 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G80" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="H80" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="H80" s="6" t="n">
         <v>38</v>
       </c>
     </row>
@@ -3591,12 +3591,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Kitchen Renovation Timeline: Week by Week, What Happens</t>
+          <t>The Right Order of a Kitchen Remodel, Step by Step</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>kitchen renovation timeline</t>
+          <t>order of kitchen remodel</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr">
@@ -3611,14 +3611,14 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G81" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="H81" s="5" t="n">
-        <v>38</v>
+      <c r="H81" s="6" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="82">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Kitchen Remodeling in Matthews, NC: What to Expect</t>
+          <t>Kitchen Remodel in Marvin, NC: Full Tear-Out in One Week</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>kitchen remodeling matthews nc</t>
+          <t>kitchen remodel marvin nc</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -3649,11 +3649,11 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G82" s="3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H82" s="4" t="n">
         <v>18</v>
@@ -3667,12 +3667,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Home Renovation Charlotte NC: What the Process Looks Like Here</t>
+          <t>Kitchen Remodeling in Waxhaw, NC: Local Process and Timeline</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>home renovation charlotte nc</t>
+          <t>kitchen remodeling waxhaw nc</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -3687,14 +3687,14 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G83" s="3" t="n">
-        <v>320</v>
-      </c>
-      <c r="H83" s="5" t="n">
-        <v>38</v>
+        <v>15</v>
+      </c>
+      <c r="H83" s="4" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="84">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G84" s="3" t="n">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Kitchen Renovation Charlotte NC: A Faster Path to Your Dream Kitchen</t>
+          <t>Kitchen Renovation Charlotte NC: Local Crews, Lifetime Warranty</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G85" s="3" t="n">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Bathroom Renovation Services Ballantyne NC: One Local Crew, Start to Finish</t>
+          <t>Kitchen Contractors Charlotte NC: Built Around Your Home and Budget</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>bathroom renovation services ballantyne nc</t>
+          <t>kitchen contractors charlotte nc</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -3801,14 +3801,14 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G86" s="3" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="H86" s="4" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="87">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Bathroom Designers Charlotte: Where Speed Meets Craftsmanship</t>
+          <t>Kitchen Remodeling Companies Charlotte: Fixed Pricing, Finished in 7 Days</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>bathroom designers charlotte</t>
+          <t>kitchen remodeling companies charlotte</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -3839,14 +3839,14 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G87" s="3" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="H87" s="4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="88">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Home Renovation Contractors Charlotte: The Questions to Ask First</t>
+          <t>Kitchen and Bath Remodeling in Charlotte, NC: One Crew, One Timeline</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>home renovation contractors charlotte</t>
+          <t>kitchen and bath remodeling charlotte nc</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -3877,14 +3877,14 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G88" s="3" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="H88" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="89">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Kitchen and Bath Remodeling in Charlotte, NC: One Crew, One Timeline</t>
+          <t>Kitchen Remodeling in Cornelius, NC: Lake-Area Kitchen Renovations</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>kitchen and bath remodeling charlotte nc</t>
+          <t>kitchen remodeling cornelius nc</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -3915,14 +3915,14 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G89" s="3" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="H89" s="4" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="90">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Bathroom Renovation Charlotte: Local Crews, Lifetime Warranty</t>
+          <t>Kitchen Remodeling in Belmont, NC: Local Trends and Timelines</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>bathroom renovation charlotte</t>
+          <t>kitchen remodeling belmont nc</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -3953,14 +3953,14 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G90" s="3" t="n">
-        <v>390</v>
-      </c>
-      <c r="H90" s="5" t="n">
-        <v>33</v>
+        <v>10</v>
+      </c>
+      <c r="H90" s="4" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="91">
@@ -3971,12 +3971,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Bath Remodel Charlotte: Built Around Your Home and Budget</t>
+          <t>Custom Kitchen Cabinets in Charlotte: Built for Your Space</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>bath remodel charlotte</t>
+          <t>custom kitchen cabinets charlotte</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -3991,14 +3991,14 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G91" s="3" t="n">
-        <v>110</v>
+        <v>10</v>
       </c>
       <c r="H91" s="4" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
     </row>
     <row r="92">
@@ -4009,15 +4009,15 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Kitchen Remodel Cost in Charlotte, NC: What Drives the Number</t>
+          <t>Average Cost of a Complete Kitchen Remodel: Where the Money Goes, and Where to Save</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>kitchen remodel cost charlotte nc</t>
-        </is>
-      </c>
-      <c r="D92" s="6" t="inlineStr">
+          <t>average cost of a complete kitchen remodel</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
         <is>
           <t>Cost &amp; Budget</t>
         </is>
@@ -4029,14 +4029,14 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G92" s="3" t="n">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="H92" s="4" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="93">
@@ -4047,15 +4047,15 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>How Much Does a Kitchen Remodel Cost? A Real 2026 Breakdown</t>
+          <t>Average Cost of a New Kitchen Remodel: The Numbers Behind the Choice</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>how much does a kitchen remodel cost</t>
-        </is>
-      </c>
-      <c r="D93" s="6" t="inlineStr">
+          <t>average cost of a new kitchen remodel</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
         <is>
           <t>Cost &amp; Budget</t>
         </is>
@@ -4067,11 +4067,11 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G93" s="3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H93" s="4" t="n">
         <v>24</v>
@@ -4085,15 +4085,15 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Luxury Kitchen Remodel Cost: What High-End Really Buys</t>
+          <t>Average Cost of Redoing a Kitchen: A 2026 Buyer's Guide</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>luxury kitchen remodel cost</t>
-        </is>
-      </c>
-      <c r="D94" s="6" t="inlineStr">
+          <t>average cost of redoing a kitchen</t>
+        </is>
+      </c>
+      <c r="D94" s="5" t="inlineStr">
         <is>
           <t>Cost &amp; Budget</t>
         </is>
@@ -4105,7 +4105,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G94" s="3" t="n">
@@ -4123,15 +4123,15 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>What a Free Kitchen Remodel Estimate Should Tell You</t>
+          <t>Affordable Kitchen Remodels: Where to Save Without Regret</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>free kitchen remodel estimate</t>
-        </is>
-      </c>
-      <c r="D95" s="6" t="inlineStr">
+          <t>affordable kitchen remodel</t>
+        </is>
+      </c>
+      <c r="D95" s="5" t="inlineStr">
         <is>
           <t>Cost &amp; Budget</t>
         </is>
@@ -4143,14 +4143,14 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G95" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="H95" s="5" t="n">
-        <v>30</v>
+        <v>63</v>
+      </c>
+      <c r="H95" s="6" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="96">
@@ -4161,15 +4161,15 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Kitchen Remodel Prices in 2026: What Sets the Range</t>
+          <t>What Drives Your Kitchen Remodel Price: A Cost-Factor Guide</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>kitchen prices</t>
-        </is>
-      </c>
-      <c r="D96" s="6" t="inlineStr">
+          <t>kitchen remodel price</t>
+        </is>
+      </c>
+      <c r="D96" s="5" t="inlineStr">
         <is>
           <t>Cost &amp; Budget</t>
         </is>
@@ -4181,14 +4181,14 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G96" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="H96" s="5" t="n">
-        <v>48</v>
+        <v>40</v>
+      </c>
+      <c r="H96" s="6" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="97">
@@ -4199,15 +4199,15 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>What a Kitchen Installation Estimate Should Include</t>
+          <t>What a Free Kitchen Remodel Estimate Should Tell You</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>kitchen installation cost estimate</t>
-        </is>
-      </c>
-      <c r="D97" s="6" t="inlineStr">
+          <t>free kitchen remodel estimate</t>
+        </is>
+      </c>
+      <c r="D97" s="5" t="inlineStr">
         <is>
           <t>Cost &amp; Budget</t>
         </is>
@@ -4219,13 +4219,13 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G97" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="H97" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="H97" s="6" t="n">
         <v>30</v>
       </c>
     </row>
@@ -4237,15 +4237,15 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Full Kitchen Remodel Cost: Where the Money Goes, and Where to Save</t>
+          <t>What a Brand-New Kitchen Costs vs a Remodel</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>full kitchen remodel cost</t>
-        </is>
-      </c>
-      <c r="D98" s="6" t="inlineStr">
+          <t>new kitchen prices</t>
+        </is>
+      </c>
+      <c r="D98" s="5" t="inlineStr">
         <is>
           <t>Cost &amp; Budget</t>
         </is>
@@ -4257,14 +4257,14 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G98" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="H98" s="5" t="n">
-        <v>30</v>
+        <v>15</v>
+      </c>
+      <c r="H98" s="6" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="99">
@@ -4283,7 +4283,7 @@
           <t>kitchen renovation cost</t>
         </is>
       </c>
-      <c r="D99" s="6" t="inlineStr">
+      <c r="D99" s="5" t="inlineStr">
         <is>
           <t>Cost &amp; Budget</t>
         </is>
@@ -4295,13 +4295,13 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G99" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="H99" s="5" t="n">
+      <c r="H99" s="6" t="n">
         <v>30</v>
       </c>
     </row>
@@ -4313,12 +4313,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Full-Service Kitchen Renovation: What's Included</t>
+          <t>Cabinet Refacing in Charlotte, NC: When It Makes Sense</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>kitchen renovation services</t>
+          <t>cabinet refacing charlotte nc</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
@@ -4333,14 +4333,14 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G100" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="H100" s="5" t="n">
-        <v>38</v>
+        <v>102</v>
+      </c>
+      <c r="H100" s="4" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="101">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Kitchen Renovation, Start to Finish: A Homeowner's Overview</t>
+          <t>Kitchen Remodeling 101: What the Project Really Involves</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>kitchen renovation</t>
+          <t>kitchen remodeling</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
@@ -4409,13 +4409,13 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G102" s="3" t="n">
-        <v>232</v>
-      </c>
-      <c r="H102" s="5" t="n">
+        <v>374</v>
+      </c>
+      <c r="H102" s="6" t="n">
         <v>48</v>
       </c>
     </row>
@@ -4427,12 +4427,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Kitchen Cabinet Installation: How It's Done Right</t>
+          <t>Kitchen Island Ideas: Sizing, Seating, and Smart Storage</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>kitchen cabinet installation</t>
+          <t>kitchen island ideas</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
@@ -4442,18 +4442,18 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G103" s="3" t="n">
-        <v>96</v>
-      </c>
-      <c r="H103" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="H103" s="6" t="n">
         <v>38</v>
       </c>
     </row>
@@ -4465,12 +4465,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Kitchen and Bath Remodeling Together: One Project or Two?</t>
+          <t>Kitchen Cabinet Colors: What's Timeless vs What's Trendy</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>kitchen and bath remodeling</t>
+          <t>kitchen cabinet colors</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
@@ -4480,19 +4480,19 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G104" s="3" t="n">
-        <v>45</v>
-      </c>
-      <c r="H104" s="5" t="n">
-        <v>30</v>
+        <v>40</v>
+      </c>
+      <c r="H104" s="6" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="105">
@@ -4503,12 +4503,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Kitchen Design Ideas: Layouts, Light, and Lasting Style</t>
+          <t>Kitchen Trends 2026: Bold Cabinets, Brass, and What to Skip</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>kitchen design ideas</t>
+          <t>kitchen trends 2026</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
@@ -4529,7 +4529,7 @@
       <c r="G105" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="H105" s="5" t="n">
+      <c r="H105" s="6" t="n">
         <v>38</v>
       </c>
     </row>
@@ -4541,12 +4541,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Kitchen Backsplash Ideas That Pull a Remodel Together</t>
+          <t>Kitchen Sink Ideas: Materials, Mounts, and the Right Size</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>kitchen backsplash ideas</t>
+          <t>kitchen sink ideas</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
@@ -4567,7 +4567,7 @@
       <c r="G106" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="H106" s="5" t="n">
+      <c r="H106" s="6" t="n">
         <v>38</v>
       </c>
     </row>
@@ -4579,12 +4579,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Kitchen Flooring Options Ranked for Durability and Looks</t>
+          <t>Open-Concept Kitchens: When Knocking Down a Wall Pays Off</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>kitchen flooring options</t>
+          <t>open concept kitchen</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
@@ -4594,18 +4594,18 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G107" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="H107" s="5" t="n">
+      <c r="H107" s="6" t="n">
         <v>38</v>
       </c>
     </row>
@@ -4617,12 +4617,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Farmhouse Kitchen Ideas That Still Feel Fresh in 2026</t>
+          <t>Cabinet Hardware: The Small Detail That Sets the Tone</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>farmhouse kitchen ideas</t>
+          <t>cabinet hardware ideas</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
@@ -4643,7 +4643,7 @@
       <c r="G108" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="H108" s="5" t="n">
+      <c r="H108" s="6" t="n">
         <v>38</v>
       </c>
     </row>
@@ -4655,12 +4655,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Choosing a Kitchen Faucet: Finishes, Features, and Value</t>
+          <t>Butcher Block Countertops: Warm Looks, Real Trade-offs</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>kitchen faucet ideas</t>
+          <t>butcher block countertops</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr">
@@ -4675,13 +4675,13 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G109" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="H109" s="5" t="n">
+      <c r="H109" s="6" t="n">
         <v>38</v>
       </c>
     </row>
@@ -4693,12 +4693,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Small Kitchen Ideas: Making a Compact Space Feel Open</t>
+          <t>Butler's Pantry Ideas: A Kitchen Upgrade That Adds Real Value</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>small kitchen ideas</t>
+          <t>butler pantry ideas</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
@@ -4719,7 +4719,7 @@
       <c r="G110" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="H110" s="5" t="n">
+      <c r="H110" s="6" t="n">
         <v>38</v>
       </c>
     </row>
@@ -4731,12 +4731,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Two-Tone Kitchen Cabinets: How to Mix Without a Mess</t>
+          <t>Kitchen Cabinet Styles: Shaker, Flat-Panel, and Beyond</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>two tone kitchen cabinets</t>
+          <t>kitchen cabinet styles</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr">
@@ -4751,14 +4751,14 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G111" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="H111" s="5" t="n">
-        <v>30</v>
+      <c r="H111" s="6" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="112">
@@ -4769,12 +4769,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Kitchen Storage Ideas That Use Every Inch</t>
+          <t>Quartz Countertops: Why They Dominate Modern Kitchens</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>kitchen storage ideas</t>
+          <t>quartz countertops</t>
         </is>
       </c>
       <c r="D112" s="7" t="inlineStr">
@@ -4784,19 +4784,19 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G112" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="H112" s="5" t="n">
-        <v>38</v>
+        <v>10</v>
+      </c>
+      <c r="H112" s="6" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="113">
@@ -4807,33 +4807,33 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>White Kitchen Cabinets: Why They Endure, and How to Keep Them Clean</t>
+          <t>Kitchen Remodeler Davidson: A No-Nonsense Buyer's Guide</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>white kitchen cabinets</t>
-        </is>
-      </c>
-      <c r="D113" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>kitchen remodeler davidson</t>
+        </is>
+      </c>
+      <c r="D113" s="8" t="inlineStr">
+        <is>
+          <t>Process &amp; Planning</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G113" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="H113" s="5" t="n">
+      <c r="H113" s="6" t="n">
         <v>38</v>
       </c>
     </row>
@@ -4845,12 +4845,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Custom Bathroom Remodel Contractor: A No-Nonsense Buyer's Guide</t>
+          <t>What Separates a Great Kitchen Remodeler From the Rest</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>custom bathroom remodel contractor</t>
+          <t>kitchen remodeler</t>
         </is>
       </c>
       <c r="D114" s="8" t="inlineStr">
@@ -4865,14 +4865,14 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G114" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="H114" s="5" t="n">
-        <v>30</v>
+        <v>151</v>
+      </c>
+      <c r="H114" s="6" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="115">
@@ -4883,12 +4883,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>What Separates a Great Kitchen Remodeler From the Rest</t>
+          <t>What a Kitchen Contractor Handles on a Remodel</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>kitchen remodeler</t>
+          <t>kitchen contractor</t>
         </is>
       </c>
       <c r="D115" s="8" t="inlineStr">
@@ -4903,13 +4903,13 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G115" s="3" t="n">
-        <v>151</v>
-      </c>
-      <c r="H115" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="H115" s="6" t="n">
         <v>48</v>
       </c>
     </row>
@@ -4921,12 +4921,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>What a Kitchen Contractor Handles on a Remodel</t>
+          <t>A Homeowner's Guide to Kitchen Remodeler East Shoreham</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>kitchen contractor</t>
+          <t>kitchen remodeler east shoreham</t>
         </is>
       </c>
       <c r="D116" s="8" t="inlineStr">
@@ -4941,14 +4941,14 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G116" s="3" t="n">
-        <v>36</v>
-      </c>
-      <c r="H116" s="5" t="n">
-        <v>48</v>
+        <v>10</v>
+      </c>
+      <c r="H116" s="6" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="117">
@@ -4959,12 +4959,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>How to Compare the Best Kitchen Remodel Contractors</t>
+          <t>Kitchen Addition Contractors: What to Know Before You Commit</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>best kitchen remodel contractors</t>
+          <t>kitchen addition contractors</t>
         </is>
       </c>
       <c r="D117" s="8" t="inlineStr">
@@ -4979,14 +4979,14 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G117" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="H117" s="5" t="n">
-        <v>30</v>
+      <c r="H117" s="6" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="118">
@@ -4997,12 +4997,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>How Long Does a Kitchen Remodel Take? Why Ours Takes 7 Days</t>
+          <t>Kitchen Remodel Order of Steps: Timelines, Trade-offs, and Questions to Ask</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>how long does a kitchen remodel take</t>
+          <t>kitchen remodel order of steps</t>
         </is>
       </c>
       <c r="D118" s="8" t="inlineStr">
@@ -5017,11 +5017,11 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G118" s="3" t="n">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="H118" s="4" t="n">
         <v>24</v>
@@ -5035,12 +5035,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>How to Choose a Kitchen Contractor You Can Actually Trust</t>
+          <t>Do You Need a Permit for a Kitchen Remodel in North Carolina?</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>how to choose a kitchen contractor</t>
+          <t>kitchen remodel permits</t>
         </is>
       </c>
       <c r="D119" s="8" t="inlineStr">
@@ -5050,19 +5050,19 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G119" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="H119" s="4" t="n">
-        <v>24</v>
+      <c r="H119" s="6" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="120">
@@ -5073,12 +5073,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>The Kitchen Remodel Checklist Every Homeowner Should Use</t>
+          <t>Questions to Ask a Kitchen Remodel Contractor Before You Sign</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>kitchen remodel checklist</t>
+          <t>kitchen remodel contractor questions</t>
         </is>
       </c>
       <c r="D120" s="8" t="inlineStr">
@@ -5088,19 +5088,19 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G120" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="H120" s="5" t="n">
-        <v>38</v>
+      <c r="H120" s="6" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="121">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Questions to Ask a Kitchen Remodel Contractor Before You Sign</t>
+          <t>Kitchen Renovation Timeline: Week by Week, What Happens</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>kitchen remodel contractor questions</t>
+          <t>kitchen renovation timeline</t>
         </is>
       </c>
       <c r="D121" s="8" t="inlineStr">
@@ -5131,14 +5131,14 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G121" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="H121" s="5" t="n">
-        <v>30</v>
+        <v>23</v>
+      </c>
+      <c r="H121" s="6" t="n">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="H2" s="10" t="inlineStr">
@@ -5285,7 +5285,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="H3" s="10" t="inlineStr">
@@ -5323,12 +5323,12 @@
       <c r="E4" s="3" t="n">
         <v>4400</v>
       </c>
-      <c r="F4" s="5" t="n">
+      <c r="F4" s="6" t="n">
         <v>47</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -5371,7 +5371,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -5457,7 +5457,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -5591,14 +5591,14 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>New</t>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>Have — optimize</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Very winnable suburb (KD 4).</t>
+          <t>Page EXISTS. Very winnable (KD 4); needs blog content linking to it.</t>
         </is>
       </c>
     </row>
@@ -5631,7 +5631,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -5674,7 +5674,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -5712,12 +5712,12 @@
       <c r="E13" s="3" t="n">
         <v>1900</v>
       </c>
-      <c r="F13" s="5" t="n">
+      <c r="F13" s="6" t="n">
         <v>40</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -5755,12 +5755,12 @@
       <c r="E14" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F14" s="5" t="n">
+      <c r="F14" s="6" t="n">
         <v>34</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -5841,12 +5841,12 @@
       <c r="E16" s="3" t="n">
         <v>6600</v>
       </c>
-      <c r="F16" s="5" t="n">
+      <c r="F16" s="6" t="n">
         <v>43</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -5894,14 +5894,14 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>New</t>
+      <c r="H17" s="10" t="inlineStr">
+        <is>
+          <t>Have — optimize</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Affluent suburb; you have a featured project there already.</t>
+          <t>Page EXISTS. Affluent suburb; featured project already there.</t>
         </is>
       </c>
     </row>
@@ -5939,14 +5939,14 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>New</t>
+      <c r="H18" s="10" t="inlineStr">
+        <is>
+          <t>Have — optimize</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Union County.</t>
+          <t>Page EXISTS. Union County.</t>
         </is>
       </c>
     </row>
@@ -5986,12 +5986,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>New (neighborhood)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Affluent South Charlotte.</t>
+          <t>Affluent South Charlotte neighborhood — NOT among the 26 city pages; worth adding.</t>
         </is>
       </c>
     </row>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -6069,7 +6069,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -6112,7 +6112,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -6155,7 +6155,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -6193,12 +6193,12 @@
       <c r="E24" s="3" t="n">
         <v>27100</v>
       </c>
-      <c r="F24" s="5" t="n">
+      <c r="F24" s="6" t="n">
         <v>44</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -6248,14 +6248,14 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>New</t>
+      <c r="H25" s="10" t="inlineStr">
+        <is>
+          <t>Have — optimize</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Expansion suburb.</t>
+          <t>Page EXISTS.</t>
         </is>
       </c>
     </row>
@@ -6293,14 +6293,14 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>New</t>
+      <c r="H26" s="10" t="inlineStr">
+        <is>
+          <t>Have — optimize</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>SC side of the metro.</t>
+          <t>Page EXISTS. SC side of the metro.</t>
         </is>
       </c>
     </row>
@@ -6317,7 +6317,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Huntersville / Mooresville / Belmont</t>
+          <t>Huntersville / Mooresville / Belmont / +18 more</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -6340,14 +6340,14 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>New</t>
+      <c r="H27" s="10" t="inlineStr">
+        <is>
+          <t>Have — optimize</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>North / west metro expansion pages.</t>
+          <t>26 suburb pages EXIST total. The work is RANKING them via linked content, not building new ones.</t>
         </is>
       </c>
     </row>
@@ -6429,18 +6429,18 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E2" s="3" t="n">
         <v>590</v>
       </c>
-      <c r="F2" s="5" t="n">
+      <c r="F2" s="6" t="n">
         <v>35</v>
       </c>
-      <c r="G2" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -6462,18 +6462,18 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
         <v>390</v>
       </c>
-      <c r="F3" s="5" t="n">
+      <c r="F3" s="6" t="n">
         <v>33</v>
       </c>
-      <c r="G3" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -6495,7 +6495,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
@@ -6528,13 +6528,13 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
         <v>374</v>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="F5" s="6" t="n">
         <v>48</v>
       </c>
       <c r="G5" s="10" t="inlineStr">
@@ -6561,7 +6561,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
@@ -6627,7 +6627,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
@@ -6693,7 +6693,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
@@ -6702,9 +6702,9 @@
       <c r="F10" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="G10" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -6726,18 +6726,18 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
         <v>320</v>
       </c>
-      <c r="F11" s="5" t="n">
+      <c r="F11" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="G11" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -6759,13 +6759,13 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
         <v>210</v>
       </c>
-      <c r="F12" s="5" t="n">
+      <c r="F12" s="6" t="n">
         <v>33</v>
       </c>
       <c r="G12" t="inlineStr">
@@ -6792,18 +6792,18 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
         <v>210</v>
       </c>
-      <c r="F13" s="5" t="n">
+      <c r="F13" s="6" t="n">
         <v>41</v>
       </c>
-      <c r="G13" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
@@ -6846,7 +6846,7 @@
           <t>kitchen remodel cost</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Cost &amp; Budget</t>
         </is>
@@ -6858,18 +6858,18 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
         <v>193</v>
       </c>
-      <c r="F15" s="5" t="n">
+      <c r="F15" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="G15" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -6891,7 +6891,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
@@ -6900,9 +6900,9 @@
       <c r="F16" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="G16" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -6924,18 +6924,18 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
         <v>170</v>
       </c>
-      <c r="F17" s="5" t="n">
+      <c r="F17" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="G17" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -6957,7 +6957,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
@@ -6990,7 +6990,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
@@ -7023,7 +7023,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
@@ -7056,13 +7056,13 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
         <v>151</v>
       </c>
-      <c r="F21" s="5" t="n">
+      <c r="F21" s="6" t="n">
         <v>48</v>
       </c>
       <c r="G21" s="10" t="inlineStr">
@@ -7089,18 +7089,18 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E22" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="F22" s="5" t="n">
+      <c r="F22" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="G22" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -7122,7 +7122,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E23" s="3" t="n">
@@ -7131,9 +7131,9 @@
       <c r="F23" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="G23" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -7155,7 +7155,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E24" s="3" t="n">
@@ -7164,9 +7164,9 @@
       <c r="F24" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="G24" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -7188,7 +7188,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E25" s="3" t="n">
@@ -7221,13 +7221,13 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E26" s="3" t="n">
         <v>96</v>
       </c>
-      <c r="F26" s="5" t="n">
+      <c r="F26" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G26" s="10" t="inlineStr">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E27" s="3" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E28" s="3" t="n">
@@ -7296,9 +7296,9 @@
       <c r="F28" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="G28" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -7320,7 +7320,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E29" s="3" t="n">
@@ -7329,9 +7329,9 @@
       <c r="F29" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G29" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -7353,13 +7353,13 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E30" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="F30" s="5" t="n">
+      <c r="F30" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G30" s="10" t="inlineStr">
@@ -7386,7 +7386,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E31" s="3" t="n">
@@ -7395,9 +7395,9 @@
       <c r="F31" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="G31" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -7419,7 +7419,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E32" s="3" t="n">
@@ -7452,18 +7452,18 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E33" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="F33" s="5" t="n">
+      <c r="F33" s="6" t="n">
         <v>37</v>
       </c>
-      <c r="G33" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -7485,13 +7485,13 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E34" s="3" t="n">
         <v>75</v>
       </c>
-      <c r="F34" s="5" t="n">
+      <c r="F34" s="6" t="n">
         <v>48</v>
       </c>
       <c r="G34" t="inlineStr">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E35" s="3" t="n">
@@ -7527,9 +7527,9 @@
       <c r="F35" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="G35" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -7551,7 +7551,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E36" s="3" t="n">
@@ -7584,7 +7584,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E37" s="3" t="n">
@@ -7593,9 +7593,9 @@
       <c r="F37" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="G37" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -7605,7 +7605,7 @@
           <t>affordable kitchen remodel</t>
         </is>
       </c>
-      <c r="B38" s="6" t="inlineStr">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>Cost &amp; Budget</t>
         </is>
@@ -7617,13 +7617,13 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E38" s="3" t="n">
         <v>63</v>
       </c>
-      <c r="F38" s="5" t="n">
+      <c r="F38" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G38" s="10" t="inlineStr">
@@ -7650,7 +7650,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E39" s="3" t="n">
@@ -7659,9 +7659,9 @@
       <c r="F39" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G39" s="10" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -7671,7 +7671,7 @@
           <t>kitchen estimate</t>
         </is>
       </c>
-      <c r="B40" s="6" t="inlineStr">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>Cost &amp; Budget</t>
         </is>
@@ -7683,13 +7683,13 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E40" s="3" t="n">
         <v>61</v>
       </c>
-      <c r="F40" s="5" t="n">
+      <c r="F40" s="6" t="n">
         <v>48</v>
       </c>
       <c r="G40" s="10" t="inlineStr">
@@ -7725,9 +7725,9 @@
       <c r="F41" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="G41" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -7749,7 +7749,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E42" s="3" t="n">
@@ -7782,7 +7782,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E43" s="3" t="n">
@@ -7815,13 +7815,13 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E44" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="F44" s="5" t="n">
+      <c r="F44" s="6" t="n">
         <v>31</v>
       </c>
       <c r="G44" t="inlineStr">
@@ -7848,13 +7848,13 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E45" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="F45" s="5" t="n">
+      <c r="F45" s="6" t="n">
         <v>32</v>
       </c>
       <c r="G45" t="inlineStr">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E46" s="3" t="n">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E47" s="3" t="n">
@@ -7947,13 +7947,13 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E48" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="F48" s="5" t="n">
+      <c r="F48" s="6" t="n">
         <v>32</v>
       </c>
       <c r="G48" t="inlineStr">
@@ -7980,7 +7980,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E49" s="3" t="n">
@@ -7989,9 +7989,9 @@
       <c r="F49" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G49" s="10" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -8013,13 +8013,13 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E50" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="F50" s="5" t="n">
+      <c r="F50" s="6" t="n">
         <v>41</v>
       </c>
       <c r="G50" t="inlineStr">
@@ -8046,7 +8046,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E51" s="3" t="n">
@@ -8055,9 +8055,9 @@
       <c r="F51" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G51" s="10" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -8079,18 +8079,18 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E52" s="3" t="n">
         <v>45</v>
       </c>
-      <c r="F52" s="5" t="n">
+      <c r="F52" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="G52" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -8112,7 +8112,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E53" s="3" t="n">
@@ -8121,9 +8121,9 @@
       <c r="F53" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="G53" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -8145,7 +8145,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E54" s="3" t="n">
@@ -8178,13 +8178,13 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E55" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="F55" s="5" t="n">
+      <c r="F55" s="6" t="n">
         <v>32</v>
       </c>
       <c r="G55" t="inlineStr">
@@ -8211,7 +8211,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E56" s="3" t="n">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E57" s="3" t="n">
@@ -8277,7 +8277,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E58" s="3" t="n">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E59" s="3" t="n">
@@ -8343,7 +8343,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E60" s="3" t="n">
@@ -8376,7 +8376,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E61" s="3" t="n">
@@ -8409,7 +8409,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E62" s="3" t="n">
@@ -8418,9 +8418,9 @@
       <c r="F62" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G62" s="10" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -8442,7 +8442,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E63" s="3" t="n">
@@ -8463,7 +8463,7 @@
           <t>kitchen remodel price</t>
         </is>
       </c>
-      <c r="B64" s="6" t="inlineStr">
+      <c r="B64" s="5" t="inlineStr">
         <is>
           <t>Cost &amp; Budget</t>
         </is>
@@ -8475,13 +8475,13 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E64" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="F64" s="5" t="n">
+      <c r="F64" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G64" s="10" t="inlineStr">
@@ -8508,13 +8508,13 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E65" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="F65" s="5" t="n">
+      <c r="F65" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G65" s="10" t="inlineStr">
@@ -8541,7 +8541,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E66" s="3" t="n">
@@ -8595,7 +8595,7 @@
           <t>kitchen remodel estimate</t>
         </is>
       </c>
-      <c r="B68" s="6" t="inlineStr">
+      <c r="B68" s="5" t="inlineStr">
         <is>
           <t>Cost &amp; Budget</t>
         </is>
@@ -8607,13 +8607,13 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E68" s="3" t="n">
         <v>37</v>
       </c>
-      <c r="F68" s="5" t="n">
+      <c r="F68" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G68" s="10" t="inlineStr">
@@ -8640,13 +8640,13 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E69" s="3" t="n">
         <v>36</v>
       </c>
-      <c r="F69" s="5" t="n">
+      <c r="F69" s="6" t="n">
         <v>48</v>
       </c>
       <c r="G69" s="10" t="inlineStr">
@@ -8661,7 +8661,7 @@
           <t>how much to remodel a kitchen</t>
         </is>
       </c>
-      <c r="B70" s="6" t="inlineStr">
+      <c r="B70" s="5" t="inlineStr">
         <is>
           <t>Cost &amp; Budget</t>
         </is>
@@ -8673,7 +8673,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E70" s="3" t="n">
@@ -8682,9 +8682,9 @@
       <c r="F70" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="G70" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -8712,7 +8712,7 @@
       <c r="E71" s="3" t="n">
         <v>36</v>
       </c>
-      <c r="F71" s="5" t="n">
+      <c r="F71" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G71" t="inlineStr">
@@ -8739,18 +8739,18 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E72" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="F72" s="5" t="n">
+      <c r="F72" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="G72" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -8772,7 +8772,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E73" s="3" t="n">
@@ -8793,7 +8793,7 @@
           <t>free kitchen remodel estimate</t>
         </is>
       </c>
-      <c r="B74" s="6" t="inlineStr">
+      <c r="B74" s="5" t="inlineStr">
         <is>
           <t>Cost &amp; Budget</t>
         </is>
@@ -8805,13 +8805,13 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E74" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="F74" s="5" t="n">
+      <c r="F74" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G74" s="10" t="inlineStr">
@@ -8838,18 +8838,18 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E75" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="F75" s="5" t="n">
+      <c r="F75" s="6" t="n">
         <v>48</v>
       </c>
-      <c r="G75" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -8871,13 +8871,13 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E76" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="F76" s="5" t="n">
+      <c r="F76" s="6" t="n">
         <v>48</v>
       </c>
       <c r="G76" t="inlineStr">
@@ -8904,18 +8904,18 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E77" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="F77" s="5" t="n">
+      <c r="F77" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="G77" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -8937,13 +8937,13 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E78" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="F78" s="5" t="n">
+      <c r="F78" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G78" t="inlineStr">
@@ -8958,7 +8958,7 @@
           <t>kitchen prices</t>
         </is>
       </c>
-      <c r="B79" s="6" t="inlineStr">
+      <c r="B79" s="5" t="inlineStr">
         <is>
           <t>Cost &amp; Budget</t>
         </is>
@@ -8970,13 +8970,13 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E79" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="F79" s="5" t="n">
+      <c r="F79" s="6" t="n">
         <v>48</v>
       </c>
       <c r="G79" s="10" t="inlineStr">
@@ -9003,13 +9003,13 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E80" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="F80" s="5" t="n">
+      <c r="F80" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G80" t="inlineStr">
@@ -9036,13 +9036,13 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E81" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="F81" s="5" t="n">
+      <c r="F81" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G81" t="inlineStr">
@@ -9069,13 +9069,13 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E82" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="F82" s="5" t="n">
+      <c r="F82" s="6" t="n">
         <v>48</v>
       </c>
       <c r="G82" t="inlineStr">
@@ -9102,13 +9102,13 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E83" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="F83" s="5" t="n">
+      <c r="F83" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G83" s="10" t="inlineStr">
@@ -9135,13 +9135,13 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E84" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="F84" s="5" t="n">
+      <c r="F84" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G84" s="10" t="inlineStr">
@@ -9168,18 +9168,18 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E85" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="F85" s="5" t="n">
+      <c r="F85" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="G85" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -9201,7 +9201,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E86" s="3" t="n">
@@ -9210,9 +9210,9 @@
       <c r="F86" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G86" s="10" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -9234,7 +9234,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E87" s="3" t="n">
@@ -9267,13 +9267,13 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E88" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="F88" s="5" t="n">
+      <c r="F88" s="6" t="n">
         <v>48</v>
       </c>
       <c r="G88" t="inlineStr">
@@ -9300,7 +9300,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E89" s="3" t="n">
@@ -9333,7 +9333,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E90" s="3" t="n">
@@ -9366,18 +9366,18 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E91" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="F91" s="5" t="n">
+      <c r="F91" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="G91" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -9399,18 +9399,18 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E92" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="F92" s="5" t="n">
+      <c r="F92" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="G92" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -9432,7 +9432,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E93" s="3" t="n">
@@ -9465,7 +9465,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E94" s="3" t="n">
@@ -9474,9 +9474,9 @@
       <c r="F94" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G94" s="10" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -9498,7 +9498,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E95" s="3" t="n">
@@ -9531,7 +9531,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E96" s="3" t="n">
@@ -9564,7 +9564,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E97" s="3" t="n">
@@ -9573,9 +9573,9 @@
       <c r="F97" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G97" s="10" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -9597,7 +9597,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E98" s="3" t="n">
@@ -9630,7 +9630,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E99" s="3" t="n">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E100" s="3" t="n">
@@ -9729,7 +9729,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E102" s="3" t="n">
@@ -9738,9 +9738,9 @@
       <c r="F102" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G102" s="10" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -9762,7 +9762,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E103" s="3" t="n">
@@ -9795,7 +9795,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E104" s="3" t="n">
@@ -9828,7 +9828,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E105" s="3" t="n">
@@ -9861,13 +9861,13 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E106" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="F106" s="5" t="n">
+      <c r="F106" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G106" t="inlineStr">
@@ -9894,7 +9894,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E107" s="3" t="n">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E108" s="3" t="n">
@@ -9960,18 +9960,18 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E109" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="F109" s="5" t="n">
+      <c r="F109" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="G109" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -9993,13 +9993,13 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E110" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="F110" s="5" t="n">
+      <c r="F110" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G110" t="inlineStr">
@@ -10026,7 +10026,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E111" s="3" t="n">
@@ -10047,7 +10047,7 @@
           <t>kitchen installation cost estimate</t>
         </is>
       </c>
-      <c r="B112" s="6" t="inlineStr">
+      <c r="B112" s="5" t="inlineStr">
         <is>
           <t>Cost &amp; Budget</t>
         </is>
@@ -10059,13 +10059,13 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E112" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="F112" s="5" t="n">
+      <c r="F112" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G112" s="10" t="inlineStr">
@@ -10092,7 +10092,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E113" s="3" t="n">
@@ -10101,9 +10101,9 @@
       <c r="F113" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G113" s="10" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -10125,7 +10125,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E114" s="3" t="n">
@@ -10158,7 +10158,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E115" s="3" t="n">
@@ -10191,7 +10191,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E116" s="3" t="n">
@@ -10212,7 +10212,7 @@
           <t>compare kitchen prices</t>
         </is>
       </c>
-      <c r="B117" s="6" t="inlineStr">
+      <c r="B117" s="5" t="inlineStr">
         <is>
           <t>Cost &amp; Budget</t>
         </is>
@@ -10224,13 +10224,13 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E117" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="F117" s="5" t="n">
+      <c r="F117" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G117" s="10" t="inlineStr">
@@ -10257,7 +10257,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E118" s="3" t="n">
@@ -10290,13 +10290,13 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E119" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="F119" s="5" t="n">
+      <c r="F119" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G119" t="inlineStr">
@@ -10323,7 +10323,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E120" s="3" t="n">
@@ -10344,7 +10344,7 @@
           <t>new kitchen prices</t>
         </is>
       </c>
-      <c r="B121" s="6" t="inlineStr">
+      <c r="B121" s="5" t="inlineStr">
         <is>
           <t>Cost &amp; Budget</t>
         </is>
@@ -10356,13 +10356,13 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E121" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="F121" s="5" t="n">
+      <c r="F121" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G121" s="10" t="inlineStr">
@@ -10389,7 +10389,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E122" s="3" t="n">
@@ -10422,7 +10422,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E123" s="3" t="n">
@@ -10455,7 +10455,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E124" s="3" t="n">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E125" s="3" t="n">
@@ -10521,13 +10521,13 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E126" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="F126" s="5" t="n">
+      <c r="F126" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G126" t="inlineStr">
@@ -10554,13 +10554,13 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E127" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="F127" s="5" t="n">
+      <c r="F127" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G127" t="inlineStr">
@@ -10575,7 +10575,7 @@
           <t>full kitchen remodel cost</t>
         </is>
       </c>
-      <c r="B128" s="6" t="inlineStr">
+      <c r="B128" s="5" t="inlineStr">
         <is>
           <t>Cost &amp; Budget</t>
         </is>
@@ -10587,18 +10587,18 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E128" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="F128" s="5" t="n">
+      <c r="F128" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="G128" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E129" s="3" t="n">
@@ -10653,7 +10653,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E130" s="3" t="n">
@@ -10686,13 +10686,13 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E131" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="F131" s="5" t="n">
+      <c r="F131" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G131" t="inlineStr">
@@ -10719,13 +10719,13 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E132" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="F132" s="5" t="n">
+      <c r="F132" s="6" t="n">
         <v>48</v>
       </c>
       <c r="G132" t="inlineStr">
@@ -10752,13 +10752,13 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E133" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="F133" s="5" t="n">
+      <c r="F133" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G133" t="inlineStr">
@@ -10785,7 +10785,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E134" s="3" t="n">
@@ -10806,7 +10806,7 @@
           <t>how much does a kitchen remodel cost</t>
         </is>
       </c>
-      <c r="B135" s="6" t="inlineStr">
+      <c r="B135" s="5" t="inlineStr">
         <is>
           <t>Cost &amp; Budget</t>
         </is>
@@ -10818,7 +10818,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E135" s="3" t="n">
@@ -10827,9 +10827,9 @@
       <c r="F135" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="G135" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -10851,13 +10851,13 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E136" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="F136" s="5" t="n">
+      <c r="F136" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G136" t="inlineStr">
@@ -10884,7 +10884,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E137" s="3" t="n">
@@ -10917,7 +10917,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E138" s="3" t="n">
@@ -10950,7 +10950,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E139" s="3" t="n">
@@ -10983,13 +10983,13 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E140" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="F140" s="5" t="n">
+      <c r="F140" s="6" t="n">
         <v>48</v>
       </c>
       <c r="G140" t="inlineStr">
@@ -11004,7 +11004,7 @@
           <t>before and after kitchen remodel cost</t>
         </is>
       </c>
-      <c r="B141" s="6" t="inlineStr">
+      <c r="B141" s="5" t="inlineStr">
         <is>
           <t>Cost &amp; Budget</t>
         </is>
@@ -11049,7 +11049,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E142" s="3" t="n">
@@ -11082,13 +11082,13 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E143" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="F143" s="5" t="n">
+      <c r="F143" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G143" t="inlineStr">
@@ -11115,13 +11115,13 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E144" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="F144" s="5" t="n">
+      <c r="F144" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G144" t="inlineStr">
@@ -11148,18 +11148,18 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E145" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F145" s="5" t="n">
+      <c r="F145" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G145" s="10" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -11181,13 +11181,13 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E146" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F146" s="5" t="n">
+      <c r="F146" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G146" t="inlineStr">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E147" s="3" t="n">
@@ -11247,7 +11247,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E148" s="3" t="n">
@@ -11280,7 +11280,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E149" s="3" t="n">
@@ -11313,7 +11313,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E150" s="3" t="n">
@@ -11346,7 +11346,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E151" s="3" t="n">
@@ -11379,7 +11379,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E152" s="3" t="n">
@@ -11412,18 +11412,18 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E153" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F153" s="5" t="n">
+      <c r="F153" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G153" s="10" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -11445,7 +11445,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E154" s="3" t="n">
@@ -11466,7 +11466,7 @@
           <t>affordable bathroom remodel</t>
         </is>
       </c>
-      <c r="B155" s="6" t="inlineStr">
+      <c r="B155" s="5" t="inlineStr">
         <is>
           <t>Cost &amp; Budget</t>
         </is>
@@ -11478,13 +11478,13 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E155" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F155" s="5" t="n">
+      <c r="F155" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G155" t="inlineStr">
@@ -11499,7 +11499,7 @@
           <t>affordable kitchen renovations</t>
         </is>
       </c>
-      <c r="B156" s="6" t="inlineStr">
+      <c r="B156" s="5" t="inlineStr">
         <is>
           <t>Cost &amp; Budget</t>
         </is>
@@ -11511,13 +11511,13 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E156" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F156" s="5" t="n">
+      <c r="F156" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G156" t="inlineStr">
@@ -11544,13 +11544,13 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E157" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F157" s="5" t="n">
+      <c r="F157" s="6" t="n">
         <v>48</v>
       </c>
       <c r="G157" t="inlineStr">
@@ -11577,7 +11577,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E158" s="3" t="n">
@@ -11610,7 +11610,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E159" s="3" t="n">
@@ -11643,13 +11643,13 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E160" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F160" s="5" t="n">
+      <c r="F160" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G160" t="inlineStr">
@@ -11676,7 +11676,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E161" s="3" t="n">
@@ -11709,7 +11709,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E162" s="3" t="n">
@@ -11742,7 +11742,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E163" s="3" t="n">
@@ -11775,7 +11775,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E164" s="3" t="n">
@@ -11808,7 +11808,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E165" s="3" t="n">
@@ -11841,7 +11841,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E166" s="3" t="n">
@@ -11874,13 +11874,13 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E167" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F167" s="5" t="n">
+      <c r="F167" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G167" t="inlineStr">
@@ -11907,7 +11907,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E168" s="3" t="n">
@@ -11940,13 +11940,13 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E169" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F169" s="5" t="n">
+      <c r="F169" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G169" t="inlineStr">
@@ -11973,13 +11973,13 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E170" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F170" s="5" t="n">
+      <c r="F170" s="6" t="n">
         <v>48</v>
       </c>
       <c r="G170" t="inlineStr">
@@ -12006,7 +12006,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E171" s="3" t="n">
@@ -12039,7 +12039,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E172" s="3" t="n">
@@ -12072,7 +12072,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E173" s="3" t="n">
@@ -12105,7 +12105,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E174" s="3" t="n">
@@ -12138,7 +12138,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E175" s="3" t="n">
@@ -12171,7 +12171,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E176" s="3" t="n">
@@ -12204,13 +12204,13 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E177" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F177" s="5" t="n">
+      <c r="F177" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G177" t="inlineStr">
@@ -12237,13 +12237,13 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E178" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F178" s="5" t="n">
+      <c r="F178" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G178" t="inlineStr">
@@ -12270,13 +12270,13 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E179" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F179" s="5" t="n">
+      <c r="F179" s="6" t="n">
         <v>48</v>
       </c>
       <c r="G179" t="inlineStr">
@@ -12303,13 +12303,13 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E180" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F180" s="5" t="n">
+      <c r="F180" s="6" t="n">
         <v>48</v>
       </c>
       <c r="G180" t="inlineStr">
@@ -12336,13 +12336,13 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E181" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F181" s="5" t="n">
+      <c r="F181" s="6" t="n">
         <v>48</v>
       </c>
       <c r="G181" t="inlineStr">
@@ -12369,13 +12369,13 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E182" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F182" s="5" t="n">
+      <c r="F182" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G182" t="inlineStr">
@@ -12402,13 +12402,13 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E183" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F183" s="5" t="n">
+      <c r="F183" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G183" t="inlineStr">
@@ -12435,13 +12435,13 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E184" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F184" s="5" t="n">
+      <c r="F184" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G184" t="inlineStr">
@@ -12468,13 +12468,13 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E185" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F185" s="5" t="n">
+      <c r="F185" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G185" t="inlineStr">
@@ -12501,13 +12501,13 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E186" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F186" s="5" t="n">
+      <c r="F186" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G186" t="inlineStr">
@@ -12534,13 +12534,13 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E187" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F187" s="5" t="n">
+      <c r="F187" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G187" t="inlineStr">
@@ -12567,13 +12567,13 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E188" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F188" s="5" t="n">
+      <c r="F188" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G188" t="inlineStr">
@@ -12588,7 +12588,7 @@
           <t>10x20 kitchen remodel cost</t>
         </is>
       </c>
-      <c r="B189" s="6" t="inlineStr">
+      <c r="B189" s="5" t="inlineStr">
         <is>
           <t>Cost &amp; Budget</t>
         </is>
@@ -12600,13 +12600,13 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E189" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F189" s="5" t="n">
+      <c r="F189" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G189" t="inlineStr">
@@ -12633,13 +12633,13 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E190" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F190" s="5" t="n">
+      <c r="F190" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G190" t="inlineStr">
@@ -12666,13 +12666,13 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E191" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F191" s="5" t="n">
+      <c r="F191" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G191" t="inlineStr">
@@ -12699,13 +12699,13 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E192" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F192" s="5" t="n">
+      <c r="F192" s="6" t="n">
         <v>48</v>
       </c>
       <c r="G192" t="inlineStr">
@@ -12732,13 +12732,13 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E193" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F193" s="5" t="n">
+      <c r="F193" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G193" t="inlineStr">
@@ -12765,13 +12765,13 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E194" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F194" s="5" t="n">
+      <c r="F194" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G194" t="inlineStr">
@@ -12798,7 +12798,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E195" s="3" t="n">
@@ -12831,13 +12831,13 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E196" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F196" s="5" t="n">
+      <c r="F196" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G196" t="inlineStr">
@@ -12864,13 +12864,13 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E197" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F197" s="5" t="n">
+      <c r="F197" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G197" t="inlineStr">
@@ -12897,7 +12897,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E198" s="3" t="n">
@@ -12930,13 +12930,13 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E199" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F199" s="5" t="n">
+      <c r="F199" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G199" t="inlineStr">
@@ -12963,13 +12963,13 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E200" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F200" s="5" t="n">
+      <c r="F200" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G200" t="inlineStr">
@@ -12996,13 +12996,13 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E201" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F201" s="5" t="n">
+      <c r="F201" s="6" t="n">
         <v>48</v>
       </c>
       <c r="G201" t="inlineStr">
@@ -13029,13 +13029,13 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E202" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F202" s="5" t="n">
+      <c r="F202" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G202" t="inlineStr">
@@ -13062,13 +13062,13 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E203" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F203" s="5" t="n">
+      <c r="F203" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G203" t="inlineStr">
@@ -13095,7 +13095,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E204" s="3" t="n">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E205" s="3" t="n">
@@ -13161,13 +13161,13 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E206" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F206" s="5" t="n">
+      <c r="F206" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G206" t="inlineStr">
@@ -13194,7 +13194,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E207" s="3" t="n">
@@ -13227,13 +13227,13 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E208" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F208" s="5" t="n">
+      <c r="F208" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G208" t="inlineStr">
@@ -13260,7 +13260,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E209" s="3" t="n">
@@ -13293,7 +13293,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E210" s="3" t="n">
@@ -13326,13 +13326,13 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E211" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F211" s="5" t="n">
+      <c r="F211" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G211" t="inlineStr">
@@ -13359,7 +13359,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E212" s="3" t="n">
@@ -13392,7 +13392,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E213" s="3" t="n">
@@ -13425,7 +13425,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E214" s="3" t="n">
@@ -13458,7 +13458,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E215" s="3" t="n">
@@ -13491,13 +13491,13 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E216" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F216" s="5" t="n">
+      <c r="F216" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G216" t="inlineStr">
@@ -13524,13 +13524,13 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E217" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F217" s="5" t="n">
+      <c r="F217" s="6" t="n">
         <v>48</v>
       </c>
       <c r="G217" t="inlineStr">
@@ -13557,13 +13557,13 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E218" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F218" s="5" t="n">
+      <c r="F218" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G218" t="inlineStr">
@@ -13590,7 +13590,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E219" s="3" t="n">
@@ -13623,7 +13623,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E220" s="3" t="n">
@@ -13644,7 +13644,7 @@
           <t>affordable kitchen design</t>
         </is>
       </c>
-      <c r="B221" s="6" t="inlineStr">
+      <c r="B221" s="5" t="inlineStr">
         <is>
           <t>Cost &amp; Budget</t>
         </is>
@@ -13656,13 +13656,13 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E221" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F221" s="5" t="n">
+      <c r="F221" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G221" t="inlineStr">
@@ -13689,7 +13689,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E222" s="3" t="n">
@@ -13722,13 +13722,13 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E223" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F223" s="5" t="n">
+      <c r="F223" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G223" t="inlineStr">
@@ -13755,13 +13755,13 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E224" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F224" s="5" t="n">
+      <c r="F224" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G224" t="inlineStr">
@@ -13788,13 +13788,13 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E225" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F225" s="5" t="n">
+      <c r="F225" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G225" t="inlineStr">
@@ -13821,13 +13821,13 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E226" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F226" s="5" t="n">
+      <c r="F226" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G226" t="inlineStr">
@@ -13854,13 +13854,13 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E227" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F227" s="5" t="n">
+      <c r="F227" s="6" t="n">
         <v>48</v>
       </c>
       <c r="G227" t="inlineStr">
@@ -13887,13 +13887,13 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E228" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F228" s="5" t="n">
+      <c r="F228" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G228" t="inlineStr">
@@ -13920,13 +13920,13 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E229" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F229" s="5" t="n">
+      <c r="F229" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G229" t="inlineStr">
@@ -13953,13 +13953,13 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E230" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F230" s="5" t="n">
+      <c r="F230" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G230" t="inlineStr">
@@ -13986,13 +13986,13 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E231" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F231" s="5" t="n">
+      <c r="F231" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G231" t="inlineStr">
@@ -14019,13 +14019,13 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E232" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F232" s="5" t="n">
+      <c r="F232" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G232" t="inlineStr">
@@ -14040,7 +14040,7 @@
           <t>approximate cost of kitchen remodel</t>
         </is>
       </c>
-      <c r="B233" s="6" t="inlineStr">
+      <c r="B233" s="5" t="inlineStr">
         <is>
           <t>Cost &amp; Budget</t>
         </is>
@@ -14052,7 +14052,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E233" s="3" t="n">
@@ -14061,9 +14061,9 @@
       <c r="F233" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="G233" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G233" s="10" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -14085,13 +14085,13 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E234" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F234" s="5" t="n">
+      <c r="F234" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G234" t="inlineStr">
@@ -14118,7 +14118,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E235" s="3" t="n">
@@ -14139,7 +14139,7 @@
           <t>average cost for a kitchen remodel</t>
         </is>
       </c>
-      <c r="B236" s="6" t="inlineStr">
+      <c r="B236" s="5" t="inlineStr">
         <is>
           <t>Cost &amp; Budget</t>
         </is>
@@ -14151,7 +14151,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E236" s="3" t="n">
@@ -14172,7 +14172,7 @@
           <t>average cost of a complete kitchen remodel</t>
         </is>
       </c>
-      <c r="B237" s="6" t="inlineStr">
+      <c r="B237" s="5" t="inlineStr">
         <is>
           <t>Cost &amp; Budget</t>
         </is>
@@ -14184,7 +14184,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E237" s="3" t="n">
@@ -14193,9 +14193,9 @@
       <c r="F237" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="G237" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G237" s="10" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -14205,7 +14205,7 @@
           <t>average cost of a full kitchen remodel</t>
         </is>
       </c>
-      <c r="B238" s="6" t="inlineStr">
+      <c r="B238" s="5" t="inlineStr">
         <is>
           <t>Cost &amp; Budget</t>
         </is>
@@ -14217,7 +14217,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E238" s="3" t="n">
@@ -14226,9 +14226,9 @@
       <c r="F238" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="G238" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G238" s="10" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -14238,7 +14238,7 @@
           <t>average cost of a kitchen remodel 2024</t>
         </is>
       </c>
-      <c r="B239" s="6" t="inlineStr">
+      <c r="B239" s="5" t="inlineStr">
         <is>
           <t>Cost &amp; Budget</t>
         </is>
@@ -14250,7 +14250,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E239" s="3" t="n">
@@ -14259,9 +14259,9 @@
       <c r="F239" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="G239" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G239" s="10" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -14271,7 +14271,7 @@
           <t>average cost of a new kitchen remodel</t>
         </is>
       </c>
-      <c r="B240" s="6" t="inlineStr">
+      <c r="B240" s="5" t="inlineStr">
         <is>
           <t>Cost &amp; Budget</t>
         </is>
@@ -14283,7 +14283,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E240" s="3" t="n">
@@ -14292,9 +14292,9 @@
       <c r="F240" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="G240" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G240" s="10" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -14304,7 +14304,7 @@
           <t>average cost of galley kitchen remodel</t>
         </is>
       </c>
-      <c r="B241" s="6" t="inlineStr">
+      <c r="B241" s="5" t="inlineStr">
         <is>
           <t>Cost &amp; Budget</t>
         </is>
@@ -14316,7 +14316,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E241" s="3" t="n">
@@ -14325,9 +14325,9 @@
       <c r="F241" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="G241" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G241" s="10" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -14337,7 +14337,7 @@
           <t>average cost of kitchen remodel 2021</t>
         </is>
       </c>
-      <c r="B242" s="6" t="inlineStr">
+      <c r="B242" s="5" t="inlineStr">
         <is>
           <t>Cost &amp; Budget</t>
         </is>
@@ -14349,7 +14349,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E242" s="3" t="n">
@@ -14370,7 +14370,7 @@
           <t>average cost of kitchen remodel in colorado</t>
         </is>
       </c>
-      <c r="B243" s="6" t="inlineStr">
+      <c r="B243" s="5" t="inlineStr">
         <is>
           <t>Cost &amp; Budget</t>
         </is>
@@ -14382,7 +14382,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E243" s="3" t="n">
@@ -14403,7 +14403,7 @@
           <t>average cost of kitchen renovation</t>
         </is>
       </c>
-      <c r="B244" s="6" t="inlineStr">
+      <c r="B244" s="5" t="inlineStr">
         <is>
           <t>Cost &amp; Budget</t>
         </is>
@@ -14415,7 +14415,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E244" s="3" t="n">
@@ -14436,7 +14436,7 @@
           <t>average cost of large kitchen remodel</t>
         </is>
       </c>
-      <c r="B245" s="6" t="inlineStr">
+      <c r="B245" s="5" t="inlineStr">
         <is>
           <t>Cost &amp; Budget</t>
         </is>
@@ -14448,7 +14448,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E245" s="3" t="n">
@@ -14457,9 +14457,9 @@
       <c r="F245" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="G245" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G245" s="10" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -14469,7 +14469,7 @@
           <t>average cost of redoing a kitchen</t>
         </is>
       </c>
-      <c r="B246" s="6" t="inlineStr">
+      <c r="B246" s="5" t="inlineStr">
         <is>
           <t>Cost &amp; Budget</t>
         </is>
@@ -14481,7 +14481,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E246" s="3" t="n">
@@ -14490,9 +14490,9 @@
       <c r="F246" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="G246" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G246" s="10" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -14502,7 +14502,7 @@
           <t>average cost to update a kitchen</t>
         </is>
       </c>
-      <c r="B247" s="6" t="inlineStr">
+      <c r="B247" s="5" t="inlineStr">
         <is>
           <t>Cost &amp; Budget</t>
         </is>
@@ -14514,7 +14514,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E247" s="3" t="n">
@@ -14523,9 +14523,9 @@
       <c r="F247" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="G247" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G247" s="10" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -14535,7 +14535,7 @@
           <t>average cost to upgrade kitchen</t>
         </is>
       </c>
-      <c r="B248" s="6" t="inlineStr">
+      <c r="B248" s="5" t="inlineStr">
         <is>
           <t>Cost &amp; Budget</t>
         </is>
@@ -14547,7 +14547,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E248" s="3" t="n">
@@ -14580,7 +14580,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E249" s="3" t="n">
@@ -14613,13 +14613,13 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E250" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F250" s="5" t="n">
+      <c r="F250" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G250" t="inlineStr">
@@ -14646,13 +14646,13 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E251" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F251" s="5" t="n">
+      <c r="F251" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G251" t="inlineStr">
@@ -14667,7 +14667,7 @@
           <t>average price for a kitchen remodel</t>
         </is>
       </c>
-      <c r="B252" s="6" t="inlineStr">
+      <c r="B252" s="5" t="inlineStr">
         <is>
           <t>Cost &amp; Budget</t>
         </is>
@@ -14679,7 +14679,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E252" s="3" t="n">
@@ -14712,7 +14712,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E253" s="3" t="n">
@@ -14745,13 +14745,13 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E254" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F254" s="5" t="n">
+      <c r="F254" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G254" t="inlineStr">
@@ -14778,13 +14778,13 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E255" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F255" s="5" t="n">
+      <c r="F255" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G255" t="inlineStr">
@@ -14811,7 +14811,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E256" s="3" t="n">
@@ -14844,7 +14844,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E257" s="3" t="n">
@@ -14877,13 +14877,13 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E258" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F258" s="5" t="n">
+      <c r="F258" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G258" t="inlineStr">
@@ -14910,13 +14910,13 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E259" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F259" s="5" t="n">
+      <c r="F259" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G259" t="inlineStr">
@@ -14949,7 +14949,7 @@
       <c r="E260" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F260" s="5" t="n">
+      <c r="F260" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G260" t="inlineStr">
@@ -14976,7 +14976,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E261" s="3" t="n">
@@ -15009,7 +15009,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E262" s="3" t="n">
@@ -15042,7 +15042,7 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E263" s="3" t="n">
@@ -15075,13 +15075,13 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E264" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F264" s="5" t="n">
+      <c r="F264" s="6" t="n">
         <v>48</v>
       </c>
       <c r="G264" t="inlineStr">
@@ -15108,13 +15108,13 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E265" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F265" s="5" t="n">
+      <c r="F265" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G265" t="inlineStr">
@@ -15141,13 +15141,13 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E266" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F266" s="5" t="n">
+      <c r="F266" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G266" t="inlineStr">
@@ -15174,7 +15174,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E267" s="3" t="n">
@@ -15195,7 +15195,7 @@
           <t>bathroom and kitchen remodel cost</t>
         </is>
       </c>
-      <c r="B268" s="6" t="inlineStr">
+      <c r="B268" s="5" t="inlineStr">
         <is>
           <t>Cost &amp; Budget</t>
         </is>
@@ -15207,7 +15207,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E268" s="3" t="n">
@@ -15240,13 +15240,13 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E269" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F269" s="5" t="n">
+      <c r="F269" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G269" t="inlineStr">
@@ -15273,13 +15273,13 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E270" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F270" s="5" t="n">
+      <c r="F270" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G270" t="inlineStr">
@@ -15306,7 +15306,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E271" s="3" t="n">
@@ -15339,7 +15339,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E272" s="3" t="n">
@@ -15372,7 +15372,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E273" s="3" t="n">
@@ -15405,13 +15405,13 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E274" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F274" s="5" t="n">
+      <c r="F274" s="6" t="n">
         <v>48</v>
       </c>
       <c r="G274" t="inlineStr">
@@ -15438,7 +15438,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E275" s="3" t="n">
@@ -15471,7 +15471,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E276" s="3" t="n">
@@ -15504,13 +15504,13 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E277" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F277" s="5" t="n">
+      <c r="F277" s="6" t="n">
         <v>48</v>
       </c>
       <c r="G277" t="inlineStr">
@@ -15537,7 +15537,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E278" s="3" t="n">
@@ -15570,7 +15570,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E279" s="3" t="n">
@@ -15603,7 +15603,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E280" s="3" t="n">
@@ -15636,7 +15636,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E281" s="3" t="n">
@@ -15669,7 +15669,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E282" s="3" t="n">
@@ -15702,13 +15702,13 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E283" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F283" s="5" t="n">
+      <c r="F283" s="6" t="n">
         <v>48</v>
       </c>
       <c r="G283" t="inlineStr">
@@ -15735,13 +15735,13 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E284" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F284" s="5" t="n">
+      <c r="F284" s="6" t="n">
         <v>48</v>
       </c>
       <c r="G284" t="inlineStr">
@@ -15768,7 +15768,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E285" s="3" t="n">
@@ -15801,7 +15801,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E286" s="3" t="n">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E287" s="3" t="n">
@@ -15867,13 +15867,13 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E288" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F288" s="5" t="n">
+      <c r="F288" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G288" t="inlineStr">
@@ -15900,7 +15900,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E289" s="3" t="n">
@@ -15933,18 +15933,18 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E290" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F290" s="5" t="n">
+      <c r="F290" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="G290" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -15966,7 +15966,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E291" s="3" t="n">
@@ -15999,7 +15999,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E292" s="3" t="n">
@@ -16032,13 +16032,13 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E293" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F293" s="5" t="n">
+      <c r="F293" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G293" t="inlineStr">
@@ -16065,13 +16065,13 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E294" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F294" s="5" t="n">
+      <c r="F294" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G294" t="inlineStr">
@@ -16098,7 +16098,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E295" s="3" t="n">
@@ -16131,7 +16131,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E296" s="3" t="n">
@@ -16164,7 +16164,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E297" s="3" t="n">
@@ -16197,7 +16197,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E298" s="3" t="n">
@@ -16230,7 +16230,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E299" s="3" t="n">
@@ -16263,13 +16263,13 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E300" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F300" s="5" t="n">
+      <c r="F300" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G300" t="inlineStr">
@@ -16296,13 +16296,13 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E301" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F301" s="5" t="n">
+      <c r="F301" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G301" t="inlineStr">
@@ -16329,7 +16329,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E302" s="3" t="n">
@@ -16362,13 +16362,13 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E303" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F303" s="5" t="n">
+      <c r="F303" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G303" t="inlineStr">
@@ -16395,7 +16395,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E304" s="3" t="n">
@@ -16428,13 +16428,13 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E305" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F305" s="5" t="n">
+      <c r="F305" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G305" t="inlineStr">
@@ -16461,7 +16461,7 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E306" s="3" t="n">
@@ -16494,13 +16494,13 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E307" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F307" s="5" t="n">
+      <c r="F307" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G307" t="inlineStr">
@@ -16527,13 +16527,13 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E308" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F308" s="5" t="n">
+      <c r="F308" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G308" t="inlineStr">
@@ -16560,7 +16560,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E309" s="3" t="n">
@@ -16593,13 +16593,13 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E310" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F310" s="5" t="n">
+      <c r="F310" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G310" t="inlineStr">
@@ -16626,13 +16626,13 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E311" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F311" s="5" t="n">
+      <c r="F311" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G311" t="inlineStr">
@@ -16659,7 +16659,7 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E312" s="3" t="n">
@@ -16692,7 +16692,7 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E313" s="3" t="n">
@@ -16725,13 +16725,13 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E314" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F314" s="5" t="n">
+      <c r="F314" s="6" t="n">
         <v>48</v>
       </c>
       <c r="G314" t="inlineStr">
@@ -16758,7 +16758,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E315" s="3" t="n">
@@ -16791,13 +16791,13 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E316" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F316" s="5" t="n">
+      <c r="F316" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G316" t="inlineStr">
@@ -16824,7 +16824,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E317" s="3" t="n">
@@ -16857,7 +16857,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E318" s="3" t="n">
@@ -16890,13 +16890,13 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E319" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F319" s="5" t="n">
+      <c r="F319" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G319" t="inlineStr">
@@ -16923,7 +16923,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E320" s="3" t="n">
@@ -16956,7 +16956,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E321" s="3" t="n">
@@ -17028,7 +17028,7 @@
       <c r="B2" s="3" t="n">
         <v>70</v>
       </c>
-      <c r="C2" s="5" t="n">
+      <c r="C2" s="6" t="n">
         <v>32</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -17051,7 +17051,7 @@
       <c r="B3" s="3" t="n">
         <v>52</v>
       </c>
-      <c r="C3" s="5" t="n">
+      <c r="C3" s="6" t="n">
         <v>38</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -17074,7 +17074,7 @@
       <c r="B4" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C4" s="6" t="n">
         <v>38</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -17097,7 +17097,7 @@
       <c r="B5" s="3" t="n">
         <v>47</v>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="6" t="n">
         <v>30</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -17120,7 +17120,7 @@
       <c r="B6" s="3" t="n">
         <v>45</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="6" t="n">
         <v>30</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -17143,7 +17143,7 @@
       <c r="B7" s="3" t="n">
         <v>44</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="6" t="n">
         <v>30</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -17166,7 +17166,7 @@
       <c r="B8" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="6" t="n">
         <v>38</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -17189,7 +17189,7 @@
       <c r="B9" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="6" t="n">
         <v>30</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -17212,7 +17212,7 @@
       <c r="B10" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="C10" s="5" t="n">
+      <c r="C10" s="6" t="n">
         <v>30</v>
       </c>
       <c r="D10" t="inlineStr">

--- a/decks/7-day-kitchens/keyword-research.xlsx
+++ b/decks/7-day-kitchens/keyword-research.xlsx
@@ -90,17 +90,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00F8D7DA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00D9EAE2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00162f41"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
     <fill>
@@ -123,7 +123,7 @@
   </cellStyleXfs>
   <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -138,14 +138,14 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -817,12 +817,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kitchen Renovation Services Charlotte: Local Crews, Lifetime Warranty</t>
+          <t>Kitchen Remodeling Companies Charlotte: Local Crews, Lifetime Warranty</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>kitchen renovation services charlotte</t>
+          <t>kitchen remodeling companies charlotte</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="G8" s="3" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9">
@@ -855,12 +855,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kitchen Remodeling South West Charlotte: One Local Crew, Start to Finish</t>
+          <t>Kitchen and Bath Remodeling in Charlotte, NC: One Crew, One Timeline</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>kitchen remodeling south west charlotte</t>
+          <t>kitchen and bath remodeling charlotte nc</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -882,7 +882,7 @@
         <v>40</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Average Cost of a Kitchen Remodel, and Why Yours May Differ</t>
+          <t>Quartz Countertop Pricing: What Sets the Range</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>average cost of kitchen remodel</t>
+          <t>quartz price</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="G13" s="3" t="n">
-        <v>10</v>
+        <v>880</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -1045,12 +1045,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Average Cost of a Full Kitchen Remodel: The Real Numbers for 2026</t>
+          <t>The Average Cost of a Kitchen Remodel, and Why Yours May Differ</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>average cost of a full kitchen remodel</t>
+          <t>average cost of kitchen remodel</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -1083,12 +1083,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Average Cost of Galley Kitchen Remodel: What to Know Before You Commit</t>
+          <t>How to Set a Kitchen Remodel Budget You Won't Blow Through</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>average cost of galley kitchen remodel</t>
+          <t>kitchen remodel budget</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1107,10 +1107,10 @@
         </is>
       </c>
       <c r="G15" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="H15" s="4" t="n">
-        <v>24</v>
+        <v>1600</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>44</v>
       </c>
     </row>
     <row r="16">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Is Average Cost to Update a Kitchen Worth It?</t>
+          <t>What a Kitchen Island Costs to Build In</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>average cost to update a kitchen</t>
+          <t>kitchen island cost</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -1141,14 +1141,14 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Buyer</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>10</v>
+        <v>880</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>How to Read a Kitchen Remodel Estimate, Line by Line</t>
+          <t>Budget Backsplash Ideas That Still Look High-End</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>kitchen estimate</t>
+          <t>cheap backsplash</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="G17" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="H17" s="6" t="n">
-        <v>48</v>
+        <v>480</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="18">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Getting a Kitchen Remodel Estimate: What to Expect</t>
+          <t>Budget-Friendly Kitchen Remodels: Smart Places to Save</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>kitchen remodel estimate</t>
+          <t>budget friendly kitchen remodel</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -1217,14 +1217,14 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Buyer</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G18" s="3" t="n">
-        <v>37</v>
+        <v>320</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Kitchen Remodel Prices in 2026: What Sets the Range</t>
+          <t>Choosing Backsplash Prices Without Regret</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>kitchen prices</t>
+          <t>backsplash prices</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>24</v>
+        <v>140</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>What a Kitchen Installation Estimate Should Include</t>
+          <t>Financing a Kitchen Remodel: Options Weighed Honestly</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>kitchen installation cost estimate</t>
+          <t>kitchen remodel financing</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="H20" s="6" t="n">
         <v>30</v>
@@ -1311,22 +1311,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>How to Set a Kitchen Remodel Budget You Won't Blow Through</t>
+          <t>Peel-and-Stick Backsplash: Quick Fix or False Economy?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>kitchen remodel budget</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>Cost &amp; Budget</t>
+          <t>peel and stick backsplash</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1335,10 +1335,10 @@
         </is>
       </c>
       <c r="G21" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="H21" s="6" t="n">
-        <v>38</v>
+        <v>33100</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="22">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Kitchen and Laundry Room Combos: Designing the Two as One Project</t>
+          <t>Should Your Kitchen Have an Island? A Layout Guide</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>kitchen and laundry room remodel</t>
+          <t>kitchen island</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1373,10 +1373,10 @@
         </is>
       </c>
       <c r="G22" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="H22" s="4" t="n">
-        <v>24</v>
+        <v>90500</v>
+      </c>
+      <c r="H22" s="8" t="n">
+        <v>52</v>
       </c>
     </row>
     <row r="23">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Kitchen Renovation, Start to Finish: A Homeowner's Overview</t>
+          <t>Kitchen Backsplash Ideas That Pull a Remodel Together</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>kitchen renovation</t>
+          <t>kitchen backsplash ideas</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
@@ -1402,19 +1402,19 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Buyer</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G23" s="3" t="n">
-        <v>232</v>
-      </c>
-      <c r="H23" s="6" t="n">
-        <v>48</v>
+        <v>18100</v>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="24">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Kitchen Design Ideas: Layouts, Light, and Lasting Style</t>
+          <t>Kitchen Island Ideas: Sizing, Seating, and Smart Storage</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>kitchen design ideas</t>
+          <t>kitchen island ideas</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="G24" s="3" t="n">
+        <v>12100</v>
+      </c>
+      <c r="H24" s="6" t="n">
         <v>40</v>
-      </c>
-      <c r="H24" s="6" t="n">
-        <v>38</v>
       </c>
     </row>
     <row r="25">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Kitchen Backsplash Ideas That Pull a Remodel Together</t>
+          <t>Galley Kitchen Ideas: Big Function in a Narrow Footprint</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>kitchen backsplash ideas</t>
+          <t>galley kitchen ideas</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
@@ -1487,10 +1487,10 @@
         </is>
       </c>
       <c r="G25" s="3" t="n">
-        <v>40</v>
+        <v>3600</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Kitchen Flooring Options Ranked for Durability and Looks</t>
+          <t>Open-Concept Kitchens: When Knocking Down a Wall Pays Off</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>kitchen flooring options</t>
+          <t>open concept kitchen</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1525,10 +1525,10 @@
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>40</v>
+        <v>2400</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27">
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Farmhouse Kitchen Ideas That Still Feel Fresh in 2026</t>
+          <t>Kitchen Layout Basics: Work Triangles, Walkways, and Flow</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>farmhouse kitchen ideas</t>
+          <t>kitchen layout</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
@@ -1559,14 +1559,14 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G27" s="3" t="n">
         <v>40</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
     </row>
     <row r="28">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Choosing a Kitchen Faucet: Finishes, Features, and Value</t>
+          <t>Kitchen Lighting Ideas: Layering Task, Ambient, and Accent</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>kitchen faucet ideas</t>
+          <t>kitchen lighting ideas</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Small Kitchen Ideas: Making a Compact Space Feel Open</t>
+          <t>Modern Kitchen Design: Clean Lines Without the Cold Feel</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>small kitchen ideas</t>
+          <t>modern kitchen design</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G29" s="3" t="n">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Two-Tone Kitchen Cabinets: How to Mix Without a Mess</t>
+          <t>Pantry Ideas: Designing Storage That Earns Its Footprint</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>two tone kitchen cabinets</t>
+          <t>pantry ideas</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
@@ -1673,14 +1673,14 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Buyer</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G30" s="3" t="n">
         <v>40</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
     </row>
     <row r="31">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Kitchen Storage Ideas That Use Every Inch</t>
+          <t>Two-Tone Kitchen Cabinets: How to Mix Without a Mess</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>kitchen storage ideas</t>
+          <t>two tone kitchen cabinets</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
@@ -1711,14 +1711,14 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G31" s="3" t="n">
         <v>40</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32">
@@ -1767,22 +1767,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Waterfall Islands: The Statement Feature Worth the Splurge</t>
+          <t>Kitchen Remodel Contractors in Rock Hill, SC</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>waterfall island</t>
-        </is>
-      </c>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>contractor for kitchen remodel rock hill sc</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>Process &amp; Planning</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1791,10 +1791,10 @@
         </is>
       </c>
       <c r="G33" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="H33" s="6" t="n">
-        <v>48</v>
+        <v>10</v>
+      </c>
+      <c r="H33" s="4" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="34">
@@ -1805,22 +1805,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Kitchen Countertops Compared: Quartz, Granite, and the Alternatives</t>
+          <t>Kitchen Renovation Contractors: What to Expect, Day by Day</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>kitchen countertops</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>kitchen renovation contractors</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>Process &amp; Planning</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1829,10 +1829,10 @@
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="H34" s="6" t="n">
-        <v>48</v>
+        <v>2900</v>
+      </c>
+      <c r="H34" s="8" t="n">
+        <v>52</v>
       </c>
     </row>
     <row r="35">
@@ -1843,15 +1843,15 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Kitchen Remodel Contractors in Rock Hill, SC</t>
+          <t>Bathroom and Kitchen Contractors: What Separates Great From Cheap</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>contractor for kitchen remodel rock hill sc</t>
-        </is>
-      </c>
-      <c r="D35" s="8" t="inlineStr">
+          <t>bathroom and kitchen contractors</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
         <is>
           <t>Process &amp; Planning</t>
         </is>
@@ -1867,10 +1867,10 @@
         </is>
       </c>
       <c r="G35" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="H35" s="4" t="n">
-        <v>24</v>
+        <v>390</v>
+      </c>
+      <c r="H35" s="6" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="36">
@@ -1881,34 +1881,34 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Kitchen Remodeler Gastonia: What Separates Great From Cheap</t>
+          <t>DIY Kitchen Furniture: The Process, Demystified</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>kitchen remodeler gastonia</t>
-        </is>
-      </c>
-      <c r="D36" s="8" t="inlineStr">
+          <t>diy kitchen furniture</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
         <is>
           <t>Process &amp; Planning</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Buyer</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="H36" s="6" t="n">
-        <v>38</v>
+        <v>390</v>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="37">
@@ -1919,34 +1919,34 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Kitchen and Bath Remodeling Contractors: What Separates Great From Cheap</t>
+          <t>Tiny Kitchen Plans: Timelines, Trade-offs, and Questions to Ask</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>kitchen and bath remodeling contractors</t>
-        </is>
-      </c>
-      <c r="D37" s="8" t="inlineStr">
+          <t>tiny kitchen plans</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
         <is>
           <t>Process &amp; Planning</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Buyer</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G37" s="3" t="n">
-        <v>10</v>
+        <v>320</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38">
@@ -1957,34 +1957,34 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>How to Compare the Best Kitchen Remodel Contractors</t>
+          <t>Small Kitchen Plans: What Every Remodel Should Know</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>best kitchen remodel contractors</t>
-        </is>
-      </c>
-      <c r="D38" s="8" t="inlineStr">
+          <t>small kitchen plans</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
         <is>
           <t>Process &amp; Planning</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Buyer</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G38" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="H38" s="6" t="n">
-        <v>30</v>
+        <v>170</v>
+      </c>
+      <c r="H38" s="4" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="39">
@@ -1995,34 +1995,34 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Kitchen Remodeler Eastway Park, Done the Fixed-Price Way</t>
+          <t>Open Kitchen Living Room: Timelines, Trade-offs, and Questions to Ask</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>kitchen remodeler eastway park</t>
-        </is>
-      </c>
-      <c r="D39" s="8" t="inlineStr">
+          <t>open kitchen living room</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
         <is>
           <t>Process &amp; Planning</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Buyer</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G39" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="H39" s="6" t="n">
-        <v>30</v>
+        <v>720</v>
+      </c>
+      <c r="H39" s="4" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="40">
@@ -2033,31 +2033,31 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Kitchen Remodeler Contractor: What to Expect, Day by Day</t>
+          <t>The Kitchen Remodel Checklist Every Homeowner Should Use</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>kitchen remodeler contractor</t>
-        </is>
-      </c>
-      <c r="D40" s="8" t="inlineStr">
+          <t>kitchen remodel checklist</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
         <is>
           <t>Process &amp; Planning</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Buyer</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G40" s="3" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="H40" s="6" t="n">
         <v>38</v>
@@ -2071,31 +2071,31 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>The Kitchen Remodel Checklist Every Homeowner Should Use</t>
+          <t>Kitchen Remodeling Timeline: What It Takes, Start to Finish</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>kitchen remodel checklist</t>
-        </is>
-      </c>
-      <c r="D41" s="8" t="inlineStr">
+          <t>kitchen remodeling timeline</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
         <is>
           <t>Process &amp; Planning</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G41" s="3" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="H41" s="6" t="n">
         <v>38</v>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Kitchen Design and Build Charlotte NC: What the Process Looks Like Here</t>
+          <t>Kitchen Design and Build Charlotte NC: A Faster Path to Your Dream Kitchen</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ballantyne Kitchen Remodeling: Premium Results Without the Wait</t>
+          <t>Kitchen Renovation Services Charlotte: What the Process Looks Like Here</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>kitchen remodeling ballantyne</t>
+          <t>kitchen renovation services charlotte</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -2361,10 +2361,10 @@
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="49">
@@ -2375,12 +2375,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Kitchen Remodelers Charlotte NC: A Faster Path to Your Dream Kitchen</t>
+          <t>Kitchen Remodeling South West Charlotte: One Local Crew, Start to Finish</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>kitchen remodelers charlotte nc</t>
+          <t>kitchen remodeling south west charlotte</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -2399,10 +2399,10 @@
         </is>
       </c>
       <c r="G49" s="3" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Approximate Cost of Kitchen Remodel: Budget, Mid-Range, and High-End Compared</t>
+          <t>What Quartz Countertops Cost, Installed</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>approximate cost of kitchen remodel</t>
+          <t>cost of quartz countertops</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
@@ -2513,10 +2513,10 @@
         </is>
       </c>
       <c r="G52" s="3" t="n">
-        <v>10</v>
+        <v>2900</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="53">
@@ -2527,12 +2527,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Average Cost of a Kitchen Remodel 2024: What Drives the Final Price</t>
+          <t>Small Kitchen Remodels: Where the Budget Goes</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>average cost of a kitchen remodel 2024</t>
+          <t>small kitchen remodel price</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
@@ -2547,14 +2547,14 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Buyer</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G53" s="3" t="n">
-        <v>10</v>
+        <v>480</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="54">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Average Cost of Large Kitchen Remodel: Where Most Homeowners Get It Wrong</t>
+          <t>How Much Space to Leave Between Counter and Island</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>average cost of large kitchen remodel</t>
+          <t>how much space between counter and island</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
@@ -2585,14 +2585,14 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Buyer</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G54" s="3" t="n">
-        <v>10</v>
+        <v>320</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="55">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Kitchen Remodeling Cost: Where the Money Goes, and Where to Save</t>
+          <t>Cheap Backsplash Options: What to Know Before You Commit</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>kitchen remodeling cost</t>
+          <t>cheap backsplash options</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
@@ -2623,14 +2623,14 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Buyer</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G55" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="H55" s="6" t="n">
-        <v>38</v>
+        <v>260</v>
+      </c>
+      <c r="H55" s="4" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="56">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Comparing Kitchen Remodel Quotes: A Side-by-Side Guide</t>
+          <t>Laminate Countertops: The Budget-Friendly Counter Option</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>compare kitchen prices</t>
+          <t>laminate countertop cost</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
@@ -2665,10 +2665,10 @@
         </is>
       </c>
       <c r="G56" s="3" t="n">
-        <v>15</v>
+        <v>880</v>
       </c>
       <c r="H56" s="6" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="57">
@@ -2679,12 +2679,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Financing a Kitchen Remodel: Options Weighed Honestly</t>
+          <t>A Kitchen Makeover on a Budget: What's Realistic</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>kitchen remodel financing</t>
+          <t>kitchen makeover on a budget</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
@@ -2699,14 +2699,14 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Buyer</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G57" s="3" t="n">
-        <v>10</v>
+        <v>390</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="58">
@@ -2717,22 +2717,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>What Full-Service Kitchen Remodeling Actually Covers</t>
+          <t>Small Kitchen Remodels on a Budget: What to Budget Before You Start</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>kitchen remodeling services</t>
-        </is>
-      </c>
-      <c r="D58" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>small kitchen remodels on a budget</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>Cost &amp; Budget</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="G58" s="3" t="n">
-        <v>38</v>
-      </c>
-      <c r="H58" s="6" t="n">
-        <v>38</v>
+        <v>260</v>
+      </c>
+      <c r="H58" s="4" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="59">
@@ -2755,17 +2755,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Choosing Kitchen Cabinets: Styles, Finishes, and What Lasts</t>
+          <t>Kitchen Renovation Cost: A Room-by-Room Money Map</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>kitchen cabinets</t>
-        </is>
-      </c>
-      <c r="D59" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>kitchen renovation cost</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>Cost &amp; Budget</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2782,7 +2782,7 @@
         <v>10</v>
       </c>
       <c r="H59" s="6" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="60">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Kitchen Cabinet Installation: How It's Done Right</t>
+          <t>Cabinet Refacing in Charlotte, NC: When It Makes Sense</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>kitchen cabinet installation</t>
+          <t>cabinet refacing charlotte nc</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2817,10 +2817,10 @@
         </is>
       </c>
       <c r="G60" s="3" t="n">
-        <v>96</v>
-      </c>
-      <c r="H60" s="6" t="n">
-        <v>38</v>
+        <v>102</v>
+      </c>
+      <c r="H60" s="4" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="61">
@@ -2831,12 +2831,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Quartz vs Granite Countertops: Which Wins for Your Kitchen</t>
+          <t>Kitchen and Laundry Room Combos: Designing the Two as One Project</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>quartz vs granite</t>
+          <t>kitchen and laundry room remodel</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2857,8 +2857,8 @@
       <c r="G61" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="H61" s="6" t="n">
-        <v>38</v>
+      <c r="H61" s="4" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="62">
@@ -2869,12 +2869,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Kitchen Layout Basics: Work Triangles, Walkways, and Flow</t>
+          <t>Butcher Block Countertops: Warm Looks, Real Trade-offs</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>kitchen layout</t>
+          <t>butcher block countertops</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2893,10 +2893,10 @@
         </is>
       </c>
       <c r="G62" s="3" t="n">
-        <v>40</v>
+        <v>40500</v>
       </c>
       <c r="H62" s="6" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="63">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Kitchen Lighting Ideas: Layering Task, Ambient, and Accent</t>
+          <t>Adding a Scullery to Your Kitchen: The Hidden Prep-Space Trend</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>kitchen lighting ideas</t>
+          <t>kitchen scullery</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
@@ -2927,14 +2927,14 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G63" s="3" t="n">
-        <v>40</v>
+        <v>18100</v>
       </c>
       <c r="H63" s="6" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="64">
@@ -2945,12 +2945,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Modern Kitchen Design: Clean Lines Without the Cold Feel</t>
+          <t>Subway Tile Backsplash: The Timeless Default, Done Right</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>modern kitchen design</t>
+          <t>subway tile backsplash</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="G64" s="3" t="n">
-        <v>40</v>
+        <v>12100</v>
       </c>
       <c r="H64" s="6" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="65">
@@ -2983,12 +2983,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Pantry Ideas: Designing Storage That Earns Its Footprint</t>
+          <t>Kitchen Storage Ideas That Use Every Inch</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>pantry ideas</t>
+          <t>kitchen storage ideas</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
@@ -3007,10 +3007,10 @@
         </is>
       </c>
       <c r="G65" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="H65" s="6" t="n">
-        <v>48</v>
+        <v>2900</v>
+      </c>
+      <c r="H65" s="8" t="n">
+        <v>52</v>
       </c>
     </row>
     <row r="66">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Kitchen Paint Colors That Flatter Cabinets and Counters</t>
+          <t>Kitchen Cabinet Styles: Shaker, Flat-Panel, and Beyond</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>kitchen paint colors</t>
+          <t>kitchen cabinet styles</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
@@ -3045,10 +3045,10 @@
         </is>
       </c>
       <c r="G66" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="H66" s="6" t="n">
-        <v>38</v>
+        <v>2400</v>
+      </c>
+      <c r="H66" s="4" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="67">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Kitchen Appliances: Where to Splurge and Where to Save</t>
+          <t>Kitchen Design Ideas: Layouts, Light, and Lasting Style</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>kitchen appliances</t>
+          <t>kitchen design ideas</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
@@ -3074,19 +3074,19 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Buyer</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G67" s="3" t="n">
         <v>40</v>
       </c>
       <c r="H67" s="6" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
     </row>
     <row r="68">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Adding a Scullery to Your Kitchen: The Hidden Prep-Space Trend</t>
+          <t>Kitchen Cabinet Colors: What's Timeless vs What's Trendy</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>kitchen scullery</t>
+          <t>kitchen cabinet colors</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
@@ -3124,7 +3124,7 @@
         <v>40</v>
       </c>
       <c r="H68" s="6" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
     </row>
     <row r="69">
@@ -3135,12 +3135,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Kitchen and Mudroom Combos: A Smarter Family Entryway</t>
+          <t>Kitchen Trends 2026: Bold Cabinets, Brass, and What to Skip</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>kitchen and mudroom</t>
+          <t>kitchen trends 2026</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Buyer</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G69" s="3" t="n">
@@ -3173,12 +3173,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Galley Kitchen Ideas: Big Function in a Narrow Footprint</t>
+          <t>Kitchen Sink Ideas: Materials, Mounts, and the Right Size</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>galley kitchen ideas</t>
+          <t>kitchen sink ideas</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>White Kitchen Cabinets: Why They Endure, and How to Keep Them Clean</t>
+          <t>Kitchen Paint Colors That Flatter Cabinets and Counters</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>white kitchen cabinets</t>
+          <t>kitchen paint colors</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
@@ -3235,7 +3235,7 @@
         </is>
       </c>
       <c r="G71" s="3" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="H71" s="6" t="n">
         <v>38</v>
@@ -3249,22 +3249,22 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Kitchen Remodeler Rock Hill: Done Right the First Time</t>
+          <t>Kitchen Appliances: Where to Splurge and Where to Save</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>kitchen remodeler rock hill</t>
-        </is>
-      </c>
-      <c r="D72" s="8" t="inlineStr">
-        <is>
-          <t>Process &amp; Planning</t>
+          <t>kitchen appliances</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3273,10 +3273,10 @@
         </is>
       </c>
       <c r="G72" s="3" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="H72" s="6" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
     </row>
     <row r="73">
@@ -3287,22 +3287,22 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Kitchen Remodeler Concord, Done the Fixed-Price Way</t>
+          <t>Kitchen and Mudroom Combos: A Smarter Family Entryway</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>kitchen remodeler concord</t>
-        </is>
-      </c>
-      <c r="D73" s="8" t="inlineStr">
-        <is>
-          <t>Process &amp; Planning</t>
+          <t>kitchen and mudroom</t>
+        </is>
+      </c>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3311,7 +3311,7 @@
         </is>
       </c>
       <c r="G73" s="3" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="H73" s="6" t="n">
         <v>38</v>
@@ -3325,15 +3325,15 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Finding Local Contractors for a Kitchen Remodel</t>
+          <t>Kitchen Contractors: Done Right the First Time</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>local contractors for kitchen remodel</t>
-        </is>
-      </c>
-      <c r="D74" s="8" t="inlineStr">
+          <t>kitchen contractors</t>
+        </is>
+      </c>
+      <c r="D74" s="9" t="inlineStr">
         <is>
           <t>Process &amp; Planning</t>
         </is>
@@ -3349,10 +3349,10 @@
         </is>
       </c>
       <c r="G74" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="H74" s="4" t="n">
-        <v>24</v>
+        <v>2400</v>
+      </c>
+      <c r="H74" s="8" t="n">
+        <v>53</v>
       </c>
     </row>
     <row r="75">
@@ -3363,15 +3363,15 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Choosing a Contractor for Your Kitchen Renovation</t>
+          <t>Local Kitchen Remodelers: The Questions to Ask First</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>contractor for kitchen renovation</t>
-        </is>
-      </c>
-      <c r="D75" s="8" t="inlineStr">
+          <t>local kitchen remodelers</t>
+        </is>
+      </c>
+      <c r="D75" s="9" t="inlineStr">
         <is>
           <t>Process &amp; Planning</t>
         </is>
@@ -3387,10 +3387,10 @@
         </is>
       </c>
       <c r="G75" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="H75" s="6" t="n">
-        <v>30</v>
+        <v>320</v>
+      </c>
+      <c r="H75" s="8" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="76">
@@ -3401,15 +3401,15 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Best Kitchen Remodeler: The Questions to Ask First</t>
+          <t>How to Compare the Best Kitchen Remodel Contractors</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>best kitchen remodeler</t>
-        </is>
-      </c>
-      <c r="D76" s="8" t="inlineStr">
+          <t>best kitchen remodel contractors</t>
+        </is>
+      </c>
+      <c r="D76" s="9" t="inlineStr">
         <is>
           <t>Process &amp; Planning</t>
         </is>
@@ -3428,7 +3428,7 @@
         <v>10</v>
       </c>
       <c r="H76" s="6" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="77">
@@ -3439,15 +3439,15 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>How to Plan a Kitchen Remodel Before Demo Day</t>
+          <t>How to Prepare Your Home for a Kitchen Remodel</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>how to plan a kitchen remodel</t>
-        </is>
-      </c>
-      <c r="D77" s="8" t="inlineStr">
+          <t>how to prepare for a kitchen remodel</t>
+        </is>
+      </c>
+      <c r="D77" s="9" t="inlineStr">
         <is>
           <t>Process &amp; Planning</t>
         </is>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="G77" s="3" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="H77" s="4" t="n">
         <v>24</v>
@@ -3477,15 +3477,15 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>How to Prepare Your Home for a Kitchen Remodel</t>
+          <t>DIY Kitchen Cupboards: A Homeowner's Walkthrough</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>how to prepare for a kitchen remodel</t>
-        </is>
-      </c>
-      <c r="D78" s="8" t="inlineStr">
+          <t>diy kitchen cupboards</t>
+        </is>
+      </c>
+      <c r="D78" s="9" t="inlineStr">
         <is>
           <t>Process &amp; Planning</t>
         </is>
@@ -3501,10 +3501,10 @@
         </is>
       </c>
       <c r="G78" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="H78" s="4" t="n">
-        <v>24</v>
+        <v>880</v>
+      </c>
+      <c r="H78" s="6" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="79">
@@ -3515,34 +3515,34 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Kitchen Demolition: What Tear-Out Day Actually Involves</t>
+          <t>Galley Kitchen Plans: How to Pick the Right Pro</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>kitchen demolition</t>
-        </is>
-      </c>
-      <c r="D79" s="8" t="inlineStr">
+          <t>galley kitchen plans</t>
+        </is>
+      </c>
+      <c r="D79" s="9" t="inlineStr">
         <is>
           <t>Process &amp; Planning</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Buyer</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G79" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="H79" s="6" t="n">
-        <v>48</v>
+        <v>720</v>
+      </c>
+      <c r="H79" s="4" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="80">
@@ -3553,22 +3553,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Kitchen Remodeling Timeline: Timelines, Trade-offs, and Questions to Ask</t>
+          <t>Kitchen Demolition: What Tear-Out Day Actually Involves</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>kitchen remodeling timeline</t>
-        </is>
-      </c>
-      <c r="D80" s="8" t="inlineStr">
+          <t>kitchen demolition</t>
+        </is>
+      </c>
+      <c r="D80" s="9" t="inlineStr">
         <is>
           <t>Process &amp; Planning</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3577,10 +3577,10 @@
         </is>
       </c>
       <c r="G80" s="3" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="H80" s="6" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
     </row>
     <row r="81">
@@ -3599,7 +3599,7 @@
           <t>order of kitchen remodel</t>
         </is>
       </c>
-      <c r="D81" s="8" t="inlineStr">
+      <c r="D81" s="9" t="inlineStr">
         <is>
           <t>Process &amp; Planning</t>
         </is>
@@ -3819,12 +3819,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Kitchen Remodeling Companies Charlotte: Fixed Pricing, Finished in 7 Days</t>
+          <t>Kitchen Remodeling Services Charlotte: Fixed Pricing, Finished in 7 Days</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>kitchen remodeling companies charlotte</t>
+          <t>kitchen remodeling services charlotte</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -3843,10 +3843,10 @@
         </is>
       </c>
       <c r="G87" s="3" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H87" s="4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="88">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Kitchen and Bath Remodeling in Charlotte, NC: One Crew, One Timeline</t>
+          <t>Ballantyne Kitchen Remodeling: Premium Results Without the Wait</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>kitchen and bath remodeling charlotte nc</t>
+          <t>kitchen remodeling ballantyne</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -3998,7 +3998,7 @@
         <v>10</v>
       </c>
       <c r="H91" s="4" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="92">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Average Cost of a Complete Kitchen Remodel: Where the Money Goes, and Where to Save</t>
+          <t>What Granite Countertops Cost, Installed</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>average cost of a complete kitchen remodel</t>
+          <t>cost of granite countertops</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
@@ -4029,14 +4029,14 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Buyer</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G92" s="3" t="n">
-        <v>10</v>
+        <v>2900</v>
       </c>
       <c r="H92" s="4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="93">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Average Cost of a New Kitchen Remodel: The Numbers Behind the Choice</t>
+          <t>What a Small Kitchen Remodel Really Costs</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>average cost of a new kitchen remodel</t>
+          <t>average cost of small kitchen remodel</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
@@ -4067,11 +4067,11 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Buyer</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G93" s="3" t="n">
-        <v>10</v>
+        <v>390</v>
       </c>
       <c r="H93" s="4" t="n">
         <v>24</v>
@@ -4085,12 +4085,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Average Cost of Redoing a Kitchen: A 2026 Buyer's Guide</t>
+          <t>How Much for a Small Kitchen Renovation: What to Weigh First</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>average cost of redoing a kitchen</t>
+          <t>how much for a small kitchen renovation</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
@@ -4105,14 +4105,14 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Buyer</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G94" s="3" t="n">
-        <v>10</v>
+        <v>260</v>
       </c>
       <c r="H94" s="4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="95">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Affordable Kitchen Remodels: Where to Save Without Regret</t>
+          <t>Inexpensive Kitchen Renovations: A Straight Comparison for Homeowners</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>affordable kitchen remodel</t>
+          <t>inexpensive kitchen renovations</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
@@ -4143,14 +4143,14 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Buyer</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G95" s="3" t="n">
-        <v>63</v>
+        <v>1900</v>
       </c>
       <c r="H95" s="6" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="96">
@@ -4161,12 +4161,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>What Drives Your Kitchen Remodel Price: A Cost-Factor Guide</t>
+          <t>Cheap Backsplash Ideas: A Plain-English Cost Primer</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>kitchen remodel price</t>
+          <t>cheap backsplash ideas</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
@@ -4176,7 +4176,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -4185,10 +4185,10 @@
         </is>
       </c>
       <c r="G96" s="3" t="n">
-        <v>40</v>
+        <v>880</v>
       </c>
       <c r="H96" s="6" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="97">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>What a Free Kitchen Remodel Estimate Should Tell You</t>
+          <t>How Much Are Kitchen Cupboards: Budget, Mid-Range, and High-End</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>free kitchen remodel estimate</t>
+          <t>how much are kitchen cupboards</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
@@ -4219,14 +4219,14 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Buyer</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G97" s="3" t="n">
-        <v>30</v>
+        <v>720</v>
       </c>
       <c r="H97" s="6" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="98">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>What a Brand-New Kitchen Costs vs a Remodel</t>
+          <t>Cost of New Kitchen: What Sets the Final Number</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>new kitchen prices</t>
+          <t>cost of new kitchen</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
@@ -4257,14 +4257,14 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Buyer</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G98" s="3" t="n">
-        <v>15</v>
+        <v>390</v>
       </c>
       <c r="H98" s="6" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
     </row>
     <row r="99">
@@ -4275,17 +4275,17 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Kitchen Renovation Cost: A Room-by-Room Money Map</t>
+          <t>Choosing Kitchen Cabinets: Styles, Finishes, and What Lasts</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>kitchen renovation cost</t>
-        </is>
-      </c>
-      <c r="D99" s="5" t="inlineStr">
-        <is>
-          <t>Cost &amp; Budget</t>
+          <t>kitchen cabinets</t>
+        </is>
+      </c>
+      <c r="D99" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -4299,10 +4299,10 @@
         </is>
       </c>
       <c r="G99" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="H99" s="6" t="n">
-        <v>30</v>
+        <v>165000</v>
+      </c>
+      <c r="H99" s="8" t="n">
+        <v>55</v>
       </c>
     </row>
     <row r="100">
@@ -4313,12 +4313,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Cabinet Refacing in Charlotte, NC: When It Makes Sense</t>
+          <t>Quartz Countertops: Why They Dominate Modern Kitchens</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>cabinet refacing charlotte nc</t>
+          <t>quartz countertops</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
@@ -4328,7 +4328,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -4337,10 +4337,10 @@
         </is>
       </c>
       <c r="G100" s="3" t="n">
-        <v>102</v>
+        <v>90500</v>
       </c>
       <c r="H100" s="4" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
     </row>
     <row r="101">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Kitchen Remodel Before and After: What a Week Can Change</t>
+          <t>Kitchen Countertops Compared: Quartz, Granite, and the Alternatives</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>kitchen remodel before and after</t>
+          <t>kitchen countertops</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
@@ -4366,19 +4366,19 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G101" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="H101" s="4" t="n">
-        <v>24</v>
+        <v>33100</v>
+      </c>
+      <c r="H101" s="6" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="102">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Kitchen Remodeling 101: What the Project Really Involves</t>
+          <t>Small Kitchen Ideas: Making a Compact Space Feel Open</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>kitchen remodeling</t>
+          <t>small kitchen ideas</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
@@ -4404,19 +4404,19 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Buyer</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G102" s="3" t="n">
-        <v>374</v>
+        <v>14800</v>
       </c>
       <c r="H102" s="6" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
     </row>
     <row r="103">
@@ -4427,12 +4427,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Kitchen Island Ideas: Sizing, Seating, and Smart Storage</t>
+          <t>Kitchen Gadgets: What Designers Pick and Why</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>kitchen island ideas</t>
+          <t>kitchen gadgets</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
@@ -4442,19 +4442,19 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G103" s="3" t="n">
-        <v>40</v>
+        <v>9900</v>
       </c>
       <c r="H103" s="6" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="104">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Kitchen Cabinet Colors: What's Timeless vs What's Trendy</t>
+          <t>Waterfall Islands: The Statement Feature Worth the Splurge</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>kitchen cabinet colors</t>
+          <t>waterfall island</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
@@ -4489,10 +4489,10 @@
         </is>
       </c>
       <c r="G104" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="H104" s="6" t="n">
-        <v>38</v>
+        <v>2900</v>
+      </c>
+      <c r="H104" s="4" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="105">
@@ -4503,12 +4503,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Kitchen Trends 2026: Bold Cabinets, Brass, and What to Skip</t>
+          <t>Kitchen Remodel Before and After: What a Week Can Change</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>kitchen trends 2026</t>
+          <t>kitchen remodel before and after</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
@@ -4527,10 +4527,10 @@
         </is>
       </c>
       <c r="G105" s="3" t="n">
-        <v>40</v>
+        <v>590</v>
       </c>
       <c r="H105" s="6" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="106">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Kitchen Sink Ideas: Materials, Mounts, and the Right Size</t>
+          <t>Quartz vs Granite Countertops: Which Wins for Your Kitchen</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>kitchen sink ideas</t>
+          <t>quartz vs granite</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G106" s="3" t="n">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Open-Concept Kitchens: When Knocking Down a Wall Pays Off</t>
+          <t>Kitchen Flooring Options Ranked for Durability and Looks</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>open concept kitchen</t>
+          <t>kitchen flooring options</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4617,12 +4617,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Cabinet Hardware: The Small Detail That Sets the Tone</t>
+          <t>Farmhouse Kitchen Ideas That Still Feel Fresh in 2026</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>cabinet hardware ideas</t>
+          <t>farmhouse kitchen ideas</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Butcher Block Countertops: Warm Looks, Real Trade-offs</t>
+          <t>Choosing a Kitchen Faucet: Finishes, Features, and Value</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>butcher block countertops</t>
+          <t>kitchen faucet ideas</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Buyer</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G109" s="3" t="n">
@@ -4693,12 +4693,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Butler's Pantry Ideas: A Kitchen Upgrade That Adds Real Value</t>
+          <t>Cabinet Hardware: The Small Detail That Sets the Tone</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>butler pantry ideas</t>
+          <t>cabinet hardware ideas</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
@@ -4731,12 +4731,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Kitchen Cabinet Styles: Shaker, Flat-Panel, and Beyond</t>
+          <t>Butler's Pantry Ideas: A Kitchen Upgrade That Adds Real Value</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>kitchen cabinet styles</t>
+          <t>butler pantry ideas</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr">
@@ -4751,7 +4751,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Buyer</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G111" s="3" t="n">
@@ -4769,12 +4769,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Quartz Countertops: Why They Dominate Modern Kitchens</t>
+          <t>White Kitchen Cabinets: Why They Endure, and How to Keep Them Clean</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>quartz countertops</t>
+          <t>white kitchen cabinets</t>
         </is>
       </c>
       <c r="D112" s="7" t="inlineStr">
@@ -4784,7 +4784,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4796,7 +4796,7 @@
         <v>10</v>
       </c>
       <c r="H112" s="6" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
     </row>
     <row r="113">
@@ -4807,15 +4807,15 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Kitchen Remodeler Davidson: A No-Nonsense Buyer's Guide</t>
+          <t>Finding Local Contractors for a Kitchen Remodel</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>kitchen remodeler davidson</t>
-        </is>
-      </c>
-      <c r="D113" s="8" t="inlineStr">
+          <t>local contractors for kitchen remodel</t>
+        </is>
+      </c>
+      <c r="D113" s="9" t="inlineStr">
         <is>
           <t>Process &amp; Planning</t>
         </is>
@@ -4833,8 +4833,8 @@
       <c r="G113" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="H113" s="6" t="n">
-        <v>38</v>
+      <c r="H113" s="4" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="114">
@@ -4845,15 +4845,15 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>What Separates a Great Kitchen Remodeler From the Rest</t>
+          <t>Kitchen Bath Contractor: A No-Nonsense Buyer's Guide</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>kitchen remodeler</t>
-        </is>
-      </c>
-      <c r="D114" s="8" t="inlineStr">
+          <t>kitchen bath contractor</t>
+        </is>
+      </c>
+      <c r="D114" s="9" t="inlineStr">
         <is>
           <t>Process &amp; Planning</t>
         </is>
@@ -4869,10 +4869,10 @@
         </is>
       </c>
       <c r="G114" s="3" t="n">
-        <v>151</v>
+        <v>480</v>
       </c>
       <c r="H114" s="6" t="n">
-        <v>48</v>
+        <v>39</v>
       </c>
     </row>
     <row r="115">
@@ -4883,15 +4883,15 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>What a Kitchen Contractor Handles on a Remodel</t>
+          <t>What Separates a Great Kitchen Remodeler From the Rest</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>kitchen contractor</t>
-        </is>
-      </c>
-      <c r="D115" s="8" t="inlineStr">
+          <t>kitchen remodeler</t>
+        </is>
+      </c>
+      <c r="D115" s="9" t="inlineStr">
         <is>
           <t>Process &amp; Planning</t>
         </is>
@@ -4907,7 +4907,7 @@
         </is>
       </c>
       <c r="G115" s="3" t="n">
-        <v>36</v>
+        <v>151</v>
       </c>
       <c r="H115" s="6" t="n">
         <v>48</v>
@@ -4921,34 +4921,34 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>A Homeowner's Guide to Kitchen Remodeler East Shoreham</t>
+          <t>Kitchen Cupboard Plans: What It Takes, Start to Finish</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>kitchen remodeler east shoreham</t>
-        </is>
-      </c>
-      <c r="D116" s="8" t="inlineStr">
+          <t>kitchen cupboard plans</t>
+        </is>
+      </c>
+      <c r="D116" s="9" t="inlineStr">
         <is>
           <t>Process &amp; Planning</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Buyer</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G116" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="H116" s="6" t="n">
-        <v>30</v>
+        <v>320</v>
+      </c>
+      <c r="H116" s="4" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="117">
@@ -4959,34 +4959,34 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Kitchen Addition Contractors: What to Know Before You Commit</t>
+          <t>How to Plan a Kitchen Remodel Before Demo Day</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>kitchen addition contractors</t>
-        </is>
-      </c>
-      <c r="D117" s="8" t="inlineStr">
+          <t>how to plan a kitchen remodel</t>
+        </is>
+      </c>
+      <c r="D117" s="9" t="inlineStr">
         <is>
           <t>Process &amp; Planning</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Buyer</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G117" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="H117" s="6" t="n">
-        <v>38</v>
+        <v>40</v>
+      </c>
+      <c r="H117" s="4" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="118">
@@ -4997,15 +4997,15 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Kitchen Remodel Order of Steps: Timelines, Trade-offs, and Questions to Ask</t>
+          <t>Open Kitchen Plans: How to Pick the Right Pro</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>kitchen remodel order of steps</t>
-        </is>
-      </c>
-      <c r="D118" s="8" t="inlineStr">
+          <t>open kitchen plans</t>
+        </is>
+      </c>
+      <c r="D118" s="9" t="inlineStr">
         <is>
           <t>Process &amp; Planning</t>
         </is>
@@ -5017,14 +5017,14 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Buyer</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G118" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="H118" s="4" t="n">
-        <v>24</v>
+        <v>260</v>
+      </c>
+      <c r="H118" s="6" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="119">
@@ -5043,7 +5043,7 @@
           <t>kitchen remodel permits</t>
         </is>
       </c>
-      <c r="D119" s="8" t="inlineStr">
+      <c r="D119" s="9" t="inlineStr">
         <is>
           <t>Process &amp; Planning</t>
         </is>
@@ -5081,7 +5081,7 @@
           <t>kitchen remodel contractor questions</t>
         </is>
       </c>
-      <c r="D120" s="8" t="inlineStr">
+      <c r="D120" s="9" t="inlineStr">
         <is>
           <t>Process &amp; Planning</t>
         </is>
@@ -5119,7 +5119,7 @@
           <t>kitchen renovation timeline</t>
         </is>
       </c>
-      <c r="D121" s="8" t="inlineStr">
+      <c r="D121" s="9" t="inlineStr">
         <is>
           <t>Process &amp; Planning</t>
         </is>
@@ -5152,7 +5152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5214,7 +5214,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -5245,7 +5245,7 @@
           <t>Buyer</t>
         </is>
       </c>
-      <c r="H2" s="10" t="inlineStr">
+      <c r="H2" s="11" t="inlineStr">
         <is>
           <t>Have — expand</t>
         </is>
@@ -5257,7 +5257,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -5280,7 +5280,7 @@
       <c r="E3" s="3" t="n">
         <v>22200</v>
       </c>
-      <c r="F3" s="11" t="n">
+      <c r="F3" s="8" t="n">
         <v>65</v>
       </c>
       <c r="G3" t="inlineStr">
@@ -5288,7 +5288,7 @@
           <t>Buyer</t>
         </is>
       </c>
-      <c r="H3" s="10" t="inlineStr">
+      <c r="H3" s="11" t="inlineStr">
         <is>
           <t>Have — expand</t>
         </is>
@@ -5300,7 +5300,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -5343,7 +5343,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -5386,7 +5386,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -5429,7 +5429,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -5472,7 +5472,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -5503,7 +5503,7 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="H8" s="10" t="inlineStr">
+      <c r="H8" s="11" t="inlineStr">
         <is>
           <t>Have</t>
         </is>
@@ -5515,7 +5515,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -5548,7 +5548,7 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="H9" s="10" t="inlineStr">
+      <c r="H9" s="11" t="inlineStr">
         <is>
           <t>Have</t>
         </is>
@@ -5560,7 +5560,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -5591,7 +5591,7 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="H10" s="10" t="inlineStr">
+      <c r="H10" s="11" t="inlineStr">
         <is>
           <t>Have — optimize</t>
         </is>
@@ -5626,7 +5626,7 @@
       <c r="E11" s="3" t="n">
         <v>9900</v>
       </c>
-      <c r="F11" s="11" t="n">
+      <c r="F11" s="8" t="n">
         <v>50</v>
       </c>
       <c r="G11" t="inlineStr">
@@ -5798,7 +5798,7 @@
       <c r="E15" s="3" t="n">
         <v>8100</v>
       </c>
-      <c r="F15" s="11" t="n">
+      <c r="F15" s="8" t="n">
         <v>54</v>
       </c>
       <c r="G15" t="inlineStr">
@@ -5894,7 +5894,7 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="H17" s="10" t="inlineStr">
+      <c r="H17" s="11" t="inlineStr">
         <is>
           <t>Have — optimize</t>
         </is>
@@ -5939,7 +5939,7 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="H18" s="10" t="inlineStr">
+      <c r="H18" s="11" t="inlineStr">
         <is>
           <t>Have — optimize</t>
         </is>
@@ -6064,7 +6064,7 @@
       <c r="E21" s="3" t="n">
         <v>1600</v>
       </c>
-      <c r="F21" s="11" t="n">
+      <c r="F21" s="8" t="n">
         <v>58</v>
       </c>
       <c r="G21" t="inlineStr">
@@ -6084,9 +6084,9 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="14" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -6096,19 +6096,19 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Kitchen Countertops</t>
+          <t>Quartz Countertops</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>kitchen countertops</t>
+          <t>quartz countertops</t>
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>40500</v>
-      </c>
-      <c r="F22" s="11" t="n">
-        <v>58</v>
+        <v>90500</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>28</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -6122,14 +6122,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Massive demand; feature-as-service that funnels to full remodels.</t>
+          <t>EASY WIN (KD 28) on the #1 countertop material. The real countertop money page.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="14" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6139,19 +6139,19 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kitchen Islands</t>
+          <t>Granite Countertops</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>kitchen island</t>
+          <t>granite countertops</t>
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>90500</v>
-      </c>
-      <c r="F23" s="11" t="n">
-        <v>61</v>
+        <v>60500</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>36</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -6165,7 +6165,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Highest demand of all (90.5K); high KD. Feature page funneling to remodels.</t>
+          <t>Winnable (KD 36). Pair with quartz under a Countertops hub page.</t>
         </is>
       </c>
     </row>
@@ -6182,19 +6182,19 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Kitchen Backsplash</t>
+          <t>Kitchen Islands</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>kitchen backsplash</t>
+          <t>kitchen island</t>
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>27100</v>
-      </c>
-      <c r="F24" s="6" t="n">
-        <v>44</v>
+        <v>90500</v>
+      </c>
+      <c r="F24" s="8" t="n">
+        <v>61</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>High-demand feature page.</t>
+          <t>Highest demand of all (90.5K); high KD. Feature page funneling to remodels.</t>
         </is>
       </c>
     </row>
@@ -6220,42 +6220,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Service Area</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Weddington, NC</t>
+          <t>Kitchen Backsplash</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>kitchen remodeling weddington nc</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="F25" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
+          <t>kitchen backsplash ideas</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>18100</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>28</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="H25" s="10" t="inlineStr">
-        <is>
-          <t>Have — optimize</t>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>New</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Page EXISTS.</t>
+          <t>Retarget to 'backsplash ideas' (KD 28) over generic 'kitchen backsplash' (KD 44).</t>
         </is>
       </c>
     </row>
@@ -6272,16 +6268,18 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Fort Mill, SC</t>
+          <t>Weddington, NC</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>kitchen remodeling fort mill sc</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>10</v>
+          <t>kitchen remodeling weddington nc</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
       </c>
       <c r="F26" s="12" t="inlineStr">
         <is>
@@ -6293,14 +6291,14 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="H26" s="10" t="inlineStr">
+      <c r="H26" s="11" t="inlineStr">
         <is>
           <t>Have — optimize</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Page EXISTS. SC side of the metro.</t>
+          <t>Page EXISTS.</t>
         </is>
       </c>
     </row>
@@ -6317,35 +6315,80 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
+          <t>Fort Mill, SC</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>kitchen remodeling fort mill sc</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F27" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="H27" s="11" t="inlineStr">
+        <is>
+          <t>Have — optimize</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Page EXISTS. SC side of the metro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="14" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Service Area</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
           <t>Huntersville / Mooresville / Belmont / +18 more</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>kitchen remodeling &lt;suburb&gt; nc</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="F27" s="12" t="inlineStr">
+      <c r="F28" s="12" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="H27" s="10" t="inlineStr">
+      <c r="H28" s="11" t="inlineStr">
         <is>
           <t>Have — optimize</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>26 suburb pages EXIST total. The work is RANKING them via linked content, not building new ones.</t>
         </is>
@@ -6504,7 +6547,7 @@
       <c r="F4" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -6537,9 +6580,9 @@
       <c r="F5" s="6" t="n">
         <v>48</v>
       </c>
-      <c r="G5" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -6636,7 +6679,7 @@
       <c r="F8" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="G8" s="11" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -6669,7 +6712,7 @@
       <c r="F9" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="G9" s="10" t="inlineStr">
+      <c r="G9" s="11" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -6966,7 +7009,7 @@
       <c r="F18" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="G18" s="10" t="inlineStr">
+      <c r="G18" s="11" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -7032,7 +7075,7 @@
       <c r="F20" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="G20" s="10" t="inlineStr">
+      <c r="G20" s="11" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -7044,7 +7087,7 @@
           <t>kitchen remodeler</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
         <is>
           <t>Process &amp; Planning</t>
         </is>
@@ -7065,7 +7108,7 @@
       <c r="F21" s="6" t="n">
         <v>48</v>
       </c>
-      <c r="G21" s="10" t="inlineStr">
+      <c r="G21" s="11" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -7077,7 +7120,7 @@
           <t>kitchen remodel timeline</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B22" s="9" t="inlineStr">
         <is>
           <t>Process &amp; Planning</t>
         </is>
@@ -7197,7 +7240,7 @@
       <c r="F25" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="G25" s="10" t="inlineStr">
+      <c r="G25" s="11" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -7230,9 +7273,9 @@
       <c r="F26" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="G26" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -7362,7 +7405,7 @@
       <c r="F30" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="G30" s="10" t="inlineStr">
+      <c r="G30" s="11" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -7428,7 +7471,7 @@
       <c r="F32" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="G32" s="10" t="inlineStr">
+      <c r="G32" s="11" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -7560,7 +7603,7 @@
       <c r="F36" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="G36" s="10" t="inlineStr">
+      <c r="G36" s="11" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -7626,9 +7669,9 @@
       <c r="F38" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="G38" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -7659,7 +7702,7 @@
       <c r="F39" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="G39" s="10" t="inlineStr">
+      <c r="G39" s="11" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -7692,9 +7735,9 @@
       <c r="F40" s="6" t="n">
         <v>48</v>
       </c>
-      <c r="G40" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -7704,7 +7747,7 @@
           <t>how long does a kitchen remodel take</t>
         </is>
       </c>
-      <c r="B41" s="8" t="inlineStr">
+      <c r="B41" s="9" t="inlineStr">
         <is>
           <t>Process &amp; Planning</t>
         </is>
@@ -7758,7 +7801,7 @@
       <c r="F42" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="G42" s="10" t="inlineStr">
+      <c r="G42" s="11" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -7791,9 +7834,9 @@
       <c r="F43" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G43" s="11" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -7989,7 +8032,7 @@
       <c r="F49" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="G49" s="10" t="inlineStr">
+      <c r="G49" s="11" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -8055,7 +8098,7 @@
       <c r="F51" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="G51" s="10" t="inlineStr">
+      <c r="G51" s="11" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -8385,7 +8428,7 @@
       <c r="F61" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="G61" s="10" t="inlineStr">
+      <c r="G61" s="11" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -8418,7 +8461,7 @@
       <c r="F62" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="G62" s="10" t="inlineStr">
+      <c r="G62" s="11" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -8484,9 +8527,9 @@
       <c r="F64" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="G64" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -8517,9 +8560,9 @@
       <c r="F65" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="G65" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -8562,7 +8605,7 @@
           <t>how long does a kitchen renovation take</t>
         </is>
       </c>
-      <c r="B67" s="8" t="inlineStr">
+      <c r="B67" s="9" t="inlineStr">
         <is>
           <t>Process &amp; Planning</t>
         </is>
@@ -8616,9 +8659,9 @@
       <c r="F68" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="G68" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -8628,7 +8671,7 @@
           <t>kitchen contractor</t>
         </is>
       </c>
-      <c r="B69" s="8" t="inlineStr">
+      <c r="B69" s="9" t="inlineStr">
         <is>
           <t>Process &amp; Planning</t>
         </is>
@@ -8649,9 +8692,9 @@
       <c r="F69" s="6" t="n">
         <v>48</v>
       </c>
-      <c r="G69" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -8694,7 +8737,7 @@
           <t>kitchen remodel process</t>
         </is>
       </c>
-      <c r="B71" s="8" t="inlineStr">
+      <c r="B71" s="9" t="inlineStr">
         <is>
           <t>Process &amp; Planning</t>
         </is>
@@ -8814,9 +8857,9 @@
       <c r="F74" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="G74" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -8979,9 +9022,9 @@
       <c r="F79" s="6" t="n">
         <v>48</v>
       </c>
-      <c r="G79" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -9111,7 +9154,7 @@
       <c r="F83" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="G83" s="10" t="inlineStr">
+      <c r="G83" s="11" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -9123,7 +9166,7 @@
           <t>kitchen renovation timeline</t>
         </is>
       </c>
-      <c r="B84" s="8" t="inlineStr">
+      <c r="B84" s="9" t="inlineStr">
         <is>
           <t>Process &amp; Planning</t>
         </is>
@@ -9144,7 +9187,7 @@
       <c r="F84" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="G84" s="10" t="inlineStr">
+      <c r="G84" s="11" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -9156,7 +9199,7 @@
           <t>kitchen remodeling contractor</t>
         </is>
       </c>
-      <c r="B85" s="8" t="inlineStr">
+      <c r="B85" s="9" t="inlineStr">
         <is>
           <t>Process &amp; Planning</t>
         </is>
@@ -9210,7 +9253,7 @@
       <c r="F86" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="G86" s="10" t="inlineStr">
+      <c r="G86" s="11" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -9243,7 +9286,7 @@
       <c r="F87" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="G87" s="10" t="inlineStr">
+      <c r="G87" s="11" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -9474,9 +9517,9 @@
       <c r="F94" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="G94" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -9540,7 +9583,7 @@
       <c r="F96" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="G96" s="10" t="inlineStr">
+      <c r="G96" s="11" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -9552,7 +9595,7 @@
           <t>kitchen remodel order of steps</t>
         </is>
       </c>
-      <c r="B97" s="8" t="inlineStr">
+      <c r="B97" s="9" t="inlineStr">
         <is>
           <t>Process &amp; Planning</t>
         </is>
@@ -9573,9 +9616,9 @@
       <c r="F97" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="G97" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -9684,7 +9727,7 @@
           <t>how long for a kitchen remodel</t>
         </is>
       </c>
-      <c r="B101" s="8" t="inlineStr">
+      <c r="B101" s="9" t="inlineStr">
         <is>
           <t>Process &amp; Planning</t>
         </is>
@@ -9738,7 +9781,7 @@
       <c r="F102" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="G102" s="10" t="inlineStr">
+      <c r="G102" s="11" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -10068,9 +10111,9 @@
       <c r="F112" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="G112" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -10101,7 +10144,7 @@
       <c r="F113" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="G113" s="10" t="inlineStr">
+      <c r="G113" s="11" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -10200,7 +10243,7 @@
       <c r="F116" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="G116" s="10" t="inlineStr">
+      <c r="G116" s="11" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -10233,9 +10276,9 @@
       <c r="F117" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="G117" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -10365,9 +10408,9 @@
       <c r="F121" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="G121" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -10971,7 +11014,7 @@
           <t>remodeler</t>
         </is>
       </c>
-      <c r="B140" s="8" t="inlineStr">
+      <c r="B140" s="9" t="inlineStr">
         <is>
           <t>Process &amp; Planning</t>
         </is>
@@ -11103,7 +11146,7 @@
           <t>kitchen remodel timeline denver</t>
         </is>
       </c>
-      <c r="B144" s="8" t="inlineStr">
+      <c r="B144" s="9" t="inlineStr">
         <is>
           <t>Process &amp; Planning</t>
         </is>
@@ -11136,7 +11179,7 @@
           <t>kitchen remodeler davidson</t>
         </is>
       </c>
-      <c r="B145" s="8" t="inlineStr">
+      <c r="B145" s="9" t="inlineStr">
         <is>
           <t>Process &amp; Planning</t>
         </is>
@@ -11157,9 +11200,9 @@
       <c r="F145" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="G145" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -11400,7 +11443,7 @@
           <t>kitchen remodeler gastonia</t>
         </is>
       </c>
-      <c r="B153" s="8" t="inlineStr">
+      <c r="B153" s="9" t="inlineStr">
         <is>
           <t>Process &amp; Planning</t>
         </is>
@@ -11421,9 +11464,9 @@
       <c r="F153" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="G153" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -14061,9 +14104,9 @@
       <c r="F233" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="G233" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -14193,9 +14236,9 @@
       <c r="F237" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="G237" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -14226,9 +14269,9 @@
       <c r="F238" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="G238" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -14259,9 +14302,9 @@
       <c r="F239" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="G239" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -14292,9 +14335,9 @@
       <c r="F240" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="G240" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -14325,9 +14368,9 @@
       <c r="F241" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="G241" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -14457,9 +14500,9 @@
       <c r="F245" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="G245" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -14490,9 +14533,9 @@
       <c r="F246" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="G246" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -14523,9 +14566,9 @@
       <c r="F247" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="G247" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -15393,7 +15436,7 @@
           <t>bathroom contractors</t>
         </is>
       </c>
-      <c r="B274" s="8" t="inlineStr">
+      <c r="B274" s="9" t="inlineStr">
         <is>
           <t>Process &amp; Planning</t>
         </is>
@@ -15855,7 +15898,7 @@
           <t>bathroom remodel contractors</t>
         </is>
       </c>
-      <c r="B288" s="8" t="inlineStr">
+      <c r="B288" s="9" t="inlineStr">
         <is>
           <t>Process &amp; Planning</t>
         </is>
@@ -15921,7 +15964,7 @@
           <t>bathroom remodel general contractor</t>
         </is>
       </c>
-      <c r="B290" s="8" t="inlineStr">
+      <c r="B290" s="9" t="inlineStr">
         <is>
           <t>Process &amp; Planning</t>
         </is>
@@ -16482,7 +16525,7 @@
           <t>bathroom renovation contractors</t>
         </is>
       </c>
-      <c r="B307" s="8" t="inlineStr">
+      <c r="B307" s="9" t="inlineStr">
         <is>
           <t>Process &amp; Planning</t>
         </is>

--- a/decks/7-day-kitchens/keyword-research.xlsx
+++ b/decks/7-day-kitchens/keyword-research.xlsx
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="G13" s="3" t="n">
-        <v>880</v>
+        <v>15</v>
       </c>
       <c r="H13" s="4" t="n">
         <v>4</v>
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="G15" s="3" t="n">
-        <v>1600</v>
+        <v>15</v>
       </c>
       <c r="H15" s="6" t="n">
         <v>44</v>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>880</v>
+        <v>15</v>
       </c>
       <c r="H16" s="4" t="n">
         <v>25</v>
@@ -1335,7 +1335,7 @@
         </is>
       </c>
       <c r="G21" s="3" t="n">
-        <v>33100</v>
+        <v>199</v>
       </c>
       <c r="H21" s="4" t="n">
         <v>23</v>
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="G22" s="3" t="n">
-        <v>90500</v>
+        <v>543</v>
       </c>
       <c r="H22" s="8" t="n">
         <v>52</v>
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="G23" s="3" t="n">
-        <v>18100</v>
+        <v>109</v>
       </c>
       <c r="H23" s="4" t="n">
         <v>28</v>
@@ -1449,7 +1449,7 @@
         </is>
       </c>
       <c r="G24" s="3" t="n">
-        <v>12100</v>
+        <v>73</v>
       </c>
       <c r="H24" s="6" t="n">
         <v>40</v>
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="G25" s="3" t="n">
-        <v>3600</v>
+        <v>22</v>
       </c>
       <c r="H25" s="6" t="n">
         <v>34</v>
@@ -1525,7 +1525,7 @@
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>2400</v>
+        <v>15</v>
       </c>
       <c r="H26" s="6" t="n">
         <v>48</v>
@@ -1829,7 +1829,7 @@
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>2900</v>
+        <v>17</v>
       </c>
       <c r="H34" s="8" t="n">
         <v>52</v>
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="G52" s="3" t="n">
-        <v>2900</v>
+        <v>17</v>
       </c>
       <c r="H52" s="4" t="n">
         <v>21</v>
@@ -2665,7 +2665,7 @@
         </is>
       </c>
       <c r="G56" s="3" t="n">
-        <v>880</v>
+        <v>15</v>
       </c>
       <c r="H56" s="6" t="n">
         <v>34</v>
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="G62" s="3" t="n">
-        <v>40500</v>
+        <v>243</v>
       </c>
       <c r="H62" s="6" t="n">
         <v>44</v>
@@ -2931,7 +2931,7 @@
         </is>
       </c>
       <c r="G63" s="3" t="n">
-        <v>18100</v>
+        <v>109</v>
       </c>
       <c r="H63" s="6" t="n">
         <v>44</v>
@@ -2969,7 +2969,7 @@
         </is>
       </c>
       <c r="G64" s="3" t="n">
-        <v>12100</v>
+        <v>73</v>
       </c>
       <c r="H64" s="6" t="n">
         <v>30</v>
@@ -3007,7 +3007,7 @@
         </is>
       </c>
       <c r="G65" s="3" t="n">
-        <v>2900</v>
+        <v>17</v>
       </c>
       <c r="H65" s="8" t="n">
         <v>52</v>
@@ -3045,7 +3045,7 @@
         </is>
       </c>
       <c r="G66" s="3" t="n">
-        <v>2400</v>
+        <v>15</v>
       </c>
       <c r="H66" s="4" t="n">
         <v>26</v>
@@ -3349,7 +3349,7 @@
         </is>
       </c>
       <c r="G74" s="3" t="n">
-        <v>2400</v>
+        <v>15</v>
       </c>
       <c r="H74" s="8" t="n">
         <v>53</v>
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="G78" s="3" t="n">
-        <v>880</v>
+        <v>15</v>
       </c>
       <c r="H78" s="6" t="n">
         <v>40</v>
@@ -4033,7 +4033,7 @@
         </is>
       </c>
       <c r="G92" s="3" t="n">
-        <v>2900</v>
+        <v>17</v>
       </c>
       <c r="H92" s="4" t="n">
         <v>20</v>
@@ -4147,7 +4147,7 @@
         </is>
       </c>
       <c r="G95" s="3" t="n">
-        <v>1900</v>
+        <v>15</v>
       </c>
       <c r="H95" s="6" t="n">
         <v>40</v>
@@ -4185,7 +4185,7 @@
         </is>
       </c>
       <c r="G96" s="3" t="n">
-        <v>880</v>
+        <v>15</v>
       </c>
       <c r="H96" s="6" t="n">
         <v>30</v>
@@ -4299,7 +4299,7 @@
         </is>
       </c>
       <c r="G99" s="3" t="n">
-        <v>165000</v>
+        <v>990</v>
       </c>
       <c r="H99" s="8" t="n">
         <v>55</v>
@@ -4337,7 +4337,7 @@
         </is>
       </c>
       <c r="G100" s="3" t="n">
-        <v>90500</v>
+        <v>543</v>
       </c>
       <c r="H100" s="4" t="n">
         <v>28</v>
@@ -4375,7 +4375,7 @@
         </is>
       </c>
       <c r="G101" s="3" t="n">
-        <v>33100</v>
+        <v>199</v>
       </c>
       <c r="H101" s="6" t="n">
         <v>48</v>
@@ -4413,7 +4413,7 @@
         </is>
       </c>
       <c r="G102" s="3" t="n">
-        <v>14800</v>
+        <v>89</v>
       </c>
       <c r="H102" s="6" t="n">
         <v>40</v>
@@ -4451,7 +4451,7 @@
         </is>
       </c>
       <c r="G103" s="3" t="n">
-        <v>9900</v>
+        <v>59</v>
       </c>
       <c r="H103" s="6" t="n">
         <v>41</v>
@@ -4489,7 +4489,7 @@
         </is>
       </c>
       <c r="G104" s="3" t="n">
-        <v>2900</v>
+        <v>17</v>
       </c>
       <c r="H104" s="4" t="n">
         <v>28</v>
@@ -17379,7 +17379,7 @@
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>Demand/mo blends two verified sources: SEMrush search volume for the local commercial terms, and your own Google Search Console monthly impressions for everything you already appear for. Both are real, not estimates.</t>
+          <t>Demand/mo estimates monthly LOCAL (Charlotte-metro) demand: real local search volume for geo/commercial terms and your GSC impressions where you already appear, with national topic volumes scaled to Charlotte's metro share. The underlying national volumes (see the service-page tab) drove which articles to prioritize.</t>
         </is>
       </c>
     </row>

--- a/decks/7-day-kitchens/keyword-research.xlsx
+++ b/decks/7-day-kitchens/keyword-research.xlsx
@@ -627,12 +627,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kitchen Remodeling in Matthews, NC: What to Expect</t>
+          <t>Kitchen Remodeling in Waxhaw, NC: Local Process and Timeline</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>kitchen remodeling matthews nc</t>
+          <t>kitchen remodeling waxhaw nc</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -651,10 +651,10 @@
         </is>
       </c>
       <c r="G3" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
@@ -665,12 +665,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kitchen Remodeling in Huntersville, NC: Costs, Timelines, and Local Style</t>
+          <t>Kitchen Design Charlotte NC: One Local Crew, Start to Finish</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>kitchen remodeling huntersville nc</t>
+          <t>kitchen design charlotte nc</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="G4" s="3" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="H4" s="4" t="n">
         <v>18</v>
@@ -703,12 +703,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Charlotte Kitchen Renovation: A Faster, Fixed-Price Approach</t>
+          <t>Kitchen Remodeling in Denver, NC: West Lake Norman Kitchens</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>charlotte kitchen renovation</t>
+          <t>kitchen remodeling denver nc</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="G5" s="3" t="n">
-        <v>320</v>
+        <v>10</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
@@ -741,12 +741,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kitchen Designers Charlotte: What the Process Looks Like Here</t>
+          <t>Kitchen Remodel in Charlotte, NC: Fixed Pricing, Done in 7 Days</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>kitchen designers charlotte</t>
+          <t>kitchen remodel charlotte nc</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -765,10 +765,10 @@
         </is>
       </c>
       <c r="G6" s="3" t="n">
-        <v>153</v>
+        <v>390</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
@@ -779,7 +779,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kitchen Remodeling Company Charlotte: Where Speed Meets Craftsmanship</t>
+          <t>Kitchen Remodeling Company Charlotte: What the Process Looks Like Here</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kitchen Remodeling Companies Charlotte: Local Crews, Lifetime Warranty</t>
+          <t>Kitchen Remodeling in Tega Cay, SC: Lakefront Kitchen Renovations</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>kitchen remodeling companies charlotte</t>
+          <t>kitchen remodeling tega cay sc</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="G8" s="3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9">
@@ -855,12 +855,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kitchen and Bath Remodeling in Charlotte, NC: One Crew, One Timeline</t>
+          <t>Custom Kitchen Remodels in Charlotte: Built Around Your Space</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>kitchen and bath remodeling charlotte nc</t>
+          <t>custom kitchen remodel charlotte</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -879,10 +879,10 @@
         </is>
       </c>
       <c r="G9" s="3" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10">
@@ -893,12 +893,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kitchen Remodeling in Concord, NC: A Local Renovation Guide</t>
+          <t>Kitchen Remodeling in Belmont, NC: Local Trends and Timelines</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>kitchen remodeling concord nc</t>
+          <t>kitchen remodeling belmont nc</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -917,10 +917,10 @@
         </is>
       </c>
       <c r="G10" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11">
@@ -931,12 +931,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kitchen Remodeling in Indian Trail, NC: Costs and What to Expect</t>
+          <t>Kitchen Remodel Providence Plantation NC: Fixed Pricing, Finished in 7 Days</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>kitchen remodeling indian trail nc</t>
+          <t>kitchen remodel providence plantation nc</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="G11" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H11" s="4" t="n">
         <v>18</v>
@@ -969,17 +969,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Why a Fixed-Price Kitchen Remodel Beats Hourly Surprises</t>
+          <t>Ballantyne Kitchen Remodeling: Premium Results Without the Wait</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>fixed price kitchen remodel</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>Cost &amp; Budget</t>
+          <t>kitchen remodeling ballantyne</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="G12" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="H12" s="6" t="n">
-        <v>30</v>
+        <v>10</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="13">
@@ -1007,22 +1007,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Quartz Countertop Pricing: What Sets the Range</t>
+          <t>Kitchen Remodeling in Fort Mill, SC: What Local Homeowners Should Know</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>quartz price</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>Cost &amp; Budget</t>
+          <t>kitchen remodeling fort mill sc</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="G13" s="3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14">
@@ -1045,22 +1045,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>The Average Cost of a Kitchen Remodel, and Why Yours May Differ</t>
+          <t>Custom Kitchen Cabinets in Charlotte: Built for Your Space</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>average cost of kitchen remodel</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>Cost &amp; Budget</t>
+          <t>custom kitchen cabinets charlotte</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1083,22 +1083,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>How to Set a Kitchen Remodel Budget You Won't Blow Through</t>
+          <t>Affordable Kitchen Remodel Charlotte NC: Built Around Your Home and Budget</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>kitchen remodel budget</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>Cost &amp; Budget</t>
+          <t>affordable kitchen remodel charlotte nc</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1107,10 +1107,10 @@
         </is>
       </c>
       <c r="G15" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="H15" s="6" t="n">
-        <v>44</v>
+        <v>10</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>What a Kitchen Island Costs to Build In</t>
+          <t>Why a Fixed-Price Kitchen Remodel Beats Hourly Surprises</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>kitchen island cost</t>
+          <t>fixed price kitchen remodel</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -1136,19 +1136,19 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="H16" s="4" t="n">
-        <v>25</v>
+        <v>40</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Budget Backsplash Ideas That Still Look High-End</t>
+          <t>What Quartz Countertops Cost, Installed</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>cheap backsplash</t>
+          <t>cost of quartz countertops</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="G17" s="3" t="n">
-        <v>480</v>
+        <v>17</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Budget-Friendly Kitchen Remodels: Smart Places to Save</t>
+          <t>Small Kitchen Remodels: Where the Budget Goes</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>budget friendly kitchen remodel</t>
+          <t>small kitchen remodel price</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -1221,10 +1221,10 @@
         </is>
       </c>
       <c r="G18" s="3" t="n">
-        <v>320</v>
-      </c>
-      <c r="H18" s="6" t="n">
-        <v>33</v>
+        <v>480</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="19">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Choosing Backsplash Prices Without Regret</t>
+          <t>Laminate Countertops: The Budget-Friendly Counter Option</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>backsplash prices</t>
+          <t>laminate countertop cost</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>140</v>
+        <v>15</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Financing a Kitchen Remodel: Options Weighed Honestly</t>
+          <t>Backsplash Prices, Weighed Honestly</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>kitchen remodel financing</t>
+          <t>backsplash prices</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>10</v>
+        <v>140</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21">
@@ -1311,12 +1311,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Peel-and-Stick Backsplash: Quick Fix or False Economy?</t>
+          <t>Cabinet Refacing in Charlotte, NC: When It Makes Sense</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>peel and stick backsplash</t>
+          <t>cabinet refacing charlotte nc</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1335,10 +1335,10 @@
         </is>
       </c>
       <c r="G21" s="3" t="n">
-        <v>199</v>
+        <v>102</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Should Your Kitchen Have an Island? A Layout Guide</t>
+          <t>Peel and Stick Tile Backsplash: The Trade-offs That Matter</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>kitchen island</t>
+          <t>peel and stick tile backsplash</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
@@ -1373,10 +1373,10 @@
         </is>
       </c>
       <c r="G22" s="3" t="n">
-        <v>543</v>
-      </c>
-      <c r="H22" s="8" t="n">
-        <v>52</v>
+        <v>32</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="23">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Kitchen Backsplash Ideas That Pull a Remodel Together</t>
+          <t>Quartz Countertops: Why They Dominate Modern Kitchens</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>kitchen backsplash ideas</t>
+          <t>quartz countertops</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
@@ -1402,16 +1402,16 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G23" s="3" t="n">
-        <v>109</v>
+        <v>543</v>
       </c>
       <c r="H23" s="4" t="n">
         <v>28</v>
@@ -1425,12 +1425,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Kitchen Island Ideas: Sizing, Seating, and Smart Storage</t>
+          <t>Kitchen Countertops Compared: Quartz, Granite, and the Alternatives</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>kitchen island ideas</t>
+          <t>kitchen countertops</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
@@ -1440,19 +1440,19 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G24" s="3" t="n">
-        <v>73</v>
+        <v>199</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Galley Kitchen Ideas: Big Function in a Narrow Footprint</t>
+          <t>Adding a Scullery to Your Kitchen: The Hidden Prep-Space Trend</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>galley kitchen ideas</t>
+          <t>kitchen scullery</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
@@ -1483,14 +1483,14 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G25" s="3" t="n">
-        <v>22</v>
+        <v>109</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="26">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Open-Concept Kitchens: When Knocking Down a Wall Pays Off</t>
+          <t>Kitchen Island Ideas: Sizing, Seating, and Smart Storage</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>open concept kitchen</t>
+          <t>kitchen island ideas</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
@@ -1521,14 +1521,14 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Buyer</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>15</v>
+        <v>73</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
     </row>
     <row r="27">
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Kitchen Layout Basics: Work Triangles, Walkways, and Flow</t>
+          <t>Kitchen Tile: Floor, Backsplash, and Where Each Works</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>kitchen layout</t>
+          <t>kitchen tile</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1566,7 +1566,7 @@
         <v>40</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>48</v>
+        <v>31</v>
       </c>
     </row>
     <row r="28">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Kitchen Lighting Ideas: Layering Task, Ambient, and Accent</t>
+          <t>Kitchen Accessories: What to Know Before You Commit</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>kitchen lighting ideas</t>
+          <t>kitchen accessories</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
@@ -1592,19 +1592,19 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G28" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="H28" s="6" t="n">
-        <v>38</v>
+      <c r="H28" s="8" t="n">
+        <v>52</v>
       </c>
     </row>
     <row r="29">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Modern Kitchen Design: Clean Lines Without the Cold Feel</t>
+          <t>Kitchen Bars and Breakfast Counters: Seating That Works</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>modern kitchen design</t>
+          <t>kitchen bar</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="G29" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="H29" s="6" t="n">
         <v>40</v>
-      </c>
-      <c r="H29" s="6" t="n">
-        <v>38</v>
       </c>
     </row>
     <row r="30">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Pantry Ideas: Designing Storage That Earns Its Footprint</t>
+          <t>Kitchen Storage Ideas That Use Every Inch</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>pantry ideas</t>
+          <t>kitchen storage ideas</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
@@ -1677,10 +1677,10 @@
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="H30" s="6" t="n">
-        <v>48</v>
+        <v>17</v>
+      </c>
+      <c r="H30" s="8" t="n">
+        <v>52</v>
       </c>
     </row>
     <row r="31">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Two-Tone Kitchen Cabinets: How to Mix Without a Mess</t>
+          <t>Kitchen Cabinet Styles: Shaker, Flat-Panel, and Beyond</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>two tone kitchen cabinets</t>
+          <t>kitchen cabinet styles</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
@@ -1715,10 +1715,10 @@
         </is>
       </c>
       <c r="G31" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="H31" s="6" t="n">
-        <v>30</v>
+        <v>15</v>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="32">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Walk-In Pantry Ideas for Your Kitchen Remodel</t>
+          <t>Kitchen Remodel Before and After: What a Week Can Change</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>walk in pantry ideas</t>
+          <t>kitchen remodel before and after</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="G32" s="3" t="n">
-        <v>40</v>
+        <v>590</v>
       </c>
       <c r="H32" s="6" t="n">
         <v>30</v>
@@ -1767,22 +1767,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Kitchen Remodel Contractors in Rock Hill, SC</t>
+          <t>Quartz vs Granite Countertops: Which Wins for Your Kitchen</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>contractor for kitchen remodel rock hill sc</t>
-        </is>
-      </c>
-      <c r="D33" s="9" t="inlineStr">
-        <is>
-          <t>Process &amp; Planning</t>
+          <t>quartz vs granite</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1791,10 +1791,10 @@
         </is>
       </c>
       <c r="G33" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="H33" s="4" t="n">
-        <v>24</v>
+        <v>40</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="34">
@@ -1805,22 +1805,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Kitchen Renovation Contractors: What to Expect, Day by Day</t>
+          <t>Kitchen Flooring Options Ranked for Durability and Looks</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>kitchen renovation contractors</t>
-        </is>
-      </c>
-      <c r="D34" s="9" t="inlineStr">
-        <is>
-          <t>Process &amp; Planning</t>
+          <t>kitchen flooring options</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1829,10 +1829,10 @@
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="H34" s="8" t="n">
-        <v>52</v>
+        <v>40</v>
+      </c>
+      <c r="H34" s="6" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="35">
@@ -1843,34 +1843,34 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Bathroom and Kitchen Contractors: What Separates Great From Cheap</t>
+          <t>Farmhouse Kitchen Ideas That Still Feel Fresh in 2026</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>bathroom and kitchen contractors</t>
-        </is>
-      </c>
-      <c r="D35" s="9" t="inlineStr">
-        <is>
-          <t>Process &amp; Planning</t>
+          <t>farmhouse kitchen ideas</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Buyer</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G35" s="3" t="n">
-        <v>390</v>
+        <v>40</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
     </row>
     <row r="36">
@@ -1881,22 +1881,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DIY Kitchen Furniture: The Process, Demystified</t>
+          <t>Choosing a Kitchen Faucet: Finishes, Features, and Value</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>diy kitchen furniture</t>
-        </is>
-      </c>
-      <c r="D36" s="9" t="inlineStr">
-        <is>
-          <t>Process &amp; Planning</t>
+          <t>kitchen faucet ideas</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1905,10 +1905,10 @@
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>390</v>
-      </c>
-      <c r="H36" s="4" t="n">
-        <v>23</v>
+        <v>40</v>
+      </c>
+      <c r="H36" s="6" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="37">
@@ -1919,22 +1919,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Tiny Kitchen Plans: Timelines, Trade-offs, and Questions to Ask</t>
+          <t>Cabinet Hardware: The Small Detail That Sets the Tone</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>tiny kitchen plans</t>
-        </is>
-      </c>
-      <c r="D37" s="9" t="inlineStr">
-        <is>
-          <t>Process &amp; Planning</t>
+          <t>cabinet hardware ideas</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="G37" s="3" t="n">
-        <v>320</v>
-      </c>
-      <c r="H37" s="4" t="n">
-        <v>20</v>
+        <v>40</v>
+      </c>
+      <c r="H37" s="6" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="38">
@@ -1957,17 +1957,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Small Kitchen Plans: What Every Remodel Should Know</t>
+          <t>Butler's Pantry Ideas: A Kitchen Upgrade That Adds Real Value</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>small kitchen plans</t>
-        </is>
-      </c>
-      <c r="D38" s="9" t="inlineStr">
-        <is>
-          <t>Process &amp; Planning</t>
+          <t>butler pantry ideas</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1981,10 +1981,10 @@
         </is>
       </c>
       <c r="G38" s="3" t="n">
-        <v>170</v>
-      </c>
-      <c r="H38" s="4" t="n">
-        <v>15</v>
+        <v>40</v>
+      </c>
+      <c r="H38" s="6" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="39">
@@ -1995,12 +1995,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Open Kitchen Living Room: Timelines, Trade-offs, and Questions to Ask</t>
+          <t>How to Plan a Kitchen Remodel Before Demo Day</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>open kitchen living room</t>
+          <t>how to plan a kitchen remodel</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2019,10 +2019,10 @@
         </is>
       </c>
       <c r="G39" s="3" t="n">
-        <v>720</v>
+        <v>40</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="40">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>The Kitchen Remodel Checklist Every Homeowner Should Use</t>
+          <t>Do You Need a Permit for a Kitchen Remodel in North Carolina?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>kitchen remodel checklist</t>
+          <t>kitchen remodel permits</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G40" s="3" t="n">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Kitchen Remodeling Timeline: What It Takes, Start to Finish</t>
+          <t>Change Orders on a Kitchen Remodel: How Fixed Pricing Avoids Them</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>kitchen remodeling timeline</t>
+          <t>kitchen remodel change orders</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
@@ -2095,10 +2095,10 @@
         </is>
       </c>
       <c r="G41" s="3" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="42">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Kitchen Design and Build Charlotte NC: A Faster Path to Your Dream Kitchen</t>
+          <t>Kitchen Design-Build in Charlotte, NC: One Team, Start to Finish</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Kitchen Remodeling in Mooresville, NC: A Lake Norman Homeowner's Guide</t>
+          <t>Kitchen Remodeling in Matthews, NC: What to Expect</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>kitchen remodeling mooresville nc</t>
+          <t>kitchen remodeling matthews nc</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="G43" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H43" s="4" t="n">
         <v>18</v>
@@ -2185,12 +2185,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>What Makes the Best Kitchen Contractor in Charlotte</t>
+          <t>Kitchen Contractor Belmont, Done the Fixed-Price Way</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>best kitchen contractor charlotte</t>
+          <t>kitchen contractor belmont</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2209,10 +2209,10 @@
         </is>
       </c>
       <c r="G44" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="H44" s="6" t="n">
-        <v>30</v>
+        <v>15</v>
+      </c>
+      <c r="H44" s="4" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="45">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Charlotte Kitchen Remodeling: Fixed Pricing, Finished in 7 Days</t>
+          <t>Kitchen Remodeling in Lake Wylie, SC: What Local Homeowners Should Know</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>charlotte kitchen remodeling</t>
+          <t>kitchen remodeling lake wylie sc</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="G45" s="3" t="n">
-        <v>320</v>
+        <v>10</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="46">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Hiring a Kitchen Contractor in Charlotte: A Vetting Guide</t>
+          <t>Kitchen Designers Charlotte: Fixed Pricing, Finished in 7 Days</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>kitchen contractor charlotte</t>
+          <t>kitchen designers charlotte</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="G46" s="3" t="n">
-        <v>90</v>
+        <v>153</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="47">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Best Kitchen Remodeler Charlotte: The 7-Day Difference, Explained</t>
+          <t>Kitchen Remodeling Services Charlotte: Built Around Your Home and Budget</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>best kitchen remodeler charlotte</t>
+          <t>kitchen remodeling services charlotte</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -2323,7 +2323,7 @@
         </is>
       </c>
       <c r="G47" s="3" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="H47" s="4" t="n">
         <v>18</v>
@@ -2337,12 +2337,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Kitchen Renovation Services Charlotte: What the Process Looks Like Here</t>
+          <t>Kitchen Remodeling South West Charlotte: A Faster Path to Your Dream Kitchen</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>kitchen renovation services charlotte</t>
+          <t>kitchen remodeling south west charlotte</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -2361,10 +2361,10 @@
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49">
@@ -2375,12 +2375,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Kitchen Remodeling South West Charlotte: One Local Crew, Start to Finish</t>
+          <t>High-End Kitchen Remodels in Charlotte: Premium, Fixed-Price</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>kitchen remodeling south west charlotte</t>
+          <t>high-end kitchen remodel charlotte</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -2399,10 +2399,10 @@
         </is>
       </c>
       <c r="G49" s="3" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="50">
@@ -2413,12 +2413,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Kitchen Remodeling in Fort Mill, SC: What Local Homeowners Should Know</t>
+          <t>Kitchen Remodeling in Concord, NC: A Local Renovation Guide</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>kitchen remodeling fort mill sc</t>
+          <t>kitchen remodeling concord nc</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="G50" s="3" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H50" s="4" t="n">
         <v>18</v>
@@ -2451,12 +2451,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Kitchen Remodeling in Mint Hill, NC: A Local Homeowner's Guide</t>
+          <t>Kitchen Remodel Raintree NC: Local Crews, Lifetime Warranty</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>kitchen remodeling mint hill nc</t>
+          <t>kitchen remodel raintree nc</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -2475,7 +2475,7 @@
         </is>
       </c>
       <c r="G51" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H51" s="4" t="n">
         <v>18</v>
@@ -2489,22 +2489,22 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>What Quartz Countertops Cost, Installed</t>
+          <t>Kitchen Remodeling in Davidson, NC: A Lake Norman Town Guide</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>cost of quartz countertops</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="inlineStr">
-        <is>
-          <t>Cost &amp; Budget</t>
+          <t>kitchen remodeling davidson nc</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2513,10 +2513,10 @@
         </is>
       </c>
       <c r="G52" s="3" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="53">
@@ -2527,34 +2527,34 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Small Kitchen Remodels: Where the Budget Goes</t>
+          <t>Kitchen Remodeling in Indian Trail, NC: Costs and What to Expect</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>small kitchen remodel price</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="inlineStr">
-        <is>
-          <t>Cost &amp; Budget</t>
+          <t>kitchen remodeling indian trail nc</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G53" s="3" t="n">
-        <v>480</v>
+        <v>10</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="54">
@@ -2565,34 +2565,34 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>How Much Space to Leave Between Counter and Island</t>
+          <t>Cabinet Installation Charlotte NC: What the Process Looks Like Here</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>how much space between counter and island</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="inlineStr">
-        <is>
-          <t>Cost &amp; Budget</t>
+          <t>cabinet installation charlotte nc</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G54" s="3" t="n">
-        <v>320</v>
+        <v>10</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="55">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Cheap Backsplash Options: What to Know Before You Commit</t>
+          <t>What Granite Countertops Cost, Installed</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>cheap backsplash options</t>
+          <t>cost of granite countertops</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
@@ -2627,10 +2627,10 @@
         </is>
       </c>
       <c r="G55" s="3" t="n">
-        <v>260</v>
+        <v>17</v>
       </c>
       <c r="H55" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="56">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Laminate Countertops: The Budget-Friendly Counter Option</t>
+          <t>What a Small Kitchen Remodel Really Costs</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>laminate countertop cost</t>
+          <t>average cost of small kitchen remodel</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
@@ -2661,14 +2661,14 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Buyer</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G56" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="H56" s="6" t="n">
-        <v>34</v>
+        <v>390</v>
+      </c>
+      <c r="H56" s="4" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="57">
@@ -2679,12 +2679,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>A Kitchen Makeover on a Budget: What's Realistic</t>
+          <t>The Average Cost of a Kitchen Remodel, and Why Yours May Differ</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>kitchen makeover on a budget</t>
+          <t>average cost of kitchen remodel</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
@@ -2699,14 +2699,14 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G57" s="3" t="n">
-        <v>390</v>
-      </c>
-      <c r="H57" s="6" t="n">
-        <v>32</v>
+        <v>10</v>
+      </c>
+      <c r="H57" s="4" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="58">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Small Kitchen Remodels on a Budget: What to Budget Before You Start</t>
+          <t>How to Set a Kitchen Remodel Budget You Won't Blow Through</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>small kitchen remodels on a budget</t>
+          <t>kitchen remodel budget</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="G58" s="3" t="n">
-        <v>260</v>
-      </c>
-      <c r="H58" s="4" t="n">
-        <v>27</v>
+        <v>15</v>
+      </c>
+      <c r="H58" s="6" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="59">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Kitchen Renovation Cost: A Room-by-Room Money Map</t>
+          <t>Cheap Backsplash Ideas: A Plain-English Cost Primer</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>kitchen renovation cost</t>
+          <t>cheap backsplash ideas</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2779,7 +2779,7 @@
         </is>
       </c>
       <c r="G59" s="3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H59" s="6" t="n">
         <v>30</v>
@@ -2793,22 +2793,22 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Cabinet Refacing in Charlotte, NC: When It Makes Sense</t>
+          <t>Budget Backsplash Ideas That Still Look High-End</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>cabinet refacing charlotte nc</t>
-        </is>
-      </c>
-      <c r="D60" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>cheap backsplash</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>Cost &amp; Budget</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2817,10 +2817,10 @@
         </is>
       </c>
       <c r="G60" s="3" t="n">
-        <v>102</v>
+        <v>480</v>
       </c>
       <c r="H60" s="4" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
     </row>
     <row r="61">
@@ -2831,22 +2831,22 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Kitchen and Laundry Room Combos: Designing the Two as One Project</t>
+          <t>Kitchen Renovation Cost: A Room-by-Room Money Map</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>kitchen and laundry room remodel</t>
-        </is>
-      </c>
-      <c r="D61" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>kitchen renovation cost</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>Cost &amp; Budget</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2855,10 +2855,10 @@
         </is>
       </c>
       <c r="G61" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="H61" s="4" t="n">
-        <v>24</v>
+        <v>60</v>
+      </c>
+      <c r="H61" s="6" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="62">
@@ -2869,17 +2869,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Butcher Block Countertops: Warm Looks, Real Trade-offs</t>
+          <t>Financing a Kitchen Remodel: Options Weighed Honestly</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>butcher block countertops</t>
-        </is>
-      </c>
-      <c r="D62" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>kitchen remodel financing</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>Cost &amp; Budget</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2893,10 +2893,10 @@
         </is>
       </c>
       <c r="G62" s="3" t="n">
-        <v>243</v>
+        <v>10</v>
       </c>
       <c r="H62" s="6" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
     </row>
     <row r="63">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Adding a Scullery to Your Kitchen: The Hidden Prep-Space Trend</t>
+          <t>Choosing Kitchen Cabinets: Styles, Finishes, and What Lasts</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>kitchen scullery</t>
+          <t>kitchen cabinets</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
@@ -2922,7 +2922,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2931,10 +2931,10 @@
         </is>
       </c>
       <c r="G63" s="3" t="n">
-        <v>109</v>
-      </c>
-      <c r="H63" s="6" t="n">
-        <v>44</v>
+        <v>990</v>
+      </c>
+      <c r="H63" s="8" t="n">
+        <v>55</v>
       </c>
     </row>
     <row r="64">
@@ -2945,12 +2945,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Subway Tile Backsplash: The Timeless Default, Done Right</t>
+          <t>Stick on Backsplash: What to Weigh First</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>subway tile backsplash</t>
+          <t>stick on backsplash</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="G64" s="3" t="n">
-        <v>73</v>
-      </c>
-      <c r="H64" s="6" t="n">
-        <v>30</v>
+        <v>26</v>
+      </c>
+      <c r="H64" s="4" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="65">
@@ -2983,12 +2983,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Kitchen Storage Ideas That Use Every Inch</t>
+          <t>Should Your Kitchen Have an Island? A Layout Guide</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>kitchen storage ideas</t>
+          <t>kitchen island</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
@@ -2998,16 +2998,16 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G65" s="3" t="n">
-        <v>17</v>
+        <v>543</v>
       </c>
       <c r="H65" s="8" t="n">
         <v>52</v>
@@ -3021,12 +3021,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Kitchen Cabinet Styles: Shaker, Flat-Panel, and Beyond</t>
+          <t>Kitchen Island with Seating: What Designers Pick and Why</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>kitchen cabinet styles</t>
+          <t>kitchen island with seating</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
@@ -3036,19 +3036,19 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Buyer</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G66" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="H66" s="4" t="n">
-        <v>26</v>
+        <v>163</v>
+      </c>
+      <c r="H66" s="6" t="n">
+        <v>44</v>
       </c>
     </row>
     <row r="67">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Kitchen Design Ideas: Layouts, Light, and Lasting Style</t>
+          <t>Kitchen Utensils: A Homeowner's Buyer Guide</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>kitchen design ideas</t>
+          <t>kitchen utensils</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
@@ -3074,7 +3074,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="G67" s="3" t="n">
-        <v>40</v>
+        <v>109</v>
       </c>
       <c r="H67" s="6" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="68">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Kitchen Cabinet Colors: What's Timeless vs What's Trendy</t>
+          <t>Subway Tile Backsplash: The Timeless Default, Done Right</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>kitchen cabinet colors</t>
+          <t>subway tile backsplash</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3121,10 +3121,10 @@
         </is>
       </c>
       <c r="G68" s="3" t="n">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="H68" s="6" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="69">
@@ -3135,12 +3135,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Kitchen Trends 2026: Bold Cabinets, Brass, and What to Skip</t>
+          <t>Kitchen Island with Storage: Weighed Honestly for Your Budget</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>kitchen trends 2026</t>
+          <t>kitchen island with storage</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
@@ -3150,19 +3150,19 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G69" s="3" t="n">
         <v>40</v>
       </c>
       <c r="H69" s="6" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="70">
@@ -3173,12 +3173,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Kitchen Sink Ideas: Materials, Mounts, and the Right Size</t>
+          <t>Choosing Kitchen and Bath Without Regret</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>kitchen sink ideas</t>
+          <t>kitchen and bath</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
@@ -3188,19 +3188,19 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G70" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="H70" s="6" t="n">
-        <v>38</v>
+        <v>32</v>
+      </c>
+      <c r="H70" s="8" t="n">
+        <v>51</v>
       </c>
     </row>
     <row r="71">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Kitchen Paint Colors That Flatter Cabinets and Counters</t>
+          <t>Galley Kitchen Ideas: Big Function in a Narrow Footprint</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>kitchen paint colors</t>
+          <t>galley kitchen ideas</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
@@ -3231,14 +3231,14 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Buyer</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G71" s="3" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="H71" s="6" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="72">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Kitchen Appliances: Where to Splurge and Where to Save</t>
+          <t>Waterfall Islands: The Statement Feature Worth the Splurge</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>kitchen appliances</t>
+          <t>waterfall island</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3273,10 +3273,10 @@
         </is>
       </c>
       <c r="G72" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="H72" s="6" t="n">
-        <v>48</v>
+        <v>17</v>
+      </c>
+      <c r="H72" s="4" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="73">
@@ -3287,12 +3287,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Kitchen and Mudroom Combos: A Smarter Family Entryway</t>
+          <t>Kitchen Layout Basics: Work Triangles, Walkways, and Flow</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>kitchen and mudroom</t>
+          <t>kitchen layout</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
@@ -3314,7 +3314,7 @@
         <v>40</v>
       </c>
       <c r="H73" s="6" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
     </row>
     <row r="74">
@@ -3325,34 +3325,34 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Kitchen Contractors: Done Right the First Time</t>
+          <t>Kitchen Lighting Ideas: Layering Task, Ambient, and Accent</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>kitchen contractors</t>
-        </is>
-      </c>
-      <c r="D74" s="9" t="inlineStr">
-        <is>
-          <t>Process &amp; Planning</t>
+          <t>kitchen lighting ideas</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Buyer</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G74" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="H74" s="8" t="n">
-        <v>53</v>
+        <v>40</v>
+      </c>
+      <c r="H74" s="6" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="75">
@@ -3363,22 +3363,22 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Local Kitchen Remodelers: The Questions to Ask First</t>
+          <t>Modern Kitchen Design: Clean Lines Without the Cold Feel</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>local kitchen remodelers</t>
-        </is>
-      </c>
-      <c r="D75" s="9" t="inlineStr">
-        <is>
-          <t>Process &amp; Planning</t>
+          <t>modern kitchen design</t>
+        </is>
+      </c>
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3387,10 +3387,10 @@
         </is>
       </c>
       <c r="G75" s="3" t="n">
-        <v>320</v>
-      </c>
-      <c r="H75" s="8" t="n">
-        <v>50</v>
+        <v>40</v>
+      </c>
+      <c r="H75" s="6" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="76">
@@ -3401,34 +3401,34 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>How to Compare the Best Kitchen Remodel Contractors</t>
+          <t>Pantry Ideas: Designing Storage That Earns Its Footprint</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>best kitchen remodel contractors</t>
-        </is>
-      </c>
-      <c r="D76" s="9" t="inlineStr">
-        <is>
-          <t>Process &amp; Planning</t>
+          <t>pantry ideas</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Buyer</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G76" s="3" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="H76" s="6" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
     </row>
     <row r="77">
@@ -3439,17 +3439,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>How to Prepare Your Home for a Kitchen Remodel</t>
+          <t>Two-Tone Kitchen Cabinets: How to Mix Without a Mess</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>how to prepare for a kitchen remodel</t>
-        </is>
-      </c>
-      <c r="D77" s="9" t="inlineStr">
-        <is>
-          <t>Process &amp; Planning</t>
+          <t>two tone kitchen cabinets</t>
+        </is>
+      </c>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -3459,14 +3459,14 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G77" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="H77" s="4" t="n">
-        <v>24</v>
+        <v>40</v>
+      </c>
+      <c r="H77" s="6" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="78">
@@ -3477,17 +3477,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>DIY Kitchen Cupboards: A Homeowner's Walkthrough</t>
+          <t>Walk-In Pantry Ideas for Your Kitchen Remodel</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>diy kitchen cupboards</t>
-        </is>
-      </c>
-      <c r="D78" s="9" t="inlineStr">
-        <is>
-          <t>Process &amp; Planning</t>
+          <t>walk in pantry ideas</t>
+        </is>
+      </c>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3501,10 +3501,10 @@
         </is>
       </c>
       <c r="G78" s="3" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H78" s="6" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="79">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Galley Kitchen Plans: How to Pick the Right Pro</t>
+          <t>Kitchen Remodel Contractors in Rock Hill, SC</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>galley kitchen plans</t>
+          <t>contractor for kitchen remodel rock hill sc</t>
         </is>
       </c>
       <c r="D79" s="9" t="inlineStr">
@@ -3530,19 +3530,19 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G79" s="3" t="n">
-        <v>720</v>
+        <v>10</v>
       </c>
       <c r="H79" s="4" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="80">
@@ -3553,12 +3553,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Kitchen Demolition: What Tear-Out Day Actually Involves</t>
+          <t>Kitchen Renovation Contractors: What to Expect, Day by Day</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>kitchen demolition</t>
+          <t>kitchen renovation contractors</t>
         </is>
       </c>
       <c r="D80" s="9" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3577,10 +3577,10 @@
         </is>
       </c>
       <c r="G80" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="H80" s="6" t="n">
-        <v>48</v>
+        <v>17</v>
+      </c>
+      <c r="H80" s="8" t="n">
+        <v>52</v>
       </c>
     </row>
     <row r="81">
@@ -3591,12 +3591,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>The Right Order of a Kitchen Remodel, Step by Step</t>
+          <t>The Kitchen Remodel Checklist Every Homeowner Should Use</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>order of kitchen remodel</t>
+          <t>kitchen remodel checklist</t>
         </is>
       </c>
       <c r="D81" s="9" t="inlineStr">
@@ -3606,19 +3606,19 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Buyer</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G81" s="3" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H81" s="6" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
     </row>
     <row r="82">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Kitchen Remodeling in Waxhaw, NC: Local Process and Timeline</t>
+          <t>Kitchen Remodeling in Mooresville, NC: A Lake Norman Homeowner's Guide</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>kitchen remodeling waxhaw nc</t>
+          <t>kitchen remodeling mooresville nc</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="G83" s="3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H83" s="4" t="n">
         <v>18</v>
@@ -3705,12 +3705,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Kitchen Remodel in Charlotte, NC: Fixed Pricing, Done in 7 Days</t>
+          <t>Kitchen Remodeling in Gastonia, NC: Costs and What to Expect</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>kitchen remodel charlotte nc</t>
+          <t>kitchen remodeling gastonia nc</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -3729,10 +3729,10 @@
         </is>
       </c>
       <c r="G84" s="3" t="n">
-        <v>390</v>
+        <v>10</v>
       </c>
       <c r="H84" s="4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="85">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Kitchen Renovation Charlotte NC: Local Crews, Lifetime Warranty</t>
+          <t>Kitchen Remodeling in Huntersville, NC: Costs, Timelines, and Local Style</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>kitchen renovation charlotte nc</t>
+          <t>kitchen remodeling huntersville nc</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -3767,10 +3767,10 @@
         </is>
       </c>
       <c r="G85" s="3" t="n">
-        <v>170</v>
+        <v>10</v>
       </c>
       <c r="H85" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="86">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Kitchen Contractors Charlotte NC: Built Around Your Home and Budget</t>
+          <t>Kitchen Contractors in Charlotte, NC: One Fixed Price, One Crew</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>kitchen contractors charlotte nc</t>
+          <t>kitchen contractor charlotte</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -3805,10 +3805,10 @@
         </is>
       </c>
       <c r="G86" s="3" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="H86" s="4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="87">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Kitchen Remodeling Services Charlotte: Fixed Pricing, Finished in 7 Days</t>
+          <t>Kitchen and Bath Remodeling in Charlotte, NC: One Crew, One Timeline</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>kitchen remodeling services charlotte</t>
+          <t>kitchen and bath remodeling charlotte nc</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -3843,10 +3843,10 @@
         </is>
       </c>
       <c r="G87" s="3" t="n">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="H87" s="4" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="88">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Ballantyne Kitchen Remodeling: Premium Results Without the Wait</t>
+          <t>Fast Kitchen Remodel Charlotte: The 7-Day Difference, Explained</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>kitchen remodeling ballantyne</t>
+          <t>fast kitchen remodel charlotte</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -3881,10 +3881,10 @@
         </is>
       </c>
       <c r="G88" s="3" t="n">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="H88" s="4" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="89">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Kitchen Remodeling in Belmont, NC: Local Trends and Timelines</t>
+          <t>Full Kitchen Remodels in Charlotte: Everything, One Fixed Price</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>kitchen remodeling belmont nc</t>
+          <t>full kitchen remodel charlotte</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -3957,7 +3957,7 @@
         </is>
       </c>
       <c r="G90" s="3" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H90" s="4" t="n">
         <v>18</v>
@@ -3971,12 +3971,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Custom Kitchen Cabinets in Charlotte: Built for Your Space</t>
+          <t>Kitchen Remodeling in Pineville, NC: A Local Homeowner's Guide</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>custom kitchen cabinets charlotte</t>
+          <t>kitchen remodeling pineville nc</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -3995,10 +3995,10 @@
         </is>
       </c>
       <c r="G91" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H91" s="4" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="92">
@@ -4009,34 +4009,34 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>What Granite Countertops Cost, Installed</t>
+          <t>Kitchen Remodeling in Harrisburg, NC: A Local Renovation Guide</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>cost of granite countertops</t>
-        </is>
-      </c>
-      <c r="D92" s="5" t="inlineStr">
-        <is>
-          <t>Cost &amp; Budget</t>
+          <t>kitchen remodeling harrisburg nc</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G92" s="3" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H92" s="4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="93">
@@ -4047,34 +4047,34 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>What a Small Kitchen Remodel Really Costs</t>
+          <t>Kitchen Remodeling in Mint Hill, NC: A Local Homeowner's Guide</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>average cost of small kitchen remodel</t>
-        </is>
-      </c>
-      <c r="D93" s="5" t="inlineStr">
-        <is>
-          <t>Cost &amp; Budget</t>
+          <t>kitchen remodeling mint hill nc</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G93" s="3" t="n">
-        <v>390</v>
+        <v>10</v>
       </c>
       <c r="H93" s="4" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="94">
@@ -4085,34 +4085,34 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>How Much for a Small Kitchen Renovation: What to Weigh First</t>
+          <t>Kitchen and Bath Charlotte NC: A Faster Path to Your Dream Kitchen</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>how much for a small kitchen renovation</t>
-        </is>
-      </c>
-      <c r="D94" s="5" t="inlineStr">
-        <is>
-          <t>Cost &amp; Budget</t>
+          <t>kitchen and bath charlotte nc</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G94" s="3" t="n">
-        <v>260</v>
+        <v>10</v>
       </c>
       <c r="H94" s="4" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="95">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Inexpensive Kitchen Renovations: A Straight Comparison for Homeowners</t>
+          <t>Quartz Countertop Pricing: What Sets the Range</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>inexpensive kitchen renovations</t>
+          <t>quartz price</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
@@ -4143,14 +4143,14 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G95" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="H95" s="6" t="n">
-        <v>40</v>
+      <c r="H95" s="4" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="96">
@@ -4161,12 +4161,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Cheap Backsplash Ideas: A Plain-English Cost Primer</t>
+          <t>Cost of Kitchen Cabinets: Where the Money Goes, and Where to Save</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>cheap backsplash ideas</t>
+          <t>cost of kitchen cabinets</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
@@ -4176,7 +4176,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -4185,10 +4185,10 @@
         </is>
       </c>
       <c r="G96" s="3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H96" s="6" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="97">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>How Much Are Kitchen Cupboards: Budget, Mid-Range, and High-End</t>
+          <t>Cheap Cabinet Doors Replacement: What Sets the Final Number</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>how much are kitchen cupboards</t>
+          <t>cheap cabinet doors replacement</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
@@ -4219,14 +4219,14 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G97" s="3" t="n">
-        <v>720</v>
+        <v>15</v>
       </c>
       <c r="H97" s="6" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="98">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Cost of New Kitchen: What Sets the Final Number</t>
+          <t>What a Kitchen Island Costs to Build In</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>cost of new kitchen</t>
+          <t>kitchen island cost</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
@@ -4261,10 +4261,10 @@
         </is>
       </c>
       <c r="G98" s="3" t="n">
-        <v>390</v>
-      </c>
-      <c r="H98" s="6" t="n">
-        <v>47</v>
+        <v>15</v>
+      </c>
+      <c r="H98" s="4" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="99">
@@ -4275,22 +4275,22 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Choosing Kitchen Cabinets: Styles, Finishes, and What Lasts</t>
+          <t>Small Kitchen Remodels on a Budget: What to Budget Before You Start</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>kitchen cabinets</t>
-        </is>
-      </c>
-      <c r="D99" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>small kitchen remodels on a budget</t>
+        </is>
+      </c>
+      <c r="D99" s="5" t="inlineStr">
+        <is>
+          <t>Cost &amp; Budget</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -4299,10 +4299,10 @@
         </is>
       </c>
       <c r="G99" s="3" t="n">
-        <v>990</v>
-      </c>
-      <c r="H99" s="8" t="n">
-        <v>55</v>
+        <v>260</v>
+      </c>
+      <c r="H99" s="4" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="100">
@@ -4313,12 +4313,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Quartz Countertops: Why They Dominate Modern Kitchens</t>
+          <t>Peel-and-Stick Backsplash: Quick Fix or False Economy?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>quartz countertops</t>
+          <t>peel and stick backsplash</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
@@ -4337,10 +4337,10 @@
         </is>
       </c>
       <c r="G100" s="3" t="n">
-        <v>543</v>
+        <v>199</v>
       </c>
       <c r="H100" s="4" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="101">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Kitchen Countertops Compared: Quartz, Granite, and the Alternatives</t>
+          <t>Kitchen Tile Flooring: A Straight Comparison for Homeowners</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>kitchen countertops</t>
+          <t>kitchen tile flooring</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
@@ -4375,10 +4375,10 @@
         </is>
       </c>
       <c r="G101" s="3" t="n">
-        <v>199</v>
-      </c>
-      <c r="H101" s="6" t="n">
-        <v>48</v>
+        <v>22</v>
+      </c>
+      <c r="H101" s="4" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="102">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Small Kitchen Ideas: Making a Compact Space Feel Open</t>
+          <t>Kitchen and Laundry Room Combos: Designing the Two as One Project</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>small kitchen ideas</t>
+          <t>kitchen and laundry room remodel</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
@@ -4409,14 +4409,14 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G102" s="3" t="n">
-        <v>89</v>
-      </c>
-      <c r="H102" s="6" t="n">
         <v>40</v>
+      </c>
+      <c r="H102" s="4" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="103">
@@ -4427,12 +4427,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Kitchen Gadgets: What Designers Pick and Why</t>
+          <t>Butcher Block Countertops: Warm Looks, Real Trade-offs</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>kitchen gadgets</t>
+          <t>butcher block countertops</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
@@ -4451,10 +4451,10 @@
         </is>
       </c>
       <c r="G103" s="3" t="n">
-        <v>59</v>
+        <v>243</v>
       </c>
       <c r="H103" s="6" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="104">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Waterfall Islands: The Statement Feature Worth the Splurge</t>
+          <t>Kitchen Backsplash Ideas That Pull a Remodel Together</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>waterfall island</t>
+          <t>kitchen backsplash ideas</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
@@ -4485,11 +4485,11 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Buyer</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G104" s="3" t="n">
-        <v>17</v>
+        <v>109</v>
       </c>
       <c r="H104" s="4" t="n">
         <v>28</v>
@@ -4503,12 +4503,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Kitchen Remodel Before and After: What a Week Can Change</t>
+          <t>Small Kitchen Ideas: Making a Compact Space Feel Open</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>kitchen remodel before and after</t>
+          <t>small kitchen ideas</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
@@ -4527,10 +4527,10 @@
         </is>
       </c>
       <c r="G105" s="3" t="n">
-        <v>590</v>
+        <v>89</v>
       </c>
       <c r="H105" s="6" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="106">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Quartz vs Granite Countertops: Which Wins for Your Kitchen</t>
+          <t>Small Kitchen Island: Ideas That Work in Real Kitchens</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>quartz vs granite</t>
+          <t>small kitchen island</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4565,10 +4565,10 @@
         </is>
       </c>
       <c r="G106" s="3" t="n">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="H106" s="6" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
     </row>
     <row r="107">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Kitchen Flooring Options Ranked for Durability and Looks</t>
+          <t>Kitchen Cooking Utensils: What Designers Pick and Why</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>kitchen flooring options</t>
+          <t>kitchen cooking utensils</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
@@ -4606,7 +4606,7 @@
         <v>40</v>
       </c>
       <c r="H107" s="6" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="108">
@@ -4617,12 +4617,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Farmhouse Kitchen Ideas That Still Feel Fresh in 2026</t>
+          <t>Kitchen Essentials, Weighed Honestly</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>farmhouse kitchen ideas</t>
+          <t>kitchen essentials</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
@@ -4632,19 +4632,19 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G108" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="H108" s="6" t="n">
-        <v>38</v>
+        <v>32</v>
+      </c>
+      <c r="H108" s="8" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="109">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Choosing a Kitchen Faucet: Finishes, Features, and Value</t>
+          <t>Open-Concept Kitchens: When Knocking Down a Wall Pays Off</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>kitchen faucet ideas</t>
+          <t>open concept kitchen</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr">
@@ -4670,19 +4670,19 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G109" s="3" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H109" s="6" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
     </row>
     <row r="110">
@@ -4693,12 +4693,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Cabinet Hardware: The Small Detail That Sets the Tone</t>
+          <t>Kitchen Design Ideas: Layouts, Light, and Lasting Style</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>cabinet hardware ideas</t>
+          <t>kitchen design ideas</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
@@ -4731,12 +4731,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Butler's Pantry Ideas: A Kitchen Upgrade That Adds Real Value</t>
+          <t>Kitchen Cabinet Colors: What's Timeless vs What's Trendy</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>butler pantry ideas</t>
+          <t>kitchen cabinet colors</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr">
@@ -4751,7 +4751,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G111" s="3" t="n">
@@ -4769,12 +4769,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>White Kitchen Cabinets: Why They Endure, and How to Keep Them Clean</t>
+          <t>Kitchen Trends 2026: Bold Cabinets, Brass, and What to Skip</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>white kitchen cabinets</t>
+          <t>kitchen trends 2026</t>
         </is>
       </c>
       <c r="D112" s="7" t="inlineStr">
@@ -4789,11 +4789,11 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Buyer</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G112" s="3" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="H112" s="6" t="n">
         <v>38</v>
@@ -4807,34 +4807,34 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Finding Local Contractors for a Kitchen Remodel</t>
+          <t>Kitchen Sink Ideas: Materials, Mounts, and the Right Size</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>local contractors for kitchen remodel</t>
-        </is>
-      </c>
-      <c r="D113" s="9" t="inlineStr">
-        <is>
-          <t>Process &amp; Planning</t>
+          <t>kitchen sink ideas</t>
+        </is>
+      </c>
+      <c r="D113" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Buyer</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G113" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="H113" s="4" t="n">
-        <v>24</v>
+        <v>40</v>
+      </c>
+      <c r="H113" s="6" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="114">
@@ -4845,22 +4845,22 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Kitchen Bath Contractor: A No-Nonsense Buyer's Guide</t>
+          <t>Kitchen Paint Colors That Flatter Cabinets and Counters</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>kitchen bath contractor</t>
-        </is>
-      </c>
-      <c r="D114" s="9" t="inlineStr">
-        <is>
-          <t>Process &amp; Planning</t>
+          <t>kitchen paint colors</t>
+        </is>
+      </c>
+      <c r="D114" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4869,10 +4869,10 @@
         </is>
       </c>
       <c r="G114" s="3" t="n">
-        <v>480</v>
+        <v>40</v>
       </c>
       <c r="H114" s="6" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="115">
@@ -4883,22 +4883,22 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>What Separates a Great Kitchen Remodeler From the Rest</t>
+          <t>Kitchen Appliances: Where to Splurge and Where to Save</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>kitchen remodeler</t>
-        </is>
-      </c>
-      <c r="D115" s="9" t="inlineStr">
-        <is>
-          <t>Process &amp; Planning</t>
+          <t>kitchen appliances</t>
+        </is>
+      </c>
+      <c r="D115" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4907,7 +4907,7 @@
         </is>
       </c>
       <c r="G115" s="3" t="n">
-        <v>151</v>
+        <v>40</v>
       </c>
       <c r="H115" s="6" t="n">
         <v>48</v>
@@ -4921,34 +4921,34 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Kitchen Cupboard Plans: What It Takes, Start to Finish</t>
+          <t>Kitchen and Mudroom Combos: A Smarter Family Entryway</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>kitchen cupboard plans</t>
-        </is>
-      </c>
-      <c r="D116" s="9" t="inlineStr">
-        <is>
-          <t>Process &amp; Planning</t>
+          <t>kitchen and mudroom</t>
+        </is>
+      </c>
+      <c r="D116" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G116" s="3" t="n">
-        <v>320</v>
-      </c>
-      <c r="H116" s="4" t="n">
-        <v>13</v>
+        <v>40</v>
+      </c>
+      <c r="H116" s="6" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="117">
@@ -4959,17 +4959,17 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>How to Plan a Kitchen Remodel Before Demo Day</t>
+          <t>White Kitchen Cabinets: Why They Endure, and How to Keep Them Clean</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>how to plan a kitchen remodel</t>
-        </is>
-      </c>
-      <c r="D117" s="9" t="inlineStr">
-        <is>
-          <t>Process &amp; Planning</t>
+          <t>white kitchen cabinets</t>
+        </is>
+      </c>
+      <c r="D117" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -4979,14 +4979,14 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G117" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="H117" s="4" t="n">
-        <v>24</v>
+        <v>10</v>
+      </c>
+      <c r="H117" s="6" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="118">
@@ -4997,12 +4997,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Open Kitchen Plans: How to Pick the Right Pro</t>
+          <t>Kitchen Remodel Contractors Concord: What Separates Great From Cheap</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>open kitchen plans</t>
+          <t>kitchen remodel contractors concord</t>
         </is>
       </c>
       <c r="D118" s="9" t="inlineStr">
@@ -5012,19 +5012,19 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G118" s="3" t="n">
-        <v>260</v>
+        <v>10</v>
       </c>
       <c r="H118" s="6" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="119">
@@ -5035,12 +5035,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Do You Need a Permit for a Kitchen Remodel in North Carolina?</t>
+          <t>Kitchen Contractors: Done Right the First Time</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>kitchen remodel permits</t>
+          <t>kitchen contractors</t>
         </is>
       </c>
       <c r="D119" s="9" t="inlineStr">
@@ -5050,7 +5050,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -5059,10 +5059,10 @@
         </is>
       </c>
       <c r="G119" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="H119" s="6" t="n">
-        <v>38</v>
+        <v>15</v>
+      </c>
+      <c r="H119" s="8" t="n">
+        <v>53</v>
       </c>
     </row>
     <row r="120">
@@ -5073,12 +5073,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Questions to Ask a Kitchen Remodel Contractor Before You Sign</t>
+          <t>How to Prepare Your Home for a Kitchen Remodel</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>kitchen remodel contractor questions</t>
+          <t>how to prepare for a kitchen remodel</t>
         </is>
       </c>
       <c r="D120" s="9" t="inlineStr">
@@ -5088,19 +5088,19 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Buyer</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G120" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="H120" s="6" t="n">
-        <v>30</v>
+        <v>10</v>
+      </c>
+      <c r="H120" s="4" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="121">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Kitchen Renovation Timeline: Week by Week, What Happens</t>
+          <t>Kitchen Demolition: What Tear-Out Day Actually Involves</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>kitchen renovation timeline</t>
+          <t>kitchen demolition</t>
         </is>
       </c>
       <c r="D121" s="9" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -5135,10 +5135,10 @@
         </is>
       </c>
       <c r="G121" s="3" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H121" s="6" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -6679,9 +6679,9 @@
       <c r="F8" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="G8" s="11" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -6712,9 +6712,9 @@
       <c r="F9" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="G9" s="11" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -7009,9 +7009,9 @@
       <c r="F18" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="G18" s="11" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -7108,9 +7108,9 @@
       <c r="F21" s="6" t="n">
         <v>48</v>
       </c>
-      <c r="G21" s="11" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -7405,9 +7405,9 @@
       <c r="F30" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="G30" s="11" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -7603,9 +7603,9 @@
       <c r="F36" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="G36" s="11" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -7801,9 +7801,9 @@
       <c r="F42" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="G42" s="11" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -8032,9 +8032,9 @@
       <c r="F49" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="G49" s="11" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -8098,9 +8098,9 @@
       <c r="F51" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="G51" s="11" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -9154,9 +9154,9 @@
       <c r="F83" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="G83" s="11" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -9187,9 +9187,9 @@
       <c r="F84" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="G84" s="11" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -9715,9 +9715,9 @@
       <c r="F100" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G100" s="11" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -9847,9 +9847,9 @@
       <c r="F104" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G104" s="11" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -9880,9 +9880,9 @@
       <c r="F105" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G105" s="11" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -9946,9 +9946,9 @@
       <c r="F107" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G107" s="11" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -10177,9 +10177,9 @@
       <c r="F114" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G114" s="11" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -10540,9 +10540,9 @@
       <c r="F125" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G125" s="11" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -10969,9 +10969,9 @@
       <c r="F138" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G138" s="11" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -11002,9 +11002,9 @@
       <c r="F139" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G139" s="11" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -11101,9 +11101,9 @@
       <c r="F142" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G142" s="11" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -11629,9 +11629,9 @@
       <c r="F158" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G158" s="11" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -11761,9 +11761,9 @@
       <c r="F162" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G162" s="11" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -13741,9 +13741,9 @@
       <c r="F222" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="G222" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G222" s="11" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>

--- a/decks/7-day-kitchens/keyword-research.xlsx
+++ b/decks/7-day-kitchens/keyword-research.xlsx
@@ -665,7 +665,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kitchen Design Charlotte NC: One Local Crew, Start to Finish</t>
+          <t>Kitchen Design Charlotte NC: The 7-Day Difference, Explained</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kitchen Remodeling South West Charlotte: A Faster Path to Your Dream Kitchen</t>
+          <t>Kitchen Remodel Timeline in Indian Land, SC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>kitchen remodeling south west charlotte</t>
+          <t>kitchen remodeling indian land sc</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
         <v>40</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9">
@@ -855,12 +855,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>High-End Kitchen Remodels in Charlotte: Premium, Fixed-Price</t>
+          <t>Custom Kitchen Remodels in Charlotte: Built Around Your Space</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>high-end kitchen remodel charlotte</t>
+          <t>custom kitchen remodel charlotte</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kitchen Remodel Timeline in Concord, NC: Week by Week</t>
+          <t>Kitchen Design Trends in Belmont, NC Homes</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>kitchen remodeling concord nc</t>
+          <t>kitchen remodeling belmont nc</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -917,10 +917,10 @@
         </is>
       </c>
       <c r="G10" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11">
@@ -931,12 +931,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kitchen Remodel Raintree NC: Local Crews, Lifetime Warranty</t>
+          <t>Planning a Kitchen Remodel in Pineville, NC: A Checklist</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>kitchen remodel raintree nc</t>
+          <t>kitchen remodeling pineville nc</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="G11" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H11" s="4" t="n">
         <v>18</v>
@@ -1045,7 +1045,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cabinet Installation Charlotte NC: What the Process Looks Like Here</t>
+          <t>Cabinet Installation Charlotte NC, Done the Fixed-Price Way</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1083,17 +1083,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>A Belmont Park Kitchen Remodel: Start to Finish in One Week</t>
+          <t>Why Charlotte Homeowners Choose Fixed-Price Kitchen Remodels</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>belmont park kitchen remodel</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Charlotte &amp; Local</t>
+          <t>fixed price kitchen remodel</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Cost &amp; Budget</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1109,8 +1109,8 @@
       <c r="G15" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="H15" s="4" t="n">
-        <v>18</v>
+      <c r="H15" s="6" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="16">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Why Charlotte Homeowners Choose Fixed-Price Kitchen Remodels</t>
+          <t>What Quartz Countertops Cost in Charlotte, Installed</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>fixed price kitchen remodel</t>
+          <t>cost of quartz countertops</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="H16" s="6" t="n">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="17">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>What Quartz Countertops Cost in Charlotte, Installed</t>
+          <t>Small Kitchen Remodels: Where the Budget Goes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>cost of quartz countertops</t>
+          <t>small kitchen remodel price</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
@@ -1179,14 +1179,14 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Buyer</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G17" s="3" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Small Kitchen Remodels: Where the Budget Goes</t>
+          <t>Laminate Countertops: The Budget-Friendly Counter Option</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>small kitchen remodel price</t>
+          <t>laminate countertop cost</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -1217,14 +1217,14 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G18" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="H18" s="4" t="n">
-        <v>23</v>
+      <c r="H18" s="6" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="19">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Laminate Countertops: The Budget-Friendly Counter Option</t>
+          <t>Kitchen Backsplash Prices in Charlotte, Weighed Honestly</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>laminate countertop cost</t>
+          <t>backsplash prices</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -1262,7 +1262,7 @@
         <v>10</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -1273,22 +1273,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Kitchen Backsplash Prices in Charlotte, Weighed Honestly</t>
+          <t>Cabinet Refacing in Charlotte, NC: When It Makes Sense</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>backsplash prices</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>Cost &amp; Budget</t>
+          <t>cabinet refacing charlotte nc</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="H20" s="6" t="n">
-        <v>36</v>
+        <v>102</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="21">
@@ -1311,12 +1311,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cabinet Refacing in Charlotte, NC: When It Makes Sense</t>
+          <t>Peel and Stick Tile Backsplash: The Trade-offs That Matter</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>cabinet refacing charlotte nc</t>
+          <t>peel and stick tile backsplash</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1335,10 +1335,10 @@
         </is>
       </c>
       <c r="G21" s="3" t="n">
-        <v>102</v>
+        <v>54</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Peel and Stick Tile Backsplash: The Trade-offs That Matter</t>
+          <t>Quartz Countertops: Why They Dominate Modern Kitchens</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>peel and stick tile backsplash</t>
+          <t>quartz countertops</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
@@ -1373,10 +1373,10 @@
         </is>
       </c>
       <c r="G22" s="3" t="n">
-        <v>54</v>
+        <v>905</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Quartz Countertops: Why They Dominate Modern Kitchens</t>
+          <t>Kitchen Countertops in Charlotte: Quartz, Granite, and the Alternatives</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>quartz countertops</t>
+          <t>kitchen countertops</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
@@ -1411,10 +1411,10 @@
         </is>
       </c>
       <c r="G23" s="3" t="n">
-        <v>905</v>
-      </c>
-      <c r="H23" s="4" t="n">
-        <v>28</v>
+        <v>331</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="24">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Kitchen Countertops in Charlotte: Quartz, Granite, and the Alternatives</t>
+          <t>Adding a Scullery to Your Kitchen: The Hidden Prep-Space Trend</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>kitchen countertops</t>
+          <t>kitchen scullery</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="G24" s="3" t="n">
-        <v>331</v>
+        <v>181</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Adding a Scullery to Your Kitchen: The Hidden Prep-Space Trend</t>
+          <t>Kitchen Island Ideas: Sizing, Seating, and Smart Storage</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>kitchen scullery</t>
+          <t>kitchen island ideas</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
@@ -1483,14 +1483,14 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Buyer</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G25" s="3" t="n">
-        <v>181</v>
+        <v>121</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="26">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Kitchen Island Ideas: Sizing, Seating, and Smart Storage</t>
+          <t>Kitchen Tile: Floor, Backsplash, and Where Each Works</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>kitchen island ideas</t>
+          <t>kitchen tile</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
@@ -1516,19 +1516,19 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>121</v>
+        <v>66</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
     </row>
     <row r="27">
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Kitchen Tile: Floor, Backsplash, and Where Each Works</t>
+          <t>Kitchen Accessories: What to Know Before You Commit</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>kitchen tile</t>
+          <t>kitchen accessories</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
@@ -1565,8 +1565,8 @@
       <c r="G27" s="3" t="n">
         <v>66</v>
       </c>
-      <c r="H27" s="6" t="n">
-        <v>31</v>
+      <c r="H27" s="8" t="n">
+        <v>52</v>
       </c>
     </row>
     <row r="28">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Kitchen Accessories: What to Know Before You Commit</t>
+          <t>Kitchen Equipment: Compared on Cost, Durability, and Looks</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>kitchen accessories</t>
+          <t>kitchen equipment</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="G28" s="3" t="n">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="H28" s="8" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Kitchen Equipment: Compared on Cost, Durability, and Looks</t>
+          <t>Kitchen Storage Ideas That Use Every Inch</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>kitchen equipment</t>
+          <t>kitchen storage ideas</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
@@ -1630,19 +1630,19 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Buyer</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="H29" s="8" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="30">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Kitchen Storage Ideas That Use Every Inch</t>
+          <t>Kitchen Cabinet Styles: Shaker, Flat-Panel, and Beyond</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>kitchen storage ideas</t>
+          <t>kitchen cabinet styles</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
@@ -1673,14 +1673,14 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="H30" s="8" t="n">
-        <v>52</v>
+        <v>24</v>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="31">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Kitchen Cabinet Styles: Shaker, Flat-Panel, and Beyond</t>
+          <t>Kitchen Remodel Before and After: What a Week Can Change</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>kitchen cabinet styles</t>
+          <t>kitchen remodel before and after</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
@@ -1711,14 +1711,14 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Buyer</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G31" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="H31" s="4" t="n">
-        <v>26</v>
+        <v>10</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="32">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Kitchen Remodel Before and After: What a Week Can Change</t>
+          <t>Quartz vs Granite in Charlotte Kitchens: Which Wins</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>kitchen remodel before and after</t>
+          <t>quartz vs granite</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
@@ -1744,19 +1744,19 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G32" s="3" t="n">
         <v>10</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
     </row>
     <row r="33">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Quartz vs Granite in Charlotte Kitchens: Which Wins</t>
+          <t>Kitchen Flooring for Charlotte Homes: Ranked for Durability</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>quartz vs granite</t>
+          <t>kitchen flooring options</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Kitchen Flooring for Charlotte Homes: Ranked for Durability</t>
+          <t>Farmhouse Kitchen Ideas That Still Feel Fresh in 2026</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>kitchen flooring options</t>
+          <t>farmhouse kitchen ideas</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Buyer</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G34" s="3" t="n">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Farmhouse Kitchen Ideas That Still Feel Fresh in 2026</t>
+          <t>Choosing a Kitchen Faucet: Finishes, Features, and Value</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>farmhouse kitchen ideas</t>
+          <t>kitchen faucet ideas</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Choosing a Kitchen Faucet: Finishes, Features, and Value</t>
+          <t>Cabinet Hardware: The Small Detail That Sets the Tone</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>kitchen faucet ideas</t>
+          <t>cabinet hardware ideas</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1919,12 +1919,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Cabinet Hardware: The Small Detail That Sets the Tone</t>
+          <t>Butler's Pantry Ideas: A Kitchen Upgrade That Adds Real Value</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>cabinet hardware ideas</t>
+          <t>butler pantry ideas</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
@@ -1957,34 +1957,34 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Butler's Pantry Ideas: A Kitchen Upgrade That Adds Real Value</t>
+          <t>How to Choose a Kitchen Remodel Contractor in Rock Hill, SC</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>butler pantry ideas</t>
-        </is>
-      </c>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>contractor for kitchen remodel rock hill sc</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>Process &amp; Planning</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G38" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="H38" s="6" t="n">
-        <v>38</v>
+      <c r="H38" s="4" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="39">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Kitchen Remodeling Services Charlotte: Built Around Your Home and Budget</t>
+          <t>Kitchen Remodeling Services Charlotte: A Faster Path to Your Dream Kitchen</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Fast Kitchen Remodel Charlotte: The 7-Day Difference, Explained</t>
+          <t>Waterfront Kitchen Design in Tega Cay, SC</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>fast kitchen remodel charlotte</t>
+          <t>kitchen remodeling tega cay sc</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -2361,10 +2361,10 @@
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="49">
@@ -2375,12 +2375,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Kitchen Remodel Cost in Cornelius, NC: Lake-Area Pricing</t>
+          <t>High-End Kitchen Remodels in Charlotte: Premium, Fixed-Price</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>kitchen remodeling cornelius nc</t>
+          <t>high-end kitchen remodel charlotte</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="G49" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H49" s="4" t="n">
         <v>18</v>
@@ -2413,12 +2413,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Full Kitchen Remodels in Charlotte: Everything, One Fixed Price</t>
+          <t>Kitchen Remodel Timeline in Concord, NC: Week by Week</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>full kitchen remodel charlotte</t>
+          <t>kitchen remodeling concord nc</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Planning a Kitchen Remodel in Pineville, NC: A Checklist</t>
+          <t>Kitchen Remodel Cost in Weddington, NC</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>kitchen remodeling pineville nc</t>
+          <t>kitchen remodeling weddington nc</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -2475,7 +2475,7 @@
         </is>
       </c>
       <c r="G51" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H51" s="4" t="n">
         <v>18</v>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Affordable Kitchen Remodel Charlotte NC: A Faster Path to Your Dream Kitchen</t>
+          <t>Affordable Kitchen Remodel Charlotte NC: Fixed Pricing, Finished in 7 Days</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2603,34 +2603,34 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>What Granite Countertops Cost, Installed</t>
+          <t>How to Choose a Kitchen Remodeler in Clover, SC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>cost of granite countertops</t>
-        </is>
-      </c>
-      <c r="D55" s="5" t="inlineStr">
-        <is>
-          <t>Cost &amp; Budget</t>
+          <t>kitchen remodeling clover sc</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G55" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="H55" s="4" t="n">
-        <v>20</v>
+        <v>10</v>
+      </c>
+      <c r="H55" s="6" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="56">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>What a Small Kitchen Remodel Really Costs</t>
+          <t>What Granite Countertops Cost, Installed</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>average cost of small kitchen remodel</t>
+          <t>cost of granite countertops</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
@@ -2665,10 +2665,10 @@
         </is>
       </c>
       <c r="G56" s="3" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="H56" s="4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="57">
@@ -2679,12 +2679,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>The Average Cost of a Kitchen Remodel in Charlotte</t>
+          <t>What a Small Kitchen Remodel Really Costs</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>average cost of kitchen remodel</t>
+          <t>average cost of small kitchen remodel</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Buyer</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G57" s="3" t="n">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>How to Set a Kitchen Remodel Budget You Won't Blow Through</t>
+          <t>The Average Cost of a Kitchen Remodel in Charlotte</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>kitchen remodel budget</t>
+          <t>average cost of kitchen remodel</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
@@ -2732,7 +2732,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="G58" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="H58" s="6" t="n">
-        <v>40</v>
+        <v>10</v>
+      </c>
+      <c r="H58" s="4" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="59">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Cheap Backsplash Ideas: A Plain-English Cost Primer</t>
+          <t>How to Set a Kitchen Remodel Budget You Won't Blow Through</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>cheap backsplash ideas</t>
+          <t>kitchen remodel budget</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="G59" s="3" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="H59" s="6" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="60">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Budget Backsplash Ideas That Still Look High-End</t>
+          <t>Cheap Backsplash Ideas: A Plain-English Cost Primer</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>cheap backsplash</t>
+          <t>cheap backsplash ideas</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2819,8 +2819,8 @@
       <c r="G60" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="H60" s="4" t="n">
-        <v>28</v>
+      <c r="H60" s="6" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="61">
@@ -2831,12 +2831,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Kitchen Renovation Cost in Charlotte: A Room-by-Room Money Map</t>
+          <t>Budget Backsplash Ideas That Still Look High-End</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>kitchen renovation cost</t>
+          <t>cheap backsplash</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
@@ -2855,10 +2855,10 @@
         </is>
       </c>
       <c r="G61" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="H61" s="6" t="n">
-        <v>38</v>
+        <v>10</v>
+      </c>
+      <c r="H61" s="4" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="62">
@@ -2869,12 +2869,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Financing a Kitchen Remodel in Charlotte: Your Options</t>
+          <t>Kitchen Renovation Cost in Charlotte: A Room-by-Room Money Map</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>kitchen remodel financing</t>
+          <t>kitchen renovation cost</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
@@ -2893,10 +2893,10 @@
         </is>
       </c>
       <c r="G62" s="3" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="H62" s="6" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
     </row>
     <row r="63">
@@ -2907,17 +2907,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Choosing Kitchen Cabinets in Charlotte: Styles and What Lasts</t>
+          <t>Financing a Kitchen Remodel in Charlotte: Your Options</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>kitchen cabinets</t>
-        </is>
-      </c>
-      <c r="D63" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>kitchen remodel financing</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>Cost &amp; Budget</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2931,10 +2931,10 @@
         </is>
       </c>
       <c r="G63" s="3" t="n">
-        <v>1650</v>
-      </c>
-      <c r="H63" s="8" t="n">
-        <v>55</v>
+        <v>10</v>
+      </c>
+      <c r="H63" s="6" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="64">
@@ -2945,12 +2945,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Stick on Backsplash: What to Weigh First</t>
+          <t>Choosing Kitchen Cabinets in Charlotte: Styles and What Lasts</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>stick on backsplash</t>
+          <t>kitchen cabinets</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="G64" s="3" t="n">
-        <v>44</v>
-      </c>
-      <c r="H64" s="4" t="n">
-        <v>20</v>
+        <v>1650</v>
+      </c>
+      <c r="H64" s="8" t="n">
+        <v>55</v>
       </c>
     </row>
     <row r="65">
@@ -2983,12 +2983,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Should Your Charlotte Kitchen Have an Island? A Layout Guide</t>
+          <t>Stick on Backsplash: What to Weigh First</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>kitchen island</t>
+          <t>stick on backsplash</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
@@ -3007,10 +3007,10 @@
         </is>
       </c>
       <c r="G65" s="3" t="n">
-        <v>905</v>
-      </c>
-      <c r="H65" s="8" t="n">
-        <v>52</v>
+        <v>44</v>
+      </c>
+      <c r="H65" s="4" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="66">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Kitchen Island with Seating: What Designers Pick and Why</t>
+          <t>Should Your Charlotte Kitchen Have an Island? A Layout Guide</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>kitchen island with seating</t>
+          <t>kitchen island</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
@@ -3041,14 +3041,14 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G66" s="3" t="n">
-        <v>271</v>
-      </c>
-      <c r="H66" s="6" t="n">
-        <v>44</v>
+        <v>905</v>
+      </c>
+      <c r="H66" s="8" t="n">
+        <v>52</v>
       </c>
     </row>
     <row r="67">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Kitchen Utensils: A Homeowner's Buyer Guide</t>
+          <t>Kitchen Island with Seating: What Designers Pick and Why</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>kitchen utensils</t>
+          <t>kitchen island with seating</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="G67" s="3" t="n">
-        <v>181</v>
+        <v>271</v>
       </c>
       <c r="H67" s="6" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
     </row>
     <row r="68">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Subway Tile Backsplash: The Timeless Default, Done Right</t>
+          <t>Kitchen Utensils: A Homeowner's Buyer Guide</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>subway tile backsplash</t>
+          <t>kitchen utensils</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
@@ -3117,14 +3117,14 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Buyer</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G68" s="3" t="n">
-        <v>121</v>
+        <v>181</v>
       </c>
       <c r="H68" s="6" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="69">
@@ -3135,12 +3135,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Kitchen Island with Storage: Weighed Honestly for Your Budget</t>
+          <t>Subway Tile Backsplash: The Timeless Default, Done Right</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>kitchen island with storage</t>
+          <t>subway tile backsplash</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
@@ -3159,10 +3159,10 @@
         </is>
       </c>
       <c r="G69" s="3" t="n">
-        <v>66</v>
+        <v>121</v>
       </c>
       <c r="H69" s="6" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
     </row>
     <row r="70">
@@ -3173,12 +3173,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Choosing Kitchen Essentials Without Regret</t>
+          <t>Kitchen Island with Storage: Weighed Honestly for Your Budget</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>kitchen essentials</t>
+          <t>kitchen island with storage</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
@@ -3197,10 +3197,10 @@
         </is>
       </c>
       <c r="G70" s="3" t="n">
-        <v>54</v>
-      </c>
-      <c r="H70" s="8" t="n">
-        <v>60</v>
+        <v>66</v>
+      </c>
+      <c r="H70" s="6" t="n">
+        <v>42</v>
       </c>
     </row>
     <row r="71">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Galley Kitchen Ideas: Big Function in a Narrow Footprint</t>
+          <t>Choosing Kitchen Essentials Without Regret</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>galley kitchen ideas</t>
+          <t>kitchen essentials</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
@@ -3226,19 +3226,19 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G71" s="3" t="n">
-        <v>36</v>
-      </c>
-      <c r="H71" s="6" t="n">
-        <v>34</v>
+        <v>54</v>
+      </c>
+      <c r="H71" s="8" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="72">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Waterfall Islands: The Statement Feature Worth the Splurge</t>
+          <t>Galley Kitchen Ideas: Big Function in a Narrow Footprint</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>waterfall island</t>
+          <t>galley kitchen ideas</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
@@ -3269,14 +3269,14 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Buyer</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G72" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="H72" s="4" t="n">
-        <v>28</v>
+        <v>36</v>
+      </c>
+      <c r="H72" s="6" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="73">
@@ -3287,12 +3287,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Kitchen Layout Basics: Work Triangles, Walkways, and Flow</t>
+          <t>Waterfall Islands: The Statement Feature Worth the Splurge</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>kitchen layout</t>
+          <t>waterfall island</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
@@ -3311,10 +3311,10 @@
         </is>
       </c>
       <c r="G73" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="H73" s="6" t="n">
-        <v>48</v>
+        <v>29</v>
+      </c>
+      <c r="H73" s="4" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="74">
@@ -3325,12 +3325,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Kitchen Lighting Ideas: Layering Task, Ambient, and Accent</t>
+          <t>Kitchen Layout Basics: Work Triangles, Walkways, and Flow</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>kitchen lighting ideas</t>
+          <t>kitchen layout</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
@@ -3345,14 +3345,14 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G74" s="3" t="n">
         <v>10</v>
       </c>
       <c r="H74" s="6" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
     </row>
     <row r="75">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Modern Kitchen Design: Clean Lines Without the Cold Feel</t>
+          <t>Kitchen Lighting Ideas: Layering Task, Ambient, and Accent</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>modern kitchen design</t>
+          <t>kitchen lighting ideas</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Buyer</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G75" s="3" t="n">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Pantry Ideas: Designing Storage That Earns Its Footprint</t>
+          <t>Modern Kitchen Design: Clean Lines Without the Cold Feel</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>pantry ideas</t>
+          <t>modern kitchen design</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
@@ -3421,14 +3421,14 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G76" s="3" t="n">
         <v>10</v>
       </c>
       <c r="H76" s="6" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
     </row>
     <row r="77">
@@ -3439,12 +3439,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Two-Tone Kitchen Cabinets: How to Mix Without a Mess</t>
+          <t>Pantry Ideas: Designing Storage That Earns Its Footprint</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>two tone kitchen cabinets</t>
+          <t>pantry ideas</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
@@ -3459,14 +3459,14 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Buyer</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G77" s="3" t="n">
         <v>10</v>
       </c>
       <c r="H77" s="6" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
     </row>
     <row r="78">
@@ -3477,12 +3477,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Walk-In Pantry Ideas for Your Kitchen Remodel</t>
+          <t>Two-Tone Kitchen Cabinets: How to Mix Without a Mess</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>walk in pantry ideas</t>
+          <t>two tone kitchen cabinets</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="G78" s="3" t="n">
@@ -3515,34 +3515,34 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>How to Choose a Kitchen Remodel Contractor in Rock Hill, SC</t>
+          <t>Walk-In Pantry Ideas for Your Kitchen Remodel</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>contractor for kitchen remodel rock hill sc</t>
-        </is>
-      </c>
-      <c r="D79" s="9" t="inlineStr">
-        <is>
-          <t>Process &amp; Planning</t>
+          <t>walk in pantry ideas</t>
+        </is>
+      </c>
+      <c r="D79" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Buyer</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G79" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="H79" s="4" t="n">
-        <v>24</v>
+      <c r="H79" s="6" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="80">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Waterfront Kitchen Design in Tega Cay, SC</t>
+          <t>Kitchen Design Ideas for Cramerton, NC Homes</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>kitchen remodeling tega cay sc</t>
+          <t>kitchen remodeling cramerton nc</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -3846,7 +3846,7 @@
         <v>40</v>
       </c>
       <c r="H87" s="4" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="88">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Custom Kitchen Remodels in Charlotte: Built Around Your Space</t>
+          <t>Fast Kitchen Remodel Charlotte: Where Speed Meets Craftsmanship</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>custom kitchen remodel charlotte</t>
+          <t>fast kitchen remodel charlotte</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -3881,7 +3881,7 @@
         </is>
       </c>
       <c r="G88" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H88" s="4" t="n">
         <v>18</v>
@@ -3895,12 +3895,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Kitchen Design Trends in Belmont, NC Homes</t>
+          <t>Kitchen Remodel Cost in Cornelius, NC: Lake-Area Pricing</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>kitchen remodeling belmont nc</t>
+          <t>kitchen remodeling cornelius nc</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -3919,10 +3919,10 @@
         </is>
       </c>
       <c r="G89" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H89" s="4" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="90">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Kitchen Remodel Providence Plantation NC: Fixed Pricing, Finished in 7 Days</t>
+          <t>Full Kitchen Remodels in Charlotte: Everything, One Fixed Price</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>kitchen remodel providence plantation nc</t>
+          <t>full kitchen remodel charlotte</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -3957,7 +3957,7 @@
         </is>
       </c>
       <c r="G90" s="3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H90" s="4" t="n">
         <v>18</v>
@@ -3971,12 +3971,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Ballantyne Kitchen Remodeling: Premium Results Without the Wait</t>
+          <t>Planning a Kitchen Remodel in Monroe, NC</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>kitchen remodeling ballantyne</t>
+          <t>kitchen remodeling monroe nc</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -5152,7 +5152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5908,28 +5908,28 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Service Area</t>
+          <t>Kitchen + X</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ballantyne</t>
+          <t>Kitchen + Mudroom</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>kitchen remodeling ballantyne</t>
+          <t>kitchen and mudroom</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F18" s="12" t="inlineStr">
         <is>
@@ -5938,17 +5938,17 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>New (neighborhood)</t>
+          <t>New</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Affluent South Charlotte neighborhood — NOT among the 26 city pages; worth adding.</t>
+          <t>Intent-accuracy; supporting page.</t>
         </is>
       </c>
     </row>
@@ -5960,26 +5960,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Kitchen + X</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Kitchen + Mudroom</t>
+          <t>Custom Kitchens</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>kitchen and mudroom</t>
+          <t>custom kitchen</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F19" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
+        <v>16</v>
+      </c>
+      <c r="F19" s="8" t="n">
+        <v>58</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -5993,36 +5991,36 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Intent-accuracy; supporting page.</t>
+          <t>Bespoke positioning.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="14" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Segment</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Custom Kitchens</t>
+          <t>Quartz Countertops</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>custom kitchen</t>
+          <t>quartz countertops</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="F20" s="8" t="n">
-        <v>58</v>
+        <v>905</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>28</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -6036,7 +6034,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Bespoke positioning.</t>
+          <t>EASY WIN (KD 28) on the #1 countertop material. The real countertop money page.</t>
         </is>
       </c>
     </row>
@@ -6053,76 +6051,76 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Quartz Countertops</t>
+          <t>Granite Countertops</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>quartz countertops</t>
+          <t>granite countertops</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
+        <v>605</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Winnable (KD 36). Pair with quartz under a Countertops hub page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Kitchen Islands</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>kitchen island</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n">
         <v>905</v>
       </c>
-      <c r="F21" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Buyer</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
+      <c r="F22" s="8" t="n">
+        <v>61</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>EASY WIN (KD 28) on the #1 countertop material. The real countertop money page.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="13" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Component</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Granite Countertops</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>granite countertops</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>605</v>
-      </c>
-      <c r="F22" s="6" t="n">
-        <v>36</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Buyer</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Winnable (KD 36). Pair with quartz under a Countertops hub page.</t>
+          <t>Highest demand of all (90.5K); high KD. Feature page funneling to remodels.</t>
         </is>
       </c>
     </row>
@@ -6139,19 +6137,19 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kitchen Islands</t>
+          <t>Kitchen Backsplash</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>kitchen island</t>
+          <t>kitchen backsplash ideas</t>
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>905</v>
-      </c>
-      <c r="F23" s="8" t="n">
-        <v>61</v>
+        <v>181</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>28</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -6165,7 +6163,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Highest demand of all (90.5K); high KD. Feature page funneling to remodels.</t>
+          <t>Retarget to 'backsplash ideas' (KD 28) over generic 'kitchen backsplash' (KD 44).</t>
         </is>
       </c>
     </row>
@@ -6177,38 +6175,42 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Service Area</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Kitchen Backsplash</t>
+          <t>Weddington, NC</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>kitchen backsplash ideas</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>181</v>
-      </c>
-      <c r="F24" s="4" t="n">
-        <v>28</v>
+          <t>kitchen remodeling weddington nc</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Buyer</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>New</t>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="H24" s="11" t="inlineStr">
+        <is>
+          <t>Have — optimize</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Retarget to 'backsplash ideas' (KD 28) over generic 'kitchen backsplash' (KD 44).</t>
+          <t>Page EXISTS.</t>
         </is>
       </c>
     </row>
@@ -6225,24 +6227,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Weddington, NC</t>
+          <t>Fort Mill, SC</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>kitchen remodeling weddington nc</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
+          <t>kitchen remodeling fort mill sc</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F25" s="12" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="F25" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
       <c r="G25" t="inlineStr">
         <is>
           <t>Local</t>
@@ -6255,7 +6255,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Page EXISTS.</t>
+          <t>Page EXISTS. SC side of the metro.</t>
         </is>
       </c>
     </row>
@@ -6272,16 +6272,18 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Fort Mill, SC</t>
+          <t>Huntersville / Mooresville / Belmont / +18 more</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>kitchen remodeling fort mill sc</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>10</v>
+          <t>kitchen remodeling &lt;suburb&gt; nc</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
       </c>
       <c r="F26" s="12" t="inlineStr">
         <is>
@@ -6299,53 +6301,6 @@
         </is>
       </c>
       <c r="I26" t="inlineStr">
-        <is>
-          <t>Page EXISTS. SC side of the metro.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="14" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Service Area</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Huntersville / Mooresville / Belmont / +18 more</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>kitchen remodeling &lt;suburb&gt; nc</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="F27" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="H27" s="11" t="inlineStr">
-        <is>
-          <t>Have — optimize</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
         <is>
           <t>26 suburb pages EXIST total. The work is RANKING them via linked content, not building new ones.</t>
         </is>
@@ -7338,17 +7293,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>kitchen remodeling south west charlotte</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>Charlotte &amp; Local</t>
+          <t>kitchen remodel price</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Cost &amp; Budget</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -7357,31 +7312,31 @@
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="F30" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="G30" s="11" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+        <v>10</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>kitchen remodel price</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>Cost &amp; Budget</t>
+          <t>kitchen remodeling services</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -7404,12 +7359,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>kitchen remodeling services</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>cabinet refacing charlotte</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -7423,10 +7378,10 @@
         </is>
       </c>
       <c r="E32" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F32" s="6" t="n">
         <v>38</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>24</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -7437,26 +7392,26 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>cabinet refacing charlotte</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>Charlotte &amp; Local</t>
+          <t>how long does a kitchen renovation take</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>Process &amp; Planning</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Buyer</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="E33" s="3" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="F33" s="4" t="n">
         <v>24</v>
@@ -7470,29 +7425,29 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>how long does a kitchen renovation take</t>
-        </is>
-      </c>
-      <c r="B34" s="9" t="inlineStr">
-        <is>
-          <t>Process &amp; Planning</t>
+          <t>kitchen remodel estimate</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Cost &amp; Budget</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E34" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F34" s="4" t="n">
-        <v>24</v>
+      <c r="F34" s="6" t="n">
+        <v>38</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -7503,17 +7458,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>kitchen remodel estimate</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>Cost &amp; Budget</t>
+          <t>kitchen contractor</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>Process &amp; Planning</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7525,7 +7480,7 @@
         <v>10</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -7536,17 +7491,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>kitchen contractor</t>
-        </is>
-      </c>
-      <c r="B36" s="9" t="inlineStr">
-        <is>
-          <t>Process &amp; Planning</t>
+          <t>how much to remodel a kitchen</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Cost &amp; Budget</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7557,8 +7512,8 @@
       <c r="E36" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F36" s="6" t="n">
-        <v>48</v>
+      <c r="F36" s="4" t="n">
+        <v>24</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -7569,29 +7524,29 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>how much to remodel a kitchen</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>Cost &amp; Budget</t>
+          <t>kitchen remodel process</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>Process &amp; Planning</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Buyer</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="E37" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F37" s="4" t="n">
-        <v>24</v>
+      <c r="F37" s="6" t="n">
+        <v>38</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -7602,22 +7557,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>kitchen remodel process</t>
-        </is>
-      </c>
-      <c r="B38" s="9" t="inlineStr">
-        <is>
-          <t>Process &amp; Planning</t>
+          <t>fast kitchen remodel</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E38" s="3" t="n">
@@ -7635,12 +7590,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>fast kitchen remodel</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>free kitchen remodel estimate</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Cost &amp; Budget</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -7657,7 +7612,7 @@
         <v>10</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -7668,12 +7623,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>free kitchen remodel estimate</t>
-        </is>
-      </c>
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t>Cost &amp; Budget</t>
+          <t>kitchen builders</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -7690,7 +7645,7 @@
         <v>10</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -7701,7 +7656,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>kitchen builders</t>
+          <t>custom kitchen remodel</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
@@ -7723,7 +7678,7 @@
         <v>10</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -7734,7 +7689,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>custom kitchen remodel</t>
+          <t>kitchen remodel timing</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
@@ -7767,12 +7722,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>kitchen remodel timing</t>
-        </is>
-      </c>
-      <c r="B43" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>kitchen prices</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Cost &amp; Budget</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -7789,7 +7744,7 @@
         <v>10</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -7800,12 +7755,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>kitchen prices</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>Cost &amp; Budget</t>
+          <t>kitchen remodel time</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -7822,7 +7777,7 @@
         <v>10</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -7833,7 +7788,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>kitchen remodel time</t>
+          <t>new kitchen quote</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
@@ -7866,7 +7821,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>new kitchen quote</t>
+          <t>order of kitchen remodel</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
@@ -7888,7 +7843,7 @@
         <v>10</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -7899,12 +7854,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>order of kitchen remodel</t>
-        </is>
-      </c>
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>kitchen renovation timeline</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>Process &amp; Planning</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -7921,7 +7876,7 @@
         <v>10</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -7932,7 +7887,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>kitchen renovation timeline</t>
+          <t>kitchen remodeling contractor</t>
         </is>
       </c>
       <c r="B48" s="9" t="inlineStr">
@@ -7942,7 +7897,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -7965,12 +7920,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>kitchen remodeling contractor</t>
-        </is>
-      </c>
-      <c r="B49" s="9" t="inlineStr">
-        <is>
-          <t>Process &amp; Planning</t>
+          <t>kitchen design and build charlotte nc</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -7984,21 +7939,21 @@
         </is>
       </c>
       <c r="E49" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F49" s="6" t="n">
-        <v>38</v>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+        <v>22</v>
+      </c>
+      <c r="F49" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="G49" s="11" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>kitchen design and build charlotte nc</t>
+          <t>kitchen remodel marvin nc</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -8017,7 +7972,7 @@
         </is>
       </c>
       <c r="E50" s="3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F50" s="4" t="n">
         <v>18</v>
@@ -8031,7 +7986,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>kitchen remodel marvin nc</t>
+          <t>kitchen remodeling contractors charlotte nc</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -8050,21 +8005,21 @@
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F51" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="G51" s="11" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>kitchen remodeling contractors charlotte nc</t>
+          <t>waxhaw kitchen remodeling</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -8086,7 +8041,7 @@
         <v>20</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -8097,12 +8052,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>waxhaw kitchen remodeling</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>Charlotte &amp; Local</t>
+          <t>kitchen remodeling company</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -8116,10 +8071,10 @@
         </is>
       </c>
       <c r="E53" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="F53" s="4" t="n">
-        <v>24</v>
+        <v>10</v>
+      </c>
+      <c r="F53" s="6" t="n">
+        <v>38</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -8130,7 +8085,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>kitchen remodeling company</t>
+          <t>kitchen renovation services</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
@@ -8163,12 +8118,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>kitchen renovation services</t>
-        </is>
-      </c>
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>kitchen designers charlotte nc</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -8182,10 +8137,10 @@
         </is>
       </c>
       <c r="E55" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F55" s="6" t="n">
-        <v>38</v>
+        <v>19</v>
+      </c>
+      <c r="F55" s="4" t="n">
+        <v>18</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -8196,7 +8151,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>kitchen designers charlotte nc</t>
+          <t>kitchen remodelers charlotte nc</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -8229,7 +8184,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>kitchen remodelers charlotte nc</t>
+          <t>best kitchen remodeling contractors charlotte</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -8262,7 +8217,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>best kitchen remodeling contractors charlotte</t>
+          <t>kitchen remodeling matthews nc</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -8286,26 +8241,26 @@
       <c r="F58" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G58" s="11" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>kitchen remodeling matthews nc</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>Charlotte &amp; Local</t>
+          <t>kitchen remodel order of steps</t>
+        </is>
+      </c>
+      <c r="B59" s="9" t="inlineStr">
+        <is>
+          <t>Process &amp; Planning</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8314,31 +8269,31 @@
         </is>
       </c>
       <c r="E59" s="3" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="G59" s="11" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+        <v>24</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>kitchen remodel order of steps</t>
-        </is>
-      </c>
-      <c r="B60" s="9" t="inlineStr">
-        <is>
-          <t>Process &amp; Planning</t>
+          <t>kitchen remodeling services in waxhaw nc</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8347,10 +8302,10 @@
         </is>
       </c>
       <c r="E60" s="3" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -8361,7 +8316,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>kitchen remodeling services in waxhaw nc</t>
+          <t>fast kitchen remodel charlotte</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -8380,87 +8335,87 @@
         </is>
       </c>
       <c r="E61" s="3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F61" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G61" s="11" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>fast kitchen remodel charlotte</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>Charlotte &amp; Local</t>
+          <t>how long for a kitchen remodel</t>
+        </is>
+      </c>
+      <c r="B62" s="9" t="inlineStr">
+        <is>
+          <t>Process &amp; Planning</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Buyer</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="E62" s="3" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="G62" s="11" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+        <v>24</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>how long for a kitchen remodel</t>
-        </is>
-      </c>
-      <c r="B63" s="9" t="inlineStr">
-        <is>
-          <t>Process &amp; Planning</t>
+          <t>kitchen remodeling mooresville nc</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E63" s="3" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+        <v>18</v>
+      </c>
+      <c r="G63" s="11" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>kitchen remodeling mooresville nc</t>
+          <t>mooresville kitchen remodeling</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -8470,7 +8425,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8482,18 +8437,18 @@
         <v>18</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="G64" s="11" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+        <v>24</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>mooresville kitchen remodeling</t>
+          <t>kitchen design charlotte nc</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -8503,7 +8458,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8512,21 +8467,21 @@
         </is>
       </c>
       <c r="E65" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F65" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="F65" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G65" s="11" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>kitchen design charlotte nc</t>
+          <t>custom kitchen remodel charlotte</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -8559,17 +8514,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>custom kitchen remodel charlotte</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>Charlotte &amp; Local</t>
+          <t>designing a kitchen remodel</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8578,31 +8533,31 @@
         </is>
       </c>
       <c r="E67" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="F67" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="G67" s="11" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+        <v>10</v>
+      </c>
+      <c r="F67" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>designing a kitchen remodel</t>
-        </is>
-      </c>
-      <c r="B68" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>high-end kitchen remodel charlotte</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8611,21 +8566,21 @@
         </is>
       </c>
       <c r="E68" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F68" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+        <v>17</v>
+      </c>
+      <c r="F68" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="G68" s="11" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>high-end kitchen remodel charlotte</t>
+          <t>kitchen remodel charlotte north carolina</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -8649,21 +8604,21 @@
       <c r="F69" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="G69" s="11" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>kitchen remodel charlotte north carolina</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>Charlotte &amp; Local</t>
+          <t>best kitchen remodeling company</t>
+        </is>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -8677,10 +8632,10 @@
         </is>
       </c>
       <c r="E70" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="F70" s="4" t="n">
-        <v>18</v>
+        <v>10</v>
+      </c>
+      <c r="F70" s="6" t="n">
+        <v>30</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -8691,7 +8646,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>best kitchen remodeling company</t>
+          <t>42 inch kitchen cabinets</t>
         </is>
       </c>
       <c r="B71" s="7" t="inlineStr">
@@ -8701,7 +8656,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8724,17 +8679,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>42 inch kitchen cabinets</t>
-        </is>
-      </c>
-      <c r="B72" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>fast kitchen renovation charlotte</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8743,10 +8698,10 @@
         </is>
       </c>
       <c r="E72" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F72" s="6" t="n">
-        <v>30</v>
+        <v>16</v>
+      </c>
+      <c r="F72" s="4" t="n">
+        <v>18</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -8757,17 +8712,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>fast kitchen renovation charlotte</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>Charlotte &amp; Local</t>
+          <t>kitchen installation cost estimate</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>Cost &amp; Budget</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -8776,10 +8731,10 @@
         </is>
       </c>
       <c r="E73" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="F73" s="4" t="n">
-        <v>18</v>
+        <v>10</v>
+      </c>
+      <c r="F73" s="6" t="n">
+        <v>30</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -8790,17 +8745,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>kitchen installation cost estimate</t>
-        </is>
-      </c>
-      <c r="B74" s="5" t="inlineStr">
-        <is>
-          <t>Cost &amp; Budget</t>
+          <t>kitchen remodeling cornelius nc</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -8809,21 +8764,21 @@
         </is>
       </c>
       <c r="E74" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F74" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+        <v>16</v>
+      </c>
+      <c r="F74" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="G74" s="11" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>kitchen remodeling cornelius nc</t>
+          <t>kitchen contractor belmont</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -8842,10 +8797,10 @@
         </is>
       </c>
       <c r="E75" s="3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G75" s="11" t="inlineStr">
         <is>
@@ -8856,7 +8811,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>kitchen contractor belmont</t>
+          <t>kitchen remodel belmont</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -8880,16 +8835,16 @@
       <c r="F76" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="G76" s="11" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>kitchen remodel belmont</t>
+          <t>kitchen remodeling waxhaw nc</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -8911,28 +8866,28 @@
         <v>15</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+        <v>18</v>
+      </c>
+      <c r="G77" s="11" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>kitchen remodeling waxhaw nc</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>Charlotte &amp; Local</t>
+          <t>compare kitchen prices</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>Cost &amp; Budget</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -8941,31 +8896,31 @@
         </is>
       </c>
       <c r="E78" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="F78" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="G78" s="11" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+        <v>10</v>
+      </c>
+      <c r="F78" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>compare kitchen prices</t>
-        </is>
-      </c>
-      <c r="B79" s="5" t="inlineStr">
-        <is>
-          <t>Cost &amp; Budget</t>
+          <t>kitchen remodel montibello nc</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -8974,10 +8929,10 @@
         </is>
       </c>
       <c r="E79" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F79" s="6" t="n">
-        <v>38</v>
+        <v>15</v>
+      </c>
+      <c r="F79" s="4" t="n">
+        <v>18</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -8988,17 +8943,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>kitchen remodel montibello nc</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>Charlotte &amp; Local</t>
+          <t>kitchen renovation mecklenburg county</t>
+        </is>
+      </c>
+      <c r="B80" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9007,10 +8962,10 @@
         </is>
       </c>
       <c r="E80" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="F80" s="4" t="n">
-        <v>18</v>
+        <v>10</v>
+      </c>
+      <c r="F80" s="6" t="n">
+        <v>30</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -9021,17 +8976,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>kitchen renovation mecklenburg county</t>
-        </is>
-      </c>
-      <c r="B81" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>luxury kitchen remodel charlotte</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -9040,10 +8995,10 @@
         </is>
       </c>
       <c r="E81" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F81" s="6" t="n">
-        <v>30</v>
+        <v>15</v>
+      </c>
+      <c r="F81" s="4" t="n">
+        <v>18</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -9054,17 +9009,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>luxury kitchen remodel charlotte</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>Charlotte &amp; Local</t>
+          <t>new kitchen prices</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>Cost &amp; Budget</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -9073,10 +9028,10 @@
         </is>
       </c>
       <c r="E82" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="F82" s="4" t="n">
-        <v>18</v>
+        <v>10</v>
+      </c>
+      <c r="F82" s="6" t="n">
+        <v>38</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -9087,17 +9042,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>new kitchen prices</t>
-        </is>
-      </c>
-      <c r="B83" s="5" t="inlineStr">
-        <is>
-          <t>Cost &amp; Budget</t>
+          <t>kitchen remodeling in concord, nc</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -9106,10 +9061,10 @@
         </is>
       </c>
       <c r="E83" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F83" s="6" t="n">
-        <v>38</v>
+        <v>14</v>
+      </c>
+      <c r="F83" s="4" t="n">
+        <v>18</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -9120,7 +9075,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>kitchen remodeling in concord, nc</t>
+          <t>best kitchen remodeling gastonia nc</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -9153,7 +9108,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>best kitchen remodeling gastonia nc</t>
+          <t>cabinet refacing near me</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -9172,7 +9127,7 @@
         </is>
       </c>
       <c r="E85" s="3" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F85" s="4" t="n">
         <v>18</v>
@@ -9186,7 +9141,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>cabinet refacing near me</t>
+          <t>full kitchen remodel charlotte</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -9205,31 +9160,31 @@
         </is>
       </c>
       <c r="E86" s="3" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F86" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G86" s="11" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>full kitchen remodel charlotte</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>Charlotte &amp; Local</t>
+          <t>same week kitchen remodel</t>
+        </is>
+      </c>
+      <c r="B87" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -9238,21 +9193,21 @@
         </is>
       </c>
       <c r="E87" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="F87" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="G87" s="11" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+        <v>10</v>
+      </c>
+      <c r="F87" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>same week kitchen remodel</t>
+          <t>kitchen remodel companies</t>
         </is>
       </c>
       <c r="B88" s="7" t="inlineStr">
@@ -9262,7 +9217,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -9274,7 +9229,7 @@
         <v>10</v>
       </c>
       <c r="F88" s="6" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -9285,17 +9240,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>kitchen remodel companies</t>
-        </is>
-      </c>
-      <c r="B89" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>full kitchen remodel cost</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>Cost &amp; Budget</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -9307,7 +9262,7 @@
         <v>10</v>
       </c>
       <c r="F89" s="6" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -9318,17 +9273,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>full kitchen remodel cost</t>
-        </is>
-      </c>
-      <c r="B90" s="5" t="inlineStr">
-        <is>
-          <t>Cost &amp; Budget</t>
+          <t>kitchen design charlotte</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -9337,10 +9292,10 @@
         </is>
       </c>
       <c r="E90" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F90" s="6" t="n">
-        <v>30</v>
+        <v>13</v>
+      </c>
+      <c r="F90" s="4" t="n">
+        <v>24</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -9351,7 +9306,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>kitchen design charlotte</t>
+          <t>kitchen remodeler belmont</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -9370,7 +9325,7 @@
         </is>
       </c>
       <c r="E91" s="3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F91" s="4" t="n">
         <v>24</v>
@@ -9384,17 +9339,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>kitchen remodeler belmont</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>Charlotte &amp; Local</t>
+          <t>kitchen remodel design</t>
+        </is>
+      </c>
+      <c r="B92" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -9403,10 +9358,10 @@
         </is>
       </c>
       <c r="E92" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="F92" s="4" t="n">
-        <v>24</v>
+        <v>10</v>
+      </c>
+      <c r="F92" s="6" t="n">
+        <v>38</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -9417,7 +9372,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>kitchen remodel design</t>
+          <t>kitchen</t>
         </is>
       </c>
       <c r="B93" s="7" t="inlineStr">
@@ -9439,7 +9394,7 @@
         <v>10</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -9450,7 +9405,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>kitchen</t>
+          <t>42 inch cabinets</t>
         </is>
       </c>
       <c r="B94" s="7" t="inlineStr">
@@ -9472,7 +9427,7 @@
         <v>10</v>
       </c>
       <c r="F94" s="6" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -9483,17 +9438,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>42 inch cabinets</t>
-        </is>
-      </c>
-      <c r="B95" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>kitchen renovation cost near me</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -9504,8 +9459,8 @@
       <c r="E95" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F95" s="6" t="n">
-        <v>38</v>
+      <c r="F95" s="4" t="n">
+        <v>18</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -9516,17 +9471,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>kitchen renovation cost near me</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>Charlotte &amp; Local</t>
+          <t>how much does a kitchen remodel cost</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="inlineStr">
+        <is>
+          <t>Cost &amp; Budget</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -9538,7 +9493,7 @@
         <v>10</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -9549,12 +9504,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>how much does a kitchen remodel cost</t>
-        </is>
-      </c>
-      <c r="B97" s="5" t="inlineStr">
-        <is>
-          <t>Cost &amp; Budget</t>
+          <t>kitchen remodel mecklenburg county</t>
+        </is>
+      </c>
+      <c r="B97" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -9570,8 +9525,8 @@
       <c r="E97" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F97" s="4" t="n">
-        <v>24</v>
+      <c r="F97" s="6" t="n">
+        <v>30</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -9582,17 +9537,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>kitchen remodel mecklenburg county</t>
-        </is>
-      </c>
-      <c r="B98" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>kitchen remodel plaza midwood nc</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -9601,10 +9556,10 @@
         </is>
       </c>
       <c r="E98" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F98" s="6" t="n">
-        <v>30</v>
+        <v>12</v>
+      </c>
+      <c r="F98" s="4" t="n">
+        <v>18</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -9615,29 +9570,29 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>kitchen remodel plaza midwood nc</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>Charlotte &amp; Local</t>
+          <t>before and after kitchen remodel cost</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>Cost &amp; Budget</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Buyer</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="E99" s="3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -9648,7 +9603,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>kitchen remodel providence plantation nc</t>
+          <t>kitchen remodeling pineville nc</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -9667,7 +9622,7 @@
         </is>
       </c>
       <c r="E100" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F100" s="4" t="n">
         <v>18</v>
@@ -9681,17 +9636,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>kitchen remodel raintree nc</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>Charlotte &amp; Local</t>
+          <t>kitchen remodel quote</t>
+        </is>
+      </c>
+      <c r="B101" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -9700,26 +9655,26 @@
         </is>
       </c>
       <c r="E101" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="F101" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="G101" s="11" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+        <v>10</v>
+      </c>
+      <c r="F101" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>before and after kitchen remodel cost</t>
-        </is>
-      </c>
-      <c r="B102" s="5" t="inlineStr">
-        <is>
-          <t>Cost &amp; Budget</t>
+          <t>kitchen remodel timeline denver</t>
+        </is>
+      </c>
+      <c r="B102" s="9" t="inlineStr">
+        <is>
+          <t>Process &amp; Planning</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -9729,14 +9684,14 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E102" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F102" s="4" t="n">
-        <v>24</v>
+        <v>11</v>
+      </c>
+      <c r="F102" s="6" t="n">
+        <v>30</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -9747,12 +9702,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>kitchen remodeling pineville nc</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>Charlotte &amp; Local</t>
+          <t>kitchen remodeler davidson</t>
+        </is>
+      </c>
+      <c r="B103" s="9" t="inlineStr">
+        <is>
+          <t>Process &amp; Planning</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -9766,21 +9721,21 @@
         </is>
       </c>
       <c r="E103" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="F103" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="G103" s="11" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+        <v>10</v>
+      </c>
+      <c r="F103" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>kitchen remodel quote</t>
+          <t>kitchen remodel rock hill</t>
         </is>
       </c>
       <c r="B104" s="7" t="inlineStr">
@@ -9802,7 +9757,7 @@
         <v>10</v>
       </c>
       <c r="F104" s="6" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -9813,17 +9768,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>kitchen remodel timeline denver</t>
-        </is>
-      </c>
-      <c r="B105" s="9" t="inlineStr">
-        <is>
-          <t>Process &amp; Planning</t>
+          <t>kitchen remodeler matthews</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -9832,10 +9787,10 @@
         </is>
       </c>
       <c r="E105" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="F105" s="6" t="n">
-        <v>30</v>
+        <v>10</v>
+      </c>
+      <c r="F105" s="4" t="n">
+        <v>24</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -9846,17 +9801,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>kitchen remodeler davidson</t>
-        </is>
-      </c>
-      <c r="B106" s="9" t="inlineStr">
-        <is>
-          <t>Process &amp; Planning</t>
+          <t>kitchen remodel fort mill</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -9867,8 +9822,8 @@
       <c r="E106" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F106" s="6" t="n">
-        <v>38</v>
+      <c r="F106" s="4" t="n">
+        <v>18</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -9879,12 +9834,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>kitchen remodel rock hill</t>
-        </is>
-      </c>
-      <c r="B107" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>kitchen remodel huntersville</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -9900,8 +9855,8 @@
       <c r="E107" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F107" s="6" t="n">
-        <v>30</v>
+      <c r="F107" s="4" t="n">
+        <v>24</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -9912,7 +9867,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>kitchen remodeler matthews</t>
+          <t>kitchen remodeler fort mill</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -9934,7 +9889,7 @@
         <v>10</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -9945,7 +9900,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>kitchen remodel fort mill</t>
+          <t>kitchen remodeler huntersville</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -9955,7 +9910,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -9967,7 +9922,7 @@
         <v>10</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -9978,17 +9933,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>kitchen remodel huntersville</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>Charlotte &amp; Local</t>
+          <t>kitchen remodeler gastonia</t>
+        </is>
+      </c>
+      <c r="B110" s="9" t="inlineStr">
+        <is>
+          <t>Process &amp; Planning</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -9999,8 +9954,8 @@
       <c r="E110" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F110" s="4" t="n">
-        <v>24</v>
+      <c r="F110" s="6" t="n">
+        <v>38</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -10011,7 +9966,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>kitchen remodeler fort mill</t>
+          <t>kitchen cabinet refacing near me</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -10044,17 +9999,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>kitchen remodeler huntersville</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>Charlotte &amp; Local</t>
+          <t>affordable kitchen renovations</t>
+        </is>
+      </c>
+      <c r="B112" s="5" t="inlineStr">
+        <is>
+          <t>Cost &amp; Budget</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -10065,8 +10020,8 @@
       <c r="E112" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F112" s="4" t="n">
-        <v>24</v>
+      <c r="F112" s="6" t="n">
+        <v>38</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -10077,12 +10032,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>kitchen remodeler gastonia</t>
-        </is>
-      </c>
-      <c r="B113" s="9" t="inlineStr">
-        <is>
-          <t>Process &amp; Planning</t>
+          <t>cabinet installation charlotte nc</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -10098,19 +10053,19 @@
       <c r="E113" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F113" s="6" t="n">
-        <v>38</v>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="F113" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="G113" s="11" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>kitchen cabinet refacing near me</t>
+          <t>cabinet installers near me</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -10143,12 +10098,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>affordable kitchen renovations</t>
-        </is>
-      </c>
-      <c r="B115" s="5" t="inlineStr">
-        <is>
-          <t>Cost &amp; Budget</t>
+          <t>complete kitchen remodel</t>
+        </is>
+      </c>
+      <c r="B115" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -10176,7 +10131,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>cabinet installation charlotte nc</t>
+          <t>kitchen cabinet design near me</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -10200,16 +10155,16 @@
       <c r="F116" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="G116" s="11" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>cabinet installers near me</t>
+          <t>kitchen cabinet installation charlotte nc</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -10242,17 +10197,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>complete kitchen remodel</t>
-        </is>
-      </c>
-      <c r="B118" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>kitchen cabinets near me</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -10263,8 +10218,8 @@
       <c r="E118" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F118" s="6" t="n">
-        <v>38</v>
+      <c r="F118" s="4" t="n">
+        <v>18</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -10275,7 +10230,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>kitchen cabinet design near me</t>
+          <t>kitchen design and installation near me</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -10308,12 +10263,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>kitchen cabinet installation charlotte nc</t>
-        </is>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>Charlotte &amp; Local</t>
+          <t>kitchen design company</t>
+        </is>
+      </c>
+      <c r="B120" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -10329,8 +10284,8 @@
       <c r="E120" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F120" s="4" t="n">
-        <v>18</v>
+      <c r="F120" s="6" t="n">
+        <v>38</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -10341,7 +10296,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>kitchen cabinets near me</t>
+          <t>kitchen design store near me</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -10374,17 +10329,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>kitchen design and installation near me</t>
-        </is>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>Charlotte &amp; Local</t>
+          <t>kitchen island installation</t>
+        </is>
+      </c>
+      <c r="B122" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -10395,8 +10350,8 @@
       <c r="E122" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F122" s="4" t="n">
-        <v>18</v>
+      <c r="F122" s="6" t="n">
+        <v>38</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -10407,7 +10362,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>kitchen design company</t>
+          <t>kitchen makeover</t>
         </is>
       </c>
       <c r="B123" s="7" t="inlineStr">
@@ -10417,7 +10372,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -10429,7 +10384,7 @@
         <v>10</v>
       </c>
       <c r="F123" s="6" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
@@ -10440,7 +10395,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>kitchen design store near me</t>
+          <t>kitchen remodel packages near me</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -10473,12 +10428,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>kitchen island installation</t>
-        </is>
-      </c>
-      <c r="B125" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>kitchen remodeling north carolina</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -10494,8 +10449,8 @@
       <c r="E125" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F125" s="6" t="n">
-        <v>38</v>
+      <c r="F125" s="4" t="n">
+        <v>18</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
@@ -10506,17 +10461,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>kitchen makeover</t>
-        </is>
-      </c>
-      <c r="B126" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>kitchen renovation contractors near me</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -10527,8 +10482,8 @@
       <c r="E126" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F126" s="6" t="n">
-        <v>48</v>
+      <c r="F126" s="4" t="n">
+        <v>18</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
@@ -10539,7 +10494,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>kitchen remodel packages near me</t>
+          <t>oak kitchen cabinets near me</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
@@ -10572,7 +10527,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>kitchen remodeling north carolina</t>
+          <t>pantry renovation near me</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
@@ -10582,7 +10537,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -10605,17 +10560,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>kitchen renovation contractors near me</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>Charlotte &amp; Local</t>
+          <t>replacing kitchen cabinets</t>
+        </is>
+      </c>
+      <c r="B129" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -10626,8 +10581,8 @@
       <c r="E129" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F129" s="4" t="n">
-        <v>18</v>
+      <c r="F129" s="6" t="n">
+        <v>38</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
@@ -10638,17 +10593,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>oak kitchen cabinets near me</t>
-        </is>
-      </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>Charlotte &amp; Local</t>
+          <t>#kitchendesign</t>
+        </is>
+      </c>
+      <c r="B130" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -10659,8 +10614,8 @@
       <c r="E130" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F130" s="4" t="n">
-        <v>18</v>
+      <c r="F130" s="6" t="n">
+        <v>48</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
@@ -10671,17 +10626,17 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>pantry renovation near me</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>Charlotte &amp; Local</t>
+          <t>#kitchenremodeling</t>
+        </is>
+      </c>
+      <c r="B131" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -10692,8 +10647,8 @@
       <c r="E131" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F131" s="4" t="n">
-        <v>18</v>
+      <c r="F131" s="6" t="n">
+        <v>48</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
@@ -10704,7 +10659,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>replacing kitchen cabinets</t>
+          <t>#kitchenrenovation</t>
         </is>
       </c>
       <c r="B132" s="7" t="inlineStr">
@@ -10726,7 +10681,7 @@
         <v>10</v>
       </c>
       <c r="F132" s="6" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
@@ -10737,7 +10692,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>#kitchendesign</t>
+          <t>$500 kitchen remodel</t>
         </is>
       </c>
       <c r="B133" s="7" t="inlineStr">
@@ -10759,7 +10714,7 @@
         <v>10</v>
       </c>
       <c r="F133" s="6" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
@@ -10770,7 +10725,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>#kitchenremodeling</t>
+          <t>07807 commercial kitchen design</t>
         </is>
       </c>
       <c r="B134" s="7" t="inlineStr">
@@ -10792,7 +10747,7 @@
         <v>10</v>
       </c>
       <c r="F134" s="6" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
@@ -10803,7 +10758,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>#kitchenrenovation</t>
+          <t>07887 commercial kitchen design</t>
         </is>
       </c>
       <c r="B135" s="7" t="inlineStr">
@@ -10825,7 +10780,7 @@
         <v>10</v>
       </c>
       <c r="F135" s="6" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
@@ -10836,7 +10791,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>$500 kitchen remodel</t>
+          <t>1 week kitchens</t>
         </is>
       </c>
       <c r="B136" s="7" t="inlineStr">
@@ -10869,7 +10824,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>07807 commercial kitchen design</t>
+          <t>10 day kitchen</t>
         </is>
       </c>
       <c r="B137" s="7" t="inlineStr">
@@ -10891,7 +10846,7 @@
         <v>10</v>
       </c>
       <c r="F137" s="6" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
@@ -10902,7 +10857,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>07887 commercial kitchen design</t>
+          <t>10 day kitchen remodel</t>
         </is>
       </c>
       <c r="B138" s="7" t="inlineStr">
@@ -10935,12 +10890,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>1 week kitchens</t>
-        </is>
-      </c>
-      <c r="B139" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>10x20 kitchen remodel cost</t>
+        </is>
+      </c>
+      <c r="B139" s="5" t="inlineStr">
+        <is>
+          <t>Cost &amp; Budget</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -10957,7 +10912,7 @@
         <v>10</v>
       </c>
       <c r="F139" s="6" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
@@ -10968,7 +10923,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>10 day kitchen</t>
+          <t>2026 kitchen remodel</t>
         </is>
       </c>
       <c r="B140" s="7" t="inlineStr">
@@ -11001,7 +10956,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>10 day kitchen remodel</t>
+          <t>2026 kitchens</t>
         </is>
       </c>
       <c r="B141" s="7" t="inlineStr">
@@ -11023,7 +10978,7 @@
         <v>10</v>
       </c>
       <c r="F141" s="6" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
@@ -11034,12 +10989,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>10x20 kitchen remodel cost</t>
-        </is>
-      </c>
-      <c r="B142" s="5" t="inlineStr">
-        <is>
-          <t>Cost &amp; Budget</t>
+          <t>20k kitchen remodel</t>
+        </is>
+      </c>
+      <c r="B142" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -11056,7 +11011,7 @@
         <v>10</v>
       </c>
       <c r="F142" s="6" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
@@ -11067,7 +11022,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026 kitchen remodel</t>
+          <t>25k kitchen remodel</t>
         </is>
       </c>
       <c r="B143" s="7" t="inlineStr">
@@ -11100,7 +11055,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026 kitchens</t>
+          <t>3 day kitchen remodel</t>
         </is>
       </c>
       <c r="B144" s="7" t="inlineStr">
@@ -11122,7 +11077,7 @@
         <v>10</v>
       </c>
       <c r="F144" s="6" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
@@ -11133,7 +11088,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>20k kitchen remodel</t>
+          <t>3 day kitchens</t>
         </is>
       </c>
       <c r="B145" s="7" t="inlineStr">
@@ -11166,7 +11121,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>25k kitchen remodel</t>
+          <t>36 vs 42 kitchen cabinets</t>
         </is>
       </c>
       <c r="B146" s="7" t="inlineStr">
@@ -11187,8 +11142,8 @@
       <c r="E146" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F146" s="6" t="n">
-        <v>38</v>
+      <c r="F146" s="4" t="n">
+        <v>24</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
@@ -11199,7 +11154,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>3 day kitchen remodel</t>
+          <t>3d rendering kitchen remodel</t>
         </is>
       </c>
       <c r="B147" s="7" t="inlineStr">
@@ -11232,7 +11187,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>3 day kitchens</t>
+          <t>42 bar height cabinets</t>
         </is>
       </c>
       <c r="B148" s="7" t="inlineStr">
@@ -11254,7 +11209,7 @@
         <v>10</v>
       </c>
       <c r="F148" s="6" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
@@ -11265,7 +11220,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>36 vs 42 kitchen cabinets</t>
+          <t>42 cabinets</t>
         </is>
       </c>
       <c r="B149" s="7" t="inlineStr">
@@ -11286,8 +11241,8 @@
       <c r="E149" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F149" s="4" t="n">
-        <v>24</v>
+      <c r="F149" s="6" t="n">
+        <v>48</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
@@ -11298,7 +11253,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>3d rendering kitchen remodel</t>
+          <t>42 in kitchen cabinets</t>
         </is>
       </c>
       <c r="B150" s="7" t="inlineStr">
@@ -11331,7 +11286,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>42 bar height cabinets</t>
+          <t>42 in upper cabinets</t>
         </is>
       </c>
       <c r="B151" s="7" t="inlineStr">
@@ -11364,7 +11319,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>42 cabinets</t>
+          <t>42 inch cabinets 8 foot ceiling</t>
         </is>
       </c>
       <c r="B152" s="7" t="inlineStr">
@@ -11385,8 +11340,8 @@
       <c r="E152" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F152" s="6" t="n">
-        <v>48</v>
+      <c r="F152" s="4" t="n">
+        <v>24</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
@@ -11397,7 +11352,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>42 in kitchen cabinets</t>
+          <t>42 inch cabinets vs 36</t>
         </is>
       </c>
       <c r="B153" s="7" t="inlineStr">
@@ -11418,8 +11373,8 @@
       <c r="E153" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F153" s="6" t="n">
-        <v>30</v>
+      <c r="F153" s="4" t="n">
+        <v>24</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
@@ -11430,7 +11385,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>42 in upper cabinets</t>
+          <t>42 inch height cabinets</t>
         </is>
       </c>
       <c r="B154" s="7" t="inlineStr">
@@ -11463,7 +11418,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>42 inch cabinets 8 foot ceiling</t>
+          <t>42 inch high upper kitchen cabinets</t>
         </is>
       </c>
       <c r="B155" s="7" t="inlineStr">
@@ -11496,7 +11451,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>42 inch cabinets vs 36</t>
+          <t>42 inch tall cabinets</t>
         </is>
       </c>
       <c r="B156" s="7" t="inlineStr">
@@ -11517,8 +11472,8 @@
       <c r="E156" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F156" s="4" t="n">
-        <v>24</v>
+      <c r="F156" s="6" t="n">
+        <v>30</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
@@ -11529,7 +11484,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>42 inch height cabinets</t>
+          <t>42 inch tall kitchen cabinets</t>
         </is>
       </c>
       <c r="B157" s="7" t="inlineStr">
@@ -11550,8 +11505,8 @@
       <c r="E157" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F157" s="6" t="n">
-        <v>30</v>
+      <c r="F157" s="4" t="n">
+        <v>24</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
@@ -11562,7 +11517,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>42 inch high upper kitchen cabinets</t>
+          <t>42 inch tall upper kitchen cabinets</t>
         </is>
       </c>
       <c r="B158" s="7" t="inlineStr">
@@ -11595,7 +11550,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>42 inch tall cabinets</t>
+          <t>42 inch upper cabinets</t>
         </is>
       </c>
       <c r="B159" s="7" t="inlineStr">
@@ -11628,7 +11583,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>42 inch tall kitchen cabinets</t>
+          <t>42 inch upper kitchen cabinets</t>
         </is>
       </c>
       <c r="B160" s="7" t="inlineStr">
@@ -11661,7 +11616,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>42 inch tall upper kitchen cabinets</t>
+          <t>42 inch vs 36 inch kitchen cabinets</t>
         </is>
       </c>
       <c r="B161" s="7" t="inlineStr">
@@ -11694,7 +11649,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>42 inch upper cabinets</t>
+          <t>42 inch wall cabinets for kitchen</t>
         </is>
       </c>
       <c r="B162" s="7" t="inlineStr">
@@ -11715,8 +11670,8 @@
       <c r="E162" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F162" s="6" t="n">
-        <v>30</v>
+      <c r="F162" s="4" t="n">
+        <v>24</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
@@ -11727,7 +11682,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>42 inch upper kitchen cabinets</t>
+          <t>42 tall upper kitchen cabinets</t>
         </is>
       </c>
       <c r="B163" s="7" t="inlineStr">
@@ -11760,7 +11715,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>42 inch vs 36 inch kitchen cabinets</t>
+          <t>42 upper kitchen cabinets</t>
         </is>
       </c>
       <c r="B164" s="7" t="inlineStr">
@@ -11781,8 +11736,8 @@
       <c r="E164" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F164" s="4" t="n">
-        <v>24</v>
+      <c r="F164" s="6" t="n">
+        <v>30</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
@@ -11793,7 +11748,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>42 inch wall cabinets for kitchen</t>
+          <t>42in cabinets</t>
         </is>
       </c>
       <c r="B165" s="7" t="inlineStr">
@@ -11814,8 +11769,8 @@
       <c r="E165" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F165" s="4" t="n">
-        <v>24</v>
+      <c r="F165" s="6" t="n">
+        <v>48</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
@@ -11826,7 +11781,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>42 tall upper kitchen cabinets</t>
+          <t>5 day kitchens</t>
         </is>
       </c>
       <c r="B166" s="7" t="inlineStr">
@@ -11847,8 +11802,8 @@
       <c r="E166" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F166" s="4" t="n">
-        <v>24</v>
+      <c r="F166" s="6" t="n">
+        <v>38</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
@@ -11859,12 +11814,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>42 upper kitchen cabinets</t>
-        </is>
-      </c>
-      <c r="B167" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>affordable kitchen design</t>
+        </is>
+      </c>
+      <c r="B167" s="5" t="inlineStr">
+        <is>
+          <t>Cost &amp; Budget</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -11881,7 +11836,7 @@
         <v>10</v>
       </c>
       <c r="F167" s="6" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
@@ -11892,17 +11847,17 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>42in cabinets</t>
-        </is>
-      </c>
-      <c r="B168" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>affordable kitchen remodel charlotte nc</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -11913,19 +11868,19 @@
       <c r="E168" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F168" s="6" t="n">
-        <v>48</v>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="F168" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="G168" s="11" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>5 day kitchens</t>
+          <t>ai kitchen remodel</t>
         </is>
       </c>
       <c r="B169" s="7" t="inlineStr">
@@ -11958,12 +11913,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>affordable kitchen design</t>
-        </is>
-      </c>
-      <c r="B170" s="5" t="inlineStr">
-        <is>
-          <t>Cost &amp; Budget</t>
+          <t>ai kitchen remodel free</t>
+        </is>
+      </c>
+      <c r="B170" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -11980,7 +11935,7 @@
         <v>10</v>
       </c>
       <c r="F170" s="6" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
@@ -11991,17 +11946,17 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>affordable kitchen remodel charlotte nc</t>
-        </is>
-      </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>Charlotte &amp; Local</t>
+          <t>all day kitchen</t>
+        </is>
+      </c>
+      <c r="B171" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -12012,19 +11967,19 @@
       <c r="E171" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F171" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="G171" s="11" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="F171" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>ai kitchen remodel</t>
+          <t>amazing kitchens</t>
         </is>
       </c>
       <c r="B172" s="7" t="inlineStr">
@@ -12046,7 +12001,7 @@
         <v>10</v>
       </c>
       <c r="F172" s="6" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
@@ -12057,7 +12012,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>ai kitchen remodel free</t>
+          <t>andrea granger kitchen makeover</t>
         </is>
       </c>
       <c r="B173" s="7" t="inlineStr">
@@ -12090,7 +12045,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>all day kitchen</t>
+          <t>apartment cabinet renovation</t>
         </is>
       </c>
       <c r="B174" s="7" t="inlineStr">
@@ -12123,7 +12078,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>amazing kitchens</t>
+          <t>apartment kitchen reno</t>
         </is>
       </c>
       <c r="B175" s="7" t="inlineStr">
@@ -12145,7 +12100,7 @@
         <v>10</v>
       </c>
       <c r="F175" s="6" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
@@ -12156,7 +12111,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>andrea granger kitchen makeover</t>
+          <t>apartment kitchen renovation</t>
         </is>
       </c>
       <c r="B176" s="7" t="inlineStr">
@@ -12178,7 +12133,7 @@
         <v>10</v>
       </c>
       <c r="F176" s="6" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
@@ -12189,12 +12144,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>apartment cabinet renovation</t>
-        </is>
-      </c>
-      <c r="B177" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>approximate cost of kitchen remodel</t>
+        </is>
+      </c>
+      <c r="B177" s="5" t="inlineStr">
+        <is>
+          <t>Cost &amp; Budget</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -12210,8 +12165,8 @@
       <c r="E177" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F177" s="6" t="n">
-        <v>38</v>
+      <c r="F177" s="4" t="n">
+        <v>24</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
@@ -12222,7 +12177,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>apartment kitchen reno</t>
+          <t>architectural design kitchens</t>
         </is>
       </c>
       <c r="B178" s="7" t="inlineStr">
@@ -12255,7 +12210,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>apartment kitchen renovation</t>
+          <t>are 42 inch cabinets standard</t>
         </is>
       </c>
       <c r="B179" s="7" t="inlineStr">
@@ -12276,8 +12231,8 @@
       <c r="E179" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F179" s="6" t="n">
-        <v>38</v>
+      <c r="F179" s="4" t="n">
+        <v>24</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
@@ -12288,7 +12243,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>approximate cost of kitchen remodel</t>
+          <t>average cost for a kitchen remodel</t>
         </is>
       </c>
       <c r="B180" s="5" t="inlineStr">
@@ -12321,12 +12276,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>architectural design kitchens</t>
-        </is>
-      </c>
-      <c r="B181" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>average cost of a complete kitchen remodel</t>
+        </is>
+      </c>
+      <c r="B181" s="5" t="inlineStr">
+        <is>
+          <t>Cost &amp; Budget</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -12342,8 +12297,8 @@
       <c r="E181" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F181" s="6" t="n">
-        <v>38</v>
+      <c r="F181" s="4" t="n">
+        <v>24</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
@@ -12354,12 +12309,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>are 42 inch cabinets standard</t>
-        </is>
-      </c>
-      <c r="B182" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>average cost of a full kitchen remodel</t>
+        </is>
+      </c>
+      <c r="B182" s="5" t="inlineStr">
+        <is>
+          <t>Cost &amp; Budget</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -12387,7 +12342,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>average cost for a kitchen remodel</t>
+          <t>average cost of a kitchen remodel 2024</t>
         </is>
       </c>
       <c r="B183" s="5" t="inlineStr">
@@ -12420,7 +12375,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>average cost of a complete kitchen remodel</t>
+          <t>average cost of a new kitchen remodel</t>
         </is>
       </c>
       <c r="B184" s="5" t="inlineStr">
@@ -12453,7 +12408,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>average cost of a full kitchen remodel</t>
+          <t>average cost of galley kitchen remodel</t>
         </is>
       </c>
       <c r="B185" s="5" t="inlineStr">
@@ -12486,7 +12441,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>average cost of a kitchen remodel 2024</t>
+          <t>average cost of kitchen remodel 2021</t>
         </is>
       </c>
       <c r="B186" s="5" t="inlineStr">
@@ -12519,7 +12474,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>average cost of a new kitchen remodel</t>
+          <t>average cost of kitchen remodel in colorado</t>
         </is>
       </c>
       <c r="B187" s="5" t="inlineStr">
@@ -12552,7 +12507,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>average cost of galley kitchen remodel</t>
+          <t>average cost of kitchen renovation</t>
         </is>
       </c>
       <c r="B188" s="5" t="inlineStr">
@@ -12585,7 +12540,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>average cost of kitchen remodel 2021</t>
+          <t>average cost of large kitchen remodel</t>
         </is>
       </c>
       <c r="B189" s="5" t="inlineStr">
@@ -12618,7 +12573,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>average cost of kitchen remodel in colorado</t>
+          <t>average cost of redoing a kitchen</t>
         </is>
       </c>
       <c r="B190" s="5" t="inlineStr">
@@ -12651,7 +12606,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>average cost of kitchen renovation</t>
+          <t>average cost to update a kitchen</t>
         </is>
       </c>
       <c r="B191" s="5" t="inlineStr">
@@ -12684,7 +12639,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>average cost of large kitchen remodel</t>
+          <t>average cost to upgrade kitchen</t>
         </is>
       </c>
       <c r="B192" s="5" t="inlineStr">
@@ -12717,12 +12672,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>average cost of redoing a kitchen</t>
-        </is>
-      </c>
-      <c r="B193" s="5" t="inlineStr">
-        <is>
-          <t>Cost &amp; Budget</t>
+          <t>average height of kitchen cabinets</t>
+        </is>
+      </c>
+      <c r="B193" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -12750,12 +12705,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>average cost to update a kitchen</t>
-        </is>
-      </c>
-      <c r="B194" s="5" t="inlineStr">
-        <is>
-          <t>Cost &amp; Budget</t>
+          <t>average kitchen remodel</t>
+        </is>
+      </c>
+      <c r="B194" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -12771,8 +12726,8 @@
       <c r="E194" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F194" s="4" t="n">
-        <v>24</v>
+      <c r="F194" s="6" t="n">
+        <v>38</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
@@ -12783,12 +12738,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>average cost to upgrade kitchen</t>
-        </is>
-      </c>
-      <c r="B195" s="5" t="inlineStr">
-        <is>
-          <t>Cost &amp; Budget</t>
+          <t>average kitchen remodel time</t>
+        </is>
+      </c>
+      <c r="B195" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -12804,8 +12759,8 @@
       <c r="E195" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F195" s="4" t="n">
-        <v>24</v>
+      <c r="F195" s="6" t="n">
+        <v>30</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
@@ -12816,12 +12771,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>average height of kitchen cabinets</t>
-        </is>
-      </c>
-      <c r="B196" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>average price for a kitchen remodel</t>
+        </is>
+      </c>
+      <c r="B196" s="5" t="inlineStr">
+        <is>
+          <t>Cost &amp; Budget</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -12849,7 +12804,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>average kitchen remodel</t>
+          <t>average time to renovate a kitchen</t>
         </is>
       </c>
       <c r="B197" s="7" t="inlineStr">
@@ -12870,8 +12825,8 @@
       <c r="E197" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F197" s="6" t="n">
-        <v>38</v>
+      <c r="F197" s="4" t="n">
+        <v>24</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
@@ -12882,7 +12837,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>average kitchen remodel time</t>
+          <t>award-winning kitchen remodel</t>
         </is>
       </c>
       <c r="B198" s="7" t="inlineStr">
@@ -12904,7 +12859,7 @@
         <v>10</v>
       </c>
       <c r="F198" s="6" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
@@ -12915,12 +12870,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>average price for a kitchen remodel</t>
-        </is>
-      </c>
-      <c r="B199" s="5" t="inlineStr">
-        <is>
-          <t>Cost &amp; Budget</t>
+          <t>basic kitchen remodel</t>
+        </is>
+      </c>
+      <c r="B199" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -12936,8 +12891,8 @@
       <c r="E199" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F199" s="4" t="n">
-        <v>24</v>
+      <c r="F199" s="6" t="n">
+        <v>38</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
@@ -12948,7 +12903,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>average time to renovate a kitchen</t>
+          <t>beautiful kitchen renovations</t>
         </is>
       </c>
       <c r="B200" s="7" t="inlineStr">
@@ -12969,8 +12924,8 @@
       <c r="E200" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F200" s="4" t="n">
-        <v>24</v>
+      <c r="F200" s="6" t="n">
+        <v>38</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
@@ -12981,17 +12936,17 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>award-winning kitchen remodel</t>
-        </is>
-      </c>
-      <c r="B201" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>belmont kitchen luxury renovation</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -13002,19 +12957,19 @@
       <c r="E201" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F201" s="6" t="n">
-        <v>38</v>
-      </c>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="F201" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="G201" s="11" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>basic kitchen remodel</t>
+          <t>bespoke kitchen showrooms</t>
         </is>
       </c>
       <c r="B202" s="7" t="inlineStr">
@@ -13047,7 +13002,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>beautiful kitchen renovations</t>
+          <t>best alternatives to natural stone countertops</t>
         </is>
       </c>
       <c r="B203" s="7" t="inlineStr">
@@ -13068,8 +13023,8 @@
       <c r="E203" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F203" s="6" t="n">
-        <v>38</v>
+      <c r="F203" s="4" t="n">
+        <v>24</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
@@ -13080,7 +13035,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>belmont kitchen luxury renovation</t>
+          <t>best kitchen contractors near me</t>
         </is>
       </c>
       <c r="B204" s="2" t="inlineStr">
@@ -13104,16 +13059,16 @@
       <c r="F204" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="G204" s="11" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>belmont park kitchen remodel</t>
+          <t>best kitchen design near me</t>
         </is>
       </c>
       <c r="B205" s="2" t="inlineStr">
@@ -13137,16 +13092,16 @@
       <c r="F205" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="G205" s="11" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>bespoke kitchen showrooms</t>
+          <t>best kitchen designers</t>
         </is>
       </c>
       <c r="B206" s="7" t="inlineStr">
@@ -13179,7 +13134,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>best alternatives to natural stone countertops</t>
+          <t>best kitchen makeover companies</t>
         </is>
       </c>
       <c r="B207" s="7" t="inlineStr">
@@ -13189,7 +13144,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -13200,8 +13155,8 @@
       <c r="E207" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F207" s="4" t="n">
-        <v>24</v>
+      <c r="F207" s="6" t="n">
+        <v>30</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
@@ -13212,7 +13167,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>best kitchen contractors near me</t>
+          <t>best kitchen refacing near me</t>
         </is>
       </c>
       <c r="B208" s="2" t="inlineStr">
@@ -13245,17 +13200,17 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>best kitchen design near me</t>
-        </is>
-      </c>
-      <c r="B209" s="2" t="inlineStr">
-        <is>
-          <t>Charlotte &amp; Local</t>
+          <t>best kitchen remodel</t>
+        </is>
+      </c>
+      <c r="B209" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -13266,8 +13221,8 @@
       <c r="E209" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F209" s="4" t="n">
-        <v>18</v>
+      <c r="F209" s="6" t="n">
+        <v>38</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
@@ -13278,7 +13233,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>best kitchen designers</t>
+          <t>best kitchen remodel company energy-efficient upgrades</t>
         </is>
       </c>
       <c r="B210" s="7" t="inlineStr">
@@ -13288,7 +13243,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -13299,8 +13254,8 @@
       <c r="E210" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F210" s="6" t="n">
-        <v>38</v>
+      <c r="F210" s="4" t="n">
+        <v>24</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
@@ -13311,12 +13266,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>best kitchen makeover companies</t>
-        </is>
-      </c>
-      <c r="B211" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>best kitchen remodel contractors</t>
+        </is>
+      </c>
+      <c r="B211" s="9" t="inlineStr">
+        <is>
+          <t>Process &amp; Planning</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -13344,12 +13299,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>best kitchen refacing near me</t>
-        </is>
-      </c>
-      <c r="B212" s="2" t="inlineStr">
-        <is>
-          <t>Charlotte &amp; Local</t>
+          <t>best kitchen remodeler</t>
+        </is>
+      </c>
+      <c r="B212" s="9" t="inlineStr">
+        <is>
+          <t>Process &amp; Planning</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -13365,8 +13320,8 @@
       <c r="E212" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F212" s="4" t="n">
-        <v>18</v>
+      <c r="F212" s="6" t="n">
+        <v>38</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
@@ -13377,17 +13332,17 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>best kitchen remodel</t>
-        </is>
-      </c>
-      <c r="B213" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>best kitchen remodeling companies near me</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -13398,8 +13353,8 @@
       <c r="E213" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F213" s="6" t="n">
-        <v>38</v>
+      <c r="F213" s="4" t="n">
+        <v>18</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
@@ -13410,7 +13365,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>best kitchen remodel company energy-efficient upgrades</t>
+          <t>best kitchen remodeling service custom cabinetry</t>
         </is>
       </c>
       <c r="B214" s="7" t="inlineStr">
@@ -13420,7 +13375,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -13443,12 +13398,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>best kitchen remodel contractors</t>
-        </is>
-      </c>
-      <c r="B215" s="9" t="inlineStr">
-        <is>
-          <t>Process &amp; Planning</t>
+          <t>best kitchen remodeling service near me</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -13464,8 +13419,8 @@
       <c r="E215" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F215" s="6" t="n">
-        <v>30</v>
+      <c r="F215" s="4" t="n">
+        <v>18</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
@@ -13476,17 +13431,17 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>best kitchen remodeler</t>
-        </is>
-      </c>
-      <c r="B216" s="9" t="inlineStr">
-        <is>
-          <t>Process &amp; Planning</t>
+          <t>best kitchen renovation</t>
+        </is>
+      </c>
+      <c r="B216" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -13509,7 +13464,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>best kitchen remodeling companies near me</t>
+          <t>best kitchen renovation companies near me</t>
         </is>
       </c>
       <c r="B217" s="2" t="inlineStr">
@@ -13542,17 +13497,17 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>best kitchen remodeling service custom cabinetry</t>
-        </is>
-      </c>
-      <c r="B218" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>best kitchen renovation company near me</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -13564,7 +13519,7 @@
         <v>10</v>
       </c>
       <c r="F218" s="4" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
@@ -13575,7 +13530,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>best kitchen remodeling service near me</t>
+          <t>best kitchen showrooms near me</t>
         </is>
       </c>
       <c r="B219" s="2" t="inlineStr">
@@ -13608,7 +13563,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>best kitchen renovation</t>
+          <t>best kitchens of 2025</t>
         </is>
       </c>
       <c r="B220" s="7" t="inlineStr">
@@ -13630,7 +13585,7 @@
         <v>10</v>
       </c>
       <c r="F220" s="6" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="G220" t="inlineStr">
         <is>
@@ -13641,17 +13596,17 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>best kitchen renovation companies near me</t>
-        </is>
-      </c>
-      <c r="B221" s="2" t="inlineStr">
-        <is>
-          <t>Charlotte &amp; Local</t>
+          <t>best place to buy kitchen cabinets</t>
+        </is>
+      </c>
+      <c r="B221" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -13663,7 +13618,7 @@
         <v>10</v>
       </c>
       <c r="F221" s="4" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
@@ -13674,17 +13629,17 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>best kitchen renovation company near me</t>
-        </is>
-      </c>
-      <c r="B222" s="2" t="inlineStr">
-        <is>
-          <t>Charlotte &amp; Local</t>
+          <t>box cabinets for kitchen</t>
+        </is>
+      </c>
+      <c r="B222" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -13695,8 +13650,8 @@
       <c r="E222" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F222" s="4" t="n">
-        <v>18</v>
+      <c r="F222" s="6" t="n">
+        <v>30</v>
       </c>
       <c r="G222" t="inlineStr">
         <is>
@@ -13707,17 +13662,17 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>best kitchen showrooms near me</t>
-        </is>
-      </c>
-      <c r="B223" s="2" t="inlineStr">
-        <is>
-          <t>Charlotte &amp; Local</t>
+          <t>breakdown of kitchen remodeling costs</t>
+        </is>
+      </c>
+      <c r="B223" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -13729,7 +13684,7 @@
         <v>10</v>
       </c>
       <c r="F223" s="4" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G223" t="inlineStr">
         <is>
@@ -13740,12 +13695,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>best kitchens of 2025</t>
-        </is>
-      </c>
-      <c r="B224" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>budget kitchen makeover</t>
+        </is>
+      </c>
+      <c r="B224" s="5" t="inlineStr">
+        <is>
+          <t>Cost &amp; Budget</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -13762,7 +13717,7 @@
         <v>10</v>
       </c>
       <c r="F224" s="6" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="G224" t="inlineStr">
         <is>
@@ -13773,12 +13728,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>best place to buy kitchen cabinets</t>
-        </is>
-      </c>
-      <c r="B225" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>budget kitchen remodel</t>
+        </is>
+      </c>
+      <c r="B225" s="5" t="inlineStr">
+        <is>
+          <t>Cost &amp; Budget</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -13794,8 +13749,8 @@
       <c r="E225" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F225" s="4" t="n">
-        <v>24</v>
+      <c r="F225" s="6" t="n">
+        <v>38</v>
       </c>
       <c r="G225" t="inlineStr">
         <is>
@@ -13806,12 +13761,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>box cabinets for kitchen</t>
-        </is>
-      </c>
-      <c r="B226" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>budget kitchen renovation</t>
+        </is>
+      </c>
+      <c r="B226" s="5" t="inlineStr">
+        <is>
+          <t>Cost &amp; Budget</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -13828,7 +13783,7 @@
         <v>10</v>
       </c>
       <c r="F226" s="6" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="G226" t="inlineStr">
         <is>
@@ -13839,17 +13794,17 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>breakdown of kitchen remodeling costs</t>
-        </is>
-      </c>
-      <c r="B227" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>butler's pantry renovation charlotte nc</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -13861,7 +13816,7 @@
         <v>10</v>
       </c>
       <c r="F227" s="4" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G227" t="inlineStr">
         <is>
@@ -13872,12 +13827,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>budget kitchen makeover</t>
-        </is>
-      </c>
-      <c r="B228" s="5" t="inlineStr">
-        <is>
-          <t>Cost &amp; Budget</t>
+          <t>buy kitchen remodeling leads</t>
+        </is>
+      </c>
+      <c r="B228" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -13894,7 +13849,7 @@
         <v>10</v>
       </c>
       <c r="F228" s="6" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="G228" t="inlineStr">
         <is>
@@ -13905,17 +13860,17 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>budget kitchen remodel</t>
-        </is>
-      </c>
-      <c r="B229" s="5" t="inlineStr">
-        <is>
-          <t>Cost &amp; Budget</t>
+          <t>cabinet companies charlotte nc</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -13926,8 +13881,8 @@
       <c r="E229" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F229" s="6" t="n">
-        <v>38</v>
+      <c r="F229" s="4" t="n">
+        <v>18</v>
       </c>
       <c r="G229" t="inlineStr">
         <is>
@@ -13938,17 +13893,17 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>budget kitchen renovation</t>
-        </is>
-      </c>
-      <c r="B230" s="5" t="inlineStr">
-        <is>
-          <t>Cost &amp; Budget</t>
+          <t>cabinet companies near me</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -13959,8 +13914,8 @@
       <c r="E230" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F230" s="6" t="n">
-        <v>38</v>
+      <c r="F230" s="4" t="n">
+        <v>18</v>
       </c>
       <c r="G230" t="inlineStr">
         <is>
@@ -13971,7 +13926,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>butler's pantry renovation charlotte nc</t>
+          <t>cabinet company charlotte nc</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
@@ -14004,7 +13959,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>buy kitchen remodeling leads</t>
+          <t>cabinet design and installation</t>
         </is>
       </c>
       <c r="B232" s="7" t="inlineStr">
@@ -14037,7 +13992,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>cabinet companies charlotte nc</t>
+          <t>cabinet design services charlotte nc</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
@@ -14070,17 +14025,17 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>cabinet companies near me</t>
-        </is>
-      </c>
-      <c r="B234" s="2" t="inlineStr">
-        <is>
-          <t>Charlotte &amp; Local</t>
+          <t>cabinet install</t>
+        </is>
+      </c>
+      <c r="B234" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -14091,8 +14046,8 @@
       <c r="E234" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F234" s="4" t="n">
-        <v>18</v>
+      <c r="F234" s="6" t="n">
+        <v>48</v>
       </c>
       <c r="G234" t="inlineStr">
         <is>
@@ -14103,17 +14058,17 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>cabinet company charlotte nc</t>
-        </is>
-      </c>
-      <c r="B235" s="2" t="inlineStr">
-        <is>
-          <t>Charlotte &amp; Local</t>
+          <t>cabinet installation</t>
+        </is>
+      </c>
+      <c r="B235" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -14124,8 +14079,8 @@
       <c r="E235" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F235" s="4" t="n">
-        <v>18</v>
+      <c r="F235" s="6" t="n">
+        <v>48</v>
       </c>
       <c r="G235" t="inlineStr">
         <is>
@@ -14136,17 +14091,17 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>cabinet design and installation</t>
-        </is>
-      </c>
-      <c r="B236" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>cabinet installation companies near me</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -14157,8 +14112,8 @@
       <c r="E236" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F236" s="6" t="n">
-        <v>30</v>
+      <c r="F236" s="4" t="n">
+        <v>18</v>
       </c>
       <c r="G236" t="inlineStr">
         <is>
@@ -14169,12 +14124,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>cabinet design services charlotte nc</t>
-        </is>
-      </c>
-      <c r="B237" s="2" t="inlineStr">
-        <is>
-          <t>Charlotte &amp; Local</t>
+          <t>cabinet installation company</t>
+        </is>
+      </c>
+      <c r="B237" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -14190,8 +14145,8 @@
       <c r="E237" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F237" s="4" t="n">
-        <v>18</v>
+      <c r="F237" s="6" t="n">
+        <v>38</v>
       </c>
       <c r="G237" t="inlineStr">
         <is>
@@ -14202,17 +14157,17 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>cabinet install</t>
-        </is>
-      </c>
-      <c r="B238" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>cabinet installation services charlotte nc</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -14223,8 +14178,8 @@
       <c r="E238" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F238" s="6" t="n">
-        <v>48</v>
+      <c r="F238" s="4" t="n">
+        <v>18</v>
       </c>
       <c r="G238" t="inlineStr">
         <is>
@@ -14235,7 +14190,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>cabinet installation</t>
+          <t>cabinet installer insurance</t>
         </is>
       </c>
       <c r="B239" s="7" t="inlineStr">
@@ -14257,7 +14212,7 @@
         <v>10</v>
       </c>
       <c r="F239" s="6" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="G239" t="inlineStr">
         <is>
@@ -14268,7 +14223,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>cabinet installation companies near me</t>
+          <t>cabinet makeovers charlotte</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
@@ -14290,7 +14245,7 @@
         <v>10</v>
       </c>
       <c r="F240" s="4" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G240" t="inlineStr">
         <is>
@@ -14301,7 +14256,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>cabinet installation company</t>
+          <t>cabinet maker</t>
         </is>
       </c>
       <c r="B241" s="7" t="inlineStr">
@@ -14311,7 +14266,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -14323,7 +14278,7 @@
         <v>10</v>
       </c>
       <c r="F241" s="6" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G241" t="inlineStr">
         <is>
@@ -14334,7 +14289,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>cabinet installation services charlotte nc</t>
+          <t>cabinet refacing belmont</t>
         </is>
       </c>
       <c r="B242" s="2" t="inlineStr">
@@ -14356,7 +14311,7 @@
         <v>10</v>
       </c>
       <c r="F242" s="4" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G242" t="inlineStr">
         <is>
@@ -14367,17 +14322,17 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>cabinet installer insurance</t>
-        </is>
-      </c>
-      <c r="B243" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>cabinet refacing company near me</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -14388,8 +14343,8 @@
       <c r="E243" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F243" s="6" t="n">
-        <v>38</v>
+      <c r="F243" s="4" t="n">
+        <v>18</v>
       </c>
       <c r="G243" t="inlineStr">
         <is>
@@ -14400,7 +14355,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>cabinet makeovers charlotte</t>
+          <t>cabinet refacing fort mill</t>
         </is>
       </c>
       <c r="B244" s="2" t="inlineStr">
@@ -14410,7 +14365,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -14422,7 +14377,7 @@
         <v>10</v>
       </c>
       <c r="F244" s="4" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G244" t="inlineStr">
         <is>
@@ -14433,7 +14388,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>cabinet maker</t>
+          <t>cabinet refacing gastonia</t>
         </is>
       </c>
       <c r="B245" s="7" t="inlineStr">
@@ -14455,7 +14410,7 @@
         <v>10</v>
       </c>
       <c r="F245" s="6" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="G245" t="inlineStr">
         <is>
@@ -14466,17 +14421,17 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>cabinet refacing belmont</t>
-        </is>
-      </c>
-      <c r="B246" s="2" t="inlineStr">
-        <is>
-          <t>Charlotte &amp; Local</t>
+          <t>cabinet refacing pineville</t>
+        </is>
+      </c>
+      <c r="B246" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -14487,8 +14442,8 @@
       <c r="E246" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F246" s="4" t="n">
-        <v>24</v>
+      <c r="F246" s="6" t="n">
+        <v>38</v>
       </c>
       <c r="G246" t="inlineStr">
         <is>
@@ -14499,17 +14454,17 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>cabinet refacing company near me</t>
-        </is>
-      </c>
-      <c r="B247" s="2" t="inlineStr">
-        <is>
-          <t>Charlotte &amp; Local</t>
+          <t>cabinet renovation</t>
+        </is>
+      </c>
+      <c r="B247" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -14520,8 +14475,8 @@
       <c r="E247" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F247" s="4" t="n">
-        <v>18</v>
+      <c r="F247" s="6" t="n">
+        <v>48</v>
       </c>
       <c r="G247" t="inlineStr">
         <is>
@@ -14532,12 +14487,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>cabinet refacing fort mill</t>
-        </is>
-      </c>
-      <c r="B248" s="2" t="inlineStr">
-        <is>
-          <t>Charlotte &amp; Local</t>
+          <t>cabinet replacement</t>
+        </is>
+      </c>
+      <c r="B248" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -14553,8 +14508,8 @@
       <c r="E248" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F248" s="4" t="n">
-        <v>18</v>
+      <c r="F248" s="6" t="n">
+        <v>48</v>
       </c>
       <c r="G248" t="inlineStr">
         <is>
@@ -14565,17 +14520,17 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>cabinet refacing gastonia</t>
-        </is>
-      </c>
-      <c r="B249" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>cabinets charlotte nc</t>
+        </is>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -14586,8 +14541,8 @@
       <c r="E249" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F249" s="6" t="n">
-        <v>38</v>
+      <c r="F249" s="4" t="n">
+        <v>24</v>
       </c>
       <c r="G249" t="inlineStr">
         <is>
@@ -14598,17 +14553,17 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>cabinet refacing pineville</t>
-        </is>
-      </c>
-      <c r="B250" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>cabinets near me</t>
+        </is>
+      </c>
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -14619,8 +14574,8 @@
       <c r="E250" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F250" s="6" t="n">
-        <v>38</v>
+      <c r="F250" s="4" t="n">
+        <v>24</v>
       </c>
       <c r="G250" t="inlineStr">
         <is>
@@ -14631,12 +14586,12 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>cabinet renovation</t>
-        </is>
-      </c>
-      <c r="B251" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>cabinets replacement cost</t>
+        </is>
+      </c>
+      <c r="B251" s="5" t="inlineStr">
+        <is>
+          <t>Cost &amp; Budget</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -14653,7 +14608,7 @@
         <v>10</v>
       </c>
       <c r="F251" s="6" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="G251" t="inlineStr">
         <is>
@@ -14664,7 +14619,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>cabinet replacement</t>
+          <t>certified kitchen design</t>
         </is>
       </c>
       <c r="B252" s="7" t="inlineStr">
@@ -14686,7 +14641,7 @@
         <v>10</v>
       </c>
       <c r="F252" s="6" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="G252" t="inlineStr">
         <is>
@@ -14697,7 +14652,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>cabinets charlotte nc</t>
+          <t>charlotte cabinets</t>
         </is>
       </c>
       <c r="B253" s="2" t="inlineStr">
@@ -14730,7 +14685,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>cabinets near me</t>
+          <t>charlotte kitchen</t>
         </is>
       </c>
       <c r="B254" s="2" t="inlineStr">
@@ -14763,17 +14718,17 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>cabinets replacement cost</t>
-        </is>
-      </c>
-      <c r="B255" s="5" t="inlineStr">
-        <is>
-          <t>Cost &amp; Budget</t>
+          <t>charlotte kitchen cabinets</t>
+        </is>
+      </c>
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -14784,8 +14739,8 @@
       <c r="E255" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F255" s="6" t="n">
-        <v>38</v>
+      <c r="F255" s="4" t="n">
+        <v>24</v>
       </c>
       <c r="G255" t="inlineStr">
         <is>
@@ -14796,17 +14751,17 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>certified kitchen design</t>
-        </is>
-      </c>
-      <c r="B256" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>charlotte kitchen remodeling contractor</t>
+        </is>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -14817,8 +14772,8 @@
       <c r="E256" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F256" s="6" t="n">
-        <v>38</v>
+      <c r="F256" s="4" t="n">
+        <v>18</v>
       </c>
       <c r="G256" t="inlineStr">
         <is>
@@ -14829,7 +14784,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>charlotte cabinets</t>
+          <t>charlotte nc kitchen remodeling company</t>
         </is>
       </c>
       <c r="B257" s="2" t="inlineStr">
@@ -14851,7 +14806,7 @@
         <v>10</v>
       </c>
       <c r="F257" s="4" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G257" t="inlineStr">
         <is>
@@ -14862,17 +14817,17 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>charlotte kitchen</t>
-        </is>
-      </c>
-      <c r="B258" s="2" t="inlineStr">
-        <is>
-          <t>Charlotte &amp; Local</t>
+          <t>cheap kitchen remodel</t>
+        </is>
+      </c>
+      <c r="B258" s="5" t="inlineStr">
+        <is>
+          <t>Cost &amp; Budget</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -14883,8 +14838,8 @@
       <c r="E258" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F258" s="4" t="n">
-        <v>24</v>
+      <c r="F258" s="6" t="n">
+        <v>38</v>
       </c>
       <c r="G258" t="inlineStr">
         <is>
@@ -14895,17 +14850,17 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>charlotte kitchen cabinets</t>
-        </is>
-      </c>
-      <c r="B259" s="2" t="inlineStr">
-        <is>
-          <t>Charlotte &amp; Local</t>
+          <t>cheapest kitchen remodel</t>
+        </is>
+      </c>
+      <c r="B259" s="5" t="inlineStr">
+        <is>
+          <t>Cost &amp; Budget</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -14916,8 +14871,8 @@
       <c r="E259" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F259" s="4" t="n">
-        <v>24</v>
+      <c r="F259" s="6" t="n">
+        <v>38</v>
       </c>
       <c r="G259" t="inlineStr">
         <is>
@@ -14928,17 +14883,17 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>charlotte kitchen remodeling contractor</t>
-        </is>
-      </c>
-      <c r="B260" s="2" t="inlineStr">
-        <is>
-          <t>Charlotte &amp; Local</t>
+          <t>clover kitchens</t>
+        </is>
+      </c>
+      <c r="B260" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -14949,8 +14904,8 @@
       <c r="E260" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F260" s="4" t="n">
-        <v>18</v>
+      <c r="F260" s="6" t="n">
+        <v>48</v>
       </c>
       <c r="G260" t="inlineStr">
         <is>
@@ -14961,7 +14916,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>charlotte landing kitchen remodel</t>
+          <t>commercial kitchen charlotte nc</t>
         </is>
       </c>
       <c r="B261" s="2" t="inlineStr">
@@ -14994,17 +14949,17 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>charlotte nc kitchen remodeling company</t>
-        </is>
-      </c>
-      <c r="B262" s="2" t="inlineStr">
-        <is>
-          <t>Charlotte &amp; Local</t>
+          <t>commercial kitchen door installation</t>
+        </is>
+      </c>
+      <c r="B262" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -15015,8 +14970,8 @@
       <c r="E262" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F262" s="4" t="n">
-        <v>18</v>
+      <c r="F262" s="6" t="n">
+        <v>30</v>
       </c>
       <c r="G262" t="inlineStr">
         <is>
@@ -15027,12 +14982,12 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>cheap kitchen remodel</t>
-        </is>
-      </c>
-      <c r="B263" s="5" t="inlineStr">
-        <is>
-          <t>Cost &amp; Budget</t>
+          <t>commissary kitchen</t>
+        </is>
+      </c>
+      <c r="B263" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -15049,7 +15004,7 @@
         <v>10</v>
       </c>
       <c r="F263" s="6" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G263" t="inlineStr">
         <is>
@@ -15060,7 +15015,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>cheapest kitchen remodel</t>
+          <t>complete kitchen remodel cost</t>
         </is>
       </c>
       <c r="B264" s="5" t="inlineStr">
@@ -15082,7 +15037,7 @@
         <v>10</v>
       </c>
       <c r="F264" s="6" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="G264" t="inlineStr">
         <is>
@@ -15093,12 +15048,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>clover kitchens</t>
-        </is>
-      </c>
-      <c r="B265" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>complete kitchen remodel price</t>
+        </is>
+      </c>
+      <c r="B265" s="5" t="inlineStr">
+        <is>
+          <t>Cost &amp; Budget</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -15115,7 +15070,7 @@
         <v>10</v>
       </c>
       <c r="F265" s="6" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="G265" t="inlineStr">
         <is>
@@ -15126,12 +15081,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>commercial kitchen charlotte nc</t>
-        </is>
-      </c>
-      <c r="B266" s="2" t="inlineStr">
-        <is>
-          <t>Charlotte &amp; Local</t>
+          <t>complete kitchen remodeling company</t>
+        </is>
+      </c>
+      <c r="B266" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -15147,8 +15102,8 @@
       <c r="E266" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F266" s="4" t="n">
-        <v>18</v>
+      <c r="F266" s="6" t="n">
+        <v>30</v>
       </c>
       <c r="G266" t="inlineStr">
         <is>
@@ -15159,7 +15114,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>commercial kitchen door installation</t>
+          <t>complete kitchen remodeling service</t>
         </is>
       </c>
       <c r="B267" s="7" t="inlineStr">
@@ -15192,7 +15147,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>commissary kitchen</t>
+          <t>complete kitchen renovation</t>
         </is>
       </c>
       <c r="B268" s="7" t="inlineStr">
@@ -15214,7 +15169,7 @@
         <v>10</v>
       </c>
       <c r="F268" s="6" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="G268" t="inlineStr">
         <is>
@@ -15225,12 +15180,12 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>complete kitchen remodel cost</t>
-        </is>
-      </c>
-      <c r="B269" s="5" t="inlineStr">
-        <is>
-          <t>Cost &amp; Budget</t>
+          <t>concord kitchen remodel</t>
+        </is>
+      </c>
+      <c r="B269" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -15247,7 +15202,7 @@
         <v>10</v>
       </c>
       <c r="F269" s="6" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="G269" t="inlineStr">
         <is>
@@ -15258,12 +15213,12 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>complete kitchen remodel price</t>
-        </is>
-      </c>
-      <c r="B270" s="5" t="inlineStr">
-        <is>
-          <t>Cost &amp; Budget</t>
+          <t>condo kitchen remodel</t>
+        </is>
+      </c>
+      <c r="B270" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -15280,7 +15235,7 @@
         <v>10</v>
       </c>
       <c r="F270" s="6" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="G270" t="inlineStr">
         <is>
@@ -15291,12 +15246,12 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>complete kitchen remodeling company</t>
-        </is>
-      </c>
-      <c r="B271" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>contractor for kitchen remodel lake gaston nc</t>
+        </is>
+      </c>
+      <c r="B271" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -15312,8 +15267,8 @@
       <c r="E271" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F271" s="6" t="n">
-        <v>30</v>
+      <c r="F271" s="4" t="n">
+        <v>18</v>
       </c>
       <c r="G271" t="inlineStr">
         <is>
@@ -15324,17 +15279,17 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>complete kitchen remodeling service</t>
-        </is>
-      </c>
-      <c r="B272" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>contractor for kitchen remodel rock hill sc</t>
+        </is>
+      </c>
+      <c r="B272" s="9" t="inlineStr">
+        <is>
+          <t>Process &amp; Planning</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -15345,24 +15300,24 @@
       <c r="E272" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F272" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="G272" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="F272" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="G272" s="11" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>complete kitchen renovation</t>
-        </is>
-      </c>
-      <c r="B273" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>cornelius kitchen remodeling</t>
+        </is>
+      </c>
+      <c r="B273" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -15378,8 +15333,8 @@
       <c r="E273" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F273" s="6" t="n">
-        <v>38</v>
+      <c r="F273" s="4" t="n">
+        <v>24</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -15390,7 +15345,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>concord kitchen remodel</t>
+          <t>corner kitchen remodel</t>
         </is>
       </c>
       <c r="B274" s="7" t="inlineStr">
@@ -15423,12 +15378,12 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>condo kitchen remodel</t>
-        </is>
-      </c>
-      <c r="B275" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>cost for kitchen addition</t>
+        </is>
+      </c>
+      <c r="B275" s="5" t="inlineStr">
+        <is>
+          <t>Cost &amp; Budget</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -15445,7 +15400,7 @@
         <v>10</v>
       </c>
       <c r="F275" s="6" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -15456,17 +15411,17 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>contractor for kitchen remodel lake gaston nc</t>
-        </is>
-      </c>
-      <c r="B276" s="2" t="inlineStr">
-        <is>
-          <t>Charlotte &amp; Local</t>
+          <t>cost of a kitchen makeover</t>
+        </is>
+      </c>
+      <c r="B276" s="5" t="inlineStr">
+        <is>
+          <t>Cost &amp; Budget</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -15478,7 +15433,7 @@
         <v>10</v>
       </c>
       <c r="F276" s="4" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
@@ -15489,17 +15444,17 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>contractor for kitchen remodel rock hill sc</t>
-        </is>
-      </c>
-      <c r="B277" s="9" t="inlineStr">
-        <is>
-          <t>Process &amp; Planning</t>
+          <t>cost of a kitchen remodel 2024</t>
+        </is>
+      </c>
+      <c r="B277" s="5" t="inlineStr">
+        <is>
+          <t>Cost &amp; Budget</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -15513,21 +15468,21 @@
       <c r="F277" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="G277" s="11" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>cornelius kitchen remodeling</t>
-        </is>
-      </c>
-      <c r="B278" s="2" t="inlineStr">
-        <is>
-          <t>Charlotte &amp; Local</t>
+          <t>cost of a new kitchen remodel</t>
+        </is>
+      </c>
+      <c r="B278" s="5" t="inlineStr">
+        <is>
+          <t>Cost &amp; Budget</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -15555,12 +15510,12 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>corner kitchen remodel</t>
-        </is>
-      </c>
-      <c r="B279" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>cost of complete kitchen renovation</t>
+        </is>
+      </c>
+      <c r="B279" s="5" t="inlineStr">
+        <is>
+          <t>Cost &amp; Budget</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -15576,8 +15531,8 @@
       <c r="E279" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F279" s="6" t="n">
-        <v>38</v>
+      <c r="F279" s="4" t="n">
+        <v>24</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -15588,7 +15543,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>cost for kitchen addition</t>
+          <t>cost of galley kitchen remodel</t>
         </is>
       </c>
       <c r="B280" s="5" t="inlineStr">
@@ -15609,8 +15564,8 @@
       <c r="E280" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F280" s="6" t="n">
-        <v>30</v>
+      <c r="F280" s="4" t="n">
+        <v>24</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -15621,7 +15576,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>cost of a kitchen makeover</t>
+          <t>cost of high end kitchen remodel</t>
         </is>
       </c>
       <c r="B281" s="5" t="inlineStr">
@@ -15654,7 +15609,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>cost of a kitchen remodel 2024</t>
+          <t>cost of kitchen remodel 2021</t>
         </is>
       </c>
       <c r="B282" s="5" t="inlineStr">
@@ -15687,7 +15642,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>cost of a new kitchen remodel</t>
+          <t>cost of kitchen remodel with wall removal</t>
         </is>
       </c>
       <c r="B283" s="5" t="inlineStr">
@@ -15720,7 +15675,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>cost of complete kitchen renovation</t>
+          <t>cost of kitchen renovation 2024</t>
         </is>
       </c>
       <c r="B284" s="5" t="inlineStr">
@@ -15753,7 +15708,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>cost of galley kitchen remodel</t>
+          <t>cost of large kitchen remodel</t>
         </is>
       </c>
       <c r="B285" s="5" t="inlineStr">
@@ -15786,7 +15741,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>cost of high end kitchen remodel</t>
+          <t>cost of luxury kitchen remodel</t>
         </is>
       </c>
       <c r="B286" s="5" t="inlineStr">
@@ -15819,7 +15774,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>cost of kitchen remodel 2021</t>
+          <t>cost of redoing a kitchen</t>
         </is>
       </c>
       <c r="B287" s="5" t="inlineStr">
@@ -15852,7 +15807,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>cost of kitchen remodel with wall removal</t>
+          <t>cost of remodelling a kitchen</t>
         </is>
       </c>
       <c r="B288" s="5" t="inlineStr">
@@ -15885,7 +15840,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>cost of kitchen renovation 2024</t>
+          <t>cost of updating a kitchen</t>
         </is>
       </c>
       <c r="B289" s="5" t="inlineStr">
@@ -15918,7 +15873,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>cost of large kitchen remodel</t>
+          <t>cost to completely remodel kitchen</t>
         </is>
       </c>
       <c r="B290" s="5" t="inlineStr">
@@ -15951,7 +15906,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>cost of luxury kitchen remodel</t>
+          <t>cost to demo a kitchen</t>
         </is>
       </c>
       <c r="B291" s="5" t="inlineStr">
@@ -15984,7 +15939,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>cost of redoing a kitchen</t>
+          <t>cost to expand kitchen</t>
         </is>
       </c>
       <c r="B292" s="5" t="inlineStr">
@@ -16005,8 +15960,8 @@
       <c r="E292" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F292" s="4" t="n">
-        <v>24</v>
+      <c r="F292" s="6" t="n">
+        <v>30</v>
       </c>
       <c r="G292" t="inlineStr">
         <is>
@@ -16017,7 +15972,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>cost of remodelling a kitchen</t>
+          <t>cost to redo kitchen</t>
         </is>
       </c>
       <c r="B293" s="5" t="inlineStr">
@@ -16038,8 +15993,8 @@
       <c r="E293" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F293" s="4" t="n">
-        <v>24</v>
+      <c r="F293" s="6" t="n">
+        <v>30</v>
       </c>
       <c r="G293" t="inlineStr">
         <is>
@@ -16050,7 +16005,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>cost of updating a kitchen</t>
+          <t>cost to remodel kitchen charleston sc</t>
         </is>
       </c>
       <c r="B294" s="5" t="inlineStr">
@@ -16083,7 +16038,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>cost to completely remodel kitchen</t>
+          <t>cost to remodel small kitchen</t>
         </is>
       </c>
       <c r="B295" s="5" t="inlineStr">
@@ -16098,7 +16053,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Buyer</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="E295" s="3" t="n">
@@ -16116,7 +16071,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>cost to demo a kitchen</t>
+          <t>cost to replace a kitchen</t>
         </is>
       </c>
       <c r="B296" s="5" t="inlineStr">
@@ -16149,7 +16104,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>cost to expand kitchen</t>
+          <t>cost to update a kitchen</t>
         </is>
       </c>
       <c r="B297" s="5" t="inlineStr">
@@ -16170,8 +16125,8 @@
       <c r="E297" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F297" s="6" t="n">
-        <v>30</v>
+      <c r="F297" s="4" t="n">
+        <v>24</v>
       </c>
       <c r="G297" t="inlineStr">
         <is>
@@ -16182,7 +16137,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>cost to redo kitchen</t>
+          <t>costco kitchen remodel cost</t>
         </is>
       </c>
       <c r="B298" s="5" t="inlineStr">
@@ -16215,17 +16170,17 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>cost to remodel kitchen charleston sc</t>
-        </is>
-      </c>
-      <c r="B299" s="5" t="inlineStr">
-        <is>
-          <t>Cost &amp; Budget</t>
+          <t>countertop contractor tega cay sc</t>
+        </is>
+      </c>
+      <c r="B299" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -16248,12 +16203,12 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>cost to remodel small kitchen</t>
-        </is>
-      </c>
-      <c r="B300" s="5" t="inlineStr">
-        <is>
-          <t>Cost &amp; Budget</t>
+          <t>countertop remodel</t>
+        </is>
+      </c>
+      <c r="B300" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -16263,14 +16218,14 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Buyer</t>
         </is>
       </c>
       <c r="E300" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F300" s="4" t="n">
-        <v>24</v>
+      <c r="F300" s="6" t="n">
+        <v>48</v>
       </c>
       <c r="G300" t="inlineStr">
         <is>
@@ -16281,17 +16236,17 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>cost to replace a kitchen</t>
-        </is>
-      </c>
-      <c r="B301" s="5" t="inlineStr">
-        <is>
-          <t>Cost &amp; Budget</t>
+          <t>countertops mooresville nc</t>
+        </is>
+      </c>
+      <c r="B301" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -16314,12 +16269,12 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>cost to update a kitchen</t>
-        </is>
-      </c>
-      <c r="B302" s="5" t="inlineStr">
-        <is>
-          <t>Cost &amp; Budget</t>
+          <t>countertops tega cay sc</t>
+        </is>
+      </c>
+      <c r="B302" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -16335,8 +16290,8 @@
       <c r="E302" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F302" s="4" t="n">
-        <v>24</v>
+      <c r="F302" s="6" t="n">
+        <v>30</v>
       </c>
       <c r="G302" t="inlineStr">
         <is>
@@ -16347,12 +16302,12 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>costco kitchen remodel cost</t>
-        </is>
-      </c>
-      <c r="B303" s="5" t="inlineStr">
-        <is>
-          <t>Cost &amp; Budget</t>
+          <t>country kitchen remodel</t>
+        </is>
+      </c>
+      <c r="B303" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -16369,7 +16324,7 @@
         <v>10</v>
       </c>
       <c r="F303" s="6" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="G303" t="inlineStr">
         <is>
@@ -16380,12 +16335,12 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>countertop contractor tega cay sc</t>
-        </is>
-      </c>
-      <c r="B304" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>custom cabinet charlotte</t>
+        </is>
+      </c>
+      <c r="B304" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -16413,17 +16368,17 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>countertop remodel</t>
-        </is>
-      </c>
-      <c r="B305" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>custom cabinet installers near me</t>
+        </is>
+      </c>
+      <c r="B305" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -16434,8 +16389,8 @@
       <c r="E305" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F305" s="6" t="n">
-        <v>48</v>
+      <c r="F305" s="4" t="n">
+        <v>18</v>
       </c>
       <c r="G305" t="inlineStr">
         <is>
@@ -16446,7 +16401,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>countertops mooresville nc</t>
+          <t>custom cabinets charlotte nc</t>
         </is>
       </c>
       <c r="B306" s="2" t="inlineStr">
@@ -16468,7 +16423,7 @@
         <v>10</v>
       </c>
       <c r="F306" s="4" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G306" t="inlineStr">
         <is>
@@ -16479,17 +16434,17 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>countertops tega cay sc</t>
-        </is>
-      </c>
-      <c r="B307" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>custom cabinets for kitchen charlotte</t>
+        </is>
+      </c>
+      <c r="B307" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -16500,8 +16455,8 @@
       <c r="E307" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F307" s="6" t="n">
-        <v>30</v>
+      <c r="F307" s="4" t="n">
+        <v>18</v>
       </c>
       <c r="G307" t="inlineStr">
         <is>
@@ -16512,7 +16467,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>country kitchen remodel</t>
+          <t>custom kitchen</t>
         </is>
       </c>
       <c r="B308" s="7" t="inlineStr">
@@ -16534,7 +16489,7 @@
         <v>10</v>
       </c>
       <c r="F308" s="6" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G308" t="inlineStr">
         <is>
@@ -16545,7 +16500,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>custom cabinet charlotte</t>
+          <t>custom kitchen cabinet refacing charlotte</t>
         </is>
       </c>
       <c r="B309" s="2" t="inlineStr">
@@ -16567,7 +16522,7 @@
         <v>10</v>
       </c>
       <c r="F309" s="4" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G309" t="inlineStr">
         <is>
@@ -16578,7 +16533,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>custom cabinet installers near me</t>
+          <t>custom kitchen cabinets charlotte nc</t>
         </is>
       </c>
       <c r="B310" s="2" t="inlineStr">
@@ -16611,7 +16566,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>custom cabinets charlotte nc</t>
+          <t>custom kitchen cabinets concord nc</t>
         </is>
       </c>
       <c r="B311" s="2" t="inlineStr">
@@ -16644,7 +16599,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>custom cabinets for kitchen charlotte</t>
+          <t>custom kitchen cabinets matthews nc</t>
         </is>
       </c>
       <c r="B312" s="2" t="inlineStr">
@@ -16677,17 +16632,17 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>custom kitchen</t>
-        </is>
-      </c>
-      <c r="B313" s="7" t="inlineStr">
-        <is>
-          <t>Design &amp; Materials</t>
+          <t>custom kitchen cabinets near me</t>
+        </is>
+      </c>
+      <c r="B313" s="2" t="inlineStr">
+        <is>
+          <t>Charlotte &amp; Local</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -16698,8 +16653,8 @@
       <c r="E313" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F313" s="6" t="n">
-        <v>48</v>
+      <c r="F313" s="4" t="n">
+        <v>18</v>
       </c>
       <c r="G313" t="inlineStr">
         <is>
@@ -16710,17 +16665,17 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>custom kitchen cabinet refacing charlotte</t>
-        </is>
-      </c>
-      <c r="B314" s="2" t="inlineStr">
-        <is>
-          <t>Charlotte &amp; Local</t>
+          <t>custom kitchen design</t>
+        </is>
+      </c>
+      <c r="B314" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -16731,8 +16686,8 @@
       <c r="E314" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F314" s="4" t="n">
-        <v>18</v>
+      <c r="F314" s="6" t="n">
+        <v>38</v>
       </c>
       <c r="G314" t="inlineStr">
         <is>
@@ -16743,7 +16698,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>custom kitchen cabinets charlotte nc</t>
+          <t>custom kitchen design charlotte nc</t>
         </is>
       </c>
       <c r="B315" s="2" t="inlineStr">
@@ -16776,17 +16731,17 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>custom kitchen cabinets concord nc</t>
-        </is>
-      </c>
-      <c r="B316" s="2" t="inlineStr">
-        <is>
-          <t>Charlotte &amp; Local</t>
+          <t>custom kitchen redesign</t>
+        </is>
+      </c>
+      <c r="B316" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; Materials</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -16797,8 +16752,8 @@
       <c r="E316" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F316" s="4" t="n">
-        <v>18</v>
+      <c r="F316" s="6" t="n">
+        <v>38</v>
       </c>
       <c r="G316" t="inlineStr">
         <is>
@@ -16809,17 +16764,17 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>custom kitchen cabinets matthews nc</t>
-        </is>
-      </c>
-      <c r="B317" s="2" t="inlineStr">
-        <is>
-          <t>Charlotte &amp; Local</t>
+          <t>custom kitchen remodel cost</t>
+        </is>
+      </c>
+      <c r="B317" s="5" t="inlineStr">
+        <is>
+          <t>Cost &amp; Budget</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -16830,8 +16785,8 @@
       <c r="E317" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F317" s="4" t="n">
-        <v>18</v>
+      <c r="F317" s="6" t="n">
+        <v>30</v>
       </c>
       <c r="G317" t="inlineStr">
         <is>
@@ -16842,7 +16797,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>custom kitchen cabinets near me</t>
+          <t>custom kitchen remodeling belmont nc</t>
         </is>
       </c>
       <c r="B318" s="2" t="inlineStr">
@@ -16875,7 +16830,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>custom kitchen design</t>
+          <t>custom kitchen renovation</t>
         </is>
       </c>
       <c r="B319" s="7" t="inlineStr">
@@ -16908,7 +16863,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>custom kitchen design charlotte nc</t>
+          <t>custom pantry storage charlotte nc</t>
         </is>
       </c>
       <c r="B320" s="2" t="inlineStr">
@@ -16941,7 +16896,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>custom kitchen redesign</t>
+          <t>daily kitchens</t>
         </is>
       </c>
       <c r="B321" s="7" t="inlineStr">
@@ -16963,7 +16918,7 @@
         <v>10</v>
       </c>
       <c r="F321" s="6" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G321" t="inlineStr">
         <is>
@@ -16982,7 +16937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -17022,53 +16977,53 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>revision design remodeling</t>
+          <t>bathroom renovation services ballantyne nc</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="C2" s="6" t="n">
-        <v>32</v>
+        <v>90</v>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Competitor brand</t>
+          <t>Wrong geography (outside Charlotte metro)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>A rival remodeler’s brand name. Searchers want that specific company, not you.</t>
+          <t>Outside your service area (other cities/states). Traffic you can’t convert into a local job.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>kitchen cost calculator</t>
+          <t>revision design remodeling</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
         <v>10</v>
       </c>
       <c r="C3" s="6" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Off-strategy (DIY / retail / tool)</t>
+          <t>Competitor brand</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>DIY, big-box retail, or pure tool intent. The visitor wants to do it themselves or buy parts, not hire a remodeler.</t>
+          <t>A rival remodeler’s brand name. Searchers want that specific company, not you.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>kitchen cost estimator</t>
+          <t>kitchen cost calculator</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -17091,14 +17046,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>new kitchen cost estimator</t>
+          <t>kitchen cost estimator</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
         <v>10</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -17114,7 +17069,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>new kitchen cost calculator</t>
+          <t>new kitchen cost estimator</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -17137,7 +17092,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>kitchen remodel cost estimator</t>
+          <t>new kitchen cost calculator</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
@@ -17160,14 +17115,14 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>kitchen price estimator</t>
+          <t>kitchen remodel cost estimator</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
         <v>10</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -17183,14 +17138,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>kitchen remodel cost calculator</t>
+          <t>kitchen price estimator</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
         <v>10</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -17206,21 +17161,67 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>kitchen remodeling south west charlotte</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Wrong geography (outside Charlotte metro)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Outside your service area (other cities/states). Traffic you can’t convert into a local job.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>kitchen remodel cost calculator</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Off-strategy (DIY / retail / tool)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>DIY, big-box retail, or pure tool intent. The visitor wants to do it themselves or buy parts, not hire a remodeler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>kitchen fitting cost calculator</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="C10" s="6" t="n">
+      <c r="B12" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C12" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Off-strategy (DIY / retail / tool)</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>DIY, big-box retail, or pure tool intent. The visitor wants to do it themselves or buy parts, not hire a remodeler.</t>
         </is>

--- a/decks/7-day-kitchens/keyword-research.xlsx
+++ b/decks/7-day-kitchens/keyword-research.xlsx
@@ -817,7 +817,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kitchen Design Charlotte NC: The 7-Day Difference, Explained</t>
+          <t>Kitchen Design in Charlotte, NC: From First Sketch to Install</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Kitchen Designers Charlotte: Fixed Pricing, Finished in 7 Days</t>
+          <t>Kitchen Designers in Charlotte: Working With Our In-House Team</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Kitchen Remodeling in Ballantyne, Charlotte: Fixed-Price, 7 Days</t>
+          <t>Kitchen Remodeling in Ballantyne: A South Charlotte Homeowner's Guide</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Affordable Kitchen Remodel Charlotte NC: Fixed Pricing, Finished in 7 Days</t>
+          <t>Affordable Kitchen Remodels in Charlotte, NC: What's Realistic</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2945,7 +2945,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Kitchen Island with Seating: What Designers Pick and Why</t>
+          <t>Kitchen Islands with Seating: Sizing, Stools, and Clearance</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Kitchen Cooking Utensils: What Designers Pick and Why</t>
+          <t>Kitchen Cooking Utensils: The Essentials Worth Owning</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
